--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ241"/>
+  <dimension ref="A1:AZ250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45832,15 +45832,11 @@
           <t>21 566</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G239" t="n">
+        <v>2</v>
+      </c>
+      <c r="H239" t="n">
+        <v>2</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
@@ -45862,15 +45858,11 @@
           <t>Atl. Madrid</t>
         </is>
       </c>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="N239" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
+      <c r="M239" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="N239" t="n">
+        <v>0.97</v>
       </c>
       <c r="O239" t="inlineStr">
         <is>
@@ -45882,135 +45874,83 @@
           <t>56%</t>
         </is>
       </c>
-      <c r="Q239" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R239" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S239" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T239" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U239" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V239" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W239" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X239" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y239" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z239" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA239" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB239" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC239" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD239" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE239" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AF239" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AG239" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH239" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI239" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AJ239" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK239" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL239" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM239" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="AN239" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AO239" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="AP239" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="Q239" t="n">
+        <v>8</v>
+      </c>
+      <c r="R239" t="n">
+        <v>10</v>
+      </c>
+      <c r="S239" t="n">
+        <v>3</v>
+      </c>
+      <c r="T239" t="n">
+        <v>5</v>
+      </c>
+      <c r="U239" t="n">
+        <v>3</v>
+      </c>
+      <c r="V239" t="n">
+        <v>4</v>
+      </c>
+      <c r="W239" t="n">
+        <v>2</v>
+      </c>
+      <c r="X239" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y239" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z239" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB239" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD239" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE239" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF239" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG239" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH239" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI239" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ239" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK239" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL239" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM239" t="n">
+        <v>102</v>
+      </c>
+      <c r="AN239" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO239" t="n">
+        <v>41</v>
+      </c>
+      <c r="AP239" t="n">
+        <v>53</v>
       </c>
       <c r="AQ239" t="inlineStr">
         <is>
@@ -46078,15 +46018,11 @@
         </is>
       </c>
       <c r="F240" t="inlineStr"/>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G240" t="n">
+        <v>1</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
@@ -46108,15 +46044,11 @@
           <t>Espanyol</t>
         </is>
       </c>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="N240" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
+      <c r="M240" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N240" t="n">
+        <v>0.26</v>
       </c>
       <c r="O240" t="inlineStr">
         <is>
@@ -46128,135 +46060,83 @@
           <t>55%</t>
         </is>
       </c>
-      <c r="Q240" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R240" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S240" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T240" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U240" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V240" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W240" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X240" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y240" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Z240" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AA240" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB240" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC240" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AD240" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE240" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AF240" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG240" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH240" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI240" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ240" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AK240" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL240" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM240" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="AN240" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AO240" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="AP240" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
+      <c r="Q240" t="n">
+        <v>12</v>
+      </c>
+      <c r="R240" t="n">
+        <v>10</v>
+      </c>
+      <c r="S240" t="n">
+        <v>3</v>
+      </c>
+      <c r="T240" t="n">
+        <v>2</v>
+      </c>
+      <c r="U240" t="n">
+        <v>5</v>
+      </c>
+      <c r="V240" t="n">
+        <v>6</v>
+      </c>
+      <c r="W240" t="n">
+        <v>4</v>
+      </c>
+      <c r="X240" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y240" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z240" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA240" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC240" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD240" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE240" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF240" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI240" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ240" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL240" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM240" t="n">
+        <v>109</v>
+      </c>
+      <c r="AN240" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO240" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP240" t="n">
+        <v>35</v>
       </c>
       <c r="AQ240" t="inlineStr">
         <is>
@@ -46324,15 +46204,11 @@
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G241" t="n">
+        <v>2</v>
+      </c>
+      <c r="H241" t="n">
+        <v>1</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
@@ -46366,135 +46242,83 @@
           <t>54%</t>
         </is>
       </c>
-      <c r="Q241" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R241" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S241" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T241" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U241" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V241" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W241" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X241" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y241" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z241" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA241" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB241" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC241" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD241" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE241" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AF241" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AG241" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH241" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI241" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ241" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AK241" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL241" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM241" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="AN241" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="AO241" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="AP241" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="Q241" t="n">
+        <v>15</v>
+      </c>
+      <c r="R241" t="n">
+        <v>13</v>
+      </c>
+      <c r="S241" t="n">
+        <v>4</v>
+      </c>
+      <c r="T241" t="n">
+        <v>5</v>
+      </c>
+      <c r="U241" t="n">
+        <v>6</v>
+      </c>
+      <c r="V241" t="n">
+        <v>6</v>
+      </c>
+      <c r="W241" t="n">
+        <v>5</v>
+      </c>
+      <c r="X241" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y241" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z241" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA241" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB241" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD241" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE241" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF241" t="n">
+        <v>33</v>
+      </c>
+      <c r="AG241" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH241" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI241" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ241" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK241" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL241" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM241" t="n">
+        <v>103</v>
+      </c>
+      <c r="AN241" t="n">
+        <v>64</v>
+      </c>
+      <c r="AO241" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP241" t="n">
+        <v>28</v>
       </c>
       <c r="AQ241" t="inlineStr">
         <is>
@@ -46532,6 +46356,2216 @@
       </c>
       <c r="AY241" t="inlineStr"/>
       <c r="AZ241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>WhAFMMRi</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>24.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Gil Manzano J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Estadi Olímpic Lluís Companys
+ (Barcelona)</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>55 926</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>46 448</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ242" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK242" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL242" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM242" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="AN242" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AO242" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="AP242" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AQ242" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="AR242" t="inlineStr">
+        <is>
+          <t>flick hans dieter</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="AT242" t="inlineStr">
+        <is>
+          <t>valverde tejedor ernesto</t>
+        </is>
+      </c>
+      <c r="AU242" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV242" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX242" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>vJDNK0d4</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>24.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Vega A. C.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>23 516</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>19 900</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD243" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AF243" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG243" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH243" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI243" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ243" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK243" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL243" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM243" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AN243" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="AO243" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AP243" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AQ243" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="AR243" t="inlineStr">
+        <is>
+          <t>moreno vicente</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="AT243" t="inlineStr">
+        <is>
+          <t>arrasate jagoba</t>
+        </is>
+      </c>
+      <c r="AU243" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV243" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX243" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>QekfJmLa</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>23.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Diaz de Mera I.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Estadio Ramón Sánchez Pizjuán
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>42 714</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>34 004</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X244" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB244" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC244" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD244" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE244" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF244" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AG244" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH244" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI244" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ244" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK244" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL244" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM244" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="AN244" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AO244" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AP244" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AQ244" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="AR244" t="inlineStr">
+        <is>
+          <t>pimienta francisco</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="AT244" t="inlineStr">
+        <is>
+          <t>marcelino</t>
+        </is>
+      </c>
+      <c r="AU244" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV244" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX244" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>8KIT2SzJ</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>23.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Munuera Montero J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Estadio de Balaídos
+ (Vigo)</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>24 791</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>23 519</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ245" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL245" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM245" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AN245" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="AO245" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AP245" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AQ245" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="AR245" t="inlineStr">
+        <is>
+          <t>giraldez claudio</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="AT245" t="inlineStr">
+        <is>
+          <t>baraja ruben</t>
+        </is>
+      </c>
+      <c r="AU245" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV245" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX245" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>fcYpyo85</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>24.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Barrera R.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Estadi Ciutat de València
+ (Valencia)</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>26 354</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>14 068</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Cadiz CF</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ246" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK246" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL246" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM246" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AN246" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AO246" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AP246" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="AQ246" t="inlineStr">
+        <is>
+          <t>fiZxGYJ3</t>
+        </is>
+      </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t>calero julian</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="AT246" t="inlineStr">
+        <is>
+          <t>lopez paco</t>
+        </is>
+      </c>
+      <c r="AU246" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV246" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>fqgCMogC</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>24.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Fuentes Molina A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Estadio Municipal da Malata
+ (Ferrol)</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>10 450</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>7 397</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>Ferrol</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Granada CF</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF247" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI247" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ247" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK247" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL247" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM247" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AN247" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AO247" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AP247" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AQ247" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="AR247" t="inlineStr">
+        <is>
+          <t>parralo cristobal</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr">
+        <is>
+          <t>K4dMCgFa</t>
+        </is>
+      </c>
+      <c r="AT247" t="inlineStr">
+        <is>
+          <t>abascal guillermo</t>
+        </is>
+      </c>
+      <c r="AU247" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV247" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX247" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>QwI4i6hn</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>24.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Perez M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Estadio El Molinón
+ (Gijón)</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>29 029</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>20 890</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>Gijon</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Eldense</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr"/>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ248" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK248" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL248" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM248" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AN248" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AO248" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AP248" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="AR248" t="inlineStr">
+        <is>
+          <t>albes ruben</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>hh4xt2Df</t>
+        </is>
+      </c>
+      <c r="AT248" t="inlineStr">
+        <is>
+          <t>ponz daniel</t>
+        </is>
+      </c>
+      <c r="AU248" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV248" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX248" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>jPRgZOxI</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>23.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Galech I.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Estadio El Alcoraz
+ (Huesca)</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>9 100</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>6 172</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>Dep. La Coruna</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr"/>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF249" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI249" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ249" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK249" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL249" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM249" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AN249" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AO249" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AP249" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AQ249" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="AR249" t="inlineStr">
+        <is>
+          <t>hidalgo antonio</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="AT249" t="inlineStr">
+        <is>
+          <t>idiakez imanol</t>
+        </is>
+      </c>
+      <c r="AU249" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV249" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX249" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>OxQ1X27U</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>23.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Sanchez A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Estadio El Sardinero
+ (Santander)</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>22 222</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>19 205</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Eibar</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr"/>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL250" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM250" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="AN250" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AO250" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="AP250" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr">
+        <is>
+          <t>rak12p9n</t>
+        </is>
+      </c>
+      <c r="AR250" t="inlineStr">
+        <is>
+          <t>lopez jose</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="AT250" t="inlineStr">
+        <is>
+          <t>etxeberria joseba</t>
+        </is>
+      </c>
+      <c r="AU250" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV250" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW250" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX250" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ250"/>
+  <dimension ref="A1:AZ258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46390,15 +46390,11 @@
           <t>46 448</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G242" t="n">
+        <v>2</v>
+      </c>
+      <c r="H242" t="n">
+        <v>1</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
@@ -46420,15 +46416,11 @@
           <t>Ath Bilbao</t>
         </is>
       </c>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="N242" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
+      <c r="M242" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="N242" t="n">
+        <v>1.22</v>
       </c>
       <c r="O242" t="inlineStr">
         <is>
@@ -46440,135 +46432,83 @@
           <t>37%</t>
         </is>
       </c>
-      <c r="Q242" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R242" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T242" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U242" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V242" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W242" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X242" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y242" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="Z242" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA242" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB242" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC242" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD242" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AE242" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF242" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG242" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH242" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI242" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ242" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK242" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL242" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AM242" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="AN242" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AO242" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="AP242" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+      <c r="Q242" t="n">
+        <v>9</v>
+      </c>
+      <c r="R242" t="n">
+        <v>8</v>
+      </c>
+      <c r="S242" t="n">
+        <v>4</v>
+      </c>
+      <c r="T242" t="n">
+        <v>3</v>
+      </c>
+      <c r="U242" t="n">
+        <v>3</v>
+      </c>
+      <c r="V242" t="n">
+        <v>3</v>
+      </c>
+      <c r="W242" t="n">
+        <v>2</v>
+      </c>
+      <c r="X242" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y242" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z242" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA242" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB242" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC242" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD242" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE242" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF242" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG242" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH242" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI242" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ242" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK242" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL242" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM242" t="n">
+        <v>136</v>
+      </c>
+      <c r="AN242" t="n">
+        <v>96</v>
+      </c>
+      <c r="AO242" t="n">
+        <v>61</v>
+      </c>
+      <c r="AP242" t="n">
+        <v>33</v>
       </c>
       <c r="AQ242" t="inlineStr">
         <is>
@@ -46640,15 +46580,11 @@
           <t>19 900</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G243" t="n">
+        <v>1</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -46670,15 +46606,11 @@
           <t>Mallorca</t>
         </is>
       </c>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="N243" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
+      <c r="M243" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="N243" t="n">
+        <v>0.35</v>
       </c>
       <c r="O243" t="inlineStr">
         <is>
@@ -46690,135 +46622,83 @@
           <t>54%</t>
         </is>
       </c>
-      <c r="Q243" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R243" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S243" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T243" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U243" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V243" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W243" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X243" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y243" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Z243" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA243" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB243" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC243" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD243" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE243" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AF243" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG243" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH243" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI243" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ243" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AK243" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL243" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM243" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="AN243" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="AO243" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="AP243" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+      <c r="Q243" t="n">
+        <v>15</v>
+      </c>
+      <c r="R243" t="n">
+        <v>11</v>
+      </c>
+      <c r="S243" t="n">
+        <v>5</v>
+      </c>
+      <c r="T243" t="n">
+        <v>2</v>
+      </c>
+      <c r="U243" t="n">
+        <v>7</v>
+      </c>
+      <c r="V243" t="n">
+        <v>4</v>
+      </c>
+      <c r="W243" t="n">
+        <v>3</v>
+      </c>
+      <c r="X243" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y243" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z243" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA243" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB243" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC243" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE243" t="n">
+        <v>31</v>
+      </c>
+      <c r="AF243" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG243" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH243" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI243" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ243" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK243" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL243" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM243" t="n">
+        <v>93</v>
+      </c>
+      <c r="AN243" t="n">
+        <v>101</v>
+      </c>
+      <c r="AO243" t="n">
+        <v>66</v>
+      </c>
+      <c r="AP243" t="n">
+        <v>54</v>
       </c>
       <c r="AQ243" t="inlineStr">
         <is>
@@ -46890,15 +46770,11 @@
           <t>34 004</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G244" t="n">
+        <v>1</v>
+      </c>
+      <c r="H244" t="n">
+        <v>2</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -46920,15 +46796,11 @@
           <t>Villarreal</t>
         </is>
       </c>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
-      </c>
-      <c r="N244" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
+      <c r="M244" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="N244" t="n">
+        <v>1.16</v>
       </c>
       <c r="O244" t="inlineStr">
         <is>
@@ -46940,135 +46812,83 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="Q244" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R244" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T244" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U244" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V244" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W244" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X244" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y244" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z244" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AA244" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB244" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC244" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD244" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE244" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AF244" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AG244" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH244" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI244" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ244" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AK244" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL244" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AM244" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="AN244" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="AO244" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AP244" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="Q244" t="n">
+        <v>16</v>
+      </c>
+      <c r="R244" t="n">
+        <v>8</v>
+      </c>
+      <c r="S244" t="n">
+        <v>9</v>
+      </c>
+      <c r="T244" t="n">
+        <v>5</v>
+      </c>
+      <c r="U244" t="n">
+        <v>6</v>
+      </c>
+      <c r="V244" t="n">
+        <v>3</v>
+      </c>
+      <c r="W244" t="n">
+        <v>1</v>
+      </c>
+      <c r="X244" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y244" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z244" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA244" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB244" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC244" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD244" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE244" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF244" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG244" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH244" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI244" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ244" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK244" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL244" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM244" t="n">
+        <v>138</v>
+      </c>
+      <c r="AN244" t="n">
+        <v>109</v>
+      </c>
+      <c r="AO244" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP244" t="n">
+        <v>32</v>
       </c>
       <c r="AQ244" t="inlineStr">
         <is>
@@ -47140,15 +46960,11 @@
           <t>23 519</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G245" t="n">
+        <v>3</v>
+      </c>
+      <c r="H245" t="n">
+        <v>1</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -47170,15 +46986,11 @@
           <t>Valencia</t>
         </is>
       </c>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>1.77</t>
-        </is>
-      </c>
-      <c r="N245" t="inlineStr">
-        <is>
-          <t>0.71</t>
-        </is>
+      <c r="M245" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="N245" t="n">
+        <v>0.71</v>
       </c>
       <c r="O245" t="inlineStr">
         <is>
@@ -47190,135 +47002,83 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="Q245" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R245" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S245" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T245" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U245" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V245" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W245" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X245" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y245" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z245" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA245" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB245" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC245" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD245" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE245" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AF245" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG245" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH245" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI245" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AJ245" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK245" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL245" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM245" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="AN245" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="AO245" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="AP245" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="Q245" t="n">
+        <v>7</v>
+      </c>
+      <c r="R245" t="n">
+        <v>13</v>
+      </c>
+      <c r="S245" t="n">
+        <v>5</v>
+      </c>
+      <c r="T245" t="n">
+        <v>5</v>
+      </c>
+      <c r="U245" t="n">
+        <v>0</v>
+      </c>
+      <c r="V245" t="n">
+        <v>8</v>
+      </c>
+      <c r="W245" t="n">
+        <v>2</v>
+      </c>
+      <c r="X245" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z245" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA245" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB245" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC245" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD245" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE245" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF245" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG245" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH245" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI245" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ245" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK245" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM245" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN245" t="n">
+        <v>127</v>
+      </c>
+      <c r="AO245" t="n">
+        <v>35</v>
+      </c>
+      <c r="AP245" t="n">
+        <v>55</v>
       </c>
       <c r="AQ245" t="inlineStr">
         <is>
@@ -47390,15 +47150,11 @@
           <t>14 068</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G246" t="n">
+        <v>1</v>
+      </c>
+      <c r="H246" t="n">
+        <v>1</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -47432,135 +47188,83 @@
           <t>56%</t>
         </is>
       </c>
-      <c r="Q246" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R246" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S246" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T246" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U246" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V246" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W246" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X246" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y246" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Z246" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA246" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB246" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD246" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE246" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AF246" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AG246" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH246" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI246" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ246" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK246" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL246" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AM246" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AN246" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AO246" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="AP246" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="Q246" t="n">
+        <v>17</v>
+      </c>
+      <c r="R246" t="n">
+        <v>16</v>
+      </c>
+      <c r="S246" t="n">
+        <v>6</v>
+      </c>
+      <c r="T246" t="n">
+        <v>8</v>
+      </c>
+      <c r="U246" t="n">
+        <v>9</v>
+      </c>
+      <c r="V246" t="n">
+        <v>7</v>
+      </c>
+      <c r="W246" t="n">
+        <v>2</v>
+      </c>
+      <c r="X246" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z246" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA246" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB246" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC246" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD246" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE246" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF246" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG246" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH246" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI246" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ246" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK246" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL246" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM246" t="n">
+        <v>97</v>
+      </c>
+      <c r="AN246" t="n">
+        <v>114</v>
+      </c>
+      <c r="AO246" t="n">
+        <v>45</v>
+      </c>
+      <c r="AP246" t="n">
+        <v>65</v>
       </c>
       <c r="AQ246" t="inlineStr">
         <is>
@@ -47632,15 +47336,11 @@
           <t>7 397</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="n">
+        <v>1</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -47674,135 +47374,83 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q247" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R247" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S247" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T247" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U247" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V247" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W247" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X247" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y247" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Z247" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA247" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB247" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC247" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD247" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE247" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AF247" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AG247" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH247" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI247" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ247" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK247" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL247" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM247" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AN247" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="AO247" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="AP247" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="Q247" t="n">
+        <v>18</v>
+      </c>
+      <c r="R247" t="n">
+        <v>16</v>
+      </c>
+      <c r="S247" t="n">
+        <v>3</v>
+      </c>
+      <c r="T247" t="n">
+        <v>7</v>
+      </c>
+      <c r="U247" t="n">
+        <v>11</v>
+      </c>
+      <c r="V247" t="n">
+        <v>4</v>
+      </c>
+      <c r="W247" t="n">
+        <v>4</v>
+      </c>
+      <c r="X247" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA247" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB247" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC247" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD247" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE247" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF247" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG247" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH247" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI247" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ247" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK247" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL247" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM247" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN247" t="n">
+        <v>106</v>
+      </c>
+      <c r="AO247" t="n">
+        <v>58</v>
+      </c>
+      <c r="AP247" t="n">
+        <v>57</v>
       </c>
       <c r="AQ247" t="inlineStr">
         <is>
@@ -47874,15 +47522,11 @@
           <t>20 890</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" t="n">
+        <v>0</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -47916,135 +47560,83 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="Q248" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R248" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T248" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U248" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V248" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W248" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X248" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y248" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z248" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA248" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB248" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC248" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD248" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE248" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AF248" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AG248" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH248" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI248" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ248" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AK248" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL248" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM248" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AN248" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="AO248" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="AP248" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+      <c r="Q248" t="n">
+        <v>21</v>
+      </c>
+      <c r="R248" t="n">
+        <v>11</v>
+      </c>
+      <c r="S248" t="n">
+        <v>4</v>
+      </c>
+      <c r="T248" t="n">
+        <v>4</v>
+      </c>
+      <c r="U248" t="n">
+        <v>11</v>
+      </c>
+      <c r="V248" t="n">
+        <v>7</v>
+      </c>
+      <c r="W248" t="n">
+        <v>6</v>
+      </c>
+      <c r="X248" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z248" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA248" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB248" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE248" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF248" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG248" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH248" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI248" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ248" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK248" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL248" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM248" t="n">
+        <v>112</v>
+      </c>
+      <c r="AN248" t="n">
+        <v>105</v>
+      </c>
+      <c r="AO248" t="n">
+        <v>64</v>
+      </c>
+      <c r="AP248" t="n">
+        <v>43</v>
       </c>
       <c r="AQ248" t="inlineStr">
         <is>
@@ -48116,15 +47708,11 @@
           <t>6 172</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G249" t="n">
+        <v>2</v>
+      </c>
+      <c r="H249" t="n">
+        <v>1</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -48158,135 +47746,83 @@
           <t>57%</t>
         </is>
       </c>
-      <c r="Q249" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R249" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S249" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T249" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U249" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V249" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W249" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X249" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y249" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z249" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA249" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB249" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AC249" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD249" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE249" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AF249" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AG249" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH249" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI249" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ249" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AK249" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL249" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM249" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="AN249" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AO249" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AP249" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
+      <c r="Q249" t="n">
+        <v>10</v>
+      </c>
+      <c r="R249" t="n">
+        <v>13</v>
+      </c>
+      <c r="S249" t="n">
+        <v>4</v>
+      </c>
+      <c r="T249" t="n">
+        <v>4</v>
+      </c>
+      <c r="U249" t="n">
+        <v>5</v>
+      </c>
+      <c r="V249" t="n">
+        <v>6</v>
+      </c>
+      <c r="W249" t="n">
+        <v>1</v>
+      </c>
+      <c r="X249" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA249" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB249" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC249" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD249" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE249" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF249" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG249" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH249" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI249" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ249" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK249" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM249" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN249" t="n">
+        <v>114</v>
+      </c>
+      <c r="AO249" t="n">
+        <v>37</v>
+      </c>
+      <c r="AP249" t="n">
+        <v>59</v>
       </c>
       <c r="AQ249" t="inlineStr">
         <is>
@@ -48358,15 +47894,11 @@
           <t>19 205</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G250" t="n">
+        <v>2</v>
+      </c>
+      <c r="H250" t="n">
+        <v>2</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -48400,135 +47932,83 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q250" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R250" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T250" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U250" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V250" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W250" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X250" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y250" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z250" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA250" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB250" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC250" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD250" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE250" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AF250" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AG250" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH250" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI250" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ250" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK250" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL250" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM250" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="AN250" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="AO250" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="AP250" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="Q250" t="n">
+        <v>15</v>
+      </c>
+      <c r="R250" t="n">
+        <v>16</v>
+      </c>
+      <c r="S250" t="n">
+        <v>6</v>
+      </c>
+      <c r="T250" t="n">
+        <v>3</v>
+      </c>
+      <c r="U250" t="n">
+        <v>4</v>
+      </c>
+      <c r="V250" t="n">
+        <v>9</v>
+      </c>
+      <c r="W250" t="n">
+        <v>5</v>
+      </c>
+      <c r="X250" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y250" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z250" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA250" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB250" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD250" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE250" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF250" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG250" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH250" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI250" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ250" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK250" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL250" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM250" t="n">
+        <v>132</v>
+      </c>
+      <c r="AN250" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO250" t="n">
+        <v>69</v>
+      </c>
+      <c r="AP250" t="n">
+        <v>37</v>
       </c>
       <c r="AQ250" t="inlineStr">
         <is>
@@ -48566,6 +48046,1998 @@
       </c>
       <c r="AY250" t="inlineStr"/>
       <c r="AZ250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>25.08.2024 14:15</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Busquets Ferrer M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Estadio Mendizorrotza
+ (Vitoria-Gasteiz)</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>19 840</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>16 623</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X251" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB251" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE251" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF251" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG251" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI251" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ251" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL251" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM251" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AN251" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AO251" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AP251" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AQ251" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="AR251" t="inlineStr">
+        <is>
+          <t>garcia luis</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="AT251" t="inlineStr">
+        <is>
+          <t>pellegrini manuel</t>
+        </is>
+      </c>
+      <c r="AU251" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV251" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW251" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>25.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Bengoetxea R.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Butarque
+ (Leganes)</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>12 454</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>10 052</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB252" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD252" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE252" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF252" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AG252" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH252" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI252" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ252" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM252" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AN252" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AO252" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AP252" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AQ252" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="AR252" t="inlineStr">
+        <is>
+          <t>jimenez borja</t>
+        </is>
+      </c>
+      <c r="AS252" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="AT252" t="inlineStr">
+        <is>
+          <t>carrion luis</t>
+        </is>
+      </c>
+      <c r="AU252" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV252" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>25.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Garcia V.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Estadio Santiago Bernabéu
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>83 186</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>70 178</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X253" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB253" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC253" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD253" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE253" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF253" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG253" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH253" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI253" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ253" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL253" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM253" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="AN253" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AO253" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AP253" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AQ253" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="AR253" t="inlineStr">
+        <is>
+          <t>ancelotti carlo</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="AT253" t="inlineStr">
+        <is>
+          <t>pezzolano paulo</t>
+        </is>
+      </c>
+      <c r="AU253" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV253" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX253" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>24.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Lopez M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Stage Front Stadium
+ (Cornella de Llobregat)</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>40 000</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>20 900</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X254" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB254" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD254" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE254" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AF254" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG254" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH254" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI254" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ254" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL254" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM254" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AN254" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AP254" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>gonzalez manolo</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="AT254" t="inlineStr">
+        <is>
+          <t>alguacil imanol</t>
+        </is>
+      </c>
+      <c r="AU254" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV254" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW254" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX254" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>24.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Rojas J. A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Coliseum
+ (Getafe)</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>16 500</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>9 529</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AF255" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH255" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ255" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK255" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL255" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM255" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="AN255" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="AO255" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AP255" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AQ255" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="AR255" t="inlineStr">
+        <is>
+          <t>bordalas pepe</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="AT255" t="inlineStr">
+        <is>
+          <t>perez inigo</t>
+        </is>
+      </c>
+      <c r="AU255" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV255" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="inlineStr">
+        <is>
+          <t>tEvOrxAE</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>25.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Orellana M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Estadio Carlos Belmonte
+ (Albacete)</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>17 524</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>11 400</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB256" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC256" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD256" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE256" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF256" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG256" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH256" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI256" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ256" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK256" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL256" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM256" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AN256" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="AO256" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AP256" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>gonzalez alberto</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>zT9gi7i9</t>
+        </is>
+      </c>
+      <c r="AT256" t="inlineStr">
+        <is>
+          <t>sarabia eder</t>
+        </is>
+      </c>
+      <c r="AU256" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV256" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="inlineStr">
+        <is>
+          <t>jBnLKPNO</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>24.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Muresan S.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Estadio La Rosaleda
+ (Málaga)</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>30 044</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>26 066</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF257" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG257" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH257" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI257" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL257" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM257" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="AN257" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AO257" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AP257" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AQ257" t="inlineStr">
+        <is>
+          <t>tjXr7SAp</t>
+        </is>
+      </c>
+      <c r="AR257" t="inlineStr">
+        <is>
+          <t>garcia sergio</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="AT257" t="inlineStr">
+        <is>
+          <t>lisci alessio</t>
+        </is>
+      </c>
+      <c r="AU257" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV257" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX257" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="inlineStr">
+        <is>
+          <t>QHtUvT8t</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>24.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Sanchez Lopez R.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Estadio Heliodoro Rodríguez López
+ (Santa Cruz de Tenerife)</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>22 824</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>14 308</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>Tenerife</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>Almeria</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z258" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB258" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC258" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD258" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE258" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF258" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG258" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH258" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI258" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ258" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL258" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM258" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AN258" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AP258" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AQ258" t="inlineStr">
+        <is>
+          <t>UBD9uzt0</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>cano oscar</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="AT258" t="inlineStr">
+        <is>
+          <t>rubi joan</t>
+        </is>
+      </c>
+      <c r="AU258" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV258" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ258"/>
+  <dimension ref="A1:AZ264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48080,15 +48080,11 @@
           <t>16 623</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -48110,15 +48106,11 @@
           <t>Betis</t>
         </is>
       </c>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="N251" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
+      <c r="M251" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N251" t="n">
+        <v>1.37</v>
       </c>
       <c r="O251" t="inlineStr">
         <is>
@@ -48130,135 +48122,83 @@
           <t>61%</t>
         </is>
       </c>
-      <c r="Q251" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R251" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S251" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T251" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U251" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V251" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W251" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AA251" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB251" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD251" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE251" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AF251" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AG251" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH251" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI251" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ251" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK251" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL251" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM251" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AN251" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AO251" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="AP251" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+      <c r="Q251" t="n">
+        <v>3</v>
+      </c>
+      <c r="R251" t="n">
+        <v>13</v>
+      </c>
+      <c r="S251" t="n">
+        <v>1</v>
+      </c>
+      <c r="T251" t="n">
+        <v>3</v>
+      </c>
+      <c r="U251" t="n">
+        <v>0</v>
+      </c>
+      <c r="V251" t="n">
+        <v>8</v>
+      </c>
+      <c r="W251" t="n">
+        <v>2</v>
+      </c>
+      <c r="X251" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y251" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z251" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA251" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB251" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE251" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF251" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG251" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI251" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ251" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL251" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM251" t="n">
+        <v>112</v>
+      </c>
+      <c r="AN251" t="n">
+        <v>96</v>
+      </c>
+      <c r="AO251" t="n">
+        <v>56</v>
+      </c>
+      <c r="AP251" t="n">
+        <v>44</v>
       </c>
       <c r="AQ251" t="inlineStr">
         <is>
@@ -48294,15 +48234,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY251" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AZ251" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AY251" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ251" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="252">
@@ -48338,15 +48274,11 @@
           <t>10 052</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G252" t="n">
+        <v>2</v>
+      </c>
+      <c r="H252" t="n">
+        <v>1</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -48368,15 +48300,11 @@
           <t>Las Palmas</t>
         </is>
       </c>
-      <c r="M252" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="N252" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
+      <c r="M252" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="N252" t="n">
+        <v>0.76</v>
       </c>
       <c r="O252" t="inlineStr">
         <is>
@@ -48388,135 +48316,83 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="Q252" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R252" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T252" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U252" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V252" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W252" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X252" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y252" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z252" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA252" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB252" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC252" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD252" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE252" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AF252" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="AG252" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH252" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI252" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ252" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK252" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL252" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM252" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AN252" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="AO252" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="AP252" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+      <c r="Q252" t="n">
+        <v>10</v>
+      </c>
+      <c r="R252" t="n">
+        <v>10</v>
+      </c>
+      <c r="S252" t="n">
+        <v>5</v>
+      </c>
+      <c r="T252" t="n">
+        <v>5</v>
+      </c>
+      <c r="U252" t="n">
+        <v>4</v>
+      </c>
+      <c r="V252" t="n">
+        <v>4</v>
+      </c>
+      <c r="W252" t="n">
+        <v>1</v>
+      </c>
+      <c r="X252" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y252" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z252" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA252" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB252" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD252" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE252" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF252" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG252" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH252" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI252" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ252" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL252" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM252" t="n">
+        <v>86</v>
+      </c>
+      <c r="AN252" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO252" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP252" t="n">
+        <v>44</v>
       </c>
       <c r="AQ252" t="inlineStr">
         <is>
@@ -48588,15 +48464,11 @@
           <t>70 178</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G253" t="n">
+        <v>3</v>
+      </c>
+      <c r="H253" t="n">
+        <v>0</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -48618,15 +48490,11 @@
           <t>Valladolid</t>
         </is>
       </c>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="N253" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
+      <c r="M253" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="N253" t="n">
+        <v>0.77</v>
       </c>
       <c r="O253" t="inlineStr">
         <is>
@@ -48638,135 +48506,83 @@
           <t>36%</t>
         </is>
       </c>
-      <c r="Q253" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R253" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T253" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U253" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V253" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W253" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X253" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y253" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z253" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA253" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB253" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC253" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD253" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE253" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF253" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG253" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH253" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI253" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ253" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK253" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL253" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM253" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="AN253" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AO253" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="AP253" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
+      <c r="Q253" t="n">
+        <v>17</v>
+      </c>
+      <c r="R253" t="n">
+        <v>8</v>
+      </c>
+      <c r="S253" t="n">
+        <v>9</v>
+      </c>
+      <c r="T253" t="n">
+        <v>2</v>
+      </c>
+      <c r="U253" t="n">
+        <v>5</v>
+      </c>
+      <c r="V253" t="n">
+        <v>4</v>
+      </c>
+      <c r="W253" t="n">
+        <v>3</v>
+      </c>
+      <c r="X253" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y253" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z253" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA253" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB253" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC253" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE253" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF253" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG253" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH253" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI253" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ253" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL253" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM253" t="n">
+        <v>166</v>
+      </c>
+      <c r="AN253" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO253" t="n">
+        <v>96</v>
+      </c>
+      <c r="AP253" t="n">
+        <v>47</v>
       </c>
       <c r="AQ253" t="inlineStr">
         <is>
@@ -48838,15 +48654,11 @@
           <t>20 900</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G254" t="n">
+        <v>0</v>
+      </c>
+      <c r="H254" t="n">
+        <v>1</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -48868,15 +48680,11 @@
           <t>Real Sociedad</t>
         </is>
       </c>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="N254" t="inlineStr">
-        <is>
-          <t>1.03</t>
-        </is>
+      <c r="M254" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="N254" t="n">
+        <v>1.03</v>
       </c>
       <c r="O254" t="inlineStr">
         <is>
@@ -48888,135 +48696,83 @@
           <t>66%</t>
         </is>
       </c>
-      <c r="Q254" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R254" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S254" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T254" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U254" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V254" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W254" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X254" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y254" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="Z254" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA254" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB254" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC254" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD254" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE254" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AF254" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG254" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH254" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI254" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ254" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK254" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL254" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM254" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AN254" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AO254" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="AP254" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
+      <c r="Q254" t="n">
+        <v>13</v>
+      </c>
+      <c r="R254" t="n">
+        <v>8</v>
+      </c>
+      <c r="S254" t="n">
+        <v>3</v>
+      </c>
+      <c r="T254" t="n">
+        <v>4</v>
+      </c>
+      <c r="U254" t="n">
+        <v>7</v>
+      </c>
+      <c r="V254" t="n">
+        <v>4</v>
+      </c>
+      <c r="W254" t="n">
+        <v>3</v>
+      </c>
+      <c r="X254" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y254" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z254" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA254" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB254" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD254" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE254" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF254" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG254" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH254" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI254" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ254" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK254" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL254" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM254" t="n">
+        <v>86</v>
+      </c>
+      <c r="AN254" t="n">
+        <v>114</v>
+      </c>
+      <c r="AO254" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP254" t="n">
+        <v>47</v>
       </c>
       <c r="AQ254" t="inlineStr">
         <is>
@@ -49088,15 +48844,11 @@
           <t>9 529</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
+      <c r="H255" t="n">
+        <v>0</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -49118,15 +48870,11 @@
           <t>Rayo Vallecano</t>
         </is>
       </c>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
-      <c r="N255" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="M255" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N255" t="n">
+        <v>0.25</v>
       </c>
       <c r="O255" t="inlineStr">
         <is>
@@ -49138,135 +48886,83 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q255" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R255" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S255" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T255" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U255" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V255" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W255" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X255" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y255" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="Z255" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA255" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB255" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC255" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD255" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE255" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AF255" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AG255" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH255" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI255" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ255" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK255" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL255" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM255" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="AN255" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="AO255" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="AP255" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="Q255" t="n">
+        <v>12</v>
+      </c>
+      <c r="R255" t="n">
+        <v>3</v>
+      </c>
+      <c r="S255" t="n">
+        <v>0</v>
+      </c>
+      <c r="T255" t="n">
+        <v>1</v>
+      </c>
+      <c r="U255" t="n">
+        <v>9</v>
+      </c>
+      <c r="V255" t="n">
+        <v>1</v>
+      </c>
+      <c r="W255" t="n">
+        <v>3</v>
+      </c>
+      <c r="X255" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y255" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z255" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA255" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB255" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD255" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE255" t="n">
+        <v>33</v>
+      </c>
+      <c r="AF255" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH255" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI255" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ255" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL255" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM255" t="n">
+        <v>141</v>
+      </c>
+      <c r="AN255" t="n">
+        <v>102</v>
+      </c>
+      <c r="AO255" t="n">
+        <v>51</v>
+      </c>
+      <c r="AP255" t="n">
+        <v>40</v>
       </c>
       <c r="AQ255" t="inlineStr">
         <is>
@@ -49338,15 +49034,11 @@
           <t>11 400</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G256" t="n">
+        <v>1</v>
+      </c>
+      <c r="H256" t="n">
+        <v>0</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -49380,135 +49072,83 @@
           <t>78%</t>
         </is>
       </c>
-      <c r="Q256" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R256" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="S256" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T256" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U256" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V256" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W256" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X256" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y256" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z256" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA256" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB256" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AC256" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD256" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE256" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF256" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AG256" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH256" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI256" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ256" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AK256" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL256" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM256" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="AN256" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="AO256" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AP256" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="Q256" t="n">
+        <v>8</v>
+      </c>
+      <c r="R256" t="n">
+        <v>18</v>
+      </c>
+      <c r="S256" t="n">
+        <v>2</v>
+      </c>
+      <c r="T256" t="n">
+        <v>4</v>
+      </c>
+      <c r="U256" t="n">
+        <v>6</v>
+      </c>
+      <c r="V256" t="n">
+        <v>4</v>
+      </c>
+      <c r="W256" t="n">
+        <v>0</v>
+      </c>
+      <c r="X256" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y256" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z256" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB256" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD256" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE256" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF256" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG256" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH256" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI256" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ256" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK256" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL256" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM256" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN256" t="n">
+        <v>160</v>
+      </c>
+      <c r="AO256" t="n">
+        <v>31</v>
+      </c>
+      <c r="AP256" t="n">
+        <v>74</v>
       </c>
       <c r="AQ256" t="inlineStr">
         <is>
@@ -49580,15 +49220,11 @@
           <t>26 066</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G257" t="n">
+        <v>1</v>
+      </c>
+      <c r="H257" t="n">
+        <v>1</v>
       </c>
       <c r="I257" t="inlineStr">
         <is>
@@ -49622,135 +49258,83 @@
           <t>35%</t>
         </is>
       </c>
-      <c r="Q257" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R257" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S257" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T257" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U257" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V257" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W257" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X257" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y257" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="Z257" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AA257" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB257" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC257" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD257" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE257" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AF257" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG257" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH257" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI257" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AJ257" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AK257" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL257" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM257" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="AN257" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AO257" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="AP257" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="Q257" t="n">
+        <v>8</v>
+      </c>
+      <c r="R257" t="n">
+        <v>7</v>
+      </c>
+      <c r="S257" t="n">
+        <v>3</v>
+      </c>
+      <c r="T257" t="n">
+        <v>3</v>
+      </c>
+      <c r="U257" t="n">
+        <v>4</v>
+      </c>
+      <c r="V257" t="n">
+        <v>2</v>
+      </c>
+      <c r="W257" t="n">
+        <v>1</v>
+      </c>
+      <c r="X257" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y257" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z257" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA257" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB257" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD257" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE257" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF257" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG257" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH257" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI257" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ257" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK257" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL257" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM257" t="n">
+        <v>147</v>
+      </c>
+      <c r="AN257" t="n">
+        <v>86</v>
+      </c>
+      <c r="AO257" t="n">
+        <v>71</v>
+      </c>
+      <c r="AP257" t="n">
+        <v>21</v>
       </c>
       <c r="AQ257" t="inlineStr">
         <is>
@@ -49822,15 +49406,11 @@
           <t>14 308</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G258" t="n">
+        <v>0</v>
+      </c>
+      <c r="H258" t="n">
+        <v>1</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
@@ -49864,135 +49444,83 @@
           <t>59%</t>
         </is>
       </c>
-      <c r="Q258" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R258" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S258" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T258" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U258" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V258" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W258" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X258" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Y258" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z258" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA258" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB258" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AC258" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD258" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE258" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF258" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AG258" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH258" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI258" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ258" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK258" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL258" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM258" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="AN258" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AO258" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="AP258" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="Q258" t="n">
+        <v>12</v>
+      </c>
+      <c r="R258" t="n">
+        <v>20</v>
+      </c>
+      <c r="S258" t="n">
+        <v>5</v>
+      </c>
+      <c r="T258" t="n">
+        <v>2</v>
+      </c>
+      <c r="U258" t="n">
+        <v>7</v>
+      </c>
+      <c r="V258" t="n">
+        <v>7</v>
+      </c>
+      <c r="W258" t="n">
+        <v>0</v>
+      </c>
+      <c r="X258" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y258" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z258" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA258" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB258" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC258" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD258" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE258" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF258" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG258" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH258" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI258" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ258" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL258" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM258" t="n">
+        <v>74</v>
+      </c>
+      <c r="AN258" t="n">
+        <v>114</v>
+      </c>
+      <c r="AO258" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP258" t="n">
+        <v>50</v>
       </c>
       <c r="AQ258" t="inlineStr">
         <is>
@@ -50028,16 +49556,1496 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY258" t="inlineStr">
+      <c r="AY258" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>27.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Ruiz A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Estadi Mallorca Son Moix
+ (Palma de Mallorca)</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>26 020</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>20 470</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD259" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AZ258" t="inlineStr">
+      <c r="AE259" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AF259" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG259" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH259" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI259" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ259" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK259" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
+      <c r="AL259" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM259" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AN259" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AO259" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AP259" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AQ259" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>arrasate jagoba</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="AT259" t="inlineStr">
+        <is>
+          <t>pimienta francisco</t>
+        </is>
+      </c>
+      <c r="AU259" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV259" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX259" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY259" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>26.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Ortiz M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Estadio de la Ceramica
+ (Villarreal)</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>23 000</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>19 651</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB260" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC260" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE260" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF260" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AG260" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH260" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI260" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ260" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK260" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL260" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM260" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AN260" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AO260" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AP260" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AQ260" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>marcelino</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="AT260" t="inlineStr">
+        <is>
+          <t>giraldez claudio</t>
+        </is>
+      </c>
+      <c r="AU260" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV260" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW260" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX260" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="inlineStr">
+        <is>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>25.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Munuera J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Metropolitano Stadium
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>70 460</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>60 414</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD261" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF261" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG261" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH261" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI261" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ261" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK261" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL261" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM261" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AN261" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="AO261" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AP261" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="AQ261" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>simeone diego</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="AT261" t="inlineStr">
+        <is>
+          <t>michel</t>
+        </is>
+      </c>
+      <c r="AU261" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV261" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW261" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX261" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>nXUxw7wg</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>26.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Muniz Munoz C.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Arcángel
+ (Córdoba)</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>21 822</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>14 415</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>Cordoba</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Burgos CF</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD262" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF262" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG262" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI262" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ262" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK262" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL262" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM262" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AN262" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AO262" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AP262" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AQ262" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="AR262" t="inlineStr">
+        <is>
+          <t>ania ivan</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr">
+        <is>
+          <t>l6JQtDqc</t>
+        </is>
+      </c>
+      <c r="AT262" t="inlineStr">
+        <is>
+          <t>bolo</t>
+        </is>
+      </c>
+      <c r="AU262" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV262" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW262" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX262" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY262" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>Q31eQTgm</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>26.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Cid Camacho G.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Estadio Municipal Cartagonova
+ (Cartagena)</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>13 745</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>8 800</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>FC Cartagena SAD</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr"/>
+      <c r="N263" t="inlineStr"/>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD263" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF263" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG263" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI263" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ263" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK263" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL263" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM263" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AN263" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="AO263" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AP263" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AQ263" t="inlineStr">
+        <is>
+          <t>M1vEw5An</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>abelardo</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="AT263" t="inlineStr">
+        <is>
+          <t>fernandez braulio victor</t>
+        </is>
+      </c>
+      <c r="AU263" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV263" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW263" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX263" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>MVf4O7Oa</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>25.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Gonzalez Esteban J. A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Castalia
+ (Castellón de la Plana)</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>15 500</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>13 709</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>Castellon</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>R. Oviedo</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr"/>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD264" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AF264" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AG264" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH264" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI264" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ264" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK264" t="inlineStr"/>
+      <c r="AL264" t="inlineStr"/>
+      <c r="AM264" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AN264" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AO264" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AP264" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AQ264" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="AR264" t="inlineStr">
+        <is>
+          <t>schreuder dick</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="AT264" t="inlineStr">
+        <is>
+          <t>calleja javier</t>
+        </is>
+      </c>
+      <c r="AU264" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV264" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX264" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ264"/>
+  <dimension ref="A1:AZ273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49596,15 +49596,11 @@
           <t>20 470</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G259" t="n">
+        <v>0</v>
+      </c>
+      <c r="H259" t="n">
+        <v>0</v>
       </c>
       <c r="I259" t="inlineStr">
         <is>
@@ -49626,15 +49622,11 @@
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="M259" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="N259" t="inlineStr">
-        <is>
-          <t>1.00</t>
-        </is>
+      <c r="M259" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="N259" t="n">
+        <v>1</v>
       </c>
       <c r="O259" t="inlineStr">
         <is>
@@ -49646,135 +49638,83 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q259" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R259" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S259" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T259" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U259" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V259" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W259" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X259" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y259" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z259" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AA259" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB259" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AC259" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD259" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE259" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AF259" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AG259" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH259" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI259" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ259" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK259" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL259" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM259" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="AN259" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="AO259" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="AP259" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="Q259" t="n">
+        <v>12</v>
+      </c>
+      <c r="R259" t="n">
+        <v>16</v>
+      </c>
+      <c r="S259" t="n">
+        <v>4</v>
+      </c>
+      <c r="T259" t="n">
+        <v>7</v>
+      </c>
+      <c r="U259" t="n">
+        <v>6</v>
+      </c>
+      <c r="V259" t="n">
+        <v>6</v>
+      </c>
+      <c r="W259" t="n">
+        <v>2</v>
+      </c>
+      <c r="X259" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y259" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z259" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA259" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB259" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC259" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD259" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE259" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF259" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG259" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH259" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI259" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ259" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL259" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM259" t="n">
+        <v>119</v>
+      </c>
+      <c r="AN259" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO259" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP259" t="n">
+        <v>48</v>
       </c>
       <c r="AQ259" t="inlineStr">
         <is>
@@ -49810,15 +49750,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY259" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ259" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AY259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ259" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="260">
@@ -49854,15 +49790,11 @@
           <t>19 651</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G260" t="n">
+        <v>4</v>
+      </c>
+      <c r="H260" t="n">
+        <v>3</v>
       </c>
       <c r="I260" t="inlineStr">
         <is>
@@ -49884,15 +49816,11 @@
           <t>Celta Vigo</t>
         </is>
       </c>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>3.77</t>
-        </is>
-      </c>
-      <c r="N260" t="inlineStr">
-        <is>
-          <t>3.18</t>
-        </is>
+      <c r="M260" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="N260" t="n">
+        <v>3.18</v>
       </c>
       <c r="O260" t="inlineStr">
         <is>
@@ -49904,135 +49832,83 @@
           <t>55%</t>
         </is>
       </c>
-      <c r="Q260" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R260" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S260" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T260" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U260" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V260" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W260" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X260" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y260" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Z260" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA260" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB260" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC260" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD260" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE260" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AF260" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AG260" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH260" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI260" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ260" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AK260" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL260" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM260" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="AN260" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="AO260" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="AP260" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+      <c r="Q260" t="n">
+        <v>24</v>
+      </c>
+      <c r="R260" t="n">
+        <v>20</v>
+      </c>
+      <c r="S260" t="n">
+        <v>9</v>
+      </c>
+      <c r="T260" t="n">
+        <v>8</v>
+      </c>
+      <c r="U260" t="n">
+        <v>11</v>
+      </c>
+      <c r="V260" t="n">
+        <v>4</v>
+      </c>
+      <c r="W260" t="n">
+        <v>4</v>
+      </c>
+      <c r="X260" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y260" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z260" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA260" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB260" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC260" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD260" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE260" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF260" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG260" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH260" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI260" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ260" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK260" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL260" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM260" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN260" t="n">
+        <v>108</v>
+      </c>
+      <c r="AO260" t="n">
+        <v>45</v>
+      </c>
+      <c r="AP260" t="n">
+        <v>52</v>
       </c>
       <c r="AQ260" t="inlineStr">
         <is>
@@ -50104,15 +49980,11 @@
           <t>60 414</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G261" t="n">
+        <v>3</v>
+      </c>
+      <c r="H261" t="n">
+        <v>0</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
@@ -50134,15 +50006,11 @@
           <t>Girona</t>
         </is>
       </c>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="N261" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
+      <c r="M261" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="N261" t="n">
+        <v>0.51</v>
       </c>
       <c r="O261" t="inlineStr">
         <is>
@@ -50154,135 +50022,83 @@
           <t>58%</t>
         </is>
       </c>
-      <c r="Q261" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R261" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S261" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T261" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U261" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V261" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W261" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X261" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y261" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z261" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA261" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB261" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AC261" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD261" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE261" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AF261" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AG261" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH261" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI261" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ261" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK261" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL261" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM261" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="AN261" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="AO261" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="AP261" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="Q261" t="n">
+        <v>11</v>
+      </c>
+      <c r="R261" t="n">
+        <v>13</v>
+      </c>
+      <c r="S261" t="n">
+        <v>6</v>
+      </c>
+      <c r="T261" t="n">
+        <v>5</v>
+      </c>
+      <c r="U261" t="n">
+        <v>2</v>
+      </c>
+      <c r="V261" t="n">
+        <v>3</v>
+      </c>
+      <c r="W261" t="n">
+        <v>3</v>
+      </c>
+      <c r="X261" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y261" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z261" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA261" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB261" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC261" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD261" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE261" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF261" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG261" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH261" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI261" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ261" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK261" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL261" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM261" t="n">
+        <v>84</v>
+      </c>
+      <c r="AN261" t="n">
+        <v>146</v>
+      </c>
+      <c r="AO261" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP261" t="n">
+        <v>69</v>
       </c>
       <c r="AQ261" t="inlineStr">
         <is>
@@ -50354,15 +50170,11 @@
           <t>14 415</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G262" t="n">
+        <v>2</v>
+      </c>
+      <c r="H262" t="n">
+        <v>2</v>
       </c>
       <c r="I262" t="inlineStr">
         <is>
@@ -50396,135 +50208,83 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q262" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R262" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S262" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T262" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U262" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V262" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W262" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X262" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y262" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Z262" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AA262" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB262" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD262" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AE262" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AF262" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AG262" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH262" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI262" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AJ262" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK262" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL262" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM262" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="AN262" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="AO262" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="AP262" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="Q262" t="n">
+        <v>11</v>
+      </c>
+      <c r="R262" t="n">
+        <v>12</v>
+      </c>
+      <c r="S262" t="n">
+        <v>4</v>
+      </c>
+      <c r="T262" t="n">
+        <v>5</v>
+      </c>
+      <c r="U262" t="n">
+        <v>5</v>
+      </c>
+      <c r="V262" t="n">
+        <v>4</v>
+      </c>
+      <c r="W262" t="n">
+        <v>2</v>
+      </c>
+      <c r="X262" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA262" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB262" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC262" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD262" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE262" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF262" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG262" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH262" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI262" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ262" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK262" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL262" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM262" t="n">
+        <v>91</v>
+      </c>
+      <c r="AN262" t="n">
+        <v>92</v>
+      </c>
+      <c r="AO262" t="n">
+        <v>54</v>
+      </c>
+      <c r="AP262" t="n">
+        <v>36</v>
       </c>
       <c r="AQ262" t="inlineStr">
         <is>
@@ -50560,15 +50320,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY262" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AZ262" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AY262" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ262" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -50604,15 +50360,11 @@
           <t>8 800</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G263" t="n">
+        <v>1</v>
+      </c>
+      <c r="H263" t="n">
+        <v>2</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
@@ -50646,135 +50398,83 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="Q263" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R263" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S263" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T263" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U263" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V263" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W263" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X263" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y263" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z263" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA263" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB263" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC263" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD263" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE263" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AF263" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AG263" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH263" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI263" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ263" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK263" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL263" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM263" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="AN263" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="AO263" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="AP263" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+      <c r="Q263" t="n">
+        <v>9</v>
+      </c>
+      <c r="R263" t="n">
+        <v>17</v>
+      </c>
+      <c r="S263" t="n">
+        <v>3</v>
+      </c>
+      <c r="T263" t="n">
+        <v>8</v>
+      </c>
+      <c r="U263" t="n">
+        <v>3</v>
+      </c>
+      <c r="V263" t="n">
+        <v>6</v>
+      </c>
+      <c r="W263" t="n">
+        <v>3</v>
+      </c>
+      <c r="X263" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB263" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD263" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE263" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF263" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG263" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH263" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI263" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ263" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK263" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL263" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM263" t="n">
+        <v>108</v>
+      </c>
+      <c r="AN263" t="n">
+        <v>124</v>
+      </c>
+      <c r="AO263" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP263" t="n">
+        <v>58</v>
       </c>
       <c r="AQ263" t="inlineStr">
         <is>
@@ -50846,15 +50546,11 @@
           <t>13 709</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" t="n">
+        <v>0</v>
       </c>
       <c r="I264" t="inlineStr">
         <is>
@@ -50888,127 +50584,79 @@
           <t>39%</t>
         </is>
       </c>
-      <c r="Q264" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R264" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S264" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T264" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U264" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V264" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W264" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X264" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y264" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z264" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AA264" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AB264" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD264" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE264" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AF264" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AG264" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH264" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI264" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ264" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="Q264" t="n">
+        <v>20</v>
+      </c>
+      <c r="R264" t="n">
+        <v>7</v>
+      </c>
+      <c r="S264" t="n">
+        <v>6</v>
+      </c>
+      <c r="T264" t="n">
+        <v>1</v>
+      </c>
+      <c r="U264" t="n">
+        <v>8</v>
+      </c>
+      <c r="V264" t="n">
+        <v>5</v>
+      </c>
+      <c r="W264" t="n">
+        <v>6</v>
+      </c>
+      <c r="X264" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA264" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB264" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC264" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD264" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE264" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF264" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG264" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH264" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI264" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ264" t="n">
+        <v>16</v>
       </c>
       <c r="AK264" t="inlineStr"/>
       <c r="AL264" t="inlineStr"/>
-      <c r="AM264" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="AN264" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AO264" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AP264" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="AM264" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN264" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO264" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP264" t="n">
+        <v>10</v>
       </c>
       <c r="AQ264" t="inlineStr">
         <is>
@@ -51046,6 +50694,2236 @@
       </c>
       <c r="AY264" t="inlineStr"/>
       <c r="AZ264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>29.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Busquets Ferrer M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Estadio de Gran Canaria
+ (Las Palmas)</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>32 392</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>31 192</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>2.74</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD265" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AF265" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AG265" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH265" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI265" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ265" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK265" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL265" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM265" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AN265" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="AO265" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AP265" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AQ265" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>carrion luis</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="AT265" t="inlineStr">
+        <is>
+          <t>ancelotti carlo</t>
+        </is>
+      </c>
+      <c r="AU265" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV265" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX265" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>29.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Maeso F.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Montilivi
+ (Girona)</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>14 624</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>13 275</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB266" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD266" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF266" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG266" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH266" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI266" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ266" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK266" t="inlineStr"/>
+      <c r="AL266" t="inlineStr"/>
+      <c r="AM266" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AN266" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AO266" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AP266" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AQ266" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="AR266" t="inlineStr">
+        <is>
+          <t>michel</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="AT266" t="inlineStr">
+        <is>
+          <t>moreno vicente</t>
+        </is>
+      </c>
+      <c r="AU266" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV266" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX266" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>KhwykQ8L</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>28.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Bengoetxea R.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Metropolitano Stadium
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>70 460</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>56 669</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AD267" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AF267" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG267" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH267" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI267" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ267" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK267" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL267" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM267" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="AN267" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AO267" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="AP267" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AQ267" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>simeone diego</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="AT267" t="inlineStr">
+        <is>
+          <t>gonzalez manolo</t>
+        </is>
+      </c>
+      <c r="AU267" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV267" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX267" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>v1KiOZ2d</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>28.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Sanchez J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Reale Arena
+ (San Sebastian)</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>40 000</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>32 220</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X268" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD268" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE268" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AF268" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG268" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH268" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI268" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ268" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK268" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL268" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM268" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AN268" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="AO268" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AP268" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AQ268" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="AR268" t="inlineStr">
+        <is>
+          <t>alguacil imanol</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="AT268" t="inlineStr">
+        <is>
+          <t>garcia luis</t>
+        </is>
+      </c>
+      <c r="AU268" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV268" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX268" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY268" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>0Y1WIvRG</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>28.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Fuertes P.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Estadio San Mamés
+ (Bilbao)</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>53 331</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>48 644</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD269" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI269" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ269" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK269" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL269" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM269" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="AN269" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="AO269" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="AP269" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="AR269" t="inlineStr">
+        <is>
+          <t>valverde tejedor ernesto</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="AT269" t="inlineStr">
+        <is>
+          <t>baraja ruben</t>
+        </is>
+      </c>
+      <c r="AU269" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV269" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX269" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>f92vnwe3</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>28.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Quintero A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Estadio José Zorrilla
+ (Valladolid)</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>27 618</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>21 764</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD270" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF270" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH270" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI270" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ270" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AK270" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL270" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM270" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AN270" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AO270" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AP270" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AQ270" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="AR270" t="inlineStr">
+        <is>
+          <t>pezzolano paulo</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="AT270" t="inlineStr">
+        <is>
+          <t>jimenez borja</t>
+        </is>
+      </c>
+      <c r="AU270" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV270" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX270" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>27.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Grado C. S.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Campo de Futbol de Vallecas
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>14 505</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>14 031</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD271" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AF271" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH271" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI271" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ271" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK271" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL271" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM271" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AN271" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AO271" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AP271" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="AQ271" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="AR271" t="inlineStr">
+        <is>
+          <t>perez inigo</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="AT271" t="inlineStr">
+        <is>
+          <t>flick hans dieter</t>
+        </is>
+      </c>
+      <c r="AU271" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV271" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW271" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX271" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="inlineStr">
+        <is>
+          <t>x2RBbu6T</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>30.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Mallo E.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Carlos Tartiere
+ (Oviedo)</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>30 500</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>R. Oviedo</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD272" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF272" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG272" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH272" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI272" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ272" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AK272" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL272" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM272" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="AN272" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AO272" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AP272" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AQ272" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="AR272" t="inlineStr">
+        <is>
+          <t>calleja javier</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr">
+        <is>
+          <t>rak12p9n</t>
+        </is>
+      </c>
+      <c r="AT272" t="inlineStr">
+        <is>
+          <t>lopez jose</t>
+        </is>
+      </c>
+      <c r="AU272" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV272" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW272" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX272" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="inlineStr">
+        <is>
+          <t>8MZf2N64</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>30.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Gonzalez Diaz M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Los Cármenes
+ (Granada)</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>22 524</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>15 089</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>Granada CF</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ273" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK273" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL273" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM273" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="AN273" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="AO273" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="AP273" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AQ273" t="inlineStr">
+        <is>
+          <t>K4dMCgFa</t>
+        </is>
+      </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>abascal guillermo</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="AT273" t="inlineStr">
+        <is>
+          <t>hidalgo antonio</t>
+        </is>
+      </c>
+      <c r="AU273" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV273" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW273" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX273" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ273"/>
+  <dimension ref="A1:AZ277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50728,15 +50728,11 @@
           <t>31 192</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G265" t="n">
+        <v>1</v>
+      </c>
+      <c r="H265" t="n">
+        <v>1</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
@@ -50758,15 +50754,11 @@
           <t>Real Madrid</t>
         </is>
       </c>
-      <c r="M265" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="N265" t="inlineStr">
-        <is>
-          <t>2.74</t>
-        </is>
+      <c r="M265" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="N265" t="n">
+        <v>2.74</v>
       </c>
       <c r="O265" t="inlineStr">
         <is>
@@ -50778,135 +50770,83 @@
           <t>56%</t>
         </is>
       </c>
-      <c r="Q265" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R265" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="S265" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T265" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U265" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V265" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W265" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X265" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y265" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z265" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AA265" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB265" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC265" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD265" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE265" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AF265" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AG265" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH265" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI265" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ265" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK265" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL265" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM265" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AN265" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="AO265" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="AP265" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
+      <c r="Q265" t="n">
+        <v>7</v>
+      </c>
+      <c r="R265" t="n">
+        <v>25</v>
+      </c>
+      <c r="S265" t="n">
+        <v>3</v>
+      </c>
+      <c r="T265" t="n">
+        <v>8</v>
+      </c>
+      <c r="U265" t="n">
+        <v>3</v>
+      </c>
+      <c r="V265" t="n">
+        <v>10</v>
+      </c>
+      <c r="W265" t="n">
+        <v>1</v>
+      </c>
+      <c r="X265" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB265" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE265" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF265" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG265" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH265" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI265" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ265" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK265" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL265" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM265" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN265" t="n">
+        <v>171</v>
+      </c>
+      <c r="AO265" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP265" t="n">
+        <v>82</v>
       </c>
       <c r="AQ265" t="inlineStr">
         <is>
@@ -50978,15 +50918,11 @@
           <t>13 275</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G266" t="n">
+        <v>4</v>
+      </c>
+      <c r="H266" t="n">
+        <v>0</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
@@ -51008,15 +50944,11 @@
           <t>Osasuna</t>
         </is>
       </c>
-      <c r="M266" t="inlineStr">
-        <is>
-          <t>2.42</t>
-        </is>
-      </c>
-      <c r="N266" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
+      <c r="M266" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="N266" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="O266" t="inlineStr">
         <is>
@@ -51028,127 +50960,79 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="Q266" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R266" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S266" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T266" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U266" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V266" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W266" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X266" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y266" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z266" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA266" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB266" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC266" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD266" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE266" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AF266" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AG266" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH266" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI266" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ266" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="Q266" t="n">
+        <v>10</v>
+      </c>
+      <c r="R266" t="n">
+        <v>1</v>
+      </c>
+      <c r="S266" t="n">
+        <v>5</v>
+      </c>
+      <c r="T266" t="n">
+        <v>0</v>
+      </c>
+      <c r="U266" t="n">
+        <v>3</v>
+      </c>
+      <c r="V266" t="n">
+        <v>1</v>
+      </c>
+      <c r="W266" t="n">
+        <v>2</v>
+      </c>
+      <c r="X266" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF266" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG266" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI266" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ266" t="n">
+        <v>9</v>
       </c>
       <c r="AK266" t="inlineStr"/>
       <c r="AL266" t="inlineStr"/>
-      <c r="AM266" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="AN266" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="AO266" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AP266" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="AM266" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN266" t="n">
+        <v>66</v>
+      </c>
+      <c r="AO266" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP266" t="n">
+        <v>18</v>
       </c>
       <c r="AQ266" t="inlineStr">
         <is>
@@ -51220,15 +51104,11 @@
           <t>56 669</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G267" t="n">
+        <v>0</v>
+      </c>
+      <c r="H267" t="n">
+        <v>0</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
@@ -51250,15 +51130,11 @@
           <t>Espanyol</t>
         </is>
       </c>
-      <c r="M267" t="inlineStr">
-        <is>
-          <t>2.67</t>
-        </is>
-      </c>
-      <c r="N267" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
+      <c r="M267" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="N267" t="n">
+        <v>0.5</v>
       </c>
       <c r="O267" t="inlineStr">
         <is>
@@ -51270,135 +51146,83 @@
           <t>38%</t>
         </is>
       </c>
-      <c r="Q267" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R267" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S267" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T267" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U267" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V267" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W267" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X267" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y267" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z267" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA267" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB267" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AD267" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE267" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AF267" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG267" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH267" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI267" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AJ267" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK267" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL267" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM267" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="AN267" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AO267" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="AP267" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="Q267" t="n">
+        <v>25</v>
+      </c>
+      <c r="R267" t="n">
+        <v>8</v>
+      </c>
+      <c r="S267" t="n">
+        <v>7</v>
+      </c>
+      <c r="T267" t="n">
+        <v>1</v>
+      </c>
+      <c r="U267" t="n">
+        <v>11</v>
+      </c>
+      <c r="V267" t="n">
+        <v>7</v>
+      </c>
+      <c r="W267" t="n">
+        <v>7</v>
+      </c>
+      <c r="X267" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB267" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF267" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH267" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI267" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ267" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK267" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL267" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM267" t="n">
+        <v>123</v>
+      </c>
+      <c r="AN267" t="n">
+        <v>97</v>
+      </c>
+      <c r="AO267" t="n">
+        <v>71</v>
+      </c>
+      <c r="AP267" t="n">
+        <v>23</v>
       </c>
       <c r="AQ267" t="inlineStr">
         <is>
@@ -51470,15 +51294,11 @@
           <t>32 220</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G268" t="n">
+        <v>1</v>
+      </c>
+      <c r="H268" t="n">
+        <v>2</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
@@ -51500,15 +51320,11 @@
           <t>Alaves</t>
         </is>
       </c>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
-      <c r="N268" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
+      <c r="M268" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="N268" t="n">
+        <v>1.42</v>
       </c>
       <c r="O268" t="inlineStr">
         <is>
@@ -51520,135 +51336,83 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q268" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R268" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S268" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T268" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U268" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V268" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W268" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X268" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y268" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA268" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB268" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD268" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE268" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AF268" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG268" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH268" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI268" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ268" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK268" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL268" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM268" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="AN268" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="AO268" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="AP268" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="Q268" t="n">
+        <v>10</v>
+      </c>
+      <c r="R268" t="n">
+        <v>14</v>
+      </c>
+      <c r="S268" t="n">
+        <v>1</v>
+      </c>
+      <c r="T268" t="n">
+        <v>5</v>
+      </c>
+      <c r="U268" t="n">
+        <v>7</v>
+      </c>
+      <c r="V268" t="n">
+        <v>8</v>
+      </c>
+      <c r="W268" t="n">
+        <v>2</v>
+      </c>
+      <c r="X268" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB268" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC268" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD268" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE268" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF268" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG268" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH268" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI268" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ268" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK268" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL268" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM268" t="n">
+        <v>98</v>
+      </c>
+      <c r="AN268" t="n">
+        <v>115</v>
+      </c>
+      <c r="AO268" t="n">
+        <v>43</v>
+      </c>
+      <c r="AP268" t="n">
+        <v>48</v>
       </c>
       <c r="AQ268" t="inlineStr">
         <is>
@@ -51684,15 +51448,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY268" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AZ268" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AY268" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ268" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="269">
@@ -51728,15 +51488,11 @@
           <t>48 644</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G269" t="n">
+        <v>1</v>
+      </c>
+      <c r="H269" t="n">
+        <v>0</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
@@ -51758,15 +51514,11 @@
           <t>Valencia</t>
         </is>
       </c>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
-      <c r="N269" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
+      <c r="M269" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N269" t="n">
+        <v>0.06</v>
       </c>
       <c r="O269" t="inlineStr">
         <is>
@@ -51778,135 +51530,83 @@
           <t>49%</t>
         </is>
       </c>
-      <c r="Q269" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R269" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S269" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T269" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U269" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V269" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W269" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X269" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y269" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z269" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AA269" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB269" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD269" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE269" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AF269" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AG269" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH269" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI269" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ269" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK269" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL269" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM269" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="AN269" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="AO269" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="AP269" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="Q269" t="n">
+        <v>13</v>
+      </c>
+      <c r="R269" t="n">
+        <v>2</v>
+      </c>
+      <c r="S269" t="n">
+        <v>4</v>
+      </c>
+      <c r="T269" t="n">
+        <v>0</v>
+      </c>
+      <c r="U269" t="n">
+        <v>4</v>
+      </c>
+      <c r="V269" t="n">
+        <v>1</v>
+      </c>
+      <c r="W269" t="n">
+        <v>5</v>
+      </c>
+      <c r="X269" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB269" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD269" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE269" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF269" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG269" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH269" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI269" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ269" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK269" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL269" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM269" t="n">
+        <v>151</v>
+      </c>
+      <c r="AN269" t="n">
+        <v>87</v>
+      </c>
+      <c r="AO269" t="n">
+        <v>49</v>
+      </c>
+      <c r="AP269" t="n">
+        <v>31</v>
       </c>
       <c r="AQ269" t="inlineStr">
         <is>
@@ -51978,15 +51678,11 @@
           <t>21 764</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G270" t="n">
+        <v>0</v>
+      </c>
+      <c r="H270" t="n">
+        <v>0</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
@@ -52008,15 +51704,11 @@
           <t>Leganes</t>
         </is>
       </c>
-      <c r="M270" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="N270" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
+      <c r="M270" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="N270" t="n">
+        <v>0.09</v>
       </c>
       <c r="O270" t="inlineStr">
         <is>
@@ -52028,135 +51720,83 @@
           <t>42%</t>
         </is>
       </c>
-      <c r="Q270" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R270" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S270" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T270" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U270" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V270" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W270" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X270" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y270" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="Z270" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA270" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB270" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC270" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD270" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE270" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF270" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG270" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH270" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI270" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ270" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AK270" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL270" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AM270" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AN270" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="AO270" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AP270" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="Q270" t="n">
+        <v>12</v>
+      </c>
+      <c r="R270" t="n">
+        <v>8</v>
+      </c>
+      <c r="S270" t="n">
+        <v>2</v>
+      </c>
+      <c r="T270" t="n">
+        <v>1</v>
+      </c>
+      <c r="U270" t="n">
+        <v>8</v>
+      </c>
+      <c r="V270" t="n">
+        <v>6</v>
+      </c>
+      <c r="W270" t="n">
+        <v>2</v>
+      </c>
+      <c r="X270" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA270" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB270" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC270" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD270" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE270" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF270" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG270" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH270" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI270" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ270" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK270" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL270" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM270" t="n">
+        <v>97</v>
+      </c>
+      <c r="AN270" t="n">
+        <v>109</v>
+      </c>
+      <c r="AO270" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP270" t="n">
+        <v>29</v>
       </c>
       <c r="AQ270" t="inlineStr">
         <is>
@@ -52228,15 +51868,11 @@
           <t>14 031</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G271" t="n">
+        <v>1</v>
+      </c>
+      <c r="H271" t="n">
+        <v>2</v>
       </c>
       <c r="I271" t="inlineStr">
         <is>
@@ -52258,15 +51894,11 @@
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
-      </c>
-      <c r="N271" t="inlineStr">
-        <is>
-          <t>1.01</t>
-        </is>
+      <c r="M271" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="N271" t="n">
+        <v>1.01</v>
       </c>
       <c r="O271" t="inlineStr">
         <is>
@@ -52278,135 +51910,83 @@
           <t>63%</t>
         </is>
       </c>
-      <c r="Q271" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R271" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S271" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T271" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U271" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V271" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W271" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X271" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Y271" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z271" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AA271" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB271" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC271" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD271" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE271" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF271" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AG271" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH271" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI271" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AJ271" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK271" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL271" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM271" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="AN271" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="AO271" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="AP271" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="Q271" t="n">
+        <v>8</v>
+      </c>
+      <c r="R271" t="n">
+        <v>22</v>
+      </c>
+      <c r="S271" t="n">
+        <v>4</v>
+      </c>
+      <c r="T271" t="n">
+        <v>5</v>
+      </c>
+      <c r="U271" t="n">
+        <v>3</v>
+      </c>
+      <c r="V271" t="n">
+        <v>6</v>
+      </c>
+      <c r="W271" t="n">
+        <v>1</v>
+      </c>
+      <c r="X271" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA271" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB271" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC271" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD271" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE271" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF271" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG271" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH271" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI271" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ271" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK271" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL271" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM271" t="n">
+        <v>74</v>
+      </c>
+      <c r="AN271" t="n">
+        <v>113</v>
+      </c>
+      <c r="AO271" t="n">
+        <v>39</v>
+      </c>
+      <c r="AP271" t="n">
+        <v>62</v>
       </c>
       <c r="AQ271" t="inlineStr">
         <is>
@@ -52474,15 +52054,11 @@
         </is>
       </c>
       <c r="F272" t="inlineStr"/>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G272" t="n">
+        <v>1</v>
+      </c>
+      <c r="H272" t="n">
+        <v>3</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
@@ -52516,135 +52092,83 @@
           <t>35%</t>
         </is>
       </c>
-      <c r="Q272" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R272" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S272" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T272" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U272" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V272" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W272" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X272" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y272" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="Z272" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA272" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB272" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC272" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD272" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE272" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AF272" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AG272" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH272" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI272" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ272" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AK272" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL272" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM272" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="AN272" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="AO272" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="AP272" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="Q272" t="n">
+        <v>18</v>
+      </c>
+      <c r="R272" t="n">
+        <v>11</v>
+      </c>
+      <c r="S272" t="n">
+        <v>3</v>
+      </c>
+      <c r="T272" t="n">
+        <v>5</v>
+      </c>
+      <c r="U272" t="n">
+        <v>7</v>
+      </c>
+      <c r="V272" t="n">
+        <v>4</v>
+      </c>
+      <c r="W272" t="n">
+        <v>8</v>
+      </c>
+      <c r="X272" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y272" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z272" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA272" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB272" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD272" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE272" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF272" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG272" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH272" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI272" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ272" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK272" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL272" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM272" t="n">
+        <v>132</v>
+      </c>
+      <c r="AN272" t="n">
+        <v>99</v>
+      </c>
+      <c r="AO272" t="n">
+        <v>57</v>
+      </c>
+      <c r="AP272" t="n">
+        <v>32</v>
       </c>
       <c r="AQ272" t="inlineStr">
         <is>
@@ -52716,15 +52240,11 @@
           <t>15 089</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G273" t="n">
+        <v>1</v>
+      </c>
+      <c r="H273" t="n">
+        <v>3</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -52758,135 +52278,83 @@
           <t>37%</t>
         </is>
       </c>
-      <c r="Q273" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R273" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S273" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T273" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U273" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V273" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W273" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X273" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y273" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z273" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA273" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB273" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC273" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD273" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE273" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="AF273" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG273" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH273" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI273" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AJ273" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK273" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL273" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM273" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="AN273" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="AO273" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AP273" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="Q273" t="n">
+        <v>16</v>
+      </c>
+      <c r="R273" t="n">
+        <v>15</v>
+      </c>
+      <c r="S273" t="n">
+        <v>6</v>
+      </c>
+      <c r="T273" t="n">
+        <v>6</v>
+      </c>
+      <c r="U273" t="n">
+        <v>7</v>
+      </c>
+      <c r="V273" t="n">
+        <v>8</v>
+      </c>
+      <c r="W273" t="n">
+        <v>3</v>
+      </c>
+      <c r="X273" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y273" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z273" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA273" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB273" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE273" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF273" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG273" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH273" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI273" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ273" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL273" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM273" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN273" t="n">
+        <v>81</v>
+      </c>
+      <c r="AO273" t="n">
+        <v>78</v>
+      </c>
+      <c r="AP273" t="n">
+        <v>48</v>
       </c>
       <c r="AQ273" t="inlineStr">
         <is>
@@ -52924,6 +52392,998 @@
       </c>
       <c r="AY273" t="inlineStr"/>
       <c r="AZ273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>31.08.2024 14:15</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Vega A. C.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Stage Front Stadium
+ (Cornella de Llobregat)</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>40 000</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>22 405</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD274" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF274" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG274" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH274" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI274" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ274" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK274" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL274" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM274" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AN274" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AO274" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AP274" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AQ274" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>gonzalez manolo</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="AT274" t="inlineStr">
+        <is>
+          <t>perez inigo</t>
+        </is>
+      </c>
+      <c r="AU274" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV274" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>31.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Hernandez A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Estadio San Mamés
+ (Bilbao)</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>53 331</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>48 617</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD275" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF275" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI275" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ275" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK275" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM275" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="AN275" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AO275" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="AP275" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AQ275" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="AR275" t="inlineStr">
+        <is>
+          <t>valverde tejedor ernesto</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="AT275" t="inlineStr">
+        <is>
+          <t>simeone diego</t>
+        </is>
+      </c>
+      <c r="AU275" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV275" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW275" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX275" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>31.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Diaz de Mera I.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Estadi Olímpic Lluís Companys
+ (Barcelona)</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>55 926</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>44 359</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>4.13</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>0.62</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD276" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF276" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG276" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI276" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ276" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK276" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL276" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM276" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="AN276" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AO276" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AP276" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AQ276" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="AR276" t="inlineStr">
+        <is>
+          <t>flick hans dieter</t>
+        </is>
+      </c>
+      <c r="AS276" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="AT276" t="inlineStr">
+        <is>
+          <t>pezzolano paulo</t>
+        </is>
+      </c>
+      <c r="AU276" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV276" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX276" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="inlineStr">
+        <is>
+          <t>2qDTo2MN</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>31.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Lax Franco S.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Mirandilla
+ (Cadiz)</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>20 776</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>16 518</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Cadiz CF</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Tenerife</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AF277" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG277" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI277" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AJ277" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK277" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AL277" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM277" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="AN277" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AO277" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="AP277" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AQ277" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="AR277" t="inlineStr">
+        <is>
+          <t>lopez paco</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr">
+        <is>
+          <t>UBD9uzt0</t>
+        </is>
+      </c>
+      <c r="AT277" t="inlineStr">
+        <is>
+          <t>cano oscar</t>
+        </is>
+      </c>
+      <c r="AU277" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV277" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX277" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ277"/>
+  <dimension ref="A1:AZ290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52426,15 +52426,11 @@
           <t>22 405</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G274" t="n">
+        <v>2</v>
+      </c>
+      <c r="H274" t="n">
+        <v>1</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -52456,15 +52452,11 @@
           <t>Rayo Vallecano</t>
         </is>
       </c>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t>2.64</t>
-        </is>
-      </c>
-      <c r="N274" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
+      <c r="M274" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N274" t="n">
+        <v>1.45</v>
       </c>
       <c r="O274" t="inlineStr">
         <is>
@@ -52476,135 +52468,83 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q274" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R274" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S274" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T274" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U274" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V274" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W274" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X274" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y274" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Z274" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA274" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB274" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC274" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD274" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE274" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF274" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG274" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH274" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI274" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ274" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK274" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL274" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM274" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="AN274" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="AO274" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="AP274" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="Q274" t="n">
+        <v>10</v>
+      </c>
+      <c r="R274" t="n">
+        <v>16</v>
+      </c>
+      <c r="S274" t="n">
+        <v>5</v>
+      </c>
+      <c r="T274" t="n">
+        <v>5</v>
+      </c>
+      <c r="U274" t="n">
+        <v>3</v>
+      </c>
+      <c r="V274" t="n">
+        <v>5</v>
+      </c>
+      <c r="W274" t="n">
+        <v>2</v>
+      </c>
+      <c r="X274" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y274" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z274" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA274" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB274" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC274" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD274" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE274" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF274" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG274" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH274" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI274" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ274" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK274" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL274" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM274" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN274" t="n">
+        <v>109</v>
+      </c>
+      <c r="AO274" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP274" t="n">
+        <v>60</v>
       </c>
       <c r="AQ274" t="inlineStr">
         <is>
@@ -52676,15 +52616,11 @@
           <t>48 617</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G275" t="n">
+        <v>0</v>
+      </c>
+      <c r="H275" t="n">
+        <v>1</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -52706,15 +52642,11 @@
           <t>Atl. Madrid</t>
         </is>
       </c>
-      <c r="M275" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="N275" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
+      <c r="M275" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N275" t="n">
+        <v>1.78</v>
       </c>
       <c r="O275" t="inlineStr">
         <is>
@@ -52726,135 +52658,83 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q275" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R275" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S275" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T275" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U275" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V275" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W275" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X275" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y275" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z275" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA275" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB275" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC275" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD275" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE275" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF275" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG275" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH275" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI275" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ275" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AK275" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL275" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM275" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="AN275" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="AO275" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AP275" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="Q275" t="n">
+        <v>8</v>
+      </c>
+      <c r="R275" t="n">
+        <v>7</v>
+      </c>
+      <c r="S275" t="n">
+        <v>1</v>
+      </c>
+      <c r="T275" t="n">
+        <v>2</v>
+      </c>
+      <c r="U275" t="n">
+        <v>5</v>
+      </c>
+      <c r="V275" t="n">
+        <v>2</v>
+      </c>
+      <c r="W275" t="n">
+        <v>2</v>
+      </c>
+      <c r="X275" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y275" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z275" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC275" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD275" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE275" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF275" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG275" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH275" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI275" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ275" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK275" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL275" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM275" t="n">
+        <v>166</v>
+      </c>
+      <c r="AN275" t="n">
+        <v>105</v>
+      </c>
+      <c r="AO275" t="n">
+        <v>78</v>
+      </c>
+      <c r="AP275" t="n">
+        <v>42</v>
       </c>
       <c r="AQ275" t="inlineStr">
         <is>
@@ -52926,15 +52806,11 @@
           <t>44 359</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G276" t="n">
+        <v>7</v>
+      </c>
+      <c r="H276" t="n">
+        <v>0</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -52956,15 +52832,11 @@
           <t>Valladolid</t>
         </is>
       </c>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>4.13</t>
-        </is>
-      </c>
-      <c r="N276" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
+      <c r="M276" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="N276" t="n">
+        <v>0.62</v>
       </c>
       <c r="O276" t="inlineStr">
         <is>
@@ -52976,135 +52848,83 @@
           <t>30%</t>
         </is>
       </c>
-      <c r="Q276" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R276" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S276" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T276" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U276" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V276" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W276" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X276" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y276" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z276" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA276" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AB276" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC276" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD276" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE276" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF276" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG276" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH276" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI276" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AJ276" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK276" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL276" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM276" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="AN276" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="AO276" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="AP276" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
+      <c r="Q276" t="n">
+        <v>23</v>
+      </c>
+      <c r="R276" t="n">
+        <v>5</v>
+      </c>
+      <c r="S276" t="n">
+        <v>10</v>
+      </c>
+      <c r="T276" t="n">
+        <v>2</v>
+      </c>
+      <c r="U276" t="n">
+        <v>10</v>
+      </c>
+      <c r="V276" t="n">
+        <v>1</v>
+      </c>
+      <c r="W276" t="n">
+        <v>3</v>
+      </c>
+      <c r="X276" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y276" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z276" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA276" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB276" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC276" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD276" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE276" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF276" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG276" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH276" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI276" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ276" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK276" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL276" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM276" t="n">
+        <v>141</v>
+      </c>
+      <c r="AN276" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO276" t="n">
+        <v>63</v>
+      </c>
+      <c r="AP276" t="n">
+        <v>57</v>
       </c>
       <c r="AQ276" t="inlineStr">
         <is>
@@ -53176,15 +52996,11 @@
           <t>16 518</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G277" t="n">
+        <v>2</v>
+      </c>
+      <c r="H277" t="n">
+        <v>2</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -53218,135 +53034,83 @@
           <t>33%</t>
         </is>
       </c>
-      <c r="Q277" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R277" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S277" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T277" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U277" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V277" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y277" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Z277" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA277" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB277" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC277" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD277" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE277" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AF277" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AG277" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH277" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI277" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AJ277" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK277" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AL277" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM277" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="AN277" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="AO277" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="AP277" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="Q277" t="n">
+        <v>4</v>
+      </c>
+      <c r="R277" t="n">
+        <v>3</v>
+      </c>
+      <c r="S277" t="n">
+        <v>3</v>
+      </c>
+      <c r="T277" t="n">
+        <v>2</v>
+      </c>
+      <c r="U277" t="n">
+        <v>1</v>
+      </c>
+      <c r="V277" t="n">
+        <v>1</v>
+      </c>
+      <c r="W277" t="n">
+        <v>0</v>
+      </c>
+      <c r="X277" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y277" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z277" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA277" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB277" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC277" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD277" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE277" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF277" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG277" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH277" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI277" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ277" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK277" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL277" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM277" t="n">
+        <v>134</v>
+      </c>
+      <c r="AN277" t="n">
+        <v>63</v>
+      </c>
+      <c r="AO277" t="n">
+        <v>77</v>
+      </c>
+      <c r="AP277" t="n">
+        <v>24</v>
       </c>
       <c r="AQ277" t="inlineStr">
         <is>
@@ -53384,6 +53148,3224 @@
       </c>
       <c r="AY277" t="inlineStr"/>
       <c r="AZ277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>01.09.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Rojas J. A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Estadio Santiago Bernabéu
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>83 186</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>73 072</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X278" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB278" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC278" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD278" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE278" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF278" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AG278" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH278" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI278" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ278" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK278" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL278" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM278" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="AN278" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AO278" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AP278" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="AQ278" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="AR278" t="inlineStr">
+        <is>
+          <t>ancelotti carlo</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="AT278" t="inlineStr">
+        <is>
+          <t>pellegrini manuel</t>
+        </is>
+      </c>
+      <c r="AU278" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV278" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX278" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>01.09.2024 14:15</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Munuera Montero J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Coliseum
+ (Getafe)</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>16 500</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>10 929</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC279" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE279" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AF279" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AG279" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI279" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ279" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM279" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AN279" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="AO279" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AP279" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AQ279" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="AR279" t="inlineStr">
+        <is>
+          <t>bordalas pepe</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="AT279" t="inlineStr">
+        <is>
+          <t>alguacil imanol</t>
+        </is>
+      </c>
+      <c r="AU279" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV279" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW279" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX279" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>01.09.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Sanchez J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Estadio Ramón Sánchez Pizjuán
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>42 714</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>35 735</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB280" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC280" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD280" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE280" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF280" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG280" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH280" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI280" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ280" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK280" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL280" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM280" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="AN280" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AO280" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AP280" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AQ280" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>pimienta francisco</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="AT280" t="inlineStr">
+        <is>
+          <t>michel</t>
+        </is>
+      </c>
+      <c r="AU280" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV280" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX280" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>01.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Garcia V.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Estadio Mendizorrotza
+ (Vitoria-Gasteiz)</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>19 840</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>16 386</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD281" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE281" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF281" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG281" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH281" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI281" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ281" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK281" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL281" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM281" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AN281" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="AO281" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AP281" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AQ281" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="AR281" t="inlineStr">
+        <is>
+          <t>garcia luis</t>
+        </is>
+      </c>
+      <c r="AS281" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="AT281" t="inlineStr">
+        <is>
+          <t>carrion luis</t>
+        </is>
+      </c>
+      <c r="AU281" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV281" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW281" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX281" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>01.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Munuera J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>23 516</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>19 908</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB282" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC282" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD282" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE282" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF282" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AG282" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH282" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI282" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ282" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK282" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL282" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM282" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="AN282" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="AO282" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AP282" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AQ282" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="AR282" t="inlineStr">
+        <is>
+          <t>moreno vicente</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="AT282" t="inlineStr">
+        <is>
+          <t>giraldez claudio</t>
+        </is>
+      </c>
+      <c r="AU282" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV282" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX282" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>31.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Lopez M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Butarque
+ (Leganes)</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>12 454</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>10 482</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD283" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE283" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF283" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AG283" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH283" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI283" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ283" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK283" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL283" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM283" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="AN283" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AO283" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AP283" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AQ283" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="AR283" t="inlineStr">
+        <is>
+          <t>jimenez borja</t>
+        </is>
+      </c>
+      <c r="AS283" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="AT283" t="inlineStr">
+        <is>
+          <t>arrasate jagoba</t>
+        </is>
+      </c>
+      <c r="AU283" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV283" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX283" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>31.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Gil Manzano J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla
+ (Valencia)</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>49 430</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>43 857</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X284" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z284" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AB284" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC284" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD284" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE284" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF284" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AG284" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH284" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI284" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ284" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK284" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL284" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM284" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="AN284" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="AO284" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AP284" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AQ284" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="AR284" t="inlineStr">
+        <is>
+          <t>baraja ruben</t>
+        </is>
+      </c>
+      <c r="AS284" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="AT284" t="inlineStr">
+        <is>
+          <t>marcelino</t>
+        </is>
+      </c>
+      <c r="AU284" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV284" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX284" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY284" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="inlineStr">
+        <is>
+          <t>lfATGMLc</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>01.09.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Guzman Mansilla J. L.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Pepico Amat
+ (Elda)</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>4 038</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>4 830</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>Eldense</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>FC Cartagena SAD</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R285" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X285" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB285" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC285" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD285" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE285" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AF285" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG285" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH285" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI285" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ285" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK285" t="inlineStr"/>
+      <c r="AL285" t="inlineStr"/>
+      <c r="AM285" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AN285" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AO285" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AP285" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AQ285" t="inlineStr">
+        <is>
+          <t>hh4xt2Df</t>
+        </is>
+      </c>
+      <c r="AR285" t="inlineStr">
+        <is>
+          <t>ponz daniel</t>
+        </is>
+      </c>
+      <c r="AS285" t="inlineStr">
+        <is>
+          <t>M1vEw5An</t>
+        </is>
+      </c>
+      <c r="AT285" t="inlineStr">
+        <is>
+          <t>abelardo</t>
+        </is>
+      </c>
+      <c r="AU285" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV285" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX285" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="1" t="inlineStr">
+        <is>
+          <t>Gnw301yH</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>01.09.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Reig S. A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Anduva
+ (Miranda de Ebro)</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>5 759</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>4 747</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr"/>
+      <c r="N286" t="inlineStr"/>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X286" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="Z286" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB286" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC286" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD286" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE286" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF286" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AG286" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH286" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI286" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ286" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AK286" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL286" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM286" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AN286" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AO286" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AP286" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AQ286" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="AR286" t="inlineStr">
+        <is>
+          <t>lisci alessio</t>
+        </is>
+      </c>
+      <c r="AS286" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="AT286" t="inlineStr">
+        <is>
+          <t>fernandez braulio victor</t>
+        </is>
+      </c>
+      <c r="AU286" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV286" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX286" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>fJ9LmOiB</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>01.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Moreno A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Estadio El Plantío
+ (Burgos)</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>12 194</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>9 105</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>Burgos CF</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Castellon</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr"/>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R287" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X287" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z287" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB287" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC287" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD287" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE287" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AF287" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG287" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH287" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI287" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AJ287" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK287" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL287" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM287" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AN287" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="AO287" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AP287" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AQ287" t="inlineStr">
+        <is>
+          <t>l6JQtDqc</t>
+        </is>
+      </c>
+      <c r="AR287" t="inlineStr">
+        <is>
+          <t>bolo</t>
+        </is>
+      </c>
+      <c r="AS287" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="AT287" t="inlineStr">
+        <is>
+          <t>schreuder dick</t>
+        </is>
+      </c>
+      <c r="AU287" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV287" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX287" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="1" t="inlineStr">
+        <is>
+          <t>K0g0ttpo</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>01.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Monescillo D.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Riazor
+ (La Coruña)</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>34 889</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>26 452</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>Dep. La Coruna</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>Racing Club Ferrol</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr"/>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R288" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD288" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE288" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AF288" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG288" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH288" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI288" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AJ288" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK288" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL288" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM288" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="AN288" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AO288" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="AP288" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AQ288" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="AR288" t="inlineStr">
+        <is>
+          <t>idiakez imanol</t>
+        </is>
+      </c>
+      <c r="AS288" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="AT288" t="inlineStr">
+        <is>
+          <t>parralo cristobal</t>
+        </is>
+      </c>
+      <c r="AU288" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV288" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX288" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="1" t="inlineStr">
+        <is>
+          <t>Y3LCkpNb</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>31.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>De La Fuente Ramos O.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Power Horse Stadium
+ (Almería)</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>17 400</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>12 787</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>Almeria</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>Gijon</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr"/>
+      <c r="N289" t="inlineStr"/>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R289" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X289" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y289" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z289" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB289" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC289" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD289" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE289" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF289" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG289" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH289" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI289" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ289" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK289" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL289" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM289" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="AN289" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AO289" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AP289" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AQ289" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="AR289" t="inlineStr">
+        <is>
+          <t>rubi joan</t>
+        </is>
+      </c>
+      <c r="AS289" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="AT289" t="inlineStr">
+        <is>
+          <t>albes ruben</t>
+        </is>
+      </c>
+      <c r="AU289" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV289" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX289" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="1" t="inlineStr">
+        <is>
+          <t>YoStgJTj</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>31.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Palencia Caballero D.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Estadio La Rosaleda
+ (Málaga)</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>30 044</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>25 861</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr"/>
+      <c r="N290" t="inlineStr"/>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R290" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W290" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X290" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y290" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Z290" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB290" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC290" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD290" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE290" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF290" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG290" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH290" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI290" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ290" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AK290" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL290" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM290" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AN290" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AO290" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AP290" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AQ290" t="inlineStr">
+        <is>
+          <t>tjXr7SAp</t>
+        </is>
+      </c>
+      <c r="AR290" t="inlineStr">
+        <is>
+          <t>garcia sergio</t>
+        </is>
+      </c>
+      <c r="AS290" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="AT290" t="inlineStr">
+        <is>
+          <t>gonzalez alberto</t>
+        </is>
+      </c>
+      <c r="AU290" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV290" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX290" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY290" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD312"/>
+  <dimension ref="A1:BD324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59310,15 +59310,11 @@
         </is>
       </c>
       <c r="F304" t="inlineStr"/>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G304" t="n">
+        <v>1</v>
+      </c>
+      <c r="H304" t="n">
+        <v>0</v>
       </c>
       <c r="I304" t="inlineStr">
         <is>
@@ -59340,15 +59336,11 @@
           <t>Getafe</t>
         </is>
       </c>
-      <c r="M304" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="N304" t="inlineStr">
-        <is>
-          <t>0.79</t>
-        </is>
+      <c r="M304" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="N304" t="n">
+        <v>0.79</v>
       </c>
       <c r="O304" t="inlineStr">
         <is>
@@ -59360,135 +59352,83 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="Q304" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R304" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S304" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T304" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U304" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V304" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W304" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X304" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y304" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z304" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AA304" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB304" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC304" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD304" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE304" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF304" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG304" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH304" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI304" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ304" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK304" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL304" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM304" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="AN304" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="AO304" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="AP304" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="Q304" t="n">
+        <v>10</v>
+      </c>
+      <c r="R304" t="n">
+        <v>16</v>
+      </c>
+      <c r="S304" t="n">
+        <v>4</v>
+      </c>
+      <c r="T304" t="n">
+        <v>5</v>
+      </c>
+      <c r="U304" t="n">
+        <v>4</v>
+      </c>
+      <c r="V304" t="n">
+        <v>5</v>
+      </c>
+      <c r="W304" t="n">
+        <v>2</v>
+      </c>
+      <c r="X304" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y304" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z304" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA304" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB304" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC304" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD304" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE304" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF304" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG304" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH304" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI304" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ304" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK304" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL304" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM304" t="n">
+        <v>124</v>
+      </c>
+      <c r="AN304" t="n">
+        <v>93</v>
+      </c>
+      <c r="AO304" t="n">
+        <v>57</v>
+      </c>
+      <c r="AP304" t="n">
+        <v>36</v>
       </c>
       <c r="AQ304" t="inlineStr">
         <is>
@@ -59524,15 +59464,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY304" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AZ304" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AY304" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ304" t="n">
+        <v>0</v>
       </c>
       <c r="BA304" t="inlineStr"/>
       <c r="BB304" t="inlineStr"/>
@@ -59572,15 +59508,11 @@
           <t>24 238</t>
         </is>
       </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G305" t="n">
+        <v>3</v>
+      </c>
+      <c r="H305" t="n">
+        <v>2</v>
       </c>
       <c r="I305" t="inlineStr">
         <is>
@@ -59602,15 +59534,11 @@
           <t>Alaves</t>
         </is>
       </c>
-      <c r="M305" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="N305" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
+      <c r="M305" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="N305" t="n">
+        <v>1.84</v>
       </c>
       <c r="O305" t="inlineStr">
         <is>
@@ -59622,135 +59550,83 @@
           <t>62%</t>
         </is>
       </c>
-      <c r="Q305" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R305" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="S305" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T305" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U305" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V305" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W305" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X305" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y305" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z305" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA305" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB305" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC305" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD305" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE305" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AF305" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AG305" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH305" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI305" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AJ305" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK305" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL305" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM305" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="AN305" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="AO305" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AP305" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="Q305" t="n">
+        <v>9</v>
+      </c>
+      <c r="R305" t="n">
+        <v>19</v>
+      </c>
+      <c r="S305" t="n">
+        <v>4</v>
+      </c>
+      <c r="T305" t="n">
+        <v>6</v>
+      </c>
+      <c r="U305" t="n">
+        <v>4</v>
+      </c>
+      <c r="V305" t="n">
+        <v>7</v>
+      </c>
+      <c r="W305" t="n">
+        <v>1</v>
+      </c>
+      <c r="X305" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y305" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z305" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB305" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC305" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE305" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF305" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG305" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH305" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI305" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ305" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK305" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL305" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM305" t="n">
+        <v>71</v>
+      </c>
+      <c r="AN305" t="n">
+        <v>108</v>
+      </c>
+      <c r="AO305" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP305" t="n">
+        <v>72</v>
       </c>
       <c r="AQ305" t="inlineStr">
         <is>
@@ -59826,15 +59702,11 @@
           <t>18 303</t>
         </is>
       </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G306" t="n">
+        <v>1</v>
+      </c>
+      <c r="H306" t="n">
+        <v>2</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -59856,15 +59728,11 @@
           <t>Villarreal</t>
         </is>
       </c>
-      <c r="M306" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="N306" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
+      <c r="M306" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="N306" t="n">
+        <v>1.45</v>
       </c>
       <c r="O306" t="inlineStr">
         <is>
@@ -59876,135 +59744,83 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q306" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R306" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="S306" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T306" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U306" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V306" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="W306" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X306" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y306" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z306" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA306" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB306" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC306" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD306" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE306" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF306" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AG306" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH306" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI306" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ306" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK306" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL306" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM306" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AN306" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="AO306" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="AP306" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="Q306" t="n">
+        <v>10</v>
+      </c>
+      <c r="R306" t="n">
+        <v>21</v>
+      </c>
+      <c r="S306" t="n">
+        <v>5</v>
+      </c>
+      <c r="T306" t="n">
+        <v>4</v>
+      </c>
+      <c r="U306" t="n">
+        <v>3</v>
+      </c>
+      <c r="V306" t="n">
+        <v>10</v>
+      </c>
+      <c r="W306" t="n">
+        <v>2</v>
+      </c>
+      <c r="X306" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y306" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z306" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA306" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB306" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC306" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD306" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE306" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF306" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG306" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH306" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI306" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ306" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK306" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL306" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM306" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN306" t="n">
+        <v>89</v>
+      </c>
+      <c r="AO306" t="n">
+        <v>54</v>
+      </c>
+      <c r="AP306" t="n">
+        <v>60</v>
       </c>
       <c r="AQ306" t="inlineStr">
         <is>
@@ -60040,15 +59856,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY306" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AZ306" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AY306" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ306" t="n">
+        <v>0</v>
       </c>
       <c r="BA306" t="inlineStr"/>
       <c r="BB306" t="inlineStr"/>
@@ -60088,15 +59900,11 @@
           <t>48 089</t>
         </is>
       </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G307" t="n">
+        <v>2</v>
+      </c>
+      <c r="H307" t="n">
+        <v>0</v>
       </c>
       <c r="I307" t="inlineStr">
         <is>
@@ -60118,15 +59926,11 @@
           <t>Leganes</t>
         </is>
       </c>
-      <c r="M307" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="N307" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
+      <c r="M307" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="N307" t="n">
+        <v>0.07000000000000001</v>
       </c>
       <c r="O307" t="inlineStr">
         <is>
@@ -60138,135 +59942,83 @@
           <t>36%</t>
         </is>
       </c>
-      <c r="Q307" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R307" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S307" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T307" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U307" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V307" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W307" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X307" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y307" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Z307" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA307" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AB307" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC307" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD307" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE307" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF307" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AG307" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH307" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI307" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ307" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK307" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL307" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM307" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="AN307" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="AO307" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="AP307" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="Q307" t="n">
+        <v>14</v>
+      </c>
+      <c r="R307" t="n">
+        <v>3</v>
+      </c>
+      <c r="S307" t="n">
+        <v>5</v>
+      </c>
+      <c r="T307" t="n">
+        <v>0</v>
+      </c>
+      <c r="U307" t="n">
+        <v>7</v>
+      </c>
+      <c r="V307" t="n">
+        <v>2</v>
+      </c>
+      <c r="W307" t="n">
+        <v>2</v>
+      </c>
+      <c r="X307" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y307" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z307" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA307" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB307" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC307" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD307" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE307" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF307" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG307" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH307" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI307" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ307" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK307" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL307" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM307" t="n">
+        <v>154</v>
+      </c>
+      <c r="AN307" t="n">
+        <v>83</v>
+      </c>
+      <c r="AO307" t="n">
+        <v>67</v>
+      </c>
+      <c r="AP307" t="n">
+        <v>19</v>
       </c>
       <c r="AQ307" t="inlineStr">
         <is>
@@ -60342,15 +60094,11 @@
           <t>26 672</t>
         </is>
       </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G308" t="n">
+        <v>1</v>
+      </c>
+      <c r="H308" t="n">
+        <v>0</v>
       </c>
       <c r="I308" t="inlineStr">
         <is>
@@ -60384,135 +60132,83 @@
           <t>43%</t>
         </is>
       </c>
-      <c r="Q308" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R308" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S308" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T308" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U308" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V308" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W308" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X308" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y308" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z308" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AA308" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB308" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC308" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD308" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE308" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AF308" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AG308" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH308" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI308" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ308" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK308" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL308" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM308" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="AN308" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="AO308" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="AP308" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="Q308" t="n">
+        <v>13</v>
+      </c>
+      <c r="R308" t="n">
+        <v>7</v>
+      </c>
+      <c r="S308" t="n">
+        <v>3</v>
+      </c>
+      <c r="T308" t="n">
+        <v>2</v>
+      </c>
+      <c r="U308" t="n">
+        <v>7</v>
+      </c>
+      <c r="V308" t="n">
+        <v>4</v>
+      </c>
+      <c r="W308" t="n">
+        <v>3</v>
+      </c>
+      <c r="X308" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y308" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z308" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA308" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB308" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC308" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD308" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE308" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF308" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG308" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH308" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI308" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ308" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK308" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL308" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM308" t="n">
+        <v>108</v>
+      </c>
+      <c r="AN308" t="n">
+        <v>99</v>
+      </c>
+      <c r="AO308" t="n">
+        <v>58</v>
+      </c>
+      <c r="AP308" t="n">
+        <v>42</v>
       </c>
       <c r="AQ308" t="inlineStr">
         <is>
@@ -60588,15 +60284,11 @@
           <t>20 846</t>
         </is>
       </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G309" t="n">
+        <v>1</v>
+      </c>
+      <c r="H309" t="n">
+        <v>0</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
@@ -60630,135 +60322,83 @@
           <t>58%</t>
         </is>
       </c>
-      <c r="Q309" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R309" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S309" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T309" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U309" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V309" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W309" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X309" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y309" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z309" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA309" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB309" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC309" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD309" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE309" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF309" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="AG309" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH309" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI309" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AJ309" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AK309" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL309" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM309" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="AN309" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="AO309" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="AP309" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
+      <c r="Q309" t="n">
+        <v>13</v>
+      </c>
+      <c r="R309" t="n">
+        <v>8</v>
+      </c>
+      <c r="S309" t="n">
+        <v>3</v>
+      </c>
+      <c r="T309" t="n">
+        <v>2</v>
+      </c>
+      <c r="U309" t="n">
+        <v>3</v>
+      </c>
+      <c r="V309" t="n">
+        <v>4</v>
+      </c>
+      <c r="W309" t="n">
+        <v>7</v>
+      </c>
+      <c r="X309" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y309" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z309" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA309" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB309" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC309" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD309" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE309" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF309" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG309" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH309" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI309" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ309" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK309" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL309" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM309" t="n">
+        <v>106</v>
+      </c>
+      <c r="AN309" t="n">
+        <v>123</v>
+      </c>
+      <c r="AO309" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP309" t="n">
+        <v>47</v>
       </c>
       <c r="AQ309" t="inlineStr">
         <is>
@@ -60834,15 +60474,11 @@
           <t>5 030</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G310" t="n">
+        <v>1</v>
+      </c>
+      <c r="H310" t="n">
+        <v>0</v>
       </c>
       <c r="I310" t="inlineStr">
         <is>
@@ -60876,135 +60512,83 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="Q310" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R310" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S310" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T310" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U310" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V310" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W310" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X310" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y310" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z310" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA310" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB310" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC310" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD310" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE310" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AF310" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG310" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH310" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI310" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ310" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK310" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL310" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM310" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="AN310" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AO310" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AP310" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="Q310" t="n">
+        <v>5</v>
+      </c>
+      <c r="R310" t="n">
+        <v>7</v>
+      </c>
+      <c r="S310" t="n">
+        <v>3</v>
+      </c>
+      <c r="T310" t="n">
+        <v>0</v>
+      </c>
+      <c r="U310" t="n">
+        <v>2</v>
+      </c>
+      <c r="V310" t="n">
+        <v>5</v>
+      </c>
+      <c r="W310" t="n">
+        <v>0</v>
+      </c>
+      <c r="X310" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y310" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z310" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA310" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB310" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD310" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH310" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI310" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ310" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK310" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL310" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM310" t="n">
+        <v>122</v>
+      </c>
+      <c r="AN310" t="n">
+        <v>111</v>
+      </c>
+      <c r="AO310" t="n">
+        <v>31</v>
+      </c>
+      <c r="AP310" t="n">
+        <v>60</v>
       </c>
       <c r="AQ310" t="inlineStr">
         <is>
@@ -61080,15 +60664,11 @@
           <t>14 904</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G311" t="n">
+        <v>3</v>
+      </c>
+      <c r="H311" t="n">
+        <v>1</v>
       </c>
       <c r="I311" t="inlineStr">
         <is>
@@ -61122,135 +60702,83 @@
           <t>32%</t>
         </is>
       </c>
-      <c r="Q311" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R311" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S311" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T311" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U311" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="V311" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W311" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X311" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y311" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z311" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA311" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AB311" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC311" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD311" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE311" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AF311" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AG311" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH311" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI311" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ311" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AK311" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL311" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AM311" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="AN311" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="AO311" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="AP311" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="Q311" t="n">
+        <v>26</v>
+      </c>
+      <c r="R311" t="n">
+        <v>5</v>
+      </c>
+      <c r="S311" t="n">
+        <v>6</v>
+      </c>
+      <c r="T311" t="n">
+        <v>3</v>
+      </c>
+      <c r="U311" t="n">
+        <v>14</v>
+      </c>
+      <c r="V311" t="n">
+        <v>1</v>
+      </c>
+      <c r="W311" t="n">
+        <v>6</v>
+      </c>
+      <c r="X311" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y311" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z311" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA311" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB311" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD311" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE311" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF311" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG311" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH311" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI311" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ311" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK311" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL311" t="n">
+        <v>7</v>
+      </c>
+      <c r="AM311" t="n">
+        <v>148</v>
+      </c>
+      <c r="AN311" t="n">
+        <v>54</v>
+      </c>
+      <c r="AO311" t="n">
+        <v>102</v>
+      </c>
+      <c r="AP311" t="n">
+        <v>20</v>
       </c>
       <c r="AQ311" t="inlineStr">
         <is>
@@ -61286,15 +60814,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY311" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ311" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AY311" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ311" t="n">
+        <v>2</v>
       </c>
       <c r="BA311" t="inlineStr"/>
       <c r="BB311" t="inlineStr"/>
@@ -61334,15 +60858,11 @@
           <t>16 435</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H312" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G312" t="n">
+        <v>2</v>
+      </c>
+      <c r="H312" t="n">
+        <v>0</v>
       </c>
       <c r="I312" t="inlineStr">
         <is>
@@ -61376,127 +60896,79 @@
           <t>56%</t>
         </is>
       </c>
-      <c r="Q312" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R312" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S312" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T312" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U312" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V312" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W312" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X312" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y312" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z312" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AA312" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB312" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC312" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD312" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE312" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AF312" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG312" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH312" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI312" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AJ312" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q312" t="n">
+        <v>16</v>
+      </c>
+      <c r="R312" t="n">
+        <v>15</v>
+      </c>
+      <c r="S312" t="n">
+        <v>6</v>
+      </c>
+      <c r="T312" t="n">
+        <v>5</v>
+      </c>
+      <c r="U312" t="n">
+        <v>7</v>
+      </c>
+      <c r="V312" t="n">
+        <v>6</v>
+      </c>
+      <c r="W312" t="n">
+        <v>3</v>
+      </c>
+      <c r="X312" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y312" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z312" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA312" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB312" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC312" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD312" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE312" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF312" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG312" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH312" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI312" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ312" t="n">
+        <v>5</v>
       </c>
       <c r="AK312" t="inlineStr"/>
       <c r="AL312" t="inlineStr"/>
-      <c r="AM312" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AN312" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="AO312" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="AP312" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="AM312" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN312" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO312" t="n">
+        <v>57</v>
+      </c>
+      <c r="AP312" t="n">
+        <v>32</v>
       </c>
       <c r="AQ312" t="inlineStr">
         <is>
@@ -61539,6 +61011,3030 @@
       <c r="BC312" t="inlineStr"/>
       <c r="BD312" t="inlineStr"/>
     </row>
+    <row r="313">
+      <c r="A313" s="1" t="inlineStr">
+        <is>
+          <t>fVeJ32M5</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>16.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Quintero A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Campo de Futbol de Vallecas
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>14 505</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>13 073</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R313" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W313" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X313" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y313" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z313" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB313" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC313" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD313" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE313" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF313" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AG313" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH313" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI313" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ313" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK313" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL313" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM313" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AN313" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AO313" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AP313" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AQ313" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="AR313" t="inlineStr">
+        <is>
+          <t>perez inigo</t>
+        </is>
+      </c>
+      <c r="AS313" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="AT313" t="inlineStr">
+        <is>
+          <t>moreno vicente</t>
+        </is>
+      </c>
+      <c r="AU313" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV313" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX313" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY313" t="inlineStr"/>
+      <c r="AZ313" t="inlineStr"/>
+      <c r="BA313" t="inlineStr"/>
+      <c r="BB313" t="inlineStr"/>
+      <c r="BC313" t="inlineStr"/>
+      <c r="BD313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="1" t="inlineStr">
+        <is>
+          <t>SdHeBgOE</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>15.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Grado C. S.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Metropolitano Stadium
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>70 460</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>61 752</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R314" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V314" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W314" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X314" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y314" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z314" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB314" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC314" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD314" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE314" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF314" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG314" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH314" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI314" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ314" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK314" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL314" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM314" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AN314" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="AO314" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AP314" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="AQ314" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="AR314" t="inlineStr">
+        <is>
+          <t>simeone diego</t>
+        </is>
+      </c>
+      <c r="AS314" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="AT314" t="inlineStr">
+        <is>
+          <t>baraja ruben</t>
+        </is>
+      </c>
+      <c r="AU314" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV314" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX314" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY314" t="inlineStr"/>
+      <c r="AZ314" t="inlineStr"/>
+      <c r="BA314" t="inlineStr"/>
+      <c r="BB314" t="inlineStr"/>
+      <c r="BC314" t="inlineStr"/>
+      <c r="BD314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="1" t="inlineStr">
+        <is>
+          <t>dzUhmsxP</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>15.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Ortiz M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Estadio de Gran Canaria
+ (Las Palmas)</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>32 392</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>25 908</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R315" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W315" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X315" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z315" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB315" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC315" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE315" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF315" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AG315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH315" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI315" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ315" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL315" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM315" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="AN315" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AO315" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="AP315" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AQ315" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="AR315" t="inlineStr">
+        <is>
+          <t>carrion luis</t>
+        </is>
+      </c>
+      <c r="AS315" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="AT315" t="inlineStr">
+        <is>
+          <t>valverde tejedor ernesto</t>
+        </is>
+      </c>
+      <c r="AU315" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV315" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW315" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX315" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY315" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BA315" t="inlineStr"/>
+      <c r="BB315" t="inlineStr"/>
+      <c r="BC315" t="inlineStr"/>
+      <c r="BD315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>na927pNt</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>15.09.2024 11:15</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Ruiz A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Montilivi
+ (Girona)</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>14 624</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>13 891</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R316" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W316" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X316" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z316" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB316" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC316" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AD316" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE316" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF316" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG316" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH316" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI316" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ316" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AK316" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL316" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM316" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="AN316" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="AO316" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AP316" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AQ316" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="AR316" t="inlineStr">
+        <is>
+          <t>michel</t>
+        </is>
+      </c>
+      <c r="AS316" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="AT316" t="inlineStr">
+        <is>
+          <t>flick hans dieter</t>
+        </is>
+      </c>
+      <c r="AU316" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV316" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX316" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY316" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BA316" t="inlineStr"/>
+      <c r="BB316" t="inlineStr"/>
+      <c r="BC316" t="inlineStr"/>
+      <c r="BD316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>SfxxiPx0</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>15.09.2024 09:00</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Maeso F.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Estadio de Balaídos
+ (Vigo)</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>24 791</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>21 670</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB317" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC317" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD317" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE317" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AF317" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG317" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH317" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI317" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ317" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK317" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL317" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM317" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AN317" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AO317" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AP317" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AQ317" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="AR317" t="inlineStr">
+        <is>
+          <t>giraldez claudio</t>
+        </is>
+      </c>
+      <c r="AS317" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="AT317" t="inlineStr">
+        <is>
+          <t>pezzolano paulo</t>
+        </is>
+      </c>
+      <c r="AU317" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV317" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW317" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX317" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY317" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BA317" t="inlineStr"/>
+      <c r="BB317" t="inlineStr"/>
+      <c r="BC317" t="inlineStr"/>
+      <c r="BD317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>jckS1tiI</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>14.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Munuera J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Reale Arena
+ (San Sebastian)</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>40 000</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>37 370</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R318" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W318" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB318" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC318" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD318" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE318" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF318" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG318" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH318" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI318" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ318" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK318" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL318" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM318" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="AN318" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AO318" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AP318" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AQ318" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="AR318" t="inlineStr">
+        <is>
+          <t>alguacil imanol</t>
+        </is>
+      </c>
+      <c r="AS318" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="AT318" t="inlineStr">
+        <is>
+          <t>ancelotti carlo</t>
+        </is>
+      </c>
+      <c r="AU318" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV318" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW318" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX318" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY318" t="inlineStr"/>
+      <c r="AZ318" t="inlineStr"/>
+      <c r="BA318" t="inlineStr"/>
+      <c r="BB318" t="inlineStr"/>
+      <c r="BC318" t="inlineStr"/>
+      <c r="BD318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>dMUW3ea6</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>16.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Gonzalez Diaz M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Power Horse Stadium
+ (Almería)</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>17 400</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>11 952</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>Almeria</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>Castellon</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr"/>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W319" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB319" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC319" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD319" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE319" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF319" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG319" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH319" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI319" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ319" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK319" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL319" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM319" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="AN319" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AO319" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AP319" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AQ319" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="AR319" t="inlineStr">
+        <is>
+          <t>rubi joan</t>
+        </is>
+      </c>
+      <c r="AS319" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="AT319" t="inlineStr">
+        <is>
+          <t>schreuder dick</t>
+        </is>
+      </c>
+      <c r="AU319" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV319" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW319" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX319" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY319" t="inlineStr"/>
+      <c r="AZ319" t="inlineStr"/>
+      <c r="BA319" t="inlineStr"/>
+      <c r="BB319" t="inlineStr"/>
+      <c r="BC319" t="inlineStr"/>
+      <c r="BD319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>nBqFGYrC</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>15.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>De La Fuente Ramos O.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Estadio Manuel Martínez Valero
+ (Elche)</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>31 388</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>15 455</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Granada CF</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr"/>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB320" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC320" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD320" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE320" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AF320" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AG320" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH320" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI320" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AJ320" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK320" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL320" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM320" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="AN320" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="AO320" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AP320" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AQ320" t="inlineStr">
+        <is>
+          <t>zT9gi7i9</t>
+        </is>
+      </c>
+      <c r="AR320" t="inlineStr">
+        <is>
+          <t>sarabia eder</t>
+        </is>
+      </c>
+      <c r="AS320" t="inlineStr">
+        <is>
+          <t>K4dMCgFa</t>
+        </is>
+      </c>
+      <c r="AT320" t="inlineStr">
+        <is>
+          <t>abascal guillermo</t>
+        </is>
+      </c>
+      <c r="AU320" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV320" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW320" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX320" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY320" t="inlineStr"/>
+      <c r="AZ320" t="inlineStr"/>
+      <c r="BA320" t="inlineStr"/>
+      <c r="BB320" t="inlineStr"/>
+      <c r="BC320" t="inlineStr"/>
+      <c r="BD320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>hlOu2ZTI</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>15.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Guzman Mansilla J. L.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Estadio El Plantío
+ (Burgos)</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>12 194</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>10 150</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>Burgos CF</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr"/>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC321" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD321" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE321" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AF321" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AG321" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH321" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI321" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ321" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK321" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL321" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM321" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AN321" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="AO321" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="AP321" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AQ321" t="inlineStr">
+        <is>
+          <t>l6JQtDqc</t>
+        </is>
+      </c>
+      <c r="AR321" t="inlineStr">
+        <is>
+          <t>bolo</t>
+        </is>
+      </c>
+      <c r="AS321" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="AT321" t="inlineStr">
+        <is>
+          <t>fernandez braulio victor</t>
+        </is>
+      </c>
+      <c r="AU321" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV321" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW321" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX321" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY321" t="inlineStr"/>
+      <c r="AZ321" t="inlineStr"/>
+      <c r="BA321" t="inlineStr"/>
+      <c r="BB321" t="inlineStr"/>
+      <c r="BC321" t="inlineStr"/>
+      <c r="BD321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>KfGRPxMP</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>15.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Gonzalez Esteban J. A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Mirandilla
+ (Cadiz)</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>20 776</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>16 868</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>Cadiz CF</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>Racing Club Ferrol</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W322" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X322" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y322" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB322" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC322" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD322" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE322" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF322" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG322" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH322" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI322" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AJ322" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK322" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL322" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM322" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AN322" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="AO322" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AP322" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AQ322" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="AR322" t="inlineStr">
+        <is>
+          <t>lopez paco</t>
+        </is>
+      </c>
+      <c r="AS322" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="AT322" t="inlineStr">
+        <is>
+          <t>parralo cristobal</t>
+        </is>
+      </c>
+      <c r="AU322" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV322" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW322" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX322" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY322" t="inlineStr"/>
+      <c r="AZ322" t="inlineStr"/>
+      <c r="BA322" t="inlineStr"/>
+      <c r="BB322" t="inlineStr"/>
+      <c r="BC322" t="inlineStr"/>
+      <c r="BD322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>4nGuXgTh</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>15.09.2024 11:15</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Barrera R.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Carlos Tartiere
+ (Oviedo)</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>30 500</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>19 492</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>R. Oviedo</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>FC Cartagena SAD</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr"/>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W323" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X323" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z323" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB323" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD323" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE323" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AF323" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG323" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH323" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI323" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ323" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK323" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL323" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM323" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="AN323" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="AO323" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AP323" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AQ323" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="AR323" t="inlineStr">
+        <is>
+          <t>calleja javier</t>
+        </is>
+      </c>
+      <c r="AS323" t="inlineStr">
+        <is>
+          <t>M1vEw5An</t>
+        </is>
+      </c>
+      <c r="AT323" t="inlineStr">
+        <is>
+          <t>abelardo</t>
+        </is>
+      </c>
+      <c r="AU323" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV323" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW323" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX323" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY323" t="inlineStr"/>
+      <c r="AZ323" t="inlineStr"/>
+      <c r="BA323" t="inlineStr"/>
+      <c r="BB323" t="inlineStr"/>
+      <c r="BC323" t="inlineStr"/>
+      <c r="BD323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>bkDXYFbt</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>15.09.2024 09:00</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Lax Franco S.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Anduva
+ (Miranda de Ebro)</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>5 759</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>2 713</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr"/>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W324" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y324" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z324" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB324" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC324" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD324" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE324" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AF324" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG324" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH324" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI324" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ324" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK324" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL324" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM324" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="AN324" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="AO324" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AP324" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AQ324" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="AR324" t="inlineStr">
+        <is>
+          <t>lisci alessio</t>
+        </is>
+      </c>
+      <c r="AS324" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="AT324" t="inlineStr">
+        <is>
+          <t>gonzalez alberto</t>
+        </is>
+      </c>
+      <c r="AU324" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV324" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW324" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX324" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY324" t="inlineStr"/>
+      <c r="AZ324" t="inlineStr"/>
+      <c r="BA324" t="inlineStr"/>
+      <c r="BB324" t="inlineStr"/>
+      <c r="BC324" t="inlineStr"/>
+      <c r="BD324" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD346"/>
+  <dimension ref="A1:BD348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61044,15 +61044,11 @@
           <t>13 646</t>
         </is>
       </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G313" t="n">
+        <v>1</v>
+      </c>
+      <c r="H313" t="n">
+        <v>1</v>
       </c>
       <c r="I313" t="inlineStr">
         <is>
@@ -61074,15 +61070,11 @@
           <t>Atl. Madrid</t>
         </is>
       </c>
-      <c r="M313" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
-      <c r="N313" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
+      <c r="M313" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="N313" t="n">
+        <v>0.67</v>
       </c>
       <c r="O313" t="inlineStr">
         <is>
@@ -61094,105 +61086,65 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q313" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R313" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S313" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T313" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U313" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V313" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W313" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X313" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y313" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z313" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA313" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB313" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC313" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD313" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE313" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AF313" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AG313" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH313" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI313" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AJ313" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="Q313" t="n">
+        <v>16</v>
+      </c>
+      <c r="R313" t="n">
+        <v>10</v>
+      </c>
+      <c r="S313" t="n">
+        <v>3</v>
+      </c>
+      <c r="T313" t="n">
+        <v>5</v>
+      </c>
+      <c r="U313" t="n">
+        <v>8</v>
+      </c>
+      <c r="V313" t="n">
+        <v>3</v>
+      </c>
+      <c r="W313" t="n">
+        <v>5</v>
+      </c>
+      <c r="X313" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y313" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z313" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA313" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB313" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD313" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE313" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF313" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG313" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH313" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI313" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ313" t="n">
+        <v>12</v>
       </c>
       <c r="AK313" t="inlineStr"/>
       <c r="AL313" t="inlineStr"/>
@@ -61274,15 +61226,11 @@
           <t>22 048</t>
         </is>
       </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H314" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="G314" t="n">
+        <v>1</v>
+      </c>
+      <c r="H314" t="n">
+        <v>5</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>
@@ -61304,15 +61252,11 @@
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="M314" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
-      </c>
-      <c r="N314" t="inlineStr">
-        <is>
-          <t>3.63</t>
-        </is>
+      <c r="M314" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="N314" t="n">
+        <v>3.63</v>
       </c>
       <c r="O314" t="inlineStr">
         <is>
@@ -61324,115 +61268,71 @@
           <t>64%</t>
         </is>
       </c>
-      <c r="Q314" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R314" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S314" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T314" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="U314" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V314" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W314" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X314" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y314" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z314" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AA314" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB314" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC314" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AD314" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE314" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF314" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AG314" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH314" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI314" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ314" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK314" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AL314" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q314" t="n">
+        <v>13</v>
+      </c>
+      <c r="R314" t="n">
+        <v>17</v>
+      </c>
+      <c r="S314" t="n">
+        <v>4</v>
+      </c>
+      <c r="T314" t="n">
+        <v>10</v>
+      </c>
+      <c r="U314" t="n">
+        <v>7</v>
+      </c>
+      <c r="V314" t="n">
+        <v>4</v>
+      </c>
+      <c r="W314" t="n">
+        <v>2</v>
+      </c>
+      <c r="X314" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y314" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z314" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA314" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB314" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC314" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD314" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE314" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF314" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG314" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH314" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI314" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ314" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK314" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL314" t="n">
+        <v>1</v>
       </c>
       <c r="AM314" t="inlineStr"/>
       <c r="AN314" t="inlineStr"/>
@@ -61512,15 +61412,11 @@
           <t>48 737</t>
         </is>
       </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G315" t="n">
+        <v>3</v>
+      </c>
+      <c r="H315" t="n">
+        <v>1</v>
       </c>
       <c r="I315" t="inlineStr">
         <is>
@@ -61542,15 +61438,11 @@
           <t>Celta Vigo</t>
         </is>
       </c>
-      <c r="M315" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="N315" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
+      <c r="M315" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N315" t="n">
+        <v>1.09</v>
       </c>
       <c r="O315" t="inlineStr">
         <is>
@@ -61562,115 +61454,71 @@
           <t>68%</t>
         </is>
       </c>
-      <c r="Q315" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R315" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S315" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T315" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U315" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V315" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W315" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X315" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y315" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z315" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA315" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB315" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC315" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD315" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE315" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF315" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG315" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH315" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI315" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ315" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK315" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL315" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q315" t="n">
+        <v>10</v>
+      </c>
+      <c r="R315" t="n">
+        <v>11</v>
+      </c>
+      <c r="S315" t="n">
+        <v>7</v>
+      </c>
+      <c r="T315" t="n">
+        <v>4</v>
+      </c>
+      <c r="U315" t="n">
+        <v>2</v>
+      </c>
+      <c r="V315" t="n">
+        <v>5</v>
+      </c>
+      <c r="W315" t="n">
+        <v>1</v>
+      </c>
+      <c r="X315" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y315" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z315" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA315" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB315" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC315" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD315" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE315" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF315" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG315" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH315" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI315" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ315" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK315" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL315" t="n">
+        <v>2</v>
       </c>
       <c r="AM315" t="inlineStr"/>
       <c r="AN315" t="inlineStr"/>
@@ -61750,15 +61598,11 @@
           <t>13 060</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G316" t="n">
+        <v>1</v>
+      </c>
+      <c r="H316" t="n">
+        <v>1</v>
       </c>
       <c r="I316" t="inlineStr">
         <is>
@@ -61780,15 +61624,11 @@
           <t>Leganes</t>
         </is>
       </c>
-      <c r="M316" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="N316" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
+      <c r="M316" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="N316" t="n">
+        <v>0.83</v>
       </c>
       <c r="O316" t="inlineStr">
         <is>
@@ -61800,115 +61640,71 @@
           <t>41%</t>
         </is>
       </c>
-      <c r="Q316" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R316" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S316" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T316" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U316" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V316" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W316" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X316" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y316" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z316" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA316" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB316" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC316" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD316" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE316" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="AF316" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AG316" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH316" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI316" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ316" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AK316" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL316" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q316" t="n">
+        <v>12</v>
+      </c>
+      <c r="R316" t="n">
+        <v>6</v>
+      </c>
+      <c r="S316" t="n">
+        <v>3</v>
+      </c>
+      <c r="T316" t="n">
+        <v>3</v>
+      </c>
+      <c r="U316" t="n">
+        <v>4</v>
+      </c>
+      <c r="V316" t="n">
+        <v>1</v>
+      </c>
+      <c r="W316" t="n">
+        <v>5</v>
+      </c>
+      <c r="X316" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y316" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z316" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA316" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB316" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC316" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD316" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE316" t="n">
+        <v>39</v>
+      </c>
+      <c r="AF316" t="n">
+        <v>33</v>
+      </c>
+      <c r="AG316" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH316" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI316" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ316" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK316" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL316" t="n">
+        <v>2</v>
       </c>
       <c r="AM316" t="inlineStr"/>
       <c r="AN316" t="inlineStr"/>
@@ -61988,15 +61784,11 @@
           <t>72 284</t>
         </is>
       </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H317" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G317" t="n">
+        <v>4</v>
+      </c>
+      <c r="H317" t="n">
+        <v>1</v>
       </c>
       <c r="I317" t="inlineStr">
         <is>
@@ -62018,15 +61810,11 @@
           <t>Espanyol</t>
         </is>
       </c>
-      <c r="M317" t="inlineStr">
-        <is>
-          <t>5.47</t>
-        </is>
-      </c>
-      <c r="N317" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
+      <c r="M317" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="N317" t="n">
+        <v>0.87</v>
       </c>
       <c r="O317" t="inlineStr">
         <is>
@@ -62038,115 +61826,71 @@
           <t>27%</t>
         </is>
       </c>
-      <c r="Q317" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="R317" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S317" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="T317" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U317" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V317" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W317" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X317" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y317" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z317" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA317" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB317" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC317" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD317" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE317" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF317" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AG317" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH317" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI317" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AJ317" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AK317" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL317" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q317" t="n">
+        <v>31</v>
+      </c>
+      <c r="R317" t="n">
+        <v>10</v>
+      </c>
+      <c r="S317" t="n">
+        <v>14</v>
+      </c>
+      <c r="T317" t="n">
+        <v>2</v>
+      </c>
+      <c r="U317" t="n">
+        <v>11</v>
+      </c>
+      <c r="V317" t="n">
+        <v>6</v>
+      </c>
+      <c r="W317" t="n">
+        <v>6</v>
+      </c>
+      <c r="X317" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y317" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z317" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA317" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB317" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC317" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD317" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE317" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF317" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG317" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH317" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI317" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ317" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK317" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL317" t="n">
+        <v>3</v>
       </c>
       <c r="AM317" t="inlineStr"/>
       <c r="AN317" t="inlineStr"/>
@@ -62226,15 +61970,11 @@
           <t>40 896</t>
         </is>
       </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G318" t="n">
+        <v>2</v>
+      </c>
+      <c r="H318" t="n">
+        <v>0</v>
       </c>
       <c r="I318" t="inlineStr">
         <is>
@@ -62256,15 +61996,11 @@
           <t>Girona</t>
         </is>
       </c>
-      <c r="M318" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="N318" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="M318" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="N318" t="n">
+        <v>0.75</v>
       </c>
       <c r="O318" t="inlineStr">
         <is>
@@ -62276,115 +62012,71 @@
           <t>68%</t>
         </is>
       </c>
-      <c r="Q318" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R318" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S318" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T318" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U318" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V318" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W318" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X318" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y318" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z318" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA318" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB318" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC318" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD318" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE318" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF318" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AG318" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH318" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI318" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ318" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK318" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL318" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q318" t="n">
+        <v>7</v>
+      </c>
+      <c r="R318" t="n">
+        <v>8</v>
+      </c>
+      <c r="S318" t="n">
+        <v>2</v>
+      </c>
+      <c r="T318" t="n">
+        <v>3</v>
+      </c>
+      <c r="U318" t="n">
+        <v>3</v>
+      </c>
+      <c r="V318" t="n">
+        <v>4</v>
+      </c>
+      <c r="W318" t="n">
+        <v>2</v>
+      </c>
+      <c r="X318" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y318" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z318" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA318" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB318" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC318" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD318" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE318" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF318" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG318" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH318" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI318" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ318" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK318" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL318" t="n">
+        <v>2</v>
       </c>
       <c r="AM318" t="inlineStr"/>
       <c r="AN318" t="inlineStr"/>
@@ -62464,15 +62156,11 @@
           <t>19 043</t>
         </is>
       </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G319" t="n">
+        <v>2</v>
+      </c>
+      <c r="H319" t="n">
+        <v>1</v>
       </c>
       <c r="I319" t="inlineStr">
         <is>
@@ -62494,15 +62182,11 @@
           <t>Las Palmas</t>
         </is>
       </c>
-      <c r="M319" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="N319" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
+      <c r="M319" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="N319" t="n">
+        <v>1.05</v>
       </c>
       <c r="O319" t="inlineStr">
         <is>
@@ -62514,115 +62198,71 @@
           <t>61%</t>
         </is>
       </c>
-      <c r="Q319" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R319" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S319" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T319" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U319" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V319" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W319" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X319" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y319" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z319" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AA319" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB319" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC319" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD319" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE319" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AF319" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AG319" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH319" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI319" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ319" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK319" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL319" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q319" t="n">
+        <v>13</v>
+      </c>
+      <c r="R319" t="n">
+        <v>11</v>
+      </c>
+      <c r="S319" t="n">
+        <v>2</v>
+      </c>
+      <c r="T319" t="n">
+        <v>4</v>
+      </c>
+      <c r="U319" t="n">
+        <v>10</v>
+      </c>
+      <c r="V319" t="n">
+        <v>7</v>
+      </c>
+      <c r="W319" t="n">
+        <v>1</v>
+      </c>
+      <c r="X319" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y319" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z319" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA319" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB319" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC319" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD319" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE319" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF319" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG319" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH319" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI319" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ319" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK319" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL319" t="n">
+        <v>5</v>
       </c>
       <c r="AM319" t="inlineStr"/>
       <c r="AN319" t="inlineStr"/>
@@ -62702,15 +62342,11 @@
           <t>21 171</t>
         </is>
       </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G320" t="n">
+        <v>0</v>
+      </c>
+      <c r="H320" t="n">
+        <v>0</v>
       </c>
       <c r="I320" t="inlineStr">
         <is>
@@ -62732,15 +62368,11 @@
           <t>Real Sociedad</t>
         </is>
       </c>
-      <c r="M320" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="N320" t="inlineStr">
-        <is>
-          <t>1.41</t>
-        </is>
+      <c r="M320" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="N320" t="n">
+        <v>1.41</v>
       </c>
       <c r="O320" t="inlineStr">
         <is>
@@ -62752,115 +62384,71 @@
           <t>65%</t>
         </is>
       </c>
-      <c r="Q320" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R320" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S320" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T320" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U320" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V320" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W320" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X320" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y320" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z320" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA320" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB320" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC320" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD320" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE320" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AF320" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AG320" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH320" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI320" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ320" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK320" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL320" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q320" t="n">
+        <v>15</v>
+      </c>
+      <c r="R320" t="n">
+        <v>14</v>
+      </c>
+      <c r="S320" t="n">
+        <v>2</v>
+      </c>
+      <c r="T320" t="n">
+        <v>4</v>
+      </c>
+      <c r="U320" t="n">
+        <v>10</v>
+      </c>
+      <c r="V320" t="n">
+        <v>6</v>
+      </c>
+      <c r="W320" t="n">
+        <v>3</v>
+      </c>
+      <c r="X320" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y320" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z320" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA320" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB320" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC320" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD320" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE320" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF320" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG320" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH320" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI320" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ320" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK320" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL320" t="n">
+        <v>4</v>
       </c>
       <c r="AM320" t="inlineStr"/>
       <c r="AN320" t="inlineStr"/>
@@ -62940,15 +62528,11 @@
           <t>16 538</t>
         </is>
       </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H321" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G321" t="n">
+        <v>2</v>
+      </c>
+      <c r="H321" t="n">
+        <v>1</v>
       </c>
       <c r="I321" t="inlineStr">
         <is>
@@ -62970,15 +62554,11 @@
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="M321" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="N321" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
+      <c r="M321" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="N321" t="n">
+        <v>0.41</v>
       </c>
       <c r="O321" t="inlineStr">
         <is>
@@ -62990,115 +62570,71 @@
           <t>66%</t>
         </is>
       </c>
-      <c r="Q321" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R321" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S321" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T321" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U321" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V321" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W321" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X321" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y321" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Z321" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA321" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB321" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC321" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD321" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE321" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF321" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AG321" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH321" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI321" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ321" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK321" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL321" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q321" t="n">
+        <v>10</v>
+      </c>
+      <c r="R321" t="n">
+        <v>8</v>
+      </c>
+      <c r="S321" t="n">
+        <v>4</v>
+      </c>
+      <c r="T321" t="n">
+        <v>2</v>
+      </c>
+      <c r="U321" t="n">
+        <v>4</v>
+      </c>
+      <c r="V321" t="n">
+        <v>4</v>
+      </c>
+      <c r="W321" t="n">
+        <v>2</v>
+      </c>
+      <c r="X321" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y321" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z321" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA321" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB321" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC321" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD321" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE321" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF321" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG321" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH321" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI321" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ321" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK321" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL321" t="n">
+        <v>4</v>
       </c>
       <c r="AM321" t="inlineStr"/>
       <c r="AN321" t="inlineStr"/>
@@ -63178,15 +62714,11 @@
           <t>8 304</t>
         </is>
       </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H322" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G322" t="n">
+        <v>0</v>
+      </c>
+      <c r="H322" t="n">
+        <v>2</v>
       </c>
       <c r="I322" t="inlineStr">
         <is>
@@ -63208,15 +62740,11 @@
           <t>Ath Bilbao</t>
         </is>
       </c>
-      <c r="M322" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="N322" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
+      <c r="M322" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="N322" t="n">
+        <v>0.9</v>
       </c>
       <c r="O322" t="inlineStr">
         <is>
@@ -63228,115 +62756,71 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q322" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R322" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S322" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T322" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U322" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V322" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W322" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X322" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y322" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z322" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA322" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB322" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC322" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD322" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE322" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AF322" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AG322" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH322" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI322" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ322" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK322" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL322" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q322" t="n">
+        <v>14</v>
+      </c>
+      <c r="R322" t="n">
+        <v>10</v>
+      </c>
+      <c r="S322" t="n">
+        <v>3</v>
+      </c>
+      <c r="T322" t="n">
+        <v>4</v>
+      </c>
+      <c r="U322" t="n">
+        <v>7</v>
+      </c>
+      <c r="V322" t="n">
+        <v>2</v>
+      </c>
+      <c r="W322" t="n">
+        <v>4</v>
+      </c>
+      <c r="X322" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y322" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z322" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA322" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB322" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC322" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD322" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE322" t="n">
+        <v>33</v>
+      </c>
+      <c r="AF322" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG322" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH322" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI322" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ322" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK322" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL322" t="n">
+        <v>0</v>
       </c>
       <c r="AM322" t="inlineStr"/>
       <c r="AN322" t="inlineStr"/>
@@ -63416,15 +62900,11 @@
           <t>48 547</t>
         </is>
       </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H323" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G323" t="n">
+        <v>2</v>
+      </c>
+      <c r="H323" t="n">
+        <v>1</v>
       </c>
       <c r="I323" t="inlineStr">
         <is>
@@ -63446,15 +62926,11 @@
           <t>Getafe</t>
         </is>
       </c>
-      <c r="M323" t="inlineStr">
-        <is>
-          <t>2.71</t>
-        </is>
-      </c>
-      <c r="N323" t="inlineStr">
-        <is>
-          <t>0.99</t>
-        </is>
+      <c r="M323" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="N323" t="n">
+        <v>0.99</v>
       </c>
       <c r="O323" t="inlineStr">
         <is>
@@ -63466,135 +62942,83 @@
           <t>34%</t>
         </is>
       </c>
-      <c r="Q323" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R323" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S323" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T323" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U323" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V323" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W323" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X323" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y323" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="Z323" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA323" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB323" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC323" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD323" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE323" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF323" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AG323" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH323" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI323" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ323" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AK323" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL323" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AM323" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="AN323" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="AO323" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="AP323" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="Q323" t="n">
+        <v>18</v>
+      </c>
+      <c r="R323" t="n">
+        <v>15</v>
+      </c>
+      <c r="S323" t="n">
+        <v>8</v>
+      </c>
+      <c r="T323" t="n">
+        <v>5</v>
+      </c>
+      <c r="U323" t="n">
+        <v>5</v>
+      </c>
+      <c r="V323" t="n">
+        <v>8</v>
+      </c>
+      <c r="W323" t="n">
+        <v>5</v>
+      </c>
+      <c r="X323" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y323" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z323" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA323" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB323" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC323" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD323" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE323" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF323" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG323" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH323" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI323" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ323" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK323" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL323" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM323" t="n">
+        <v>126</v>
+      </c>
+      <c r="AN323" t="n">
+        <v>109</v>
+      </c>
+      <c r="AO323" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP323" t="n">
+        <v>60</v>
       </c>
       <c r="AQ323" t="inlineStr">
         <is>
@@ -63670,15 +63094,11 @@
           <t>17 132</t>
         </is>
       </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G324" t="n">
+        <v>1</v>
+      </c>
+      <c r="H324" t="n">
+        <v>0</v>
       </c>
       <c r="I324" t="inlineStr">
         <is>
@@ -63700,15 +63120,11 @@
           <t>Real Sociedad</t>
         </is>
       </c>
-      <c r="M324" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="N324" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
+      <c r="M324" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="N324" t="n">
+        <v>0.58</v>
       </c>
       <c r="O324" t="inlineStr">
         <is>
@@ -63720,135 +63136,83 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="Q324" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R324" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S324" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T324" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U324" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V324" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W324" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X324" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y324" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z324" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA324" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB324" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC324" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD324" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE324" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AF324" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG324" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH324" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI324" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AJ324" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK324" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL324" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM324" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AN324" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="AO324" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AP324" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+      <c r="Q324" t="n">
+        <v>10</v>
+      </c>
+      <c r="R324" t="n">
+        <v>13</v>
+      </c>
+      <c r="S324" t="n">
+        <v>4</v>
+      </c>
+      <c r="T324" t="n">
+        <v>4</v>
+      </c>
+      <c r="U324" t="n">
+        <v>6</v>
+      </c>
+      <c r="V324" t="n">
+        <v>7</v>
+      </c>
+      <c r="W324" t="n">
+        <v>0</v>
+      </c>
+      <c r="X324" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y324" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z324" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA324" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB324" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC324" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD324" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE324" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF324" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG324" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH324" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI324" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ324" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK324" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL324" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM324" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN324" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO324" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP324" t="n">
+        <v>63</v>
       </c>
       <c r="AQ324" t="inlineStr">
         <is>
@@ -63924,15 +63288,11 @@
           <t>13 073</t>
         </is>
       </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H325" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G325" t="n">
+        <v>3</v>
+      </c>
+      <c r="H325" t="n">
+        <v>1</v>
       </c>
       <c r="I325" t="inlineStr">
         <is>
@@ -63954,15 +63314,11 @@
           <t>Osasuna</t>
         </is>
       </c>
-      <c r="M325" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="N325" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
+      <c r="M325" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N325" t="n">
+        <v>0.65</v>
       </c>
       <c r="O325" t="inlineStr">
         <is>
@@ -63974,135 +63330,83 @@
           <t>34%</t>
         </is>
       </c>
-      <c r="Q325" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R325" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S325" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T325" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U325" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V325" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W325" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X325" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y325" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z325" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA325" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB325" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC325" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD325" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE325" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AF325" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AG325" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH325" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI325" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ325" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK325" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL325" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM325" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="AN325" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="AO325" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="AP325" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+      <c r="Q325" t="n">
+        <v>17</v>
+      </c>
+      <c r="R325" t="n">
+        <v>5</v>
+      </c>
+      <c r="S325" t="n">
+        <v>6</v>
+      </c>
+      <c r="T325" t="n">
+        <v>2</v>
+      </c>
+      <c r="U325" t="n">
+        <v>7</v>
+      </c>
+      <c r="V325" t="n">
+        <v>3</v>
+      </c>
+      <c r="W325" t="n">
+        <v>4</v>
+      </c>
+      <c r="X325" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y325" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z325" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA325" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB325" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC325" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD325" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE325" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF325" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG325" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH325" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI325" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ325" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK325" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL325" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM325" t="n">
+        <v>108</v>
+      </c>
+      <c r="AN325" t="n">
+        <v>105</v>
+      </c>
+      <c r="AO325" t="n">
+        <v>56</v>
+      </c>
+      <c r="AP325" t="n">
+        <v>36</v>
       </c>
       <c r="AQ325" t="inlineStr">
         <is>
@@ -64173,15 +63477,11 @@
           <t>61 752</t>
         </is>
       </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H326" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G326" t="n">
+        <v>3</v>
+      </c>
+      <c r="H326" t="n">
+        <v>0</v>
       </c>
       <c r="I326" t="inlineStr">
         <is>
@@ -64203,15 +63503,11 @@
           <t>Valencia</t>
         </is>
       </c>
-      <c r="M326" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="N326" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
+      <c r="M326" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N326" t="n">
+        <v>0.15</v>
       </c>
       <c r="O326" t="inlineStr">
         <is>
@@ -64223,135 +63519,83 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q326" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R326" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S326" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T326" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U326" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V326" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W326" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X326" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y326" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z326" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA326" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB326" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC326" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD326" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE326" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AF326" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG326" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH326" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI326" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ326" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AK326" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL326" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM326" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="AN326" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="AO326" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="AP326" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="Q326" t="n">
+        <v>14</v>
+      </c>
+      <c r="R326" t="n">
+        <v>5</v>
+      </c>
+      <c r="S326" t="n">
+        <v>5</v>
+      </c>
+      <c r="T326" t="n">
+        <v>1</v>
+      </c>
+      <c r="U326" t="n">
+        <v>7</v>
+      </c>
+      <c r="V326" t="n">
+        <v>4</v>
+      </c>
+      <c r="W326" t="n">
+        <v>2</v>
+      </c>
+      <c r="X326" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y326" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z326" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA326" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB326" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC326" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD326" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE326" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF326" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG326" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH326" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI326" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ326" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK326" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL326" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM326" t="n">
+        <v>107</v>
+      </c>
+      <c r="AN326" t="n">
+        <v>142</v>
+      </c>
+      <c r="AO326" t="n">
+        <v>58</v>
+      </c>
+      <c r="AP326" t="n">
+        <v>50</v>
       </c>
       <c r="AQ326" t="inlineStr">
         <is>
@@ -64427,15 +63671,11 @@
           <t>25 908</t>
         </is>
       </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H327" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G327" t="n">
+        <v>2</v>
+      </c>
+      <c r="H327" t="n">
+        <v>3</v>
       </c>
       <c r="I327" t="inlineStr">
         <is>
@@ -64457,15 +63697,11 @@
           <t>Ath Bilbao</t>
         </is>
       </c>
-      <c r="M327" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="N327" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
+      <c r="M327" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="N327" t="n">
+        <v>2.38</v>
       </c>
       <c r="O327" t="inlineStr">
         <is>
@@ -64477,135 +63713,83 @@
           <t>36%</t>
         </is>
       </c>
-      <c r="Q327" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R327" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S327" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T327" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U327" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V327" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W327" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X327" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y327" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z327" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA327" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB327" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC327" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD327" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE327" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF327" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AG327" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH327" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI327" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ327" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK327" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL327" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM327" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="AN327" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AO327" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="AP327" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="Q327" t="n">
+        <v>15</v>
+      </c>
+      <c r="R327" t="n">
+        <v>9</v>
+      </c>
+      <c r="S327" t="n">
+        <v>6</v>
+      </c>
+      <c r="T327" t="n">
+        <v>4</v>
+      </c>
+      <c r="U327" t="n">
+        <v>4</v>
+      </c>
+      <c r="V327" t="n">
+        <v>5</v>
+      </c>
+      <c r="W327" t="n">
+        <v>5</v>
+      </c>
+      <c r="X327" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y327" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z327" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA327" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB327" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD327" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE327" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF327" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG327" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH327" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI327" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ327" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK327" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL327" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM327" t="n">
+        <v>143</v>
+      </c>
+      <c r="AN327" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO327" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP327" t="n">
+        <v>32</v>
       </c>
       <c r="AQ327" t="inlineStr">
         <is>
@@ -64641,15 +63825,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY327" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ327" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AY327" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ327" t="n">
+        <v>1</v>
       </c>
       <c r="BA327" t="inlineStr"/>
       <c r="BB327" t="inlineStr"/>
@@ -64689,15 +63869,11 @@
           <t>13 891</t>
         </is>
       </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H328" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G328" t="n">
+        <v>1</v>
+      </c>
+      <c r="H328" t="n">
+        <v>4</v>
       </c>
       <c r="I328" t="inlineStr">
         <is>
@@ -64719,15 +63895,11 @@
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="M328" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="N328" t="inlineStr">
-        <is>
-          <t>2.16</t>
-        </is>
+      <c r="M328" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N328" t="n">
+        <v>2.16</v>
       </c>
       <c r="O328" t="inlineStr">
         <is>
@@ -64739,135 +63911,83 @@
           <t>55%</t>
         </is>
       </c>
-      <c r="Q328" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R328" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S328" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T328" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U328" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V328" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="W328" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X328" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y328" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Z328" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AA328" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB328" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC328" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AD328" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE328" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AF328" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG328" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH328" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI328" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ328" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK328" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL328" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM328" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="AN328" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AO328" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="AP328" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
+      <c r="Q328" t="n">
+        <v>9</v>
+      </c>
+      <c r="R328" t="n">
+        <v>20</v>
+      </c>
+      <c r="S328" t="n">
+        <v>4</v>
+      </c>
+      <c r="T328" t="n">
+        <v>9</v>
+      </c>
+      <c r="U328" t="n">
+        <v>4</v>
+      </c>
+      <c r="V328" t="n">
+        <v>9</v>
+      </c>
+      <c r="W328" t="n">
+        <v>1</v>
+      </c>
+      <c r="X328" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y328" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z328" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA328" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB328" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC328" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD328" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE328" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF328" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG328" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH328" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI328" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ328" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK328" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL328" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM328" t="n">
+        <v>77</v>
+      </c>
+      <c r="AN328" t="n">
+        <v>116</v>
+      </c>
+      <c r="AO328" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP328" t="n">
+        <v>59</v>
       </c>
       <c r="AQ328" t="inlineStr">
         <is>
@@ -64903,15 +64023,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY328" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ328" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AY328" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ328" t="n">
+        <v>1</v>
       </c>
       <c r="BA328" t="inlineStr"/>
       <c r="BB328" t="inlineStr"/>
@@ -64951,15 +64067,11 @@
           <t>21 670</t>
         </is>
       </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H329" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G329" t="n">
+        <v>3</v>
+      </c>
+      <c r="H329" t="n">
+        <v>1</v>
       </c>
       <c r="I329" t="inlineStr">
         <is>
@@ -64981,15 +64093,11 @@
           <t>Valladolid</t>
         </is>
       </c>
-      <c r="M329" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="N329" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
+      <c r="M329" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="N329" t="n">
+        <v>0.55</v>
       </c>
       <c r="O329" t="inlineStr">
         <is>
@@ -65001,135 +64109,83 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q329" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R329" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S329" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T329" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U329" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V329" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W329" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X329" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y329" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z329" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AA329" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB329" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC329" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD329" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE329" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AF329" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AG329" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH329" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI329" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ329" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK329" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL329" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AM329" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="AN329" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="AO329" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="AP329" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+      <c r="Q329" t="n">
+        <v>14</v>
+      </c>
+      <c r="R329" t="n">
+        <v>6</v>
+      </c>
+      <c r="S329" t="n">
+        <v>7</v>
+      </c>
+      <c r="T329" t="n">
+        <v>1</v>
+      </c>
+      <c r="U329" t="n">
+        <v>5</v>
+      </c>
+      <c r="V329" t="n">
+        <v>4</v>
+      </c>
+      <c r="W329" t="n">
+        <v>2</v>
+      </c>
+      <c r="X329" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y329" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z329" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA329" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB329" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC329" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD329" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE329" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF329" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH329" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI329" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ329" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK329" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL329" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM329" t="n">
+        <v>111</v>
+      </c>
+      <c r="AN329" t="n">
+        <v>82</v>
+      </c>
+      <c r="AO329" t="n">
+        <v>39</v>
+      </c>
+      <c r="AP329" t="n">
+        <v>39</v>
       </c>
       <c r="AQ329" t="inlineStr">
         <is>
@@ -65165,15 +64221,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY329" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ329" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AY329" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ329" t="n">
+        <v>1</v>
       </c>
       <c r="BA329" t="inlineStr"/>
       <c r="BB329" t="inlineStr"/>
@@ -65213,15 +64265,11 @@
           <t>37 370</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H330" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G330" t="n">
+        <v>0</v>
+      </c>
+      <c r="H330" t="n">
+        <v>2</v>
       </c>
       <c r="I330" t="inlineStr">
         <is>
@@ -65243,15 +64291,11 @@
           <t>Real Madrid</t>
         </is>
       </c>
-      <c r="M330" t="inlineStr">
-        <is>
-          <t>1.43</t>
-        </is>
-      </c>
-      <c r="N330" t="inlineStr">
-        <is>
-          <t>2.37</t>
-        </is>
+      <c r="M330" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N330" t="n">
+        <v>2.37</v>
       </c>
       <c r="O330" t="inlineStr">
         <is>
@@ -65263,135 +64307,83 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q330" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R330" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S330" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T330" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U330" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V330" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W330" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X330" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y330" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z330" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA330" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB330" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC330" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD330" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE330" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF330" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG330" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH330" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI330" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ330" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK330" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL330" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AM330" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="AN330" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="AO330" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="AP330" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+      <c r="Q330" t="n">
+        <v>11</v>
+      </c>
+      <c r="R330" t="n">
+        <v>16</v>
+      </c>
+      <c r="S330" t="n">
+        <v>2</v>
+      </c>
+      <c r="T330" t="n">
+        <v>7</v>
+      </c>
+      <c r="U330" t="n">
+        <v>6</v>
+      </c>
+      <c r="V330" t="n">
+        <v>2</v>
+      </c>
+      <c r="W330" t="n">
+        <v>3</v>
+      </c>
+      <c r="X330" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y330" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z330" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA330" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB330" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC330" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD330" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE330" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF330" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG330" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH330" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI330" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ330" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK330" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL330" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM330" t="n">
+        <v>113</v>
+      </c>
+      <c r="AN330" t="n">
+        <v>93</v>
+      </c>
+      <c r="AO330" t="n">
+        <v>53</v>
+      </c>
+      <c r="AP330" t="n">
+        <v>63</v>
       </c>
       <c r="AQ330" t="inlineStr">
         <is>
@@ -65467,15 +64459,11 @@
           <t>10 811</t>
         </is>
       </c>
-      <c r="G331" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G331" t="n">
+        <v>2</v>
+      </c>
+      <c r="H331" t="n">
+        <v>2</v>
       </c>
       <c r="I331" t="inlineStr">
         <is>
@@ -65509,115 +64497,71 @@
           <t>34%</t>
         </is>
       </c>
-      <c r="Q331" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R331" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S331" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T331" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U331" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V331" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W331" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X331" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y331" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Z331" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA331" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB331" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC331" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD331" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE331" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AF331" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AG331" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH331" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI331" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ331" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK331" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL331" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q331" t="n">
+        <v>13</v>
+      </c>
+      <c r="R331" t="n">
+        <v>8</v>
+      </c>
+      <c r="S331" t="n">
+        <v>5</v>
+      </c>
+      <c r="T331" t="n">
+        <v>2</v>
+      </c>
+      <c r="U331" t="n">
+        <v>5</v>
+      </c>
+      <c r="V331" t="n">
+        <v>5</v>
+      </c>
+      <c r="W331" t="n">
+        <v>3</v>
+      </c>
+      <c r="X331" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y331" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z331" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA331" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB331" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC331" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD331" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE331" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF331" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG331" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH331" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI331" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ331" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK331" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL331" t="n">
+        <v>4</v>
       </c>
       <c r="AM331" t="inlineStr"/>
       <c r="AN331" t="inlineStr"/>
@@ -65657,15 +64601,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY331" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ331" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AY331" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ331" t="n">
+        <v>1</v>
       </c>
       <c r="BA331" t="inlineStr"/>
       <c r="BB331" t="inlineStr"/>
@@ -65705,15 +64645,11 @@
           <t>16 276</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G332" t="n">
+        <v>1</v>
+      </c>
+      <c r="H332" t="n">
+        <v>0</v>
       </c>
       <c r="I332" t="inlineStr">
         <is>
@@ -65747,115 +64683,71 @@
           <t>42%</t>
         </is>
       </c>
-      <c r="Q332" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R332" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S332" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T332" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U332" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V332" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W332" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X332" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y332" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Z332" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA332" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB332" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC332" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD332" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE332" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF332" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG332" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH332" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI332" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ332" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK332" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL332" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q332" t="n">
+        <v>19</v>
+      </c>
+      <c r="R332" t="n">
+        <v>5</v>
+      </c>
+      <c r="S332" t="n">
+        <v>9</v>
+      </c>
+      <c r="T332" t="n">
+        <v>3</v>
+      </c>
+      <c r="U332" t="n">
+        <v>9</v>
+      </c>
+      <c r="V332" t="n">
+        <v>2</v>
+      </c>
+      <c r="W332" t="n">
+        <v>1</v>
+      </c>
+      <c r="X332" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y332" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z332" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA332" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB332" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC332" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD332" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE332" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF332" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG332" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH332" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI332" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ332" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK332" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL332" t="n">
+        <v>3</v>
       </c>
       <c r="AM332" t="inlineStr"/>
       <c r="AN332" t="inlineStr"/>
@@ -65935,15 +64827,11 @@
           <t>12 022</t>
         </is>
       </c>
-      <c r="G333" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G333" t="n">
+        <v>0</v>
+      </c>
+      <c r="H333" t="n">
+        <v>1</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -65977,115 +64865,71 @@
           <t>42%</t>
         </is>
       </c>
-      <c r="Q333" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R333" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S333" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T333" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U333" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V333" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W333" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X333" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y333" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Z333" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA333" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB333" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC333" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD333" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AE333" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AF333" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AG333" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH333" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AI333" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AJ333" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK333" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL333" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q333" t="n">
+        <v>18</v>
+      </c>
+      <c r="R333" t="n">
+        <v>10</v>
+      </c>
+      <c r="S333" t="n">
+        <v>10</v>
+      </c>
+      <c r="T333" t="n">
+        <v>8</v>
+      </c>
+      <c r="U333" t="n">
+        <v>5</v>
+      </c>
+      <c r="V333" t="n">
+        <v>2</v>
+      </c>
+      <c r="W333" t="n">
+        <v>3</v>
+      </c>
+      <c r="X333" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y333" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z333" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA333" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB333" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC333" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD333" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE333" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF333" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG333" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH333" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI333" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ333" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK333" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL333" t="n">
+        <v>2</v>
       </c>
       <c r="AM333" t="inlineStr"/>
       <c r="AN333" t="inlineStr"/>
@@ -66165,15 +65009,11 @@
           <t>7 771</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H334" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G334" t="n">
+        <v>1</v>
+      </c>
+      <c r="H334" t="n">
+        <v>2</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -66207,115 +65047,71 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q334" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R334" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S334" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T334" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U334" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V334" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W334" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X334" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y334" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z334" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AA334" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AB334" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AC334" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD334" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE334" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF334" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AG334" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH334" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI334" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ334" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK334" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL334" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q334" t="n">
+        <v>12</v>
+      </c>
+      <c r="R334" t="n">
+        <v>13</v>
+      </c>
+      <c r="S334" t="n">
+        <v>4</v>
+      </c>
+      <c r="T334" t="n">
+        <v>6</v>
+      </c>
+      <c r="U334" t="n">
+        <v>5</v>
+      </c>
+      <c r="V334" t="n">
+        <v>5</v>
+      </c>
+      <c r="W334" t="n">
+        <v>3</v>
+      </c>
+      <c r="X334" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y334" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z334" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA334" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB334" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC334" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD334" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE334" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF334" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG334" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH334" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI334" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ334" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK334" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL334" t="n">
+        <v>4</v>
       </c>
       <c r="AM334" t="inlineStr"/>
       <c r="AN334" t="inlineStr"/>
@@ -66395,15 +65191,11 @@
           <t>15 450</t>
         </is>
       </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G335" t="n">
+        <v>1</v>
+      </c>
+      <c r="H335" t="n">
+        <v>1</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
@@ -66437,115 +65229,71 @@
           <t>41%</t>
         </is>
       </c>
-      <c r="Q335" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R335" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S335" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T335" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U335" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V335" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W335" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X335" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y335" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z335" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA335" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB335" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC335" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD335" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE335" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AF335" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG335" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH335" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI335" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ335" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AK335" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL335" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q335" t="n">
+        <v>14</v>
+      </c>
+      <c r="R335" t="n">
+        <v>7</v>
+      </c>
+      <c r="S335" t="n">
+        <v>3</v>
+      </c>
+      <c r="T335" t="n">
+        <v>3</v>
+      </c>
+      <c r="U335" t="n">
+        <v>8</v>
+      </c>
+      <c r="V335" t="n">
+        <v>3</v>
+      </c>
+      <c r="W335" t="n">
+        <v>3</v>
+      </c>
+      <c r="X335" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y335" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z335" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA335" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB335" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC335" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD335" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE335" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF335" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG335" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH335" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI335" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ335" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK335" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL335" t="n">
+        <v>2</v>
       </c>
       <c r="AM335" t="inlineStr"/>
       <c r="AN335" t="inlineStr"/>
@@ -66625,15 +65373,11 @@
           <t>17 241</t>
         </is>
       </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G336" t="n">
+        <v>2</v>
+      </c>
+      <c r="H336" t="n">
+        <v>1</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
@@ -66667,115 +65411,71 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="Q336" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R336" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S336" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T336" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U336" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V336" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W336" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X336" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y336" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Z336" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA336" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB336" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AC336" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD336" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE336" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF336" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AG336" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH336" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI336" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AJ336" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK336" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL336" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q336" t="n">
+        <v>19</v>
+      </c>
+      <c r="R336" t="n">
+        <v>13</v>
+      </c>
+      <c r="S336" t="n">
+        <v>6</v>
+      </c>
+      <c r="T336" t="n">
+        <v>4</v>
+      </c>
+      <c r="U336" t="n">
+        <v>9</v>
+      </c>
+      <c r="V336" t="n">
+        <v>5</v>
+      </c>
+      <c r="W336" t="n">
+        <v>4</v>
+      </c>
+      <c r="X336" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y336" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z336" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA336" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB336" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC336" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD336" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE336" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF336" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG336" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH336" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI336" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ336" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK336" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL336" t="n">
+        <v>2</v>
       </c>
       <c r="AM336" t="inlineStr"/>
       <c r="AN336" t="inlineStr"/>
@@ -66855,15 +65555,11 @@
           <t>22 533</t>
         </is>
       </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H337" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G337" t="n">
+        <v>0</v>
+      </c>
+      <c r="H337" t="n">
+        <v>2</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
@@ -66897,115 +65593,71 @@
           <t>41%</t>
         </is>
       </c>
-      <c r="Q337" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R337" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S337" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T337" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U337" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V337" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W337" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X337" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y337" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z337" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA337" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AB337" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC337" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD337" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE337" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AF337" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AG337" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH337" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI337" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ337" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK337" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL337" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q337" t="n">
+        <v>16</v>
+      </c>
+      <c r="R337" t="n">
+        <v>7</v>
+      </c>
+      <c r="S337" t="n">
+        <v>3</v>
+      </c>
+      <c r="T337" t="n">
+        <v>4</v>
+      </c>
+      <c r="U337" t="n">
+        <v>7</v>
+      </c>
+      <c r="V337" t="n">
+        <v>3</v>
+      </c>
+      <c r="W337" t="n">
+        <v>6</v>
+      </c>
+      <c r="X337" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y337" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z337" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA337" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB337" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC337" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD337" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE337" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF337" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG337" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH337" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI337" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ337" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK337" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL337" t="n">
+        <v>1</v>
       </c>
       <c r="AM337" t="inlineStr"/>
       <c r="AN337" t="inlineStr"/>
@@ -67085,15 +65737,11 @@
           <t>3 897</t>
         </is>
       </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H338" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G338" t="n">
+        <v>1</v>
+      </c>
+      <c r="H338" t="n">
+        <v>1</v>
       </c>
       <c r="I338" t="inlineStr">
         <is>
@@ -67127,115 +65775,71 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="Q338" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R338" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S338" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T338" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U338" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V338" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W338" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X338" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y338" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z338" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA338" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB338" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC338" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD338" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE338" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AF338" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AG338" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH338" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI338" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ338" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK338" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL338" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q338" t="n">
+        <v>16</v>
+      </c>
+      <c r="R338" t="n">
+        <v>10</v>
+      </c>
+      <c r="S338" t="n">
+        <v>4</v>
+      </c>
+      <c r="T338" t="n">
+        <v>5</v>
+      </c>
+      <c r="U338" t="n">
+        <v>7</v>
+      </c>
+      <c r="V338" t="n">
+        <v>3</v>
+      </c>
+      <c r="W338" t="n">
+        <v>5</v>
+      </c>
+      <c r="X338" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y338" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z338" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA338" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB338" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC338" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD338" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE338" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF338" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG338" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH338" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI338" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ338" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK338" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL338" t="n">
+        <v>3</v>
       </c>
       <c r="AM338" t="inlineStr"/>
       <c r="AN338" t="inlineStr"/>
@@ -67275,15 +65879,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY338" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AZ338" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AY338" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ338" t="n">
+        <v>0</v>
       </c>
       <c r="BA338" t="inlineStr"/>
       <c r="BB338" t="inlineStr"/>
@@ -67323,15 +65923,11 @@
           <t>6 680</t>
         </is>
       </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H339" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G339" t="n">
+        <v>1</v>
+      </c>
+      <c r="H339" t="n">
+        <v>4</v>
       </c>
       <c r="I339" t="inlineStr">
         <is>
@@ -67365,115 +65961,71 @@
           <t>44%</t>
         </is>
       </c>
-      <c r="Q339" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R339" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S339" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T339" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="U339" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V339" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W339" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X339" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y339" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Z339" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA339" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB339" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC339" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD339" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE339" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AF339" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AG339" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH339" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI339" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AJ339" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK339" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL339" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q339" t="n">
+        <v>16</v>
+      </c>
+      <c r="R339" t="n">
+        <v>22</v>
+      </c>
+      <c r="S339" t="n">
+        <v>3</v>
+      </c>
+      <c r="T339" t="n">
+        <v>10</v>
+      </c>
+      <c r="U339" t="n">
+        <v>6</v>
+      </c>
+      <c r="V339" t="n">
+        <v>8</v>
+      </c>
+      <c r="W339" t="n">
+        <v>7</v>
+      </c>
+      <c r="X339" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y339" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z339" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA339" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB339" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC339" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD339" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE339" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF339" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG339" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH339" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI339" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ339" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK339" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL339" t="n">
+        <v>2</v>
       </c>
       <c r="AM339" t="inlineStr"/>
       <c r="AN339" t="inlineStr"/>
@@ -67553,15 +66105,11 @@
           <t>18 827</t>
         </is>
       </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H340" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G340" t="n">
+        <v>2</v>
+      </c>
+      <c r="H340" t="n">
+        <v>2</v>
       </c>
       <c r="I340" t="inlineStr">
         <is>
@@ -67595,115 +66143,71 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="Q340" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R340" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S340" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T340" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U340" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V340" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W340" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X340" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y340" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z340" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AA340" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB340" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC340" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD340" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE340" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AF340" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG340" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH340" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI340" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AJ340" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK340" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL340" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q340" t="n">
+        <v>12</v>
+      </c>
+      <c r="R340" t="n">
+        <v>13</v>
+      </c>
+      <c r="S340" t="n">
+        <v>6</v>
+      </c>
+      <c r="T340" t="n">
+        <v>5</v>
+      </c>
+      <c r="U340" t="n">
+        <v>4</v>
+      </c>
+      <c r="V340" t="n">
+        <v>6</v>
+      </c>
+      <c r="W340" t="n">
+        <v>2</v>
+      </c>
+      <c r="X340" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y340" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z340" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA340" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB340" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC340" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD340" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE340" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF340" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG340" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH340" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI340" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ340" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK340" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL340" t="n">
+        <v>5</v>
       </c>
       <c r="AM340" t="inlineStr"/>
       <c r="AN340" t="inlineStr"/>
@@ -67783,15 +66287,11 @@
           <t>11 952</t>
         </is>
       </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="G341" t="n">
+        <v>2</v>
+      </c>
+      <c r="H341" t="n">
+        <v>5</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
@@ -67825,135 +66325,83 @@
           <t>56%</t>
         </is>
       </c>
-      <c r="Q341" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R341" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S341" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T341" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U341" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V341" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W341" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X341" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y341" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Z341" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA341" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB341" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC341" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD341" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE341" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AF341" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AG341" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH341" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI341" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AJ341" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK341" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL341" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM341" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="AN341" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="AO341" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="AP341" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="Q341" t="n">
+        <v>17</v>
+      </c>
+      <c r="R341" t="n">
+        <v>10</v>
+      </c>
+      <c r="S341" t="n">
+        <v>5</v>
+      </c>
+      <c r="T341" t="n">
+        <v>7</v>
+      </c>
+      <c r="U341" t="n">
+        <v>8</v>
+      </c>
+      <c r="V341" t="n">
+        <v>1</v>
+      </c>
+      <c r="W341" t="n">
+        <v>4</v>
+      </c>
+      <c r="X341" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y341" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z341" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA341" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB341" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC341" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD341" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE341" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF341" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG341" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH341" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI341" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ341" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK341" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL341" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM341" t="n">
+        <v>61</v>
+      </c>
+      <c r="AN341" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO341" t="n">
+        <v>37</v>
+      </c>
+      <c r="AP341" t="n">
+        <v>42</v>
       </c>
       <c r="AQ341" t="inlineStr">
         <is>
@@ -68029,15 +66477,11 @@
           <t>15 455</t>
         </is>
       </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H342" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G342" t="n">
+        <v>2</v>
+      </c>
+      <c r="H342" t="n">
+        <v>2</v>
       </c>
       <c r="I342" t="inlineStr">
         <is>
@@ -68071,135 +66515,83 @@
           <t>39%</t>
         </is>
       </c>
-      <c r="Q342" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R342" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S342" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T342" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U342" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V342" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W342" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X342" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y342" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z342" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AA342" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB342" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC342" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD342" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE342" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AF342" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AG342" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH342" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI342" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AJ342" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK342" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL342" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AM342" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="AN342" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="AO342" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="AP342" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
+      <c r="Q342" t="n">
+        <v>13</v>
+      </c>
+      <c r="R342" t="n">
+        <v>10</v>
+      </c>
+      <c r="S342" t="n">
+        <v>3</v>
+      </c>
+      <c r="T342" t="n">
+        <v>3</v>
+      </c>
+      <c r="U342" t="n">
+        <v>2</v>
+      </c>
+      <c r="V342" t="n">
+        <v>5</v>
+      </c>
+      <c r="W342" t="n">
+        <v>8</v>
+      </c>
+      <c r="X342" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y342" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z342" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA342" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB342" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC342" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD342" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE342" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF342" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG342" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH342" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI342" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ342" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK342" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL342" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM342" t="n">
+        <v>126</v>
+      </c>
+      <c r="AN342" t="n">
+        <v>87</v>
+      </c>
+      <c r="AO342" t="n">
+        <v>47</v>
+      </c>
+      <c r="AP342" t="n">
+        <v>43</v>
       </c>
       <c r="AQ342" t="inlineStr">
         <is>
@@ -68275,15 +66667,11 @@
           <t>10 150</t>
         </is>
       </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H343" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G343" t="n">
+        <v>1</v>
+      </c>
+      <c r="H343" t="n">
+        <v>0</v>
       </c>
       <c r="I343" t="inlineStr">
         <is>
@@ -68317,135 +66705,83 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q343" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R343" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S343" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T343" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U343" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V343" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W343" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X343" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y343" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z343" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA343" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB343" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC343" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD343" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE343" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AF343" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AG343" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH343" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI343" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ343" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK343" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL343" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM343" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="AN343" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="AO343" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="AP343" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="Q343" t="n">
+        <v>16</v>
+      </c>
+      <c r="R343" t="n">
+        <v>13</v>
+      </c>
+      <c r="S343" t="n">
+        <v>7</v>
+      </c>
+      <c r="T343" t="n">
+        <v>4</v>
+      </c>
+      <c r="U343" t="n">
+        <v>7</v>
+      </c>
+      <c r="V343" t="n">
+        <v>6</v>
+      </c>
+      <c r="W343" t="n">
+        <v>2</v>
+      </c>
+      <c r="X343" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y343" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z343" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA343" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB343" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC343" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD343" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE343" t="n">
+        <v>31</v>
+      </c>
+      <c r="AF343" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG343" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH343" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI343" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ343" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK343" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL343" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM343" t="n">
+        <v>97</v>
+      </c>
+      <c r="AN343" t="n">
+        <v>119</v>
+      </c>
+      <c r="AO343" t="n">
+        <v>52</v>
+      </c>
+      <c r="AP343" t="n">
+        <v>64</v>
       </c>
       <c r="AQ343" t="inlineStr">
         <is>
@@ -68521,15 +66857,11 @@
           <t>16 868</t>
         </is>
       </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H344" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G344" t="n">
+        <v>0</v>
+      </c>
+      <c r="H344" t="n">
+        <v>0</v>
       </c>
       <c r="I344" t="inlineStr">
         <is>
@@ -68563,135 +66895,83 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="Q344" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R344" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S344" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T344" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U344" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V344" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W344" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X344" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y344" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z344" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AA344" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB344" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC344" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD344" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE344" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF344" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AG344" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH344" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI344" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AJ344" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK344" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL344" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM344" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="AN344" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="AO344" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AP344" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
+      <c r="Q344" t="n">
+        <v>13</v>
+      </c>
+      <c r="R344" t="n">
+        <v>16</v>
+      </c>
+      <c r="S344" t="n">
+        <v>3</v>
+      </c>
+      <c r="T344" t="n">
+        <v>1</v>
+      </c>
+      <c r="U344" t="n">
+        <v>6</v>
+      </c>
+      <c r="V344" t="n">
+        <v>6</v>
+      </c>
+      <c r="W344" t="n">
+        <v>4</v>
+      </c>
+      <c r="X344" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y344" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z344" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA344" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB344" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC344" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD344" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE344" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF344" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG344" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH344" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI344" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ344" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK344" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL344" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM344" t="n">
+        <v>105</v>
+      </c>
+      <c r="AN344" t="n">
+        <v>118</v>
+      </c>
+      <c r="AO344" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP344" t="n">
+        <v>44</v>
       </c>
       <c r="AQ344" t="inlineStr">
         <is>
@@ -68767,15 +67047,11 @@
           <t>19 492</t>
         </is>
       </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H345" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G345" t="n">
+        <v>1</v>
+      </c>
+      <c r="H345" t="n">
+        <v>0</v>
       </c>
       <c r="I345" t="inlineStr">
         <is>
@@ -68809,135 +67085,83 @@
           <t>33%</t>
         </is>
       </c>
-      <c r="Q345" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R345" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S345" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T345" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U345" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V345" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W345" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X345" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y345" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z345" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AA345" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB345" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC345" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD345" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE345" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AF345" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AG345" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH345" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI345" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AJ345" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AK345" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL345" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM345" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="AN345" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="AO345" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="AP345" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="Q345" t="n">
+        <v>16</v>
+      </c>
+      <c r="R345" t="n">
+        <v>5</v>
+      </c>
+      <c r="S345" t="n">
+        <v>3</v>
+      </c>
+      <c r="T345" t="n">
+        <v>2</v>
+      </c>
+      <c r="U345" t="n">
+        <v>7</v>
+      </c>
+      <c r="V345" t="n">
+        <v>1</v>
+      </c>
+      <c r="W345" t="n">
+        <v>6</v>
+      </c>
+      <c r="X345" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y345" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z345" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA345" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB345" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC345" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD345" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE345" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF345" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG345" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH345" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI345" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ345" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK345" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL345" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM345" t="n">
+        <v>151</v>
+      </c>
+      <c r="AN345" t="n">
+        <v>68</v>
+      </c>
+      <c r="AO345" t="n">
+        <v>63</v>
+      </c>
+      <c r="AP345" t="n">
+        <v>16</v>
       </c>
       <c r="AQ345" t="inlineStr">
         <is>
@@ -69013,15 +67237,11 @@
           <t>2 713</t>
         </is>
       </c>
-      <c r="G346" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H346" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G346" t="n">
+        <v>2</v>
+      </c>
+      <c r="H346" t="n">
+        <v>0</v>
       </c>
       <c r="I346" t="inlineStr">
         <is>
@@ -69055,135 +67275,83 @@
           <t>52%</t>
         </is>
       </c>
-      <c r="Q346" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R346" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S346" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T346" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U346" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V346" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W346" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X346" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y346" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z346" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA346" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB346" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC346" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD346" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE346" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AF346" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AG346" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH346" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI346" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ346" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK346" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL346" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AM346" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="AN346" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="AO346" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="AP346" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
+      <c r="Q346" t="n">
+        <v>18</v>
+      </c>
+      <c r="R346" t="n">
+        <v>6</v>
+      </c>
+      <c r="S346" t="n">
+        <v>5</v>
+      </c>
+      <c r="T346" t="n">
+        <v>2</v>
+      </c>
+      <c r="U346" t="n">
+        <v>6</v>
+      </c>
+      <c r="V346" t="n">
+        <v>3</v>
+      </c>
+      <c r="W346" t="n">
+        <v>7</v>
+      </c>
+      <c r="X346" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y346" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z346" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA346" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB346" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC346" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD346" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE346" t="n">
+        <v>31</v>
+      </c>
+      <c r="AF346" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG346" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH346" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI346" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ346" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK346" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL346" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM346" t="n">
+        <v>129</v>
+      </c>
+      <c r="AN346" t="n">
+        <v>102</v>
+      </c>
+      <c r="AO346" t="n">
+        <v>59</v>
+      </c>
+      <c r="AP346" t="n">
+        <v>34</v>
       </c>
       <c r="AQ346" t="inlineStr">
         <is>
@@ -69226,6 +67394,482 @@
       <c r="BC346" t="inlineStr"/>
       <c r="BD346" t="inlineStr"/>
     </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>23.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Garcia V.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Estadio Benito Villamarín
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>60 721</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>47 017</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T347" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W347" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X347" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y347" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z347" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA347" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB347" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC347" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD347" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE347" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AF347" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG347" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH347" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI347" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ347" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK347" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL347" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM347" t="inlineStr"/>
+      <c r="AN347" t="inlineStr"/>
+      <c r="AO347" t="inlineStr"/>
+      <c r="AP347" t="inlineStr"/>
+      <c r="AQ347" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="AR347" t="inlineStr">
+        <is>
+          <t>pellegrini manuel</t>
+        </is>
+      </c>
+      <c r="AS347" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="AT347" t="inlineStr">
+        <is>
+          <t>arrasate jagoba</t>
+        </is>
+      </c>
+      <c r="AU347" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV347" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW347" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX347" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY347" t="inlineStr"/>
+      <c r="AZ347" t="inlineStr"/>
+      <c r="BA347" t="inlineStr"/>
+      <c r="BB347" t="inlineStr"/>
+      <c r="BC347" t="inlineStr"/>
+      <c r="BD347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>8Ia7s2mS</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>23.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Muresan S.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Estadio El Alcoraz
+ (Huesca)</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>9 100</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>5 899</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>Cordoba</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr"/>
+      <c r="N348" t="inlineStr"/>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T348" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W348" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X348" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y348" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z348" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA348" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB348" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC348" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD348" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE348" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF348" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AG348" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH348" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI348" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ348" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK348" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL348" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM348" t="inlineStr"/>
+      <c r="AN348" t="inlineStr"/>
+      <c r="AO348" t="inlineStr"/>
+      <c r="AP348" t="inlineStr"/>
+      <c r="AQ348" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="AR348" t="inlineStr">
+        <is>
+          <t>hidalgo antonio</t>
+        </is>
+      </c>
+      <c r="AS348" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="AT348" t="inlineStr">
+        <is>
+          <t>ania ivan</t>
+        </is>
+      </c>
+      <c r="AU348" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV348" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW348" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX348" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY348" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BA348" t="inlineStr"/>
+      <c r="BB348" t="inlineStr"/>
+      <c r="BC348" t="inlineStr"/>
+      <c r="BD348" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD356"/>
+  <dimension ref="A1:BD366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67427,15 +67427,11 @@
           <t>21 533</t>
         </is>
       </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H347" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G347" t="n">
+        <v>0</v>
+      </c>
+      <c r="H347" t="n">
+        <v>1</v>
       </c>
       <c r="I347" t="inlineStr">
         <is>
@@ -67457,15 +67453,11 @@
           <t>Atl. Madrid</t>
         </is>
       </c>
-      <c r="M347" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="N347" t="inlineStr">
-        <is>
-          <t>0.60</t>
-        </is>
+      <c r="M347" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="N347" t="n">
+        <v>0.6</v>
       </c>
       <c r="O347" t="inlineStr">
         <is>
@@ -67477,115 +67469,71 @@
           <t>41%</t>
         </is>
       </c>
-      <c r="Q347" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R347" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S347" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T347" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U347" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V347" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W347" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X347" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y347" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z347" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA347" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB347" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC347" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD347" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE347" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF347" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG347" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH347" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI347" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ347" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK347" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL347" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q347" t="n">
+        <v>10</v>
+      </c>
+      <c r="R347" t="n">
+        <v>8</v>
+      </c>
+      <c r="S347" t="n">
+        <v>4</v>
+      </c>
+      <c r="T347" t="n">
+        <v>2</v>
+      </c>
+      <c r="U347" t="n">
+        <v>6</v>
+      </c>
+      <c r="V347" t="n">
+        <v>2</v>
+      </c>
+      <c r="W347" t="n">
+        <v>0</v>
+      </c>
+      <c r="X347" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y347" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z347" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA347" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB347" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC347" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD347" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE347" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF347" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG347" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH347" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI347" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ347" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK347" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL347" t="n">
+        <v>2</v>
       </c>
       <c r="AM347" t="inlineStr"/>
       <c r="AN347" t="inlineStr"/>
@@ -67665,15 +67613,11 @@
           <t>23 147</t>
         </is>
       </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H348" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G348" t="n">
+        <v>1</v>
+      </c>
+      <c r="H348" t="n">
+        <v>2</v>
       </c>
       <c r="I348" t="inlineStr">
         <is>
@@ -67695,15 +67639,11 @@
           <t>Villarreal</t>
         </is>
       </c>
-      <c r="M348" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="N348" t="inlineStr">
-        <is>
-          <t>1.11</t>
-        </is>
+      <c r="M348" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="N348" t="n">
+        <v>1.11</v>
       </c>
       <c r="O348" t="inlineStr">
         <is>
@@ -67715,115 +67655,71 @@
           <t>44%</t>
         </is>
       </c>
-      <c r="Q348" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R348" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S348" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T348" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U348" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V348" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W348" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X348" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y348" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z348" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA348" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB348" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC348" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD348" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE348" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF348" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG348" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH348" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI348" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ348" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK348" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AL348" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q348" t="n">
+        <v>11</v>
+      </c>
+      <c r="R348" t="n">
+        <v>15</v>
+      </c>
+      <c r="S348" t="n">
+        <v>2</v>
+      </c>
+      <c r="T348" t="n">
+        <v>4</v>
+      </c>
+      <c r="U348" t="n">
+        <v>4</v>
+      </c>
+      <c r="V348" t="n">
+        <v>7</v>
+      </c>
+      <c r="W348" t="n">
+        <v>5</v>
+      </c>
+      <c r="X348" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y348" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z348" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA348" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB348" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC348" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD348" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE348" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF348" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG348" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH348" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI348" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ348" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK348" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL348" t="n">
+        <v>3</v>
       </c>
       <c r="AM348" t="inlineStr"/>
       <c r="AN348" t="inlineStr"/>
@@ -67903,15 +67799,11 @@
           <t>22 722</t>
         </is>
       </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H349" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G349" t="n">
+        <v>1</v>
+      </c>
+      <c r="H349" t="n">
+        <v>1</v>
       </c>
       <c r="I349" t="inlineStr">
         <is>
@@ -67933,15 +67825,11 @@
           <t>Betis</t>
         </is>
       </c>
-      <c r="M349" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="N349" t="inlineStr">
-        <is>
-          <t>1.96</t>
-        </is>
+      <c r="M349" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N349" t="n">
+        <v>1.96</v>
       </c>
       <c r="O349" t="inlineStr">
         <is>
@@ -67953,115 +67841,71 @@
           <t>45%</t>
         </is>
       </c>
-      <c r="Q349" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R349" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S349" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T349" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U349" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V349" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W349" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X349" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y349" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z349" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AA349" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB349" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC349" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD349" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE349" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF349" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG349" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH349" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI349" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AJ349" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK349" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL349" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q349" t="n">
+        <v>8</v>
+      </c>
+      <c r="R349" t="n">
+        <v>14</v>
+      </c>
+      <c r="S349" t="n">
+        <v>2</v>
+      </c>
+      <c r="T349" t="n">
+        <v>5</v>
+      </c>
+      <c r="U349" t="n">
+        <v>4</v>
+      </c>
+      <c r="V349" t="n">
+        <v>7</v>
+      </c>
+      <c r="W349" t="n">
+        <v>2</v>
+      </c>
+      <c r="X349" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y349" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z349" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA349" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB349" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC349" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD349" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE349" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF349" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG349" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH349" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI349" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ349" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK349" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL349" t="n">
+        <v>2</v>
       </c>
       <c r="AM349" t="inlineStr"/>
       <c r="AN349" t="inlineStr"/>
@@ -68141,15 +67985,11 @@
           <t>44 407</t>
         </is>
       </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H350" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G350" t="n">
+        <v>1</v>
+      </c>
+      <c r="H350" t="n">
+        <v>0</v>
       </c>
       <c r="I350" t="inlineStr">
         <is>
@@ -68171,15 +68011,11 @@
           <t>Getafe</t>
         </is>
       </c>
-      <c r="M350" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="N350" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
+      <c r="M350" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="N350" t="n">
+        <v>0.4</v>
       </c>
       <c r="O350" t="inlineStr">
         <is>
@@ -68191,115 +68027,71 @@
           <t>22%</t>
         </is>
       </c>
-      <c r="Q350" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R350" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S350" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T350" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U350" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V350" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W350" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X350" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y350" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="Z350" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA350" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB350" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC350" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD350" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AE350" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF350" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG350" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH350" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI350" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ350" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK350" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL350" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q350" t="n">
+        <v>15</v>
+      </c>
+      <c r="R350" t="n">
+        <v>7</v>
+      </c>
+      <c r="S350" t="n">
+        <v>4</v>
+      </c>
+      <c r="T350" t="n">
+        <v>1</v>
+      </c>
+      <c r="U350" t="n">
+        <v>6</v>
+      </c>
+      <c r="V350" t="n">
+        <v>3</v>
+      </c>
+      <c r="W350" t="n">
+        <v>5</v>
+      </c>
+      <c r="X350" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y350" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z350" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA350" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB350" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC350" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD350" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE350" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF350" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG350" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH350" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI350" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ350" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK350" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL350" t="n">
+        <v>1</v>
       </c>
       <c r="AM350" t="inlineStr"/>
       <c r="AN350" t="inlineStr"/>
@@ -68379,15 +68171,11 @@
           <t>12 272</t>
         </is>
       </c>
-      <c r="G351" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H351" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G351" t="n">
+        <v>0</v>
+      </c>
+      <c r="H351" t="n">
+        <v>0</v>
       </c>
       <c r="I351" t="inlineStr">
         <is>
@@ -68409,15 +68197,11 @@
           <t>Rayo Vallecano</t>
         </is>
       </c>
-      <c r="M351" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="N351" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
+      <c r="M351" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N351" t="n">
+        <v>0.53</v>
       </c>
       <c r="O351" t="inlineStr">
         <is>
@@ -68429,115 +68213,71 @@
           <t>29%</t>
         </is>
       </c>
-      <c r="Q351" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R351" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S351" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T351" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U351" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V351" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W351" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X351" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y351" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z351" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA351" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB351" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC351" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD351" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE351" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="AF351" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG351" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH351" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI351" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ351" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK351" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL351" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q351" t="n">
+        <v>11</v>
+      </c>
+      <c r="R351" t="n">
+        <v>2</v>
+      </c>
+      <c r="S351" t="n">
+        <v>0</v>
+      </c>
+      <c r="T351" t="n">
+        <v>0</v>
+      </c>
+      <c r="U351" t="n">
+        <v>9</v>
+      </c>
+      <c r="V351" t="n">
+        <v>2</v>
+      </c>
+      <c r="W351" t="n">
+        <v>2</v>
+      </c>
+      <c r="X351" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y351" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z351" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA351" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB351" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC351" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD351" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE351" t="n">
+        <v>43</v>
+      </c>
+      <c r="AF351" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG351" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH351" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI351" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ351" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK351" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL351" t="n">
+        <v>4</v>
       </c>
       <c r="AM351" t="inlineStr"/>
       <c r="AN351" t="inlineStr"/>
@@ -68617,15 +68357,11 @@
           <t>67 480</t>
         </is>
       </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H352" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G352" t="n">
+        <v>3</v>
+      </c>
+      <c r="H352" t="n">
+        <v>2</v>
       </c>
       <c r="I352" t="inlineStr">
         <is>
@@ -68647,15 +68383,11 @@
           <t>Alaves</t>
         </is>
       </c>
-      <c r="M352" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="N352" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
+      <c r="M352" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N352" t="n">
+        <v>0.76</v>
       </c>
       <c r="O352" t="inlineStr">
         <is>
@@ -68667,115 +68399,71 @@
           <t>31%</t>
         </is>
       </c>
-      <c r="Q352" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R352" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S352" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T352" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U352" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V352" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W352" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X352" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y352" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z352" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA352" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB352" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC352" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD352" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE352" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF352" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AG352" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH352" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI352" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AJ352" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK352" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL352" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q352" t="n">
+        <v>10</v>
+      </c>
+      <c r="R352" t="n">
+        <v>12</v>
+      </c>
+      <c r="S352" t="n">
+        <v>4</v>
+      </c>
+      <c r="T352" t="n">
+        <v>3</v>
+      </c>
+      <c r="U352" t="n">
+        <v>4</v>
+      </c>
+      <c r="V352" t="n">
+        <v>7</v>
+      </c>
+      <c r="W352" t="n">
+        <v>2</v>
+      </c>
+      <c r="X352" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y352" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z352" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA352" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB352" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC352" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD352" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE352" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF352" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG352" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH352" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI352" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ352" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK352" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL352" t="n">
+        <v>0</v>
       </c>
       <c r="AM352" t="inlineStr"/>
       <c r="AN352" t="inlineStr"/>
@@ -68855,15 +68543,11 @@
           <t>35 292</t>
         </is>
       </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H353" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G353" t="n">
+        <v>2</v>
+      </c>
+      <c r="H353" t="n">
+        <v>1</v>
       </c>
       <c r="I353" t="inlineStr">
         <is>
@@ -68885,15 +68569,11 @@
           <t>Valladolid</t>
         </is>
       </c>
-      <c r="M353" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="N353" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
+      <c r="M353" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="N353" t="n">
+        <v>0.67</v>
       </c>
       <c r="O353" t="inlineStr">
         <is>
@@ -68905,115 +68585,71 @@
           <t>45%</t>
         </is>
       </c>
-      <c r="Q353" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R353" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S353" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T353" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U353" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V353" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W353" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X353" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y353" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z353" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA353" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB353" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC353" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD353" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE353" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AF353" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AG353" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH353" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI353" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ353" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK353" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AL353" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q353" t="n">
+        <v>22</v>
+      </c>
+      <c r="R353" t="n">
+        <v>8</v>
+      </c>
+      <c r="S353" t="n">
+        <v>5</v>
+      </c>
+      <c r="T353" t="n">
+        <v>2</v>
+      </c>
+      <c r="U353" t="n">
+        <v>11</v>
+      </c>
+      <c r="V353" t="n">
+        <v>2</v>
+      </c>
+      <c r="W353" t="n">
+        <v>6</v>
+      </c>
+      <c r="X353" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y353" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z353" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA353" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB353" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC353" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD353" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE353" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF353" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG353" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH353" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI353" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ353" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK353" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL353" t="n">
+        <v>4</v>
       </c>
       <c r="AM353" t="inlineStr"/>
       <c r="AN353" t="inlineStr"/>
@@ -69053,15 +68689,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY353" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AZ353" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AY353" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ353" t="n">
+        <v>0</v>
       </c>
       <c r="BA353" t="inlineStr"/>
       <c r="BB353" t="inlineStr"/>
@@ -69101,15 +68733,11 @@
           <t>40 425</t>
         </is>
       </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G354" t="n">
+        <v>0</v>
+      </c>
+      <c r="H354" t="n">
+        <v>0</v>
       </c>
       <c r="I354" t="inlineStr">
         <is>
@@ -69131,15 +68759,11 @@
           <t>Osasuna</t>
         </is>
       </c>
-      <c r="M354" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
-      <c r="N354" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
+      <c r="M354" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="N354" t="n">
+        <v>0.43</v>
       </c>
       <c r="O354" t="inlineStr">
         <is>
@@ -69151,115 +68775,71 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q354" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R354" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S354" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T354" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U354" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V354" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W354" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X354" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y354" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z354" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA354" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AB354" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC354" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD354" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE354" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AF354" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AG354" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH354" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI354" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AJ354" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK354" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL354" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q354" t="n">
+        <v>10</v>
+      </c>
+      <c r="R354" t="n">
+        <v>9</v>
+      </c>
+      <c r="S354" t="n">
+        <v>2</v>
+      </c>
+      <c r="T354" t="n">
+        <v>2</v>
+      </c>
+      <c r="U354" t="n">
+        <v>4</v>
+      </c>
+      <c r="V354" t="n">
+        <v>5</v>
+      </c>
+      <c r="W354" t="n">
+        <v>4</v>
+      </c>
+      <c r="X354" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y354" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z354" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA354" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB354" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC354" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD354" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE354" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF354" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG354" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH354" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI354" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ354" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK354" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL354" t="n">
+        <v>3</v>
       </c>
       <c r="AM354" t="inlineStr"/>
       <c r="AN354" t="inlineStr"/>
@@ -69339,15 +68919,11 @@
           <t>47 017</t>
         </is>
       </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G355" t="n">
+        <v>1</v>
+      </c>
+      <c r="H355" t="n">
+        <v>2</v>
       </c>
       <c r="I355" t="inlineStr">
         <is>
@@ -69369,15 +68945,11 @@
           <t>Mallorca</t>
         </is>
       </c>
-      <c r="M355" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
-      <c r="N355" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
+      <c r="M355" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="N355" t="n">
+        <v>1.15</v>
       </c>
       <c r="O355" t="inlineStr">
         <is>
@@ -69389,115 +68961,71 @@
           <t>39%</t>
         </is>
       </c>
-      <c r="Q355" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R355" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S355" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T355" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U355" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V355" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W355" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X355" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y355" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z355" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA355" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB355" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC355" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD355" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE355" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AF355" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG355" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH355" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI355" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ355" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK355" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL355" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q355" t="n">
+        <v>16</v>
+      </c>
+      <c r="R355" t="n">
+        <v>7</v>
+      </c>
+      <c r="S355" t="n">
+        <v>6</v>
+      </c>
+      <c r="T355" t="n">
+        <v>6</v>
+      </c>
+      <c r="U355" t="n">
+        <v>5</v>
+      </c>
+      <c r="V355" t="n">
+        <v>1</v>
+      </c>
+      <c r="W355" t="n">
+        <v>5</v>
+      </c>
+      <c r="X355" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y355" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z355" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA355" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB355" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC355" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD355" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE355" t="n">
+        <v>33</v>
+      </c>
+      <c r="AF355" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG355" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH355" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI355" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ355" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK355" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL355" t="n">
+        <v>3</v>
       </c>
       <c r="AM355" t="inlineStr"/>
       <c r="AN355" t="inlineStr"/>
@@ -69577,15 +69105,11 @@
           <t>5 899</t>
         </is>
       </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H356" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G356" t="n">
+        <v>4</v>
+      </c>
+      <c r="H356" t="n">
+        <v>1</v>
       </c>
       <c r="I356" t="inlineStr">
         <is>
@@ -69619,115 +69143,71 @@
           <t>66%</t>
         </is>
       </c>
-      <c r="Q356" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R356" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S356" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T356" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U356" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V356" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W356" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X356" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y356" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z356" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA356" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB356" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC356" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD356" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE356" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AF356" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AG356" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH356" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI356" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AJ356" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AK356" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL356" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q356" t="n">
+        <v>9</v>
+      </c>
+      <c r="R356" t="n">
+        <v>16</v>
+      </c>
+      <c r="S356" t="n">
+        <v>5</v>
+      </c>
+      <c r="T356" t="n">
+        <v>4</v>
+      </c>
+      <c r="U356" t="n">
+        <v>3</v>
+      </c>
+      <c r="V356" t="n">
+        <v>6</v>
+      </c>
+      <c r="W356" t="n">
+        <v>1</v>
+      </c>
+      <c r="X356" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y356" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z356" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA356" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB356" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC356" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD356" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE356" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF356" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG356" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH356" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI356" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ356" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK356" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL356" t="n">
+        <v>2</v>
       </c>
       <c r="AM356" t="inlineStr"/>
       <c r="AN356" t="inlineStr"/>
@@ -69767,21 +69247,2357 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY356" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ356" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AY356" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ356" t="n">
+        <v>1</v>
       </c>
       <c r="BA356" t="inlineStr"/>
       <c r="BB356" t="inlineStr"/>
       <c r="BC356" t="inlineStr"/>
       <c r="BD356" t="inlineStr"/>
     </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>4vvdzeEs</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>28.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Cuadra G.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>23 516</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>22 322</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W357" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X357" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y357" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z357" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB357" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC357" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD357" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE357" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF357" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG357" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH357" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI357" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ357" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK357" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL357" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM357" t="inlineStr"/>
+      <c r="AN357" t="inlineStr"/>
+      <c r="AO357" t="inlineStr"/>
+      <c r="AP357" t="inlineStr"/>
+      <c r="AQ357" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="AR357" t="inlineStr">
+        <is>
+          <t>moreno vicente</t>
+        </is>
+      </c>
+      <c r="AS357" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="AT357" t="inlineStr">
+        <is>
+          <t>flick hans dieter</t>
+        </is>
+      </c>
+      <c r="AU357" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV357" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW357" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX357" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY357" t="inlineStr"/>
+      <c r="AZ357" t="inlineStr"/>
+      <c r="BA357" t="inlineStr"/>
+      <c r="BB357" t="inlineStr"/>
+      <c r="BC357" t="inlineStr"/>
+      <c r="BD357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>28.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Rojas J. A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Reale Arena
+ (San Sebastian)</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>40 000</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>32 332</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W358" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X358" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y358" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z358" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB358" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC358" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD358" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE358" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AF358" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AG358" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH358" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI358" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ358" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK358" t="inlineStr"/>
+      <c r="AL358" t="inlineStr"/>
+      <c r="AM358" t="inlineStr"/>
+      <c r="AN358" t="inlineStr"/>
+      <c r="AO358" t="inlineStr"/>
+      <c r="AP358" t="inlineStr"/>
+      <c r="AQ358" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="AR358" t="inlineStr">
+        <is>
+          <t>alguacil imanol</t>
+        </is>
+      </c>
+      <c r="AS358" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="AT358" t="inlineStr">
+        <is>
+          <t>baraja ruben</t>
+        </is>
+      </c>
+      <c r="AU358" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV358" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW358" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX358" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY358" t="inlineStr"/>
+      <c r="AZ358" t="inlineStr"/>
+      <c r="BA358" t="inlineStr"/>
+      <c r="BB358" t="inlineStr"/>
+      <c r="BC358" t="inlineStr"/>
+      <c r="BD358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>28.09.2024 11:15</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Ruiz A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Campo de Futbol de Vallecas
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>14 708</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>13 186</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W359" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X359" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y359" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z359" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB359" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC359" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD359" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE359" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AF359" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG359" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH359" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI359" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ359" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK359" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL359" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM359" t="inlineStr"/>
+      <c r="AN359" t="inlineStr"/>
+      <c r="AO359" t="inlineStr"/>
+      <c r="AP359" t="inlineStr"/>
+      <c r="AQ359" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="AR359" t="inlineStr">
+        <is>
+          <t>perez inigo</t>
+        </is>
+      </c>
+      <c r="AS359" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="AT359" t="inlineStr">
+        <is>
+          <t>jimenez borja</t>
+        </is>
+      </c>
+      <c r="AU359" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV359" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW359" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX359" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY359" t="inlineStr"/>
+      <c r="AZ359" t="inlineStr"/>
+      <c r="BA359" t="inlineStr"/>
+      <c r="BB359" t="inlineStr"/>
+      <c r="BC359" t="inlineStr"/>
+      <c r="BD359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>28.09.2024 09:00</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Diaz de Mera I.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Coliseum
+ (Getafe)</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>16 500</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>10 006</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T360" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W360" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X360" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y360" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="Z360" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB360" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC360" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD360" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE360" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AF360" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AG360" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH360" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI360" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ360" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AK360" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL360" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AM360" t="inlineStr"/>
+      <c r="AN360" t="inlineStr"/>
+      <c r="AO360" t="inlineStr"/>
+      <c r="AP360" t="inlineStr"/>
+      <c r="AQ360" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="AR360" t="inlineStr">
+        <is>
+          <t>bordalas pepe</t>
+        </is>
+      </c>
+      <c r="AS360" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="AT360" t="inlineStr">
+        <is>
+          <t>garcia luis</t>
+        </is>
+      </c>
+      <c r="AU360" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV360" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW360" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX360" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY360" t="inlineStr"/>
+      <c r="AZ360" t="inlineStr"/>
+      <c r="BA360" t="inlineStr"/>
+      <c r="BB360" t="inlineStr"/>
+      <c r="BC360" t="inlineStr"/>
+      <c r="BD360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>27.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Munuera Montero J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Estadio José Zorrilla
+ (Valladolid)</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>27 618</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>20 338</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T361" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W361" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X361" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y361" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z361" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB361" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC361" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD361" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE361" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF361" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG361" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH361" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI361" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ361" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK361" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL361" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM361" t="inlineStr"/>
+      <c r="AN361" t="inlineStr"/>
+      <c r="AO361" t="inlineStr"/>
+      <c r="AP361" t="inlineStr"/>
+      <c r="AQ361" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="AR361" t="inlineStr">
+        <is>
+          <t>pezzolano paulo</t>
+        </is>
+      </c>
+      <c r="AS361" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="AT361" t="inlineStr">
+        <is>
+          <t>arrasate jagoba</t>
+        </is>
+      </c>
+      <c r="AU361" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV361" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW361" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX361" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY361" t="inlineStr"/>
+      <c r="AZ361" t="inlineStr"/>
+      <c r="BA361" t="inlineStr"/>
+      <c r="BB361" t="inlineStr"/>
+      <c r="BC361" t="inlineStr"/>
+      <c r="BD361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="inlineStr">
+        <is>
+          <t>n7g3az9D</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>28.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Lax Franco S.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Estadio La Rosaleda
+ (Málaga)</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>30 044</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>26 377</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr"/>
+      <c r="N362" t="inlineStr"/>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T362" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W362" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X362" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y362" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Z362" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB362" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC362" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD362" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE362" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF362" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG362" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH362" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI362" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ362" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AK362" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AL362" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM362" t="inlineStr"/>
+      <c r="AN362" t="inlineStr"/>
+      <c r="AO362" t="inlineStr"/>
+      <c r="AP362" t="inlineStr"/>
+      <c r="AQ362" t="inlineStr">
+        <is>
+          <t>tjXr7SAp</t>
+        </is>
+      </c>
+      <c r="AR362" t="inlineStr">
+        <is>
+          <t>garcia sergio</t>
+        </is>
+      </c>
+      <c r="AS362" t="inlineStr">
+        <is>
+          <t>zT9gi7i9</t>
+        </is>
+      </c>
+      <c r="AT362" t="inlineStr">
+        <is>
+          <t>sarabia eder</t>
+        </is>
+      </c>
+      <c r="AU362" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV362" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW362" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX362" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY362" t="inlineStr"/>
+      <c r="AZ362" t="inlineStr"/>
+      <c r="BA362" t="inlineStr"/>
+      <c r="BB362" t="inlineStr"/>
+      <c r="BC362" t="inlineStr"/>
+      <c r="BD362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="inlineStr">
+        <is>
+          <t>SteFA0HE</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>28.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Moreno A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Estadio El Molinón
+ (Gijón)</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>29 029</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>22 426</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>Gijon</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr"/>
+      <c r="N363" t="inlineStr"/>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T363" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W363" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X363" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y363" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z363" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB363" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC363" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD363" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE363" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF363" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AG363" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH363" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI363" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ363" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK363" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL363" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM363" t="inlineStr"/>
+      <c r="AN363" t="inlineStr"/>
+      <c r="AO363" t="inlineStr"/>
+      <c r="AP363" t="inlineStr"/>
+      <c r="AQ363" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="AR363" t="inlineStr">
+        <is>
+          <t>albes ruben</t>
+        </is>
+      </c>
+      <c r="AS363" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="AT363" t="inlineStr">
+        <is>
+          <t>fernandez braulio victor</t>
+        </is>
+      </c>
+      <c r="AU363" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV363" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW363" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX363" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY363" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="BA363" t="inlineStr"/>
+      <c r="BB363" t="inlineStr"/>
+      <c r="BC363" t="inlineStr"/>
+      <c r="BD363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>bB6CjuQr</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>28.09.2024 11:15</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>De La Fuente Ramos O.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Mirandilla
+ (Cadiz)</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>20 776</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>15 315</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>Cadiz CF</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>Eldense</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr"/>
+      <c r="N364" t="inlineStr"/>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W364" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X364" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y364" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z364" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB364" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC364" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD364" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE364" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF364" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG364" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH364" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI364" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AJ364" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK364" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL364" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM364" t="inlineStr"/>
+      <c r="AN364" t="inlineStr"/>
+      <c r="AO364" t="inlineStr"/>
+      <c r="AP364" t="inlineStr"/>
+      <c r="AQ364" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="AR364" t="inlineStr">
+        <is>
+          <t>lopez paco</t>
+        </is>
+      </c>
+      <c r="AS364" t="inlineStr">
+        <is>
+          <t>hh4xt2Df</t>
+        </is>
+      </c>
+      <c r="AT364" t="inlineStr">
+        <is>
+          <t>ponz daniel</t>
+        </is>
+      </c>
+      <c r="AU364" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV364" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW364" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX364" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY364" t="inlineStr"/>
+      <c r="AZ364" t="inlineStr"/>
+      <c r="BA364" t="inlineStr"/>
+      <c r="BB364" t="inlineStr"/>
+      <c r="BC364" t="inlineStr"/>
+      <c r="BD364" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="1" t="inlineStr">
+        <is>
+          <t>CnAE6iGt</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>28.09.2024 11:15</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Barrera R.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Anduva
+ (Miranda de Ebro)</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>5 759</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>3 193</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr"/>
+      <c r="N365" t="inlineStr"/>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T365" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W365" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X365" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y365" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z365" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB365" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC365" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD365" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE365" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF365" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AG365" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH365" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI365" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ365" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK365" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL365" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AM365" t="inlineStr"/>
+      <c r="AN365" t="inlineStr"/>
+      <c r="AO365" t="inlineStr"/>
+      <c r="AP365" t="inlineStr"/>
+      <c r="AQ365" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="AR365" t="inlineStr">
+        <is>
+          <t>lisci alessio</t>
+        </is>
+      </c>
+      <c r="AS365" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="AT365" t="inlineStr">
+        <is>
+          <t>hidalgo antonio</t>
+        </is>
+      </c>
+      <c r="AU365" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV365" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW365" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX365" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY365" t="inlineStr"/>
+      <c r="AZ365" t="inlineStr"/>
+      <c r="BA365" t="inlineStr"/>
+      <c r="BB365" t="inlineStr"/>
+      <c r="BC365" t="inlineStr"/>
+      <c r="BD365" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="1" t="inlineStr">
+        <is>
+          <t>6DRXcNX8</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>27.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Guzman Mansilla J. L.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Estadio Carlos Belmonte
+ (Albacete)</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>17 524</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>11 509</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>Dep. La Coruna</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr"/>
+      <c r="N366" t="inlineStr"/>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T366" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V366" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W366" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X366" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y366" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z366" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA366" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB366" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC366" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD366" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE366" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AF366" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG366" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH366" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI366" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ366" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK366" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL366" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM366" t="inlineStr"/>
+      <c r="AN366" t="inlineStr"/>
+      <c r="AO366" t="inlineStr"/>
+      <c r="AP366" t="inlineStr"/>
+      <c r="AQ366" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="AR366" t="inlineStr">
+        <is>
+          <t>gonzalez alberto</t>
+        </is>
+      </c>
+      <c r="AS366" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="AT366" t="inlineStr">
+        <is>
+          <t>idiakez imanol</t>
+        </is>
+      </c>
+      <c r="AU366" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV366" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW366" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX366" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY366" t="inlineStr"/>
+      <c r="AZ366" t="inlineStr"/>
+      <c r="BA366" t="inlineStr"/>
+      <c r="BB366" t="inlineStr"/>
+      <c r="BC366" t="inlineStr"/>
+      <c r="BD366" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD366"/>
+  <dimension ref="A1:BD375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69291,15 +69291,11 @@
           <t>22 322</t>
         </is>
       </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H357" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G357" t="n">
+        <v>4</v>
+      </c>
+      <c r="H357" t="n">
+        <v>2</v>
       </c>
       <c r="I357" t="inlineStr">
         <is>
@@ -69321,15 +69317,11 @@
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="M357" t="inlineStr">
-        <is>
-          <t>2.81</t>
-        </is>
-      </c>
-      <c r="N357" t="inlineStr">
-        <is>
-          <t>1.93</t>
-        </is>
+      <c r="M357" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="N357" t="n">
+        <v>1.93</v>
       </c>
       <c r="O357" t="inlineStr">
         <is>
@@ -69341,115 +69333,71 @@
           <t>75%</t>
         </is>
       </c>
-      <c r="Q357" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R357" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S357" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T357" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U357" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V357" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W357" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X357" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y357" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Z357" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AA357" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB357" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AC357" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AD357" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE357" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AF357" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AG357" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH357" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI357" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ357" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AK357" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL357" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q357" t="n">
+        <v>11</v>
+      </c>
+      <c r="R357" t="n">
+        <v>12</v>
+      </c>
+      <c r="S357" t="n">
+        <v>6</v>
+      </c>
+      <c r="T357" t="n">
+        <v>5</v>
+      </c>
+      <c r="U357" t="n">
+        <v>3</v>
+      </c>
+      <c r="V357" t="n">
+        <v>6</v>
+      </c>
+      <c r="W357" t="n">
+        <v>2</v>
+      </c>
+      <c r="X357" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y357" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z357" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA357" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB357" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC357" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD357" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE357" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF357" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG357" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH357" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI357" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ357" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK357" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL357" t="n">
+        <v>2</v>
       </c>
       <c r="AM357" t="inlineStr"/>
       <c r="AN357" t="inlineStr"/>
@@ -69529,15 +69477,11 @@
           <t>32 332</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H358" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G358" t="n">
+        <v>3</v>
+      </c>
+      <c r="H358" t="n">
+        <v>0</v>
       </c>
       <c r="I358" t="inlineStr">
         <is>
@@ -69559,15 +69503,11 @@
           <t>Valencia</t>
         </is>
       </c>
-      <c r="M358" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="N358" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
+      <c r="M358" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="N358" t="n">
+        <v>0.41</v>
       </c>
       <c r="O358" t="inlineStr">
         <is>
@@ -69579,105 +69519,65 @@
           <t>39%</t>
         </is>
       </c>
-      <c r="Q358" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R358" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S358" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T358" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U358" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V358" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W358" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X358" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y358" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z358" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA358" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB358" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC358" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD358" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE358" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AF358" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AG358" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH358" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI358" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AJ358" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="Q358" t="n">
+        <v>11</v>
+      </c>
+      <c r="R358" t="n">
+        <v>9</v>
+      </c>
+      <c r="S358" t="n">
+        <v>6</v>
+      </c>
+      <c r="T358" t="n">
+        <v>4</v>
+      </c>
+      <c r="U358" t="n">
+        <v>3</v>
+      </c>
+      <c r="V358" t="n">
+        <v>3</v>
+      </c>
+      <c r="W358" t="n">
+        <v>2</v>
+      </c>
+      <c r="X358" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y358" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z358" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA358" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB358" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC358" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD358" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE358" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF358" t="n">
+        <v>33</v>
+      </c>
+      <c r="AG358" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH358" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI358" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ358" t="n">
+        <v>12</v>
       </c>
       <c r="AK358" t="inlineStr"/>
       <c r="AL358" t="inlineStr"/>
@@ -69759,15 +69659,11 @@
           <t>13 186</t>
         </is>
       </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H359" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G359" t="n">
+        <v>1</v>
+      </c>
+      <c r="H359" t="n">
+        <v>1</v>
       </c>
       <c r="I359" t="inlineStr">
         <is>
@@ -69789,15 +69685,11 @@
           <t>Leganes</t>
         </is>
       </c>
-      <c r="M359" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
-      </c>
-      <c r="N359" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
+      <c r="M359" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="N359" t="n">
+        <v>0.5600000000000001</v>
       </c>
       <c r="O359" t="inlineStr">
         <is>
@@ -69809,115 +69701,71 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q359" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R359" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S359" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T359" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U359" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V359" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W359" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X359" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y359" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Z359" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA359" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB359" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC359" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD359" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE359" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AF359" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG359" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH359" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI359" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ359" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AK359" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL359" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q359" t="n">
+        <v>15</v>
+      </c>
+      <c r="R359" t="n">
+        <v>13</v>
+      </c>
+      <c r="S359" t="n">
+        <v>6</v>
+      </c>
+      <c r="T359" t="n">
+        <v>3</v>
+      </c>
+      <c r="U359" t="n">
+        <v>5</v>
+      </c>
+      <c r="V359" t="n">
+        <v>6</v>
+      </c>
+      <c r="W359" t="n">
+        <v>4</v>
+      </c>
+      <c r="X359" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y359" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z359" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA359" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB359" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC359" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD359" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE359" t="n">
+        <v>31</v>
+      </c>
+      <c r="AF359" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG359" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH359" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI359" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ359" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK359" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL359" t="n">
+        <v>1</v>
       </c>
       <c r="AM359" t="inlineStr"/>
       <c r="AN359" t="inlineStr"/>
@@ -69997,15 +69845,11 @@
           <t>10 006</t>
         </is>
       </c>
-      <c r="G360" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H360" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G360" t="n">
+        <v>2</v>
+      </c>
+      <c r="H360" t="n">
+        <v>0</v>
       </c>
       <c r="I360" t="inlineStr">
         <is>
@@ -70027,15 +69871,11 @@
           <t>Alaves</t>
         </is>
       </c>
-      <c r="M360" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="N360" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
+      <c r="M360" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="N360" t="n">
+        <v>0.51</v>
       </c>
       <c r="O360" t="inlineStr">
         <is>
@@ -70047,115 +69887,71 @@
           <t>55%</t>
         </is>
       </c>
-      <c r="Q360" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R360" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S360" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T360" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U360" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V360" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W360" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X360" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y360" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="Z360" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AA360" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB360" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC360" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD360" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE360" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="AF360" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AG360" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH360" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI360" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AJ360" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AK360" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL360" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Q360" t="n">
+        <v>14</v>
+      </c>
+      <c r="R360" t="n">
+        <v>9</v>
+      </c>
+      <c r="S360" t="n">
+        <v>8</v>
+      </c>
+      <c r="T360" t="n">
+        <v>1</v>
+      </c>
+      <c r="U360" t="n">
+        <v>3</v>
+      </c>
+      <c r="V360" t="n">
+        <v>5</v>
+      </c>
+      <c r="W360" t="n">
+        <v>3</v>
+      </c>
+      <c r="X360" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y360" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z360" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA360" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB360" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC360" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD360" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE360" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF360" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG360" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH360" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI360" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ360" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK360" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL360" t="n">
+        <v>6</v>
       </c>
       <c r="AM360" t="inlineStr"/>
       <c r="AN360" t="inlineStr"/>
@@ -70235,15 +70031,11 @@
           <t>20 338</t>
         </is>
       </c>
-      <c r="G361" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H361" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G361" t="n">
+        <v>1</v>
+      </c>
+      <c r="H361" t="n">
+        <v>2</v>
       </c>
       <c r="I361" t="inlineStr">
         <is>
@@ -70265,15 +70057,11 @@
           <t>Mallorca</t>
         </is>
       </c>
-      <c r="M361" t="inlineStr">
-        <is>
-          <t>0.68</t>
-        </is>
-      </c>
-      <c r="N361" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
+      <c r="M361" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="N361" t="n">
+        <v>1.82</v>
       </c>
       <c r="O361" t="inlineStr">
         <is>
@@ -70285,115 +70073,71 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="Q361" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R361" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="S361" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T361" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U361" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V361" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W361" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X361" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y361" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z361" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AA361" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB361" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC361" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD361" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE361" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF361" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AG361" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH361" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI361" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ361" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK361" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL361" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q361" t="n">
+        <v>13</v>
+      </c>
+      <c r="R361" t="n">
+        <v>17</v>
+      </c>
+      <c r="S361" t="n">
+        <v>1</v>
+      </c>
+      <c r="T361" t="n">
+        <v>6</v>
+      </c>
+      <c r="U361" t="n">
+        <v>10</v>
+      </c>
+      <c r="V361" t="n">
+        <v>8</v>
+      </c>
+      <c r="W361" t="n">
+        <v>2</v>
+      </c>
+      <c r="X361" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y361" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z361" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA361" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB361" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC361" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD361" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE361" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF361" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG361" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH361" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI361" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ361" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK361" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL361" t="n">
+        <v>2</v>
       </c>
       <c r="AM361" t="inlineStr"/>
       <c r="AN361" t="inlineStr"/>
@@ -70473,15 +70217,11 @@
           <t>26 377</t>
         </is>
       </c>
-      <c r="G362" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H362" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G362" t="n">
+        <v>0</v>
+      </c>
+      <c r="H362" t="n">
+        <v>3</v>
       </c>
       <c r="I362" t="inlineStr">
         <is>
@@ -70515,115 +70255,71 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q362" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R362" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S362" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T362" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U362" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V362" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W362" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X362" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y362" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="Z362" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AA362" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB362" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC362" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD362" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE362" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF362" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG362" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH362" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI362" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ362" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AK362" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AL362" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q362" t="n">
+        <v>5</v>
+      </c>
+      <c r="R362" t="n">
+        <v>14</v>
+      </c>
+      <c r="S362" t="n">
+        <v>0</v>
+      </c>
+      <c r="T362" t="n">
+        <v>8</v>
+      </c>
+      <c r="U362" t="n">
+        <v>3</v>
+      </c>
+      <c r="V362" t="n">
+        <v>2</v>
+      </c>
+      <c r="W362" t="n">
+        <v>2</v>
+      </c>
+      <c r="X362" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y362" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z362" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA362" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB362" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC362" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD362" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE362" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF362" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG362" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH362" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI362" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ362" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK362" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL362" t="n">
+        <v>4</v>
       </c>
       <c r="AM362" t="inlineStr"/>
       <c r="AN362" t="inlineStr"/>
@@ -70703,15 +70399,11 @@
           <t>22 426</t>
         </is>
       </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H363" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G363" t="n">
+        <v>1</v>
+      </c>
+      <c r="H363" t="n">
+        <v>0</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
@@ -70745,115 +70437,71 @@
           <t>38%</t>
         </is>
       </c>
-      <c r="Q363" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R363" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S363" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T363" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U363" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V363" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W363" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X363" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y363" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z363" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA363" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB363" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC363" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD363" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE363" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AF363" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AG363" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH363" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI363" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AJ363" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK363" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL363" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q363" t="n">
+        <v>22</v>
+      </c>
+      <c r="R363" t="n">
+        <v>7</v>
+      </c>
+      <c r="S363" t="n">
+        <v>8</v>
+      </c>
+      <c r="T363" t="n">
+        <v>2</v>
+      </c>
+      <c r="U363" t="n">
+        <v>11</v>
+      </c>
+      <c r="V363" t="n">
+        <v>5</v>
+      </c>
+      <c r="W363" t="n">
+        <v>3</v>
+      </c>
+      <c r="X363" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y363" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z363" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA363" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB363" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC363" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD363" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE363" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF363" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG363" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH363" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI363" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ363" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK363" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL363" t="n">
+        <v>5</v>
       </c>
       <c r="AM363" t="inlineStr"/>
       <c r="AN363" t="inlineStr"/>
@@ -70893,15 +70541,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AY363" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ363" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AY363" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ363" t="n">
+        <v>2</v>
       </c>
       <c r="BA363" t="inlineStr"/>
       <c r="BB363" t="inlineStr"/>
@@ -70941,15 +70585,11 @@
           <t>15 315</t>
         </is>
       </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H364" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G364" t="n">
+        <v>1</v>
+      </c>
+      <c r="H364" t="n">
+        <v>2</v>
       </c>
       <c r="I364" t="inlineStr">
         <is>
@@ -70983,115 +70623,71 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q364" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R364" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S364" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T364" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U364" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V364" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W364" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X364" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y364" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Z364" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AA364" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB364" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC364" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD364" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE364" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF364" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG364" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH364" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI364" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AJ364" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK364" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL364" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q364" t="n">
+        <v>23</v>
+      </c>
+      <c r="R364" t="n">
+        <v>15</v>
+      </c>
+      <c r="S364" t="n">
+        <v>7</v>
+      </c>
+      <c r="T364" t="n">
+        <v>6</v>
+      </c>
+      <c r="U364" t="n">
+        <v>9</v>
+      </c>
+      <c r="V364" t="n">
+        <v>5</v>
+      </c>
+      <c r="W364" t="n">
+        <v>7</v>
+      </c>
+      <c r="X364" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y364" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z364" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA364" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB364" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC364" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD364" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE364" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF364" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG364" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH364" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI364" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ364" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK364" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL364" t="n">
+        <v>5</v>
       </c>
       <c r="AM364" t="inlineStr"/>
       <c r="AN364" t="inlineStr"/>
@@ -71171,15 +70767,11 @@
           <t>3 193</t>
         </is>
       </c>
-      <c r="G365" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H365" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G365" t="n">
+        <v>1</v>
+      </c>
+      <c r="H365" t="n">
+        <v>0</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
@@ -71213,115 +70805,71 @@
           <t>56%</t>
         </is>
       </c>
-      <c r="Q365" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R365" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S365" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T365" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U365" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V365" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W365" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X365" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y365" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z365" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AA365" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB365" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC365" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD365" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE365" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AF365" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AG365" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH365" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI365" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AJ365" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK365" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL365" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Q365" t="n">
+        <v>16</v>
+      </c>
+      <c r="R365" t="n">
+        <v>6</v>
+      </c>
+      <c r="S365" t="n">
+        <v>2</v>
+      </c>
+      <c r="T365" t="n">
+        <v>1</v>
+      </c>
+      <c r="U365" t="n">
+        <v>7</v>
+      </c>
+      <c r="V365" t="n">
+        <v>3</v>
+      </c>
+      <c r="W365" t="n">
+        <v>7</v>
+      </c>
+      <c r="X365" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y365" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z365" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA365" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB365" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC365" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD365" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE365" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF365" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG365" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH365" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI365" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ365" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK365" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL365" t="n">
+        <v>6</v>
       </c>
       <c r="AM365" t="inlineStr"/>
       <c r="AN365" t="inlineStr"/>
@@ -71401,15 +70949,11 @@
           <t>11 509</t>
         </is>
       </c>
-      <c r="G366" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H366" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="G366" t="n">
+        <v>2</v>
+      </c>
+      <c r="H366" t="n">
+        <v>5</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
@@ -71443,115 +70987,71 @@
           <t>43%</t>
         </is>
       </c>
-      <c r="Q366" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R366" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S366" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T366" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U366" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V366" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W366" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X366" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y366" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z366" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA366" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AB366" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC366" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD366" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE366" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AF366" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG366" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH366" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI366" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ366" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AK366" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL366" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q366" t="n">
+        <v>20</v>
+      </c>
+      <c r="R366" t="n">
+        <v>14</v>
+      </c>
+      <c r="S366" t="n">
+        <v>7</v>
+      </c>
+      <c r="T366" t="n">
+        <v>7</v>
+      </c>
+      <c r="U366" t="n">
+        <v>9</v>
+      </c>
+      <c r="V366" t="n">
+        <v>4</v>
+      </c>
+      <c r="W366" t="n">
+        <v>4</v>
+      </c>
+      <c r="X366" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y366" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z366" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA366" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB366" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC366" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD366" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE366" t="n">
+        <v>31</v>
+      </c>
+      <c r="AF366" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG366" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH366" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI366" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ366" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK366" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL366" t="n">
+        <v>2</v>
       </c>
       <c r="AM366" t="inlineStr"/>
       <c r="AN366" t="inlineStr"/>
@@ -71598,6 +71098,2132 @@
       <c r="BC366" t="inlineStr"/>
       <c r="BD366" t="inlineStr"/>
     </row>
+    <row r="367">
+      <c r="A367" s="1" t="inlineStr">
+        <is>
+          <t>n37VJZT0</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>29.09.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Busquets Ferrer M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Metropolitano Stadium
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>70 460</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>70 112</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W367" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X367" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y367" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z367" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA367" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB367" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC367" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD367" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE367" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF367" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AG367" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH367" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI367" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ367" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK367" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL367" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM367" t="inlineStr"/>
+      <c r="AN367" t="inlineStr"/>
+      <c r="AO367" t="inlineStr"/>
+      <c r="AP367" t="inlineStr"/>
+      <c r="AQ367" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="AR367" t="inlineStr">
+        <is>
+          <t>simeone diego</t>
+        </is>
+      </c>
+      <c r="AS367" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="AT367" t="inlineStr">
+        <is>
+          <t>ancelotti carlo</t>
+        </is>
+      </c>
+      <c r="AU367" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV367" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW367" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX367" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY367" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BA367" t="inlineStr"/>
+      <c r="BB367" t="inlineStr"/>
+      <c r="BC367" t="inlineStr"/>
+      <c r="BD367" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="1" t="inlineStr">
+        <is>
+          <t>4rQsoH7m</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>29.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Hernandez A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Estadio Benito Villamarín
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>60 721</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>53 065</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>0.44</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V368" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W368" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X368" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y368" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Z368" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB368" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC368" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD368" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE368" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF368" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG368" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH368" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI368" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ368" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AK368" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL368" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM368" t="inlineStr"/>
+      <c r="AN368" t="inlineStr"/>
+      <c r="AO368" t="inlineStr"/>
+      <c r="AP368" t="inlineStr"/>
+      <c r="AQ368" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="AR368" t="inlineStr">
+        <is>
+          <t>pellegrini manuel</t>
+        </is>
+      </c>
+      <c r="AS368" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="AT368" t="inlineStr">
+        <is>
+          <t>gonzalez manolo</t>
+        </is>
+      </c>
+      <c r="AU368" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV368" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW368" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX368" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY368" t="inlineStr"/>
+      <c r="AZ368" t="inlineStr"/>
+      <c r="BA368" t="inlineStr"/>
+      <c r="BB368" t="inlineStr"/>
+      <c r="BC368" t="inlineStr"/>
+      <c r="BD368" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="1" t="inlineStr">
+        <is>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>29.09.2024 11:15</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Grado C. S.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Estadio San Mamés
+ (Bilbao)</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>53 331</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>48 288</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W369" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X369" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y369" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z369" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA369" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB369" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC369" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD369" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE369" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF369" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG369" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH369" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI369" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ369" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK369" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL369" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM369" t="inlineStr"/>
+      <c r="AN369" t="inlineStr"/>
+      <c r="AO369" t="inlineStr"/>
+      <c r="AP369" t="inlineStr"/>
+      <c r="AQ369" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="AR369" t="inlineStr">
+        <is>
+          <t>valverde tejedor ernesto</t>
+        </is>
+      </c>
+      <c r="AS369" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="AT369" t="inlineStr">
+        <is>
+          <t>pimienta francisco</t>
+        </is>
+      </c>
+      <c r="AU369" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV369" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW369" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX369" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY369" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BA369" t="inlineStr"/>
+      <c r="BB369" t="inlineStr"/>
+      <c r="BC369" t="inlineStr"/>
+      <c r="BD369" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="1" t="inlineStr">
+        <is>
+          <t>h0AwIDbD</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>29.09.2024 09:00</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Bengoetxea R.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Estadio de Balaídos
+ (Vigo)</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>24 791</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>21 347</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T370" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U370" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V370" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W370" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X370" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y370" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z370" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA370" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB370" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC370" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD370" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE370" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF370" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG370" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH370" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI370" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ370" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK370" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL370" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM370" t="inlineStr"/>
+      <c r="AN370" t="inlineStr"/>
+      <c r="AO370" t="inlineStr"/>
+      <c r="AP370" t="inlineStr"/>
+      <c r="AQ370" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="AR370" t="inlineStr">
+        <is>
+          <t>giraldez claudio</t>
+        </is>
+      </c>
+      <c r="AS370" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="AT370" t="inlineStr">
+        <is>
+          <t>michel</t>
+        </is>
+      </c>
+      <c r="AU370" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV370" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW370" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX370" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY370" t="inlineStr"/>
+      <c r="AZ370" t="inlineStr"/>
+      <c r="BA370" t="inlineStr"/>
+      <c r="BB370" t="inlineStr"/>
+      <c r="BC370" t="inlineStr"/>
+      <c r="BD370" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="1" t="inlineStr">
+        <is>
+          <t>noISncP7</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>29.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Cid Camacho G.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Arcángel
+ (Córdoba)</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>21 822</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>16 130</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>Cordoba</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>Racing Club Ferrol</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr"/>
+      <c r="N371" t="inlineStr"/>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T371" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V371" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W371" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X371" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y371" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Z371" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AA371" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB371" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC371" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD371" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE371" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF371" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG371" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH371" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI371" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AJ371" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK371" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL371" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM371" t="inlineStr"/>
+      <c r="AN371" t="inlineStr"/>
+      <c r="AO371" t="inlineStr"/>
+      <c r="AP371" t="inlineStr"/>
+      <c r="AQ371" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="AR371" t="inlineStr">
+        <is>
+          <t>ania ivan</t>
+        </is>
+      </c>
+      <c r="AS371" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="AT371" t="inlineStr">
+        <is>
+          <t>parralo cristobal</t>
+        </is>
+      </c>
+      <c r="AU371" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV371" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW371" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX371" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY371" t="inlineStr"/>
+      <c r="AZ371" t="inlineStr"/>
+      <c r="BA371" t="inlineStr"/>
+      <c r="BB371" t="inlineStr"/>
+      <c r="BC371" t="inlineStr"/>
+      <c r="BD371" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="inlineStr">
+        <is>
+          <t>S4w21dv1</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>29.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Sanchez Lopez R.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Carlos Tartiere
+ (Oviedo)</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>30 500</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>19 281</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>R. Oviedo</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>Eibar</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr"/>
+      <c r="N372" t="inlineStr"/>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T372" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V372" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W372" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X372" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y372" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z372" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA372" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB372" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC372" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD372" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE372" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF372" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AG372" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH372" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI372" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ372" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK372" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL372" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM372" t="inlineStr"/>
+      <c r="AN372" t="inlineStr"/>
+      <c r="AO372" t="inlineStr"/>
+      <c r="AP372" t="inlineStr"/>
+      <c r="AQ372" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="AR372" t="inlineStr">
+        <is>
+          <t>calleja javier</t>
+        </is>
+      </c>
+      <c r="AS372" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="AT372" t="inlineStr">
+        <is>
+          <t>etxeberria joseba</t>
+        </is>
+      </c>
+      <c r="AU372" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV372" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW372" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX372" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY372" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ372" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BA372" t="inlineStr"/>
+      <c r="BB372" t="inlineStr"/>
+      <c r="BC372" t="inlineStr"/>
+      <c r="BD372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2uLtd12L</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>29.09.2024 11:15</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Reig S. A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Estadio El Plantío
+ (Burgos)</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>12 194</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>9 890</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>Burgos CF</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>Granada CF</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr"/>
+      <c r="N373" t="inlineStr"/>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T373" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V373" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W373" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X373" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y373" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z373" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AA373" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB373" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC373" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD373" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE373" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF373" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AG373" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH373" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI373" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ373" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK373" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL373" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AM373" t="inlineStr"/>
+      <c r="AN373" t="inlineStr"/>
+      <c r="AO373" t="inlineStr"/>
+      <c r="AP373" t="inlineStr"/>
+      <c r="AQ373" t="inlineStr">
+        <is>
+          <t>l6JQtDqc</t>
+        </is>
+      </c>
+      <c r="AR373" t="inlineStr">
+        <is>
+          <t>bolo</t>
+        </is>
+      </c>
+      <c r="AS373" t="inlineStr">
+        <is>
+          <t>K0UZov8F</t>
+        </is>
+      </c>
+      <c r="AT373" t="inlineStr">
+        <is>
+          <t>escriba fran</t>
+        </is>
+      </c>
+      <c r="AU373" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV373" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW373" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX373" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY373" t="inlineStr"/>
+      <c r="AZ373" t="inlineStr"/>
+      <c r="BA373" t="inlineStr"/>
+      <c r="BB373" t="inlineStr"/>
+      <c r="BC373" t="inlineStr"/>
+      <c r="BD373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>fw0LlJfe</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>29.09.2024 11:15</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Mallo E.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Castalia
+ (Castellón de la Plana)</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>15 500</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>11 439</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>Castellon</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>Tenerife</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr"/>
+      <c r="N374" t="inlineStr"/>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T374" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V374" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W374" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X374" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y374" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z374" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB374" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC374" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD374" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE374" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AF374" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG374" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH374" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI374" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ374" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK374" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL374" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM374" t="inlineStr"/>
+      <c r="AN374" t="inlineStr"/>
+      <c r="AO374" t="inlineStr"/>
+      <c r="AP374" t="inlineStr"/>
+      <c r="AQ374" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="AR374" t="inlineStr">
+        <is>
+          <t>schreuder dick</t>
+        </is>
+      </c>
+      <c r="AS374" t="inlineStr">
+        <is>
+          <t>CYND5rZG</t>
+        </is>
+      </c>
+      <c r="AT374" t="inlineStr">
+        <is>
+          <t>mel pepe</t>
+        </is>
+      </c>
+      <c r="AU374" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV374" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW374" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX374" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY374" t="inlineStr"/>
+      <c r="AZ374" t="inlineStr"/>
+      <c r="BA374" t="inlineStr"/>
+      <c r="BB374" t="inlineStr"/>
+      <c r="BC374" t="inlineStr"/>
+      <c r="BD374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>z7bN8vnR</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>29.09.2024 09:00</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Gonzalez Esteban J. A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Estadi Ciutat de València
+ (Valencia)</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>26 354</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>14 528</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>Almeria</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr"/>
+      <c r="N375" t="inlineStr"/>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V375" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W375" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X375" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y375" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z375" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB375" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC375" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD375" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE375" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF375" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG375" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH375" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI375" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ375" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK375" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL375" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM375" t="inlineStr"/>
+      <c r="AN375" t="inlineStr"/>
+      <c r="AO375" t="inlineStr"/>
+      <c r="AP375" t="inlineStr"/>
+      <c r="AQ375" t="inlineStr">
+        <is>
+          <t>fiZxGYJ3</t>
+        </is>
+      </c>
+      <c r="AR375" t="inlineStr">
+        <is>
+          <t>calero julian</t>
+        </is>
+      </c>
+      <c r="AS375" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="AT375" t="inlineStr">
+        <is>
+          <t>rubi joan</t>
+        </is>
+      </c>
+      <c r="AU375" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV375" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW375" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX375" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY375" t="inlineStr"/>
+      <c r="AZ375" t="inlineStr"/>
+      <c r="BA375" t="inlineStr"/>
+      <c r="BB375" t="inlineStr"/>
+      <c r="BC375" t="inlineStr"/>
+      <c r="BD375" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD398"/>
+  <dimension ref="A1:BD418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75232,15 +75232,11 @@
           <t>31 983</t>
         </is>
       </c>
-      <c r="G389" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H389" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G389" t="n">
+        <v>1</v>
+      </c>
+      <c r="H389" t="n">
+        <v>1</v>
       </c>
       <c r="I389" t="inlineStr">
         <is>
@@ -75262,15 +75258,11 @@
           <t>Atl. Madrid</t>
         </is>
       </c>
-      <c r="M389" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
-      </c>
-      <c r="N389" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
+      <c r="M389" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="N389" t="n">
+        <v>0.39</v>
       </c>
       <c r="O389" t="inlineStr">
         <is>
@@ -75282,115 +75274,71 @@
           <t>33%</t>
         </is>
       </c>
-      <c r="Q389" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R389" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S389" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T389" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U389" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V389" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W389" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X389" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y389" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z389" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA389" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB389" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC389" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD389" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE389" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF389" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AG389" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH389" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI389" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ389" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK389" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL389" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q389" t="n">
+        <v>16</v>
+      </c>
+      <c r="R389" t="n">
+        <v>4</v>
+      </c>
+      <c r="S389" t="n">
+        <v>7</v>
+      </c>
+      <c r="T389" t="n">
+        <v>1</v>
+      </c>
+      <c r="U389" t="n">
+        <v>9</v>
+      </c>
+      <c r="V389" t="n">
+        <v>3</v>
+      </c>
+      <c r="W389" t="n">
+        <v>0</v>
+      </c>
+      <c r="X389" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y389" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z389" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA389" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB389" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC389" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD389" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE389" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF389" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG389" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH389" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI389" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ389" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK389" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL389" t="n">
+        <v>2</v>
       </c>
       <c r="AM389" t="inlineStr">
         <is>
@@ -75470,15 +75418,11 @@
           <t>42 571</t>
         </is>
       </c>
-      <c r="G390" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H390" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G390" t="n">
+        <v>1</v>
+      </c>
+      <c r="H390" t="n">
+        <v>0</v>
       </c>
       <c r="I390" t="inlineStr">
         <is>
@@ -75500,15 +75444,11 @@
           <t>Betis</t>
         </is>
       </c>
-      <c r="M390" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="N390" t="inlineStr">
-        <is>
-          <t>0.79</t>
-        </is>
+      <c r="M390" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N390" t="n">
+        <v>0.79</v>
       </c>
       <c r="O390" t="inlineStr">
         <is>
@@ -75520,115 +75460,71 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q390" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R390" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S390" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T390" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U390" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V390" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W390" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X390" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y390" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z390" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AA390" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB390" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC390" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD390" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE390" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF390" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AG390" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH390" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI390" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ390" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK390" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AL390" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q390" t="n">
+        <v>14</v>
+      </c>
+      <c r="R390" t="n">
+        <v>11</v>
+      </c>
+      <c r="S390" t="n">
+        <v>5</v>
+      </c>
+      <c r="T390" t="n">
+        <v>3</v>
+      </c>
+      <c r="U390" t="n">
+        <v>5</v>
+      </c>
+      <c r="V390" t="n">
+        <v>7</v>
+      </c>
+      <c r="W390" t="n">
+        <v>4</v>
+      </c>
+      <c r="X390" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y390" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z390" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA390" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB390" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC390" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD390" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE390" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF390" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG390" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH390" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI390" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ390" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK390" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL390" t="n">
+        <v>3</v>
       </c>
       <c r="AM390" t="inlineStr">
         <is>
@@ -75664,15 +75560,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU390" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AV390" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AU390" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV390" t="n">
+        <v>0</v>
       </c>
       <c r="AW390" t="inlineStr"/>
       <c r="AX390" t="inlineStr"/>
@@ -75716,15 +75608,11 @@
           <t>19 468</t>
         </is>
       </c>
-      <c r="G391" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H391" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G391" t="n">
+        <v>0</v>
+      </c>
+      <c r="H391" t="n">
+        <v>3</v>
       </c>
       <c r="I391" t="inlineStr">
         <is>
@@ -75746,15 +75634,11 @@
           <t>Barcelona</t>
         </is>
       </c>
-      <c r="M391" t="inlineStr">
-        <is>
-          <t>0.83</t>
-        </is>
-      </c>
-      <c r="N391" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
+      <c r="M391" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N391" t="n">
+        <v>1.65</v>
       </c>
       <c r="O391" t="inlineStr">
         <is>
@@ -75766,115 +75650,71 @@
           <t>73%</t>
         </is>
       </c>
-      <c r="Q391" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R391" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S391" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T391" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="U391" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V391" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W391" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X391" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y391" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z391" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AA391" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AB391" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC391" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AD391" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE391" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF391" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG391" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH391" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI391" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ391" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AK391" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL391" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q391" t="n">
+        <v>11</v>
+      </c>
+      <c r="R391" t="n">
+        <v>15</v>
+      </c>
+      <c r="S391" t="n">
+        <v>2</v>
+      </c>
+      <c r="T391" t="n">
+        <v>9</v>
+      </c>
+      <c r="U391" t="n">
+        <v>5</v>
+      </c>
+      <c r="V391" t="n">
+        <v>4</v>
+      </c>
+      <c r="W391" t="n">
+        <v>4</v>
+      </c>
+      <c r="X391" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y391" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z391" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA391" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB391" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC391" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD391" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE391" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF391" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG391" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH391" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI391" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ391" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK391" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL391" t="n">
+        <v>2</v>
       </c>
       <c r="AM391" t="inlineStr">
         <is>
@@ -75954,15 +75794,11 @@
           <t>13 396</t>
         </is>
       </c>
-      <c r="G392" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H392" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G392" t="n">
+        <v>2</v>
+      </c>
+      <c r="H392" t="n">
+        <v>1</v>
       </c>
       <c r="I392" t="inlineStr">
         <is>
@@ -75984,15 +75820,11 @@
           <t>Ath Bilbao</t>
         </is>
       </c>
-      <c r="M392" t="inlineStr">
-        <is>
-          <t>2.29</t>
-        </is>
-      </c>
-      <c r="N392" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
+      <c r="M392" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="N392" t="n">
+        <v>2.34</v>
       </c>
       <c r="O392" t="inlineStr">
         <is>
@@ -76004,115 +75836,71 @@
           <t>34%</t>
         </is>
       </c>
-      <c r="Q392" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R392" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S392" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T392" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U392" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V392" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W392" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X392" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y392" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z392" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA392" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB392" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC392" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD392" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE392" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF392" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AG392" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH392" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI392" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ392" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK392" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL392" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q392" t="n">
+        <v>14</v>
+      </c>
+      <c r="R392" t="n">
+        <v>13</v>
+      </c>
+      <c r="S392" t="n">
+        <v>6</v>
+      </c>
+      <c r="T392" t="n">
+        <v>4</v>
+      </c>
+      <c r="U392" t="n">
+        <v>5</v>
+      </c>
+      <c r="V392" t="n">
+        <v>6</v>
+      </c>
+      <c r="W392" t="n">
+        <v>3</v>
+      </c>
+      <c r="X392" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y392" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z392" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA392" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB392" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC392" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD392" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE392" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF392" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG392" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH392" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI392" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ392" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK392" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL392" t="n">
+        <v>3</v>
       </c>
       <c r="AM392" t="inlineStr">
         <is>
@@ -76148,15 +75936,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU392" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV392" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AU392" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV392" t="n">
+        <v>1</v>
       </c>
       <c r="AW392" t="inlineStr"/>
       <c r="AX392" t="inlineStr"/>
@@ -76200,15 +75984,11 @@
           <t>73 842</t>
         </is>
       </c>
-      <c r="G393" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H393" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G393" t="n">
+        <v>2</v>
+      </c>
+      <c r="H393" t="n">
+        <v>0</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
@@ -76230,15 +76010,11 @@
           <t>Villarreal</t>
         </is>
       </c>
-      <c r="M393" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="N393" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
+      <c r="M393" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N393" t="n">
+        <v>0.51</v>
       </c>
       <c r="O393" t="inlineStr">
         <is>
@@ -76250,115 +76026,71 @@
           <t>45%</t>
         </is>
       </c>
-      <c r="Q393" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R393" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S393" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T393" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U393" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V393" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W393" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X393" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y393" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z393" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA393" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB393" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC393" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD393" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE393" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AF393" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG393" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH393" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI393" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AJ393" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK393" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL393" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q393" t="n">
+        <v>11</v>
+      </c>
+      <c r="R393" t="n">
+        <v>12</v>
+      </c>
+      <c r="S393" t="n">
+        <v>2</v>
+      </c>
+      <c r="T393" t="n">
+        <v>1</v>
+      </c>
+      <c r="U393" t="n">
+        <v>5</v>
+      </c>
+      <c r="V393" t="n">
+        <v>8</v>
+      </c>
+      <c r="W393" t="n">
+        <v>4</v>
+      </c>
+      <c r="X393" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y393" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z393" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA393" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB393" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC393" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD393" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE393" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF393" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG393" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH393" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI393" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ393" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK393" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL393" t="n">
+        <v>1</v>
       </c>
       <c r="AM393" t="inlineStr">
         <is>
@@ -76438,15 +76170,11 @@
           <t>9 327</t>
         </is>
       </c>
-      <c r="G394" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H394" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G394" t="n">
+        <v>1</v>
+      </c>
+      <c r="H394" t="n">
+        <v>1</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
@@ -76480,115 +76208,71 @@
           <t>61%</t>
         </is>
       </c>
-      <c r="Q394" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R394" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S394" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T394" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U394" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V394" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W394" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X394" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y394" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z394" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA394" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB394" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC394" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD394" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE394" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF394" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AG394" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH394" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI394" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AJ394" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK394" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL394" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q394" t="n">
+        <v>19</v>
+      </c>
+      <c r="R394" t="n">
+        <v>11</v>
+      </c>
+      <c r="S394" t="n">
+        <v>5</v>
+      </c>
+      <c r="T394" t="n">
+        <v>3</v>
+      </c>
+      <c r="U394" t="n">
+        <v>10</v>
+      </c>
+      <c r="V394" t="n">
+        <v>6</v>
+      </c>
+      <c r="W394" t="n">
+        <v>4</v>
+      </c>
+      <c r="X394" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y394" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z394" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA394" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB394" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC394" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD394" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE394" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF394" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG394" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH394" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI394" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ394" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK394" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL394" t="n">
+        <v>2</v>
       </c>
       <c r="AM394" t="inlineStr">
         <is>
@@ -76668,15 +76352,11 @@
           <t>15 406</t>
         </is>
       </c>
-      <c r="G395" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H395" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G395" t="n">
+        <v>0</v>
+      </c>
+      <c r="H395" t="n">
+        <v>0</v>
       </c>
       <c r="I395" t="inlineStr">
         <is>
@@ -76710,115 +76390,71 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="Q395" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R395" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S395" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T395" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U395" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V395" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W395" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X395" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y395" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Z395" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA395" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB395" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AC395" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD395" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE395" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AF395" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AG395" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH395" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI395" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ395" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AK395" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL395" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q395" t="n">
+        <v>8</v>
+      </c>
+      <c r="R395" t="n">
+        <v>12</v>
+      </c>
+      <c r="S395" t="n">
+        <v>1</v>
+      </c>
+      <c r="T395" t="n">
+        <v>1</v>
+      </c>
+      <c r="U395" t="n">
+        <v>4</v>
+      </c>
+      <c r="V395" t="n">
+        <v>4</v>
+      </c>
+      <c r="W395" t="n">
+        <v>3</v>
+      </c>
+      <c r="X395" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y395" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z395" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA395" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB395" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC395" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD395" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE395" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF395" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG395" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH395" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI395" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ395" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK395" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL395" t="n">
+        <v>3</v>
       </c>
       <c r="AM395" t="inlineStr">
         <is>
@@ -76898,15 +76534,11 @@
           <t>5 167</t>
         </is>
       </c>
-      <c r="G396" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H396" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G396" t="n">
+        <v>2</v>
+      </c>
+      <c r="H396" t="n">
+        <v>3</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>
@@ -76940,115 +76572,71 @@
           <t>55%</t>
         </is>
       </c>
-      <c r="Q396" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R396" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S396" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T396" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U396" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V396" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W396" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X396" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y396" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Z396" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA396" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AB396" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC396" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD396" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AE396" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="AF396" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AG396" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH396" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI396" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ396" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK396" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL396" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q396" t="n">
+        <v>14</v>
+      </c>
+      <c r="R396" t="n">
+        <v>13</v>
+      </c>
+      <c r="S396" t="n">
+        <v>6</v>
+      </c>
+      <c r="T396" t="n">
+        <v>6</v>
+      </c>
+      <c r="U396" t="n">
+        <v>5</v>
+      </c>
+      <c r="V396" t="n">
+        <v>5</v>
+      </c>
+      <c r="W396" t="n">
+        <v>3</v>
+      </c>
+      <c r="X396" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y396" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z396" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA396" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB396" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC396" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD396" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE396" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF396" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG396" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH396" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI396" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ396" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK396" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL396" t="n">
+        <v>1</v>
       </c>
       <c r="AM396" t="inlineStr">
         <is>
@@ -77128,15 +76716,11 @@
           <t>21 346</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H397" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G397" t="n">
+        <v>0</v>
+      </c>
+      <c r="H397" t="n">
+        <v>0</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
@@ -77170,115 +76754,71 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q397" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R397" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S397" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T397" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U397" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V397" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W397" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X397" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y397" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Z397" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA397" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB397" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC397" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD397" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE397" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AF397" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG397" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH397" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI397" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ397" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AK397" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL397" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q397" t="n">
+        <v>22</v>
+      </c>
+      <c r="R397" t="n">
+        <v>13</v>
+      </c>
+      <c r="S397" t="n">
+        <v>6</v>
+      </c>
+      <c r="T397" t="n">
+        <v>5</v>
+      </c>
+      <c r="U397" t="n">
+        <v>9</v>
+      </c>
+      <c r="V397" t="n">
+        <v>6</v>
+      </c>
+      <c r="W397" t="n">
+        <v>7</v>
+      </c>
+      <c r="X397" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y397" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z397" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA397" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB397" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC397" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD397" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE397" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF397" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG397" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH397" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI397" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ397" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK397" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL397" t="n">
+        <v>1</v>
       </c>
       <c r="AM397" t="inlineStr">
         <is>
@@ -77358,15 +76898,11 @@
           <t>13 590</t>
         </is>
       </c>
-      <c r="G398" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H398" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G398" t="n">
+        <v>2</v>
+      </c>
+      <c r="H398" t="n">
+        <v>0</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
@@ -77400,115 +76936,71 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q398" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R398" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="S398" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T398" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U398" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V398" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W398" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X398" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y398" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z398" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AA398" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB398" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC398" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD398" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE398" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF398" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AG398" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH398" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI398" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AJ398" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK398" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL398" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q398" t="n">
+        <v>19</v>
+      </c>
+      <c r="R398" t="n">
+        <v>4</v>
+      </c>
+      <c r="S398" t="n">
+        <v>5</v>
+      </c>
+      <c r="T398" t="n">
+        <v>3</v>
+      </c>
+      <c r="U398" t="n">
+        <v>9</v>
+      </c>
+      <c r="V398" t="n">
+        <v>1</v>
+      </c>
+      <c r="W398" t="n">
+        <v>5</v>
+      </c>
+      <c r="X398" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y398" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z398" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA398" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB398" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC398" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD398" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE398" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF398" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG398" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH398" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI398" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ398" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK398" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL398" t="n">
+        <v>1</v>
       </c>
       <c r="AM398" t="inlineStr">
         <is>
@@ -77555,6 +77047,3340 @@
       <c r="BC398" t="inlineStr"/>
       <c r="BD398" t="inlineStr"/>
     </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>4Id1wB8F</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>13.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Barrera R.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Estadio Manuel Martínez Valero
+ (Elche)</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>31 388</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>15 810</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>Dep. La Coruna</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr"/>
+      <c r="N399" t="inlineStr"/>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T399" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U399" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V399" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W399" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X399" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y399" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Z399" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA399" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB399" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC399" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD399" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE399" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF399" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG399" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH399" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI399" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ399" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AK399" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL399" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM399" t="inlineStr">
+        <is>
+          <t>zT9gi7i9</t>
+        </is>
+      </c>
+      <c r="AN399" t="inlineStr">
+        <is>
+          <t>sarabia eder</t>
+        </is>
+      </c>
+      <c r="AO399" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="AP399" t="inlineStr">
+        <is>
+          <t>idiakez imanol</t>
+        </is>
+      </c>
+      <c r="AQ399" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR399" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS399" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT399" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU399" t="inlineStr"/>
+      <c r="AV399" t="inlineStr"/>
+      <c r="AW399" t="inlineStr"/>
+      <c r="AX399" t="inlineStr"/>
+      <c r="AY399" t="inlineStr"/>
+      <c r="AZ399" t="inlineStr"/>
+      <c r="BA399" t="inlineStr"/>
+      <c r="BB399" t="inlineStr"/>
+      <c r="BC399" t="inlineStr"/>
+      <c r="BD399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>2FgfSPrH</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>13.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Palencia Caballero D.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Estadio El Plantío
+ (Burgos)</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>12 194</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>11 300</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>Burgos CF</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr"/>
+      <c r="N400" t="inlineStr"/>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R400" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T400" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U400" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V400" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W400" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X400" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y400" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z400" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA400" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB400" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC400" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD400" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE400" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AF400" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG400" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH400" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI400" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ400" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK400" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AL400" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM400" t="inlineStr">
+        <is>
+          <t>l6JQtDqc</t>
+        </is>
+      </c>
+      <c r="AN400" t="inlineStr">
+        <is>
+          <t>bolo</t>
+        </is>
+      </c>
+      <c r="AO400" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="AP400" t="inlineStr">
+        <is>
+          <t>lisci alessio</t>
+        </is>
+      </c>
+      <c r="AQ400" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR400" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS400" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT400" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU400" t="inlineStr"/>
+      <c r="AV400" t="inlineStr"/>
+      <c r="AW400" t="inlineStr"/>
+      <c r="AX400" t="inlineStr"/>
+      <c r="AY400" t="inlineStr"/>
+      <c r="AZ400" t="inlineStr"/>
+      <c r="BA400" t="inlineStr"/>
+      <c r="BB400" t="inlineStr"/>
+      <c r="BC400" t="inlineStr"/>
+      <c r="BD400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>O8lguXw3</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>13.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Sanchez Lopez R.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Los Cármenes
+ (Granada)</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>22 524</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>18 036</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>Granada CF</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>Cordoba</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr"/>
+      <c r="N401" t="inlineStr"/>
+      <c r="O401" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R401" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T401" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U401" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V401" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W401" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X401" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y401" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z401" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA401" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB401" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC401" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD401" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE401" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AF401" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG401" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH401" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI401" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ401" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK401" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL401" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM401" t="inlineStr">
+        <is>
+          <t>K0UZov8F</t>
+        </is>
+      </c>
+      <c r="AN401" t="inlineStr">
+        <is>
+          <t>escriba fran</t>
+        </is>
+      </c>
+      <c r="AO401" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="AP401" t="inlineStr">
+        <is>
+          <t>ania ivan</t>
+        </is>
+      </c>
+      <c r="AQ401" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR401" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS401" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT401" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU401" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV401" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AW401" t="inlineStr"/>
+      <c r="AX401" t="inlineStr"/>
+      <c r="AY401" t="inlineStr"/>
+      <c r="AZ401" t="inlineStr"/>
+      <c r="BA401" t="inlineStr"/>
+      <c r="BB401" t="inlineStr"/>
+      <c r="BC401" t="inlineStr"/>
+      <c r="BD401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>zm8bJkHq</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>13.10.2024 11:15</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>De Aza M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Carlos Tartiere
+ (Oviedo)</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>30 500</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>19 426</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>R. Oviedo</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>Almeria</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr"/>
+      <c r="N402" t="inlineStr"/>
+      <c r="O402" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R402" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U402" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V402" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W402" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X402" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y402" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z402" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AA402" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB402" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC402" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD402" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE402" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF402" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG402" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH402" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI402" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ402" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AK402" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL402" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM402" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="AN402" t="inlineStr">
+        <is>
+          <t>calleja javier</t>
+        </is>
+      </c>
+      <c r="AO402" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="AP402" t="inlineStr">
+        <is>
+          <t>rubi joan</t>
+        </is>
+      </c>
+      <c r="AQ402" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR402" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS402" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT402" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU402" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV402" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AW402" t="inlineStr"/>
+      <c r="AX402" t="inlineStr"/>
+      <c r="AY402" t="inlineStr"/>
+      <c r="AZ402" t="inlineStr"/>
+      <c r="BA402" t="inlineStr"/>
+      <c r="BB402" t="inlineStr"/>
+      <c r="BC402" t="inlineStr"/>
+      <c r="BD402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>z5JYK2hl</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>13.10.2024 11:15</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Guzman Mansilla J. L.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Estadio El Sardinero
+ (Santander)</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>22 222</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>20 680</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr"/>
+      <c r="N403" t="inlineStr"/>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R403" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T403" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U403" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V403" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W403" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X403" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y403" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="Z403" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA403" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB403" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC403" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD403" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AE403" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF403" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG403" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH403" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI403" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AJ403" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK403" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL403" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM403" t="inlineStr">
+        <is>
+          <t>rak12p9n</t>
+        </is>
+      </c>
+      <c r="AN403" t="inlineStr">
+        <is>
+          <t>lopez jose</t>
+        </is>
+      </c>
+      <c r="AO403" t="inlineStr">
+        <is>
+          <t>fiZxGYJ3</t>
+        </is>
+      </c>
+      <c r="AP403" t="inlineStr">
+        <is>
+          <t>calero julian</t>
+        </is>
+      </c>
+      <c r="AQ403" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR403" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS403" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT403" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU403" t="inlineStr"/>
+      <c r="AV403" t="inlineStr"/>
+      <c r="AW403" t="inlineStr"/>
+      <c r="AX403" t="inlineStr"/>
+      <c r="AY403" t="inlineStr"/>
+      <c r="AZ403" t="inlineStr"/>
+      <c r="BA403" t="inlineStr"/>
+      <c r="BB403" t="inlineStr"/>
+      <c r="BC403" t="inlineStr"/>
+      <c r="BD403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>44HSOBgM</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>13.10.2024 09:00</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Cid Camacho G.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Estadio El Alcoraz
+ (Huesca)</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>9 100</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>5 722</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr"/>
+      <c r="N404" t="inlineStr"/>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R404" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T404" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U404" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V404" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W404" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X404" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y404" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z404" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA404" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB404" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC404" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD404" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE404" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AF404" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG404" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH404" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI404" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ404" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK404" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL404" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM404" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="AN404" t="inlineStr">
+        <is>
+          <t>hidalgo antonio</t>
+        </is>
+      </c>
+      <c r="AO404" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="AP404" t="inlineStr">
+        <is>
+          <t>gonzalez alberto</t>
+        </is>
+      </c>
+      <c r="AQ404" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR404" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS404" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT404" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU404" t="inlineStr"/>
+      <c r="AV404" t="inlineStr"/>
+      <c r="AW404" t="inlineStr"/>
+      <c r="AX404" t="inlineStr"/>
+      <c r="AY404" t="inlineStr"/>
+      <c r="AZ404" t="inlineStr"/>
+      <c r="BA404" t="inlineStr"/>
+      <c r="BB404" t="inlineStr"/>
+      <c r="BC404" t="inlineStr"/>
+      <c r="BD404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>OUs3Q3DT</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>12.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Moreno A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Mirandilla
+ (Cadiz)</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>20 776</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>11 507</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>Cadiz CF</t>
+        </is>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr"/>
+      <c r="N405" t="inlineStr"/>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R405" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T405" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U405" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V405" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W405" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X405" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y405" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z405" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA405" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB405" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC405" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD405" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE405" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF405" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG405" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH405" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI405" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AJ405" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK405" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL405" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM405" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="AN405" t="inlineStr">
+        <is>
+          <t>lopez paco</t>
+        </is>
+      </c>
+      <c r="AO405" t="inlineStr">
+        <is>
+          <t>tjXr7SAp</t>
+        </is>
+      </c>
+      <c r="AP405" t="inlineStr">
+        <is>
+          <t>garcia sergio</t>
+        </is>
+      </c>
+      <c r="AQ405" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR405" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS405" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT405" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU405" t="inlineStr"/>
+      <c r="AV405" t="inlineStr"/>
+      <c r="AW405" t="inlineStr"/>
+      <c r="AX405" t="inlineStr"/>
+      <c r="AY405" t="inlineStr"/>
+      <c r="AZ405" t="inlineStr"/>
+      <c r="BA405" t="inlineStr"/>
+      <c r="BB405" t="inlineStr"/>
+      <c r="BC405" t="inlineStr"/>
+      <c r="BD405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="1" t="inlineStr">
+        <is>
+          <t>Cl3JSgfc</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>12.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Mallo E.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Ipurua
+ (Eibar)</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>8 164</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>5 097</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>Eibar</t>
+        </is>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>Eldense</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr"/>
+      <c r="N406" t="inlineStr"/>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T406" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U406" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V406" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W406" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X406" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y406" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z406" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA406" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB406" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC406" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD406" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE406" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF406" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AG406" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH406" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI406" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AJ406" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK406" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL406" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM406" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="AN406" t="inlineStr">
+        <is>
+          <t>etxeberria joseba</t>
+        </is>
+      </c>
+      <c r="AO406" t="inlineStr">
+        <is>
+          <t>hh4xt2Df</t>
+        </is>
+      </c>
+      <c r="AP406" t="inlineStr">
+        <is>
+          <t>ponz daniel</t>
+        </is>
+      </c>
+      <c r="AQ406" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR406" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS406" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT406" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU406" t="inlineStr"/>
+      <c r="AV406" t="inlineStr"/>
+      <c r="AW406" t="inlineStr"/>
+      <c r="AX406" t="inlineStr"/>
+      <c r="AY406" t="inlineStr"/>
+      <c r="AZ406" t="inlineStr"/>
+      <c r="BA406" t="inlineStr"/>
+      <c r="BB406" t="inlineStr"/>
+      <c r="BC406" t="inlineStr"/>
+      <c r="BD406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="1" t="inlineStr">
+        <is>
+          <t>fDYYKsyi</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>12.10.2024 11:15</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Reig S. A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Estadio Municipal Cartagonova
+ (Cartagena)</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>13 745</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>6 223</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>FC Cartagena SAD</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>Racing Club Ferrol</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr"/>
+      <c r="N407" t="inlineStr"/>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R407" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T407" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U407" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V407" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W407" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X407" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y407" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Z407" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA407" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB407" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC407" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD407" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE407" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF407" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG407" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH407" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI407" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ407" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK407" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL407" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM407" t="inlineStr">
+        <is>
+          <t>hlQINAie</t>
+        </is>
+      </c>
+      <c r="AN407" t="inlineStr">
+        <is>
+          <t>jandro</t>
+        </is>
+      </c>
+      <c r="AO407" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="AP407" t="inlineStr">
+        <is>
+          <t>parralo cristobal</t>
+        </is>
+      </c>
+      <c r="AQ407" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR407" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS407" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT407" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU407" t="inlineStr"/>
+      <c r="AV407" t="inlineStr"/>
+      <c r="AW407" t="inlineStr"/>
+      <c r="AX407" t="inlineStr"/>
+      <c r="AY407" t="inlineStr"/>
+      <c r="AZ407" t="inlineStr"/>
+      <c r="BA407" t="inlineStr"/>
+      <c r="BB407" t="inlineStr"/>
+      <c r="BC407" t="inlineStr"/>
+      <c r="BD407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>p21RQXO9</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>11.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Lax Franco S.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Estadio Heliodoro Rodríguez López
+ (Santa Cruz de Tenerife)</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>22 824</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>15 155</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>Tenerife</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr"/>
+      <c r="N408" t="inlineStr"/>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T408" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V408" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W408" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X408" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y408" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Z408" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA408" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB408" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC408" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD408" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE408" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF408" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AG408" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH408" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI408" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ408" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK408" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL408" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM408" t="inlineStr">
+        <is>
+          <t>CYND5rZG</t>
+        </is>
+      </c>
+      <c r="AN408" t="inlineStr">
+        <is>
+          <t>mel pepe</t>
+        </is>
+      </c>
+      <c r="AO408" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="AP408" t="inlineStr">
+        <is>
+          <t>fernandez braulio victor</t>
+        </is>
+      </c>
+      <c r="AQ408" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR408" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS408" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT408" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU408" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV408" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW408" t="inlineStr"/>
+      <c r="AX408" t="inlineStr"/>
+      <c r="AY408" t="inlineStr"/>
+      <c r="AZ408" t="inlineStr"/>
+      <c r="BA408" t="inlineStr"/>
+      <c r="BB408" t="inlineStr"/>
+      <c r="BC408" t="inlineStr"/>
+      <c r="BD408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="inlineStr">
+        <is>
+          <t>Wbg14s0S</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>09.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr"/>
+      <c r="D409" t="inlineStr"/>
+      <c r="E409" t="inlineStr"/>
+      <c r="F409" t="inlineStr"/>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>6mTyxt2G</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Chiclana</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>MJ3pLO5t</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>Melilla CD</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr"/>
+      <c r="N409" t="inlineStr"/>
+      <c r="O409" t="inlineStr"/>
+      <c r="P409" t="inlineStr"/>
+      <c r="Q409" t="inlineStr"/>
+      <c r="R409" t="inlineStr"/>
+      <c r="S409" t="inlineStr"/>
+      <c r="T409" t="inlineStr"/>
+      <c r="U409" t="inlineStr"/>
+      <c r="V409" t="inlineStr"/>
+      <c r="W409" t="inlineStr"/>
+      <c r="X409" t="inlineStr"/>
+      <c r="Y409" t="inlineStr"/>
+      <c r="Z409" t="inlineStr"/>
+      <c r="AA409" t="inlineStr"/>
+      <c r="AB409" t="inlineStr"/>
+      <c r="AC409" t="inlineStr"/>
+      <c r="AD409" t="inlineStr"/>
+      <c r="AE409" t="inlineStr"/>
+      <c r="AF409" t="inlineStr"/>
+      <c r="AG409" t="inlineStr"/>
+      <c r="AH409" t="inlineStr"/>
+      <c r="AI409" t="inlineStr"/>
+      <c r="AJ409" t="inlineStr"/>
+      <c r="AK409" t="inlineStr"/>
+      <c r="AL409" t="inlineStr"/>
+      <c r="AM409" t="inlineStr"/>
+      <c r="AN409" t="inlineStr"/>
+      <c r="AO409" t="inlineStr"/>
+      <c r="AP409" t="inlineStr"/>
+      <c r="AQ409" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR409" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS409" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT409" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU409" t="inlineStr"/>
+      <c r="AV409" t="inlineStr"/>
+      <c r="AW409" t="inlineStr"/>
+      <c r="AX409" t="inlineStr"/>
+      <c r="AY409" t="inlineStr"/>
+      <c r="AZ409" t="inlineStr"/>
+      <c r="BA409" t="inlineStr"/>
+      <c r="BB409" t="inlineStr"/>
+      <c r="BC409" t="inlineStr"/>
+      <c r="BD409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="inlineStr">
+        <is>
+          <t>nBJcpM8d</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>09.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr"/>
+      <c r="D410" t="inlineStr"/>
+      <c r="E410" t="inlineStr"/>
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>lYt2HNv2</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Gevora</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>GvZmuRW8</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>UD Playas de Sotavento</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr"/>
+      <c r="N410" t="inlineStr"/>
+      <c r="O410" t="inlineStr"/>
+      <c r="P410" t="inlineStr"/>
+      <c r="Q410" t="inlineStr"/>
+      <c r="R410" t="inlineStr"/>
+      <c r="S410" t="inlineStr"/>
+      <c r="T410" t="inlineStr"/>
+      <c r="U410" t="inlineStr"/>
+      <c r="V410" t="inlineStr"/>
+      <c r="W410" t="inlineStr"/>
+      <c r="X410" t="inlineStr"/>
+      <c r="Y410" t="inlineStr"/>
+      <c r="Z410" t="inlineStr"/>
+      <c r="AA410" t="inlineStr"/>
+      <c r="AB410" t="inlineStr"/>
+      <c r="AC410" t="inlineStr"/>
+      <c r="AD410" t="inlineStr"/>
+      <c r="AE410" t="inlineStr"/>
+      <c r="AF410" t="inlineStr"/>
+      <c r="AG410" t="inlineStr"/>
+      <c r="AH410" t="inlineStr"/>
+      <c r="AI410" t="inlineStr"/>
+      <c r="AJ410" t="inlineStr"/>
+      <c r="AK410" t="inlineStr"/>
+      <c r="AL410" t="inlineStr"/>
+      <c r="AM410" t="inlineStr"/>
+      <c r="AN410" t="inlineStr"/>
+      <c r="AO410" t="inlineStr"/>
+      <c r="AP410" t="inlineStr"/>
+      <c r="AQ410" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR410" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS410" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT410" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU410" t="inlineStr"/>
+      <c r="AV410" t="inlineStr"/>
+      <c r="AW410" t="inlineStr"/>
+      <c r="AX410" t="inlineStr"/>
+      <c r="AY410" t="inlineStr"/>
+      <c r="AZ410" t="inlineStr"/>
+      <c r="BA410" t="inlineStr"/>
+      <c r="BB410" t="inlineStr"/>
+      <c r="BC410" t="inlineStr"/>
+      <c r="BD410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="inlineStr">
+        <is>
+          <t>2J1p8P03</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>09.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr"/>
+      <c r="D411" t="inlineStr"/>
+      <c r="E411" t="inlineStr"/>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>SGQrDLqm</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+UE Vic</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>UkXwRzCb</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>Mahon</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr"/>
+      <c r="N411" t="inlineStr"/>
+      <c r="O411" t="inlineStr"/>
+      <c r="P411" t="inlineStr"/>
+      <c r="Q411" t="inlineStr"/>
+      <c r="R411" t="inlineStr"/>
+      <c r="S411" t="inlineStr"/>
+      <c r="T411" t="inlineStr"/>
+      <c r="U411" t="inlineStr"/>
+      <c r="V411" t="inlineStr"/>
+      <c r="W411" t="inlineStr"/>
+      <c r="X411" t="inlineStr"/>
+      <c r="Y411" t="inlineStr"/>
+      <c r="Z411" t="inlineStr"/>
+      <c r="AA411" t="inlineStr"/>
+      <c r="AB411" t="inlineStr"/>
+      <c r="AC411" t="inlineStr"/>
+      <c r="AD411" t="inlineStr"/>
+      <c r="AE411" t="inlineStr"/>
+      <c r="AF411" t="inlineStr"/>
+      <c r="AG411" t="inlineStr"/>
+      <c r="AH411" t="inlineStr"/>
+      <c r="AI411" t="inlineStr"/>
+      <c r="AJ411" t="inlineStr"/>
+      <c r="AK411" t="inlineStr"/>
+      <c r="AL411" t="inlineStr"/>
+      <c r="AM411" t="inlineStr"/>
+      <c r="AN411" t="inlineStr"/>
+      <c r="AO411" t="inlineStr"/>
+      <c r="AP411" t="inlineStr"/>
+      <c r="AQ411" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR411" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS411" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT411" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU411" t="inlineStr"/>
+      <c r="AV411" t="inlineStr"/>
+      <c r="AW411" t="inlineStr"/>
+      <c r="AX411" t="inlineStr"/>
+      <c r="AY411" t="inlineStr"/>
+      <c r="AZ411" t="inlineStr"/>
+      <c r="BA411" t="inlineStr"/>
+      <c r="BB411" t="inlineStr"/>
+      <c r="BC411" t="inlineStr"/>
+      <c r="BD411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="inlineStr">
+        <is>
+          <t>8dtBgQoA</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>09.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr"/>
+      <c r="D412" t="inlineStr"/>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>rDwfNhBN</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>Dolorense</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>MJQLyhQG</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>Manises
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr"/>
+      <c r="N412" t="inlineStr"/>
+      <c r="O412" t="inlineStr"/>
+      <c r="P412" t="inlineStr"/>
+      <c r="Q412" t="inlineStr"/>
+      <c r="R412" t="inlineStr"/>
+      <c r="S412" t="inlineStr"/>
+      <c r="T412" t="inlineStr"/>
+      <c r="U412" t="inlineStr"/>
+      <c r="V412" t="inlineStr"/>
+      <c r="W412" t="inlineStr"/>
+      <c r="X412" t="inlineStr"/>
+      <c r="Y412" t="inlineStr"/>
+      <c r="Z412" t="inlineStr"/>
+      <c r="AA412" t="inlineStr"/>
+      <c r="AB412" t="inlineStr"/>
+      <c r="AC412" t="inlineStr"/>
+      <c r="AD412" t="inlineStr"/>
+      <c r="AE412" t="inlineStr"/>
+      <c r="AF412" t="inlineStr"/>
+      <c r="AG412" t="inlineStr"/>
+      <c r="AH412" t="inlineStr"/>
+      <c r="AI412" t="inlineStr"/>
+      <c r="AJ412" t="inlineStr"/>
+      <c r="AK412" t="inlineStr"/>
+      <c r="AL412" t="inlineStr"/>
+      <c r="AM412" t="inlineStr"/>
+      <c r="AN412" t="inlineStr"/>
+      <c r="AO412" t="inlineStr"/>
+      <c r="AP412" t="inlineStr"/>
+      <c r="AQ412" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR412" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS412" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT412" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU412" t="inlineStr"/>
+      <c r="AV412" t="inlineStr"/>
+      <c r="AW412" t="inlineStr"/>
+      <c r="AX412" t="inlineStr"/>
+      <c r="AY412" t="inlineStr"/>
+      <c r="AZ412" t="inlineStr"/>
+      <c r="BA412" t="inlineStr"/>
+      <c r="BB412" t="inlineStr"/>
+      <c r="BC412" t="inlineStr"/>
+      <c r="BD412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="1" t="inlineStr">
+        <is>
+          <t>nPbWbLNk</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>09.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>vBEEUw07</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+CD Villamuriel</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>IV2PZfX0</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>Aurrera de Vitoria</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr"/>
+      <c r="N413" t="inlineStr"/>
+      <c r="O413" t="inlineStr"/>
+      <c r="P413" t="inlineStr"/>
+      <c r="Q413" t="inlineStr"/>
+      <c r="R413" t="inlineStr"/>
+      <c r="S413" t="inlineStr"/>
+      <c r="T413" t="inlineStr"/>
+      <c r="U413" t="inlineStr"/>
+      <c r="V413" t="inlineStr"/>
+      <c r="W413" t="inlineStr"/>
+      <c r="X413" t="inlineStr"/>
+      <c r="Y413" t="inlineStr"/>
+      <c r="Z413" t="inlineStr"/>
+      <c r="AA413" t="inlineStr"/>
+      <c r="AB413" t="inlineStr"/>
+      <c r="AC413" t="inlineStr"/>
+      <c r="AD413" t="inlineStr"/>
+      <c r="AE413" t="inlineStr"/>
+      <c r="AF413" t="inlineStr"/>
+      <c r="AG413" t="inlineStr"/>
+      <c r="AH413" t="inlineStr"/>
+      <c r="AI413" t="inlineStr"/>
+      <c r="AJ413" t="inlineStr"/>
+      <c r="AK413" t="inlineStr"/>
+      <c r="AL413" t="inlineStr"/>
+      <c r="AM413" t="inlineStr"/>
+      <c r="AN413" t="inlineStr"/>
+      <c r="AO413" t="inlineStr"/>
+      <c r="AP413" t="inlineStr"/>
+      <c r="AQ413" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR413" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS413" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT413" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU413" t="inlineStr"/>
+      <c r="AV413" t="inlineStr"/>
+      <c r="AW413" t="inlineStr"/>
+      <c r="AX413" t="inlineStr"/>
+      <c r="AY413" t="inlineStr"/>
+      <c r="AZ413" t="inlineStr"/>
+      <c r="BA413" t="inlineStr"/>
+      <c r="BB413" t="inlineStr"/>
+      <c r="BC413" t="inlineStr"/>
+      <c r="BD413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="1" t="inlineStr">
+        <is>
+          <t>zXah63VF</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>09.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>dKlL6OBq</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Astur</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>8CIs7tLP</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>Promesas EDF</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr"/>
+      <c r="N414" t="inlineStr"/>
+      <c r="O414" t="inlineStr"/>
+      <c r="P414" t="inlineStr"/>
+      <c r="Q414" t="inlineStr"/>
+      <c r="R414" t="inlineStr"/>
+      <c r="S414" t="inlineStr"/>
+      <c r="T414" t="inlineStr"/>
+      <c r="U414" t="inlineStr"/>
+      <c r="V414" t="inlineStr"/>
+      <c r="W414" t="inlineStr"/>
+      <c r="X414" t="inlineStr"/>
+      <c r="Y414" t="inlineStr"/>
+      <c r="Z414" t="inlineStr"/>
+      <c r="AA414" t="inlineStr"/>
+      <c r="AB414" t="inlineStr"/>
+      <c r="AC414" t="inlineStr"/>
+      <c r="AD414" t="inlineStr"/>
+      <c r="AE414" t="inlineStr"/>
+      <c r="AF414" t="inlineStr"/>
+      <c r="AG414" t="inlineStr"/>
+      <c r="AH414" t="inlineStr"/>
+      <c r="AI414" t="inlineStr"/>
+      <c r="AJ414" t="inlineStr"/>
+      <c r="AK414" t="inlineStr"/>
+      <c r="AL414" t="inlineStr"/>
+      <c r="AM414" t="inlineStr"/>
+      <c r="AN414" t="inlineStr"/>
+      <c r="AO414" t="inlineStr"/>
+      <c r="AP414" t="inlineStr"/>
+      <c r="AQ414" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR414" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS414" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT414" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU414" t="inlineStr"/>
+      <c r="AV414" t="inlineStr"/>
+      <c r="AW414" t="inlineStr"/>
+      <c r="AX414" t="inlineStr"/>
+      <c r="AY414" t="inlineStr"/>
+      <c r="AZ414" t="inlineStr"/>
+      <c r="BA414" t="inlineStr"/>
+      <c r="BB414" t="inlineStr"/>
+      <c r="BC414" t="inlineStr"/>
+      <c r="BD414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="1" t="inlineStr">
+        <is>
+          <t>CUn2enHc</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>09.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>WpoAThMp</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>CD Baztan</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>6mKmGJct</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>Ontinena
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr"/>
+      <c r="N415" t="inlineStr"/>
+      <c r="O415" t="inlineStr"/>
+      <c r="P415" t="inlineStr"/>
+      <c r="Q415" t="inlineStr"/>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="inlineStr"/>
+      <c r="T415" t="inlineStr"/>
+      <c r="U415" t="inlineStr"/>
+      <c r="V415" t="inlineStr"/>
+      <c r="W415" t="inlineStr"/>
+      <c r="X415" t="inlineStr"/>
+      <c r="Y415" t="inlineStr"/>
+      <c r="Z415" t="inlineStr"/>
+      <c r="AA415" t="inlineStr"/>
+      <c r="AB415" t="inlineStr"/>
+      <c r="AC415" t="inlineStr"/>
+      <c r="AD415" t="inlineStr"/>
+      <c r="AE415" t="inlineStr"/>
+      <c r="AF415" t="inlineStr"/>
+      <c r="AG415" t="inlineStr"/>
+      <c r="AH415" t="inlineStr"/>
+      <c r="AI415" t="inlineStr"/>
+      <c r="AJ415" t="inlineStr"/>
+      <c r="AK415" t="inlineStr"/>
+      <c r="AL415" t="inlineStr"/>
+      <c r="AM415" t="inlineStr"/>
+      <c r="AN415" t="inlineStr"/>
+      <c r="AO415" t="inlineStr"/>
+      <c r="AP415" t="inlineStr"/>
+      <c r="AQ415" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR415" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS415" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT415" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU415" t="inlineStr"/>
+      <c r="AV415" t="inlineStr"/>
+      <c r="AW415" t="inlineStr"/>
+      <c r="AX415" t="inlineStr"/>
+      <c r="AY415" t="inlineStr"/>
+      <c r="AZ415" t="inlineStr"/>
+      <c r="BA415" t="inlineStr"/>
+      <c r="BB415" t="inlineStr"/>
+      <c r="BC415" t="inlineStr"/>
+      <c r="BD415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>0fLknrvp</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>09.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr"/>
+      <c r="D416" t="inlineStr"/>
+      <c r="E416" t="inlineStr"/>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>8WJ5ilVD</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+UD San Pedro</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>2mXiTVM1</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>Ceuta 6 de Junio</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr"/>
+      <c r="N416" t="inlineStr"/>
+      <c r="O416" t="inlineStr"/>
+      <c r="P416" t="inlineStr"/>
+      <c r="Q416" t="inlineStr"/>
+      <c r="R416" t="inlineStr"/>
+      <c r="S416" t="inlineStr"/>
+      <c r="T416" t="inlineStr"/>
+      <c r="U416" t="inlineStr"/>
+      <c r="V416" t="inlineStr"/>
+      <c r="W416" t="inlineStr"/>
+      <c r="X416" t="inlineStr"/>
+      <c r="Y416" t="inlineStr"/>
+      <c r="Z416" t="inlineStr"/>
+      <c r="AA416" t="inlineStr"/>
+      <c r="AB416" t="inlineStr"/>
+      <c r="AC416" t="inlineStr"/>
+      <c r="AD416" t="inlineStr"/>
+      <c r="AE416" t="inlineStr"/>
+      <c r="AF416" t="inlineStr"/>
+      <c r="AG416" t="inlineStr"/>
+      <c r="AH416" t="inlineStr"/>
+      <c r="AI416" t="inlineStr"/>
+      <c r="AJ416" t="inlineStr"/>
+      <c r="AK416" t="inlineStr"/>
+      <c r="AL416" t="inlineStr"/>
+      <c r="AM416" t="inlineStr"/>
+      <c r="AN416" t="inlineStr"/>
+      <c r="AO416" t="inlineStr"/>
+      <c r="AP416" t="inlineStr"/>
+      <c r="AQ416" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR416" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS416" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT416" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU416" t="inlineStr"/>
+      <c r="AV416" t="inlineStr"/>
+      <c r="AW416" t="inlineStr"/>
+      <c r="AX416" t="inlineStr"/>
+      <c r="AY416" t="inlineStr"/>
+      <c r="AZ416" t="inlineStr"/>
+      <c r="BA416" t="inlineStr"/>
+      <c r="BB416" t="inlineStr"/>
+      <c r="BC416" t="inlineStr"/>
+      <c r="BD416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="1" t="inlineStr">
+        <is>
+          <t>GMqJi4GM</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>09.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr"/>
+      <c r="D417" t="inlineStr"/>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>YmhEXW3h</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>Sonseca</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>YBWcQMQD</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>CP Parla
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr"/>
+      <c r="N417" t="inlineStr"/>
+      <c r="O417" t="inlineStr"/>
+      <c r="P417" t="inlineStr"/>
+      <c r="Q417" t="inlineStr"/>
+      <c r="R417" t="inlineStr"/>
+      <c r="S417" t="inlineStr"/>
+      <c r="T417" t="inlineStr"/>
+      <c r="U417" t="inlineStr"/>
+      <c r="V417" t="inlineStr"/>
+      <c r="W417" t="inlineStr"/>
+      <c r="X417" t="inlineStr"/>
+      <c r="Y417" t="inlineStr"/>
+      <c r="Z417" t="inlineStr"/>
+      <c r="AA417" t="inlineStr"/>
+      <c r="AB417" t="inlineStr"/>
+      <c r="AC417" t="inlineStr"/>
+      <c r="AD417" t="inlineStr"/>
+      <c r="AE417" t="inlineStr"/>
+      <c r="AF417" t="inlineStr"/>
+      <c r="AG417" t="inlineStr"/>
+      <c r="AH417" t="inlineStr"/>
+      <c r="AI417" t="inlineStr"/>
+      <c r="AJ417" t="inlineStr"/>
+      <c r="AK417" t="inlineStr"/>
+      <c r="AL417" t="inlineStr"/>
+      <c r="AM417" t="inlineStr"/>
+      <c r="AN417" t="inlineStr"/>
+      <c r="AO417" t="inlineStr"/>
+      <c r="AP417" t="inlineStr"/>
+      <c r="AQ417" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR417" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS417" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT417" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU417" t="inlineStr"/>
+      <c r="AV417" t="inlineStr"/>
+      <c r="AW417" t="inlineStr"/>
+      <c r="AX417" t="inlineStr"/>
+      <c r="AY417" t="inlineStr"/>
+      <c r="AZ417" t="inlineStr"/>
+      <c r="BA417" t="inlineStr"/>
+      <c r="BB417" t="inlineStr"/>
+      <c r="BC417" t="inlineStr"/>
+      <c r="BD417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="1" t="inlineStr">
+        <is>
+          <t>8vmucah2</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>09.10.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr"/>
+      <c r="D418" t="inlineStr"/>
+      <c r="E418" t="inlineStr"/>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>0AcMabDa</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+San Tirso</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>QDq1LYOm</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>Selaya</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr"/>
+      <c r="N418" t="inlineStr"/>
+      <c r="O418" t="inlineStr"/>
+      <c r="P418" t="inlineStr"/>
+      <c r="Q418" t="inlineStr"/>
+      <c r="R418" t="inlineStr"/>
+      <c r="S418" t="inlineStr"/>
+      <c r="T418" t="inlineStr"/>
+      <c r="U418" t="inlineStr"/>
+      <c r="V418" t="inlineStr"/>
+      <c r="W418" t="inlineStr"/>
+      <c r="X418" t="inlineStr"/>
+      <c r="Y418" t="inlineStr"/>
+      <c r="Z418" t="inlineStr"/>
+      <c r="AA418" t="inlineStr"/>
+      <c r="AB418" t="inlineStr"/>
+      <c r="AC418" t="inlineStr"/>
+      <c r="AD418" t="inlineStr"/>
+      <c r="AE418" t="inlineStr"/>
+      <c r="AF418" t="inlineStr"/>
+      <c r="AG418" t="inlineStr"/>
+      <c r="AH418" t="inlineStr"/>
+      <c r="AI418" t="inlineStr"/>
+      <c r="AJ418" t="inlineStr"/>
+      <c r="AK418" t="inlineStr"/>
+      <c r="AL418" t="inlineStr"/>
+      <c r="AM418" t="inlineStr"/>
+      <c r="AN418" t="inlineStr"/>
+      <c r="AO418" t="inlineStr"/>
+      <c r="AP418" t="inlineStr"/>
+      <c r="AQ418" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR418" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS418" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT418" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU418" t="inlineStr"/>
+      <c r="AV418" t="inlineStr"/>
+      <c r="AW418" t="inlineStr"/>
+      <c r="AX418" t="inlineStr"/>
+      <c r="AY418" t="inlineStr"/>
+      <c r="AZ418" t="inlineStr"/>
+      <c r="BA418" t="inlineStr"/>
+      <c r="BB418" t="inlineStr"/>
+      <c r="BC418" t="inlineStr"/>
+      <c r="BD418" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD418"/>
+  <dimension ref="A1:BH428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -702,6 +702,26 @@
       <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_home</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_away</t>
         </is>
       </c>
     </row>
@@ -890,6 +910,10 @@
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1080,6 +1104,10 @@
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1266,6 +1294,10 @@
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1456,6 +1488,10 @@
       <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1642,6 +1678,10 @@
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1828,6 +1868,10 @@
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr"/>
       <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2010,6 +2054,10 @@
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -2196,6 +2244,10 @@
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -2382,6 +2434,10 @@
       <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -2568,6 +2624,10 @@
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
       <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -2754,6 +2814,10 @@
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr"/>
       <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -2940,6 +3004,10 @@
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
       <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -3126,6 +3194,10 @@
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
       <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -3312,6 +3384,10 @@
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
       <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -3498,6 +3574,10 @@
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="inlineStr"/>
       <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -3684,6 +3764,10 @@
       <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="inlineStr"/>
       <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -3874,6 +3958,10 @@
       <c r="BB18" t="inlineStr"/>
       <c r="BC18" t="inlineStr"/>
       <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -4060,6 +4148,10 @@
       <c r="BB19" t="inlineStr"/>
       <c r="BC19" t="inlineStr"/>
       <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -4246,6 +4338,10 @@
       <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="inlineStr"/>
       <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -4428,6 +4524,10 @@
       <c r="BB21" t="inlineStr"/>
       <c r="BC21" t="inlineStr"/>
       <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -4614,6 +4714,10 @@
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>
       <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -4800,6 +4904,10 @@
       <c r="BB23" t="inlineStr"/>
       <c r="BC23" t="inlineStr"/>
       <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -4986,6 +5094,10 @@
       <c r="BB24" t="inlineStr"/>
       <c r="BC24" t="inlineStr"/>
       <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -5172,6 +5284,10 @@
       <c r="BB25" t="inlineStr"/>
       <c r="BC25" t="inlineStr"/>
       <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -5358,6 +5474,10 @@
       <c r="BB26" t="inlineStr"/>
       <c r="BC26" t="inlineStr"/>
       <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -5544,6 +5664,10 @@
       <c r="BB27" t="inlineStr"/>
       <c r="BC27" t="inlineStr"/>
       <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
+      <c r="BH27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -5730,6 +5854,10 @@
       <c r="BB28" t="inlineStr"/>
       <c r="BC28" t="inlineStr"/>
       <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
+      <c r="BH28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -5916,6 +6044,10 @@
       <c r="BB29" t="inlineStr"/>
       <c r="BC29" t="inlineStr"/>
       <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="inlineStr"/>
+      <c r="BH29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -6102,6 +6234,10 @@
       <c r="BB30" t="inlineStr"/>
       <c r="BC30" t="inlineStr"/>
       <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr"/>
+      <c r="BF30" t="inlineStr"/>
+      <c r="BG30" t="inlineStr"/>
+      <c r="BH30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -6296,6 +6432,10 @@
       <c r="BB31" t="inlineStr"/>
       <c r="BC31" t="inlineStr"/>
       <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr"/>
+      <c r="BF31" t="inlineStr"/>
+      <c r="BG31" t="inlineStr"/>
+      <c r="BH31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -6490,6 +6630,10 @@
       <c r="BB32" t="inlineStr"/>
       <c r="BC32" t="inlineStr"/>
       <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="inlineStr"/>
+      <c r="BF32" t="inlineStr"/>
+      <c r="BG32" t="inlineStr"/>
+      <c r="BH32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -6684,6 +6828,10 @@
       <c r="BB33" t="inlineStr"/>
       <c r="BC33" t="inlineStr"/>
       <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="inlineStr"/>
+      <c r="BF33" t="inlineStr"/>
+      <c r="BG33" t="inlineStr"/>
+      <c r="BH33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -6878,6 +7026,10 @@
       <c r="BB34" t="inlineStr"/>
       <c r="BC34" t="inlineStr"/>
       <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="inlineStr"/>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -7076,6 +7228,10 @@
       <c r="BB35" t="inlineStr"/>
       <c r="BC35" t="inlineStr"/>
       <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="inlineStr"/>
+      <c r="BG35" t="inlineStr"/>
+      <c r="BH35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -7274,6 +7430,10 @@
       <c r="BB36" t="inlineStr"/>
       <c r="BC36" t="inlineStr"/>
       <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr"/>
+      <c r="BF36" t="inlineStr"/>
+      <c r="BG36" t="inlineStr"/>
+      <c r="BH36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -7472,6 +7632,10 @@
       <c r="BB37" t="inlineStr"/>
       <c r="BC37" t="inlineStr"/>
       <c r="BD37" t="inlineStr"/>
+      <c r="BE37" t="inlineStr"/>
+      <c r="BF37" t="inlineStr"/>
+      <c r="BG37" t="inlineStr"/>
+      <c r="BH37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -7666,6 +7830,10 @@
       <c r="BB38" t="inlineStr"/>
       <c r="BC38" t="inlineStr"/>
       <c r="BD38" t="inlineStr"/>
+      <c r="BE38" t="inlineStr"/>
+      <c r="BF38" t="inlineStr"/>
+      <c r="BG38" t="inlineStr"/>
+      <c r="BH38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -7864,6 +8032,10 @@
       <c r="BB39" t="inlineStr"/>
       <c r="BC39" t="inlineStr"/>
       <c r="BD39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="inlineStr"/>
+      <c r="BG39" t="inlineStr"/>
+      <c r="BH39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -8058,6 +8230,10 @@
       <c r="BB40" t="inlineStr"/>
       <c r="BC40" t="inlineStr"/>
       <c r="BD40" t="inlineStr"/>
+      <c r="BE40" t="inlineStr"/>
+      <c r="BF40" t="inlineStr"/>
+      <c r="BG40" t="inlineStr"/>
+      <c r="BH40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -8256,6 +8432,10 @@
       <c r="BB41" t="inlineStr"/>
       <c r="BC41" t="inlineStr"/>
       <c r="BD41" t="inlineStr"/>
+      <c r="BE41" t="inlineStr"/>
+      <c r="BF41" t="inlineStr"/>
+      <c r="BG41" t="inlineStr"/>
+      <c r="BH41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -8450,6 +8630,10 @@
       <c r="BB42" t="inlineStr"/>
       <c r="BC42" t="inlineStr"/>
       <c r="BD42" t="inlineStr"/>
+      <c r="BE42" t="inlineStr"/>
+      <c r="BF42" t="inlineStr"/>
+      <c r="BG42" t="inlineStr"/>
+      <c r="BH42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -8644,6 +8828,10 @@
       <c r="BB43" t="inlineStr"/>
       <c r="BC43" t="inlineStr"/>
       <c r="BD43" t="inlineStr"/>
+      <c r="BE43" t="inlineStr"/>
+      <c r="BF43" t="inlineStr"/>
+      <c r="BG43" t="inlineStr"/>
+      <c r="BH43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -8838,6 +9026,10 @@
       <c r="BB44" t="inlineStr"/>
       <c r="BC44" t="inlineStr"/>
       <c r="BD44" t="inlineStr"/>
+      <c r="BE44" t="inlineStr"/>
+      <c r="BF44" t="inlineStr"/>
+      <c r="BG44" t="inlineStr"/>
+      <c r="BH44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -9032,6 +9224,10 @@
       <c r="BB45" t="inlineStr"/>
       <c r="BC45" t="inlineStr"/>
       <c r="BD45" t="inlineStr"/>
+      <c r="BE45" t="inlineStr"/>
+      <c r="BF45" t="inlineStr"/>
+      <c r="BG45" t="inlineStr"/>
+      <c r="BH45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -9226,6 +9422,10 @@
       <c r="BB46" t="inlineStr"/>
       <c r="BC46" t="inlineStr"/>
       <c r="BD46" t="inlineStr"/>
+      <c r="BE46" t="inlineStr"/>
+      <c r="BF46" t="inlineStr"/>
+      <c r="BG46" t="inlineStr"/>
+      <c r="BH46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -9424,6 +9624,10 @@
       <c r="BB47" t="inlineStr"/>
       <c r="BC47" t="inlineStr"/>
       <c r="BD47" t="inlineStr"/>
+      <c r="BE47" t="inlineStr"/>
+      <c r="BF47" t="inlineStr"/>
+      <c r="BG47" t="inlineStr"/>
+      <c r="BH47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -9618,6 +9822,10 @@
       <c r="BB48" t="inlineStr"/>
       <c r="BC48" t="inlineStr"/>
       <c r="BD48" t="inlineStr"/>
+      <c r="BE48" t="inlineStr"/>
+      <c r="BF48" t="inlineStr"/>
+      <c r="BG48" t="inlineStr"/>
+      <c r="BH48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -9816,6 +10024,10 @@
       <c r="BB49" t="inlineStr"/>
       <c r="BC49" t="inlineStr"/>
       <c r="BD49" t="inlineStr"/>
+      <c r="BE49" t="inlineStr"/>
+      <c r="BF49" t="inlineStr"/>
+      <c r="BG49" t="inlineStr"/>
+      <c r="BH49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -10010,6 +10222,10 @@
       <c r="BB50" t="inlineStr"/>
       <c r="BC50" t="inlineStr"/>
       <c r="BD50" t="inlineStr"/>
+      <c r="BE50" t="inlineStr"/>
+      <c r="BF50" t="inlineStr"/>
+      <c r="BG50" t="inlineStr"/>
+      <c r="BH50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -10204,6 +10420,10 @@
       <c r="BB51" t="inlineStr"/>
       <c r="BC51" t="inlineStr"/>
       <c r="BD51" t="inlineStr"/>
+      <c r="BE51" t="inlineStr"/>
+      <c r="BF51" t="inlineStr"/>
+      <c r="BG51" t="inlineStr"/>
+      <c r="BH51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -10398,6 +10618,10 @@
       <c r="BB52" t="inlineStr"/>
       <c r="BC52" t="inlineStr"/>
       <c r="BD52" t="inlineStr"/>
+      <c r="BE52" t="inlineStr"/>
+      <c r="BF52" t="inlineStr"/>
+      <c r="BG52" t="inlineStr"/>
+      <c r="BH52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -10592,6 +10816,10 @@
       <c r="BB53" t="inlineStr"/>
       <c r="BC53" t="inlineStr"/>
       <c r="BD53" t="inlineStr"/>
+      <c r="BE53" t="inlineStr"/>
+      <c r="BF53" t="inlineStr"/>
+      <c r="BG53" t="inlineStr"/>
+      <c r="BH53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -10782,6 +11010,10 @@
       <c r="BB54" t="inlineStr"/>
       <c r="BC54" t="inlineStr"/>
       <c r="BD54" t="inlineStr"/>
+      <c r="BE54" t="inlineStr"/>
+      <c r="BF54" t="inlineStr"/>
+      <c r="BG54" t="inlineStr"/>
+      <c r="BH54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -10976,6 +11208,10 @@
       <c r="BB55" t="inlineStr"/>
       <c r="BC55" t="inlineStr"/>
       <c r="BD55" t="inlineStr"/>
+      <c r="BE55" t="inlineStr"/>
+      <c r="BF55" t="inlineStr"/>
+      <c r="BG55" t="inlineStr"/>
+      <c r="BH55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -11174,6 +11410,10 @@
       <c r="BB56" t="inlineStr"/>
       <c r="BC56" t="inlineStr"/>
       <c r="BD56" t="inlineStr"/>
+      <c r="BE56" t="inlineStr"/>
+      <c r="BF56" t="inlineStr"/>
+      <c r="BG56" t="inlineStr"/>
+      <c r="BH56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -11368,6 +11608,10 @@
       <c r="BB57" t="inlineStr"/>
       <c r="BC57" t="inlineStr"/>
       <c r="BD57" t="inlineStr"/>
+      <c r="BE57" t="inlineStr"/>
+      <c r="BF57" t="inlineStr"/>
+      <c r="BG57" t="inlineStr"/>
+      <c r="BH57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -11562,6 +11806,10 @@
       <c r="BB58" t="inlineStr"/>
       <c r="BC58" t="inlineStr"/>
       <c r="BD58" t="inlineStr"/>
+      <c r="BE58" t="inlineStr"/>
+      <c r="BF58" t="inlineStr"/>
+      <c r="BG58" t="inlineStr"/>
+      <c r="BH58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -11756,6 +12004,10 @@
       <c r="BB59" t="inlineStr"/>
       <c r="BC59" t="inlineStr"/>
       <c r="BD59" t="inlineStr"/>
+      <c r="BE59" t="inlineStr"/>
+      <c r="BF59" t="inlineStr"/>
+      <c r="BG59" t="inlineStr"/>
+      <c r="BH59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -11954,6 +12206,10 @@
       <c r="BB60" t="inlineStr"/>
       <c r="BC60" t="inlineStr"/>
       <c r="BD60" t="inlineStr"/>
+      <c r="BE60" t="inlineStr"/>
+      <c r="BF60" t="inlineStr"/>
+      <c r="BG60" t="inlineStr"/>
+      <c r="BH60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -12148,6 +12404,10 @@
       <c r="BB61" t="inlineStr"/>
       <c r="BC61" t="inlineStr"/>
       <c r="BD61" t="inlineStr"/>
+      <c r="BE61" t="inlineStr"/>
+      <c r="BF61" t="inlineStr"/>
+      <c r="BG61" t="inlineStr"/>
+      <c r="BH61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -12342,6 +12602,10 @@
       <c r="BB62" t="inlineStr"/>
       <c r="BC62" t="inlineStr"/>
       <c r="BD62" t="inlineStr"/>
+      <c r="BE62" t="inlineStr"/>
+      <c r="BF62" t="inlineStr"/>
+      <c r="BG62" t="inlineStr"/>
+      <c r="BH62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -12540,6 +12804,10 @@
       <c r="BB63" t="inlineStr"/>
       <c r="BC63" t="inlineStr"/>
       <c r="BD63" t="inlineStr"/>
+      <c r="BE63" t="inlineStr"/>
+      <c r="BF63" t="inlineStr"/>
+      <c r="BG63" t="inlineStr"/>
+      <c r="BH63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -12734,6 +13002,10 @@
       <c r="BB64" t="inlineStr"/>
       <c r="BC64" t="inlineStr"/>
       <c r="BD64" t="inlineStr"/>
+      <c r="BE64" t="inlineStr"/>
+      <c r="BF64" t="inlineStr"/>
+      <c r="BG64" t="inlineStr"/>
+      <c r="BH64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -12928,6 +13200,10 @@
       <c r="BB65" t="inlineStr"/>
       <c r="BC65" t="inlineStr"/>
       <c r="BD65" t="inlineStr"/>
+      <c r="BE65" t="inlineStr"/>
+      <c r="BF65" t="inlineStr"/>
+      <c r="BG65" t="inlineStr"/>
+      <c r="BH65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -13122,6 +13398,10 @@
       <c r="BB66" t="inlineStr"/>
       <c r="BC66" t="inlineStr"/>
       <c r="BD66" t="inlineStr"/>
+      <c r="BE66" t="inlineStr"/>
+      <c r="BF66" t="inlineStr"/>
+      <c r="BG66" t="inlineStr"/>
+      <c r="BH66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -13316,6 +13596,10 @@
       <c r="BB67" t="inlineStr"/>
       <c r="BC67" t="inlineStr"/>
       <c r="BD67" t="inlineStr"/>
+      <c r="BE67" t="inlineStr"/>
+      <c r="BF67" t="inlineStr"/>
+      <c r="BG67" t="inlineStr"/>
+      <c r="BH67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -13510,6 +13794,10 @@
       <c r="BB68" t="inlineStr"/>
       <c r="BC68" t="inlineStr"/>
       <c r="BD68" t="inlineStr"/>
+      <c r="BE68" t="inlineStr"/>
+      <c r="BF68" t="inlineStr"/>
+      <c r="BG68" t="inlineStr"/>
+      <c r="BH68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -13704,6 +13992,10 @@
       <c r="BB69" t="inlineStr"/>
       <c r="BC69" t="inlineStr"/>
       <c r="BD69" t="inlineStr"/>
+      <c r="BE69" t="inlineStr"/>
+      <c r="BF69" t="inlineStr"/>
+      <c r="BG69" t="inlineStr"/>
+      <c r="BH69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -13898,6 +14190,10 @@
       <c r="BB70" t="inlineStr"/>
       <c r="BC70" t="inlineStr"/>
       <c r="BD70" t="inlineStr"/>
+      <c r="BE70" t="inlineStr"/>
+      <c r="BF70" t="inlineStr"/>
+      <c r="BG70" t="inlineStr"/>
+      <c r="BH70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -14092,6 +14388,10 @@
       <c r="BB71" t="inlineStr"/>
       <c r="BC71" t="inlineStr"/>
       <c r="BD71" t="inlineStr"/>
+      <c r="BE71" t="inlineStr"/>
+      <c r="BF71" t="inlineStr"/>
+      <c r="BG71" t="inlineStr"/>
+      <c r="BH71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -14286,6 +14586,10 @@
       <c r="BB72" t="inlineStr"/>
       <c r="BC72" t="inlineStr"/>
       <c r="BD72" t="inlineStr"/>
+      <c r="BE72" t="inlineStr"/>
+      <c r="BF72" t="inlineStr"/>
+      <c r="BG72" t="inlineStr"/>
+      <c r="BH72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -14480,6 +14784,10 @@
       <c r="BB73" t="inlineStr"/>
       <c r="BC73" t="inlineStr"/>
       <c r="BD73" t="inlineStr"/>
+      <c r="BE73" t="inlineStr"/>
+      <c r="BF73" t="inlineStr"/>
+      <c r="BG73" t="inlineStr"/>
+      <c r="BH73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -14678,6 +14986,10 @@
       <c r="BB74" t="inlineStr"/>
       <c r="BC74" t="inlineStr"/>
       <c r="BD74" t="inlineStr"/>
+      <c r="BE74" t="inlineStr"/>
+      <c r="BF74" t="inlineStr"/>
+      <c r="BG74" t="inlineStr"/>
+      <c r="BH74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -14872,6 +15184,10 @@
       <c r="BB75" t="inlineStr"/>
       <c r="BC75" t="inlineStr"/>
       <c r="BD75" t="inlineStr"/>
+      <c r="BE75" t="inlineStr"/>
+      <c r="BF75" t="inlineStr"/>
+      <c r="BG75" t="inlineStr"/>
+      <c r="BH75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -15066,6 +15382,10 @@
       <c r="BB76" t="inlineStr"/>
       <c r="BC76" t="inlineStr"/>
       <c r="BD76" t="inlineStr"/>
+      <c r="BE76" t="inlineStr"/>
+      <c r="BF76" t="inlineStr"/>
+      <c r="BG76" t="inlineStr"/>
+      <c r="BH76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -15260,6 +15580,10 @@
       <c r="BB77" t="inlineStr"/>
       <c r="BC77" t="inlineStr"/>
       <c r="BD77" t="inlineStr"/>
+      <c r="BE77" t="inlineStr"/>
+      <c r="BF77" t="inlineStr"/>
+      <c r="BG77" t="inlineStr"/>
+      <c r="BH77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -15454,6 +15778,10 @@
       <c r="BB78" t="inlineStr"/>
       <c r="BC78" t="inlineStr"/>
       <c r="BD78" t="inlineStr"/>
+      <c r="BE78" t="inlineStr"/>
+      <c r="BF78" t="inlineStr"/>
+      <c r="BG78" t="inlineStr"/>
+      <c r="BH78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -15648,6 +15976,10 @@
       <c r="BB79" t="inlineStr"/>
       <c r="BC79" t="inlineStr"/>
       <c r="BD79" t="inlineStr"/>
+      <c r="BE79" t="inlineStr"/>
+      <c r="BF79" t="inlineStr"/>
+      <c r="BG79" t="inlineStr"/>
+      <c r="BH79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -15842,6 +16174,10 @@
       <c r="BB80" t="inlineStr"/>
       <c r="BC80" t="inlineStr"/>
       <c r="BD80" t="inlineStr"/>
+      <c r="BE80" t="inlineStr"/>
+      <c r="BF80" t="inlineStr"/>
+      <c r="BG80" t="inlineStr"/>
+      <c r="BH80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -16036,6 +16372,10 @@
       <c r="BB81" t="inlineStr"/>
       <c r="BC81" t="inlineStr"/>
       <c r="BD81" t="inlineStr"/>
+      <c r="BE81" t="inlineStr"/>
+      <c r="BF81" t="inlineStr"/>
+      <c r="BG81" t="inlineStr"/>
+      <c r="BH81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -16230,6 +16570,10 @@
       <c r="BB82" t="inlineStr"/>
       <c r="BC82" t="inlineStr"/>
       <c r="BD82" t="inlineStr"/>
+      <c r="BE82" t="inlineStr"/>
+      <c r="BF82" t="inlineStr"/>
+      <c r="BG82" t="inlineStr"/>
+      <c r="BH82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -16420,6 +16764,10 @@
       <c r="BB83" t="inlineStr"/>
       <c r="BC83" t="inlineStr"/>
       <c r="BD83" t="inlineStr"/>
+      <c r="BE83" t="inlineStr"/>
+      <c r="BF83" t="inlineStr"/>
+      <c r="BG83" t="inlineStr"/>
+      <c r="BH83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -16614,6 +16962,10 @@
       <c r="BB84" t="inlineStr"/>
       <c r="BC84" t="inlineStr"/>
       <c r="BD84" t="inlineStr"/>
+      <c r="BE84" t="inlineStr"/>
+      <c r="BF84" t="inlineStr"/>
+      <c r="BG84" t="inlineStr"/>
+      <c r="BH84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -16808,6 +17160,10 @@
       <c r="BB85" t="inlineStr"/>
       <c r="BC85" t="inlineStr"/>
       <c r="BD85" t="inlineStr"/>
+      <c r="BE85" t="inlineStr"/>
+      <c r="BF85" t="inlineStr"/>
+      <c r="BG85" t="inlineStr"/>
+      <c r="BH85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -17002,6 +17358,10 @@
       <c r="BB86" t="inlineStr"/>
       <c r="BC86" t="inlineStr"/>
       <c r="BD86" t="inlineStr"/>
+      <c r="BE86" t="inlineStr"/>
+      <c r="BF86" t="inlineStr"/>
+      <c r="BG86" t="inlineStr"/>
+      <c r="BH86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -17196,6 +17556,10 @@
       <c r="BB87" t="inlineStr"/>
       <c r="BC87" t="inlineStr"/>
       <c r="BD87" t="inlineStr"/>
+      <c r="BE87" t="inlineStr"/>
+      <c r="BF87" t="inlineStr"/>
+      <c r="BG87" t="inlineStr"/>
+      <c r="BH87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -17390,6 +17754,10 @@
       <c r="BB88" t="inlineStr"/>
       <c r="BC88" t="inlineStr"/>
       <c r="BD88" t="inlineStr"/>
+      <c r="BE88" t="inlineStr"/>
+      <c r="BF88" t="inlineStr"/>
+      <c r="BG88" t="inlineStr"/>
+      <c r="BH88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -17588,6 +17956,10 @@
       <c r="BB89" t="inlineStr"/>
       <c r="BC89" t="inlineStr"/>
       <c r="BD89" t="inlineStr"/>
+      <c r="BE89" t="inlineStr"/>
+      <c r="BF89" t="inlineStr"/>
+      <c r="BG89" t="inlineStr"/>
+      <c r="BH89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
@@ -17782,6 +18154,10 @@
       <c r="BB90" t="inlineStr"/>
       <c r="BC90" t="inlineStr"/>
       <c r="BD90" t="inlineStr"/>
+      <c r="BE90" t="inlineStr"/>
+      <c r="BF90" t="inlineStr"/>
+      <c r="BG90" t="inlineStr"/>
+      <c r="BH90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -17980,6 +18356,10 @@
       <c r="BB91" t="inlineStr"/>
       <c r="BC91" t="inlineStr"/>
       <c r="BD91" t="inlineStr"/>
+      <c r="BE91" t="inlineStr"/>
+      <c r="BF91" t="inlineStr"/>
+      <c r="BG91" t="inlineStr"/>
+      <c r="BH91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -18174,6 +18554,10 @@
       <c r="BB92" t="inlineStr"/>
       <c r="BC92" t="inlineStr"/>
       <c r="BD92" t="inlineStr"/>
+      <c r="BE92" t="inlineStr"/>
+      <c r="BF92" t="inlineStr"/>
+      <c r="BG92" t="inlineStr"/>
+      <c r="BH92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -18368,6 +18752,10 @@
       <c r="BB93" t="inlineStr"/>
       <c r="BC93" t="inlineStr"/>
       <c r="BD93" t="inlineStr"/>
+      <c r="BE93" t="inlineStr"/>
+      <c r="BF93" t="inlineStr"/>
+      <c r="BG93" t="inlineStr"/>
+      <c r="BH93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -18562,6 +18950,10 @@
       <c r="BB94" t="inlineStr"/>
       <c r="BC94" t="inlineStr"/>
       <c r="BD94" t="inlineStr"/>
+      <c r="BE94" t="inlineStr"/>
+      <c r="BF94" t="inlineStr"/>
+      <c r="BG94" t="inlineStr"/>
+      <c r="BH94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -18756,6 +19148,10 @@
       <c r="BB95" t="inlineStr"/>
       <c r="BC95" t="inlineStr"/>
       <c r="BD95" t="inlineStr"/>
+      <c r="BE95" t="inlineStr"/>
+      <c r="BF95" t="inlineStr"/>
+      <c r="BG95" t="inlineStr"/>
+      <c r="BH95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -18954,6 +19350,10 @@
       <c r="BB96" t="inlineStr"/>
       <c r="BC96" t="inlineStr"/>
       <c r="BD96" t="inlineStr"/>
+      <c r="BE96" t="inlineStr"/>
+      <c r="BF96" t="inlineStr"/>
+      <c r="BG96" t="inlineStr"/>
+      <c r="BH96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -19148,6 +19548,10 @@
       <c r="BB97" t="inlineStr"/>
       <c r="BC97" t="inlineStr"/>
       <c r="BD97" t="inlineStr"/>
+      <c r="BE97" t="inlineStr"/>
+      <c r="BF97" t="inlineStr"/>
+      <c r="BG97" t="inlineStr"/>
+      <c r="BH97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -19342,6 +19746,10 @@
       <c r="BB98" t="inlineStr"/>
       <c r="BC98" t="inlineStr"/>
       <c r="BD98" t="inlineStr"/>
+      <c r="BE98" t="inlineStr"/>
+      <c r="BF98" t="inlineStr"/>
+      <c r="BG98" t="inlineStr"/>
+      <c r="BH98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
@@ -19536,6 +19944,10 @@
       <c r="BB99" t="inlineStr"/>
       <c r="BC99" t="inlineStr"/>
       <c r="BD99" t="inlineStr"/>
+      <c r="BE99" t="inlineStr"/>
+      <c r="BF99" t="inlineStr"/>
+      <c r="BG99" t="inlineStr"/>
+      <c r="BH99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -19730,6 +20142,10 @@
       <c r="BB100" t="inlineStr"/>
       <c r="BC100" t="inlineStr"/>
       <c r="BD100" t="inlineStr"/>
+      <c r="BE100" t="inlineStr"/>
+      <c r="BF100" t="inlineStr"/>
+      <c r="BG100" t="inlineStr"/>
+      <c r="BH100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -19928,6 +20344,10 @@
       <c r="BB101" t="inlineStr"/>
       <c r="BC101" t="inlineStr"/>
       <c r="BD101" t="inlineStr"/>
+      <c r="BE101" t="inlineStr"/>
+      <c r="BF101" t="inlineStr"/>
+      <c r="BG101" t="inlineStr"/>
+      <c r="BH101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -20122,6 +20542,10 @@
       <c r="BB102" t="inlineStr"/>
       <c r="BC102" t="inlineStr"/>
       <c r="BD102" t="inlineStr"/>
+      <c r="BE102" t="inlineStr"/>
+      <c r="BF102" t="inlineStr"/>
+      <c r="BG102" t="inlineStr"/>
+      <c r="BH102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -20316,6 +20740,10 @@
       <c r="BB103" t="inlineStr"/>
       <c r="BC103" t="inlineStr"/>
       <c r="BD103" t="inlineStr"/>
+      <c r="BE103" t="inlineStr"/>
+      <c r="BF103" t="inlineStr"/>
+      <c r="BG103" t="inlineStr"/>
+      <c r="BH103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -20510,6 +20938,10 @@
       <c r="BB104" t="inlineStr"/>
       <c r="BC104" t="inlineStr"/>
       <c r="BD104" t="inlineStr"/>
+      <c r="BE104" t="inlineStr"/>
+      <c r="BF104" t="inlineStr"/>
+      <c r="BG104" t="inlineStr"/>
+      <c r="BH104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -20704,6 +21136,10 @@
       <c r="BB105" t="inlineStr"/>
       <c r="BC105" t="inlineStr"/>
       <c r="BD105" t="inlineStr"/>
+      <c r="BE105" t="inlineStr"/>
+      <c r="BF105" t="inlineStr"/>
+      <c r="BG105" t="inlineStr"/>
+      <c r="BH105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -20898,6 +21334,10 @@
       <c r="BB106" t="inlineStr"/>
       <c r="BC106" t="inlineStr"/>
       <c r="BD106" t="inlineStr"/>
+      <c r="BE106" t="inlineStr"/>
+      <c r="BF106" t="inlineStr"/>
+      <c r="BG106" t="inlineStr"/>
+      <c r="BH106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
@@ -21096,6 +21536,10 @@
       <c r="BB107" t="inlineStr"/>
       <c r="BC107" t="inlineStr"/>
       <c r="BD107" t="inlineStr"/>
+      <c r="BE107" t="inlineStr"/>
+      <c r="BF107" t="inlineStr"/>
+      <c r="BG107" t="inlineStr"/>
+      <c r="BH107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -21290,6 +21734,10 @@
       <c r="BB108" t="inlineStr"/>
       <c r="BC108" t="inlineStr"/>
       <c r="BD108" t="inlineStr"/>
+      <c r="BE108" t="inlineStr"/>
+      <c r="BF108" t="inlineStr"/>
+      <c r="BG108" t="inlineStr"/>
+      <c r="BH108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -21488,6 +21936,10 @@
       <c r="BB109" t="inlineStr"/>
       <c r="BC109" t="inlineStr"/>
       <c r="BD109" t="inlineStr"/>
+      <c r="BE109" t="inlineStr"/>
+      <c r="BF109" t="inlineStr"/>
+      <c r="BG109" t="inlineStr"/>
+      <c r="BH109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
@@ -21682,6 +22134,10 @@
       <c r="BB110" t="inlineStr"/>
       <c r="BC110" t="inlineStr"/>
       <c r="BD110" t="inlineStr"/>
+      <c r="BE110" t="inlineStr"/>
+      <c r="BF110" t="inlineStr"/>
+      <c r="BG110" t="inlineStr"/>
+      <c r="BH110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -21876,6 +22332,10 @@
       <c r="BB111" t="inlineStr"/>
       <c r="BC111" t="inlineStr"/>
       <c r="BD111" t="inlineStr"/>
+      <c r="BE111" t="inlineStr"/>
+      <c r="BF111" t="inlineStr"/>
+      <c r="BG111" t="inlineStr"/>
+      <c r="BH111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -22070,6 +22530,10 @@
       <c r="BB112" t="inlineStr"/>
       <c r="BC112" t="inlineStr"/>
       <c r="BD112" t="inlineStr"/>
+      <c r="BE112" t="inlineStr"/>
+      <c r="BF112" t="inlineStr"/>
+      <c r="BG112" t="inlineStr"/>
+      <c r="BH112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -22264,6 +22728,10 @@
       <c r="BB113" t="inlineStr"/>
       <c r="BC113" t="inlineStr"/>
       <c r="BD113" t="inlineStr"/>
+      <c r="BE113" t="inlineStr"/>
+      <c r="BF113" t="inlineStr"/>
+      <c r="BG113" t="inlineStr"/>
+      <c r="BH113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
@@ -22458,6 +22926,10 @@
       <c r="BB114" t="inlineStr"/>
       <c r="BC114" t="inlineStr"/>
       <c r="BD114" t="inlineStr"/>
+      <c r="BE114" t="inlineStr"/>
+      <c r="BF114" t="inlineStr"/>
+      <c r="BG114" t="inlineStr"/>
+      <c r="BH114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -22652,6 +23124,10 @@
       <c r="BB115" t="inlineStr"/>
       <c r="BC115" t="inlineStr"/>
       <c r="BD115" t="inlineStr"/>
+      <c r="BE115" t="inlineStr"/>
+      <c r="BF115" t="inlineStr"/>
+      <c r="BG115" t="inlineStr"/>
+      <c r="BH115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -22846,6 +23322,10 @@
       <c r="BB116" t="inlineStr"/>
       <c r="BC116" t="inlineStr"/>
       <c r="BD116" t="inlineStr"/>
+      <c r="BE116" t="inlineStr"/>
+      <c r="BF116" t="inlineStr"/>
+      <c r="BG116" t="inlineStr"/>
+      <c r="BH116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
@@ -23040,6 +23520,10 @@
       <c r="BB117" t="inlineStr"/>
       <c r="BC117" t="inlineStr"/>
       <c r="BD117" t="inlineStr"/>
+      <c r="BE117" t="inlineStr"/>
+      <c r="BF117" t="inlineStr"/>
+      <c r="BG117" t="inlineStr"/>
+      <c r="BH117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
@@ -23234,6 +23718,10 @@
       <c r="BB118" t="inlineStr"/>
       <c r="BC118" t="inlineStr"/>
       <c r="BD118" t="inlineStr"/>
+      <c r="BE118" t="inlineStr"/>
+      <c r="BF118" t="inlineStr"/>
+      <c r="BG118" t="inlineStr"/>
+      <c r="BH118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
@@ -23428,6 +23916,10 @@
       <c r="BB119" t="inlineStr"/>
       <c r="BC119" t="inlineStr"/>
       <c r="BD119" t="inlineStr"/>
+      <c r="BE119" t="inlineStr"/>
+      <c r="BF119" t="inlineStr"/>
+      <c r="BG119" t="inlineStr"/>
+      <c r="BH119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -23622,6 +24114,10 @@
       <c r="BB120" t="inlineStr"/>
       <c r="BC120" t="inlineStr"/>
       <c r="BD120" t="inlineStr"/>
+      <c r="BE120" t="inlineStr"/>
+      <c r="BF120" t="inlineStr"/>
+      <c r="BG120" t="inlineStr"/>
+      <c r="BH120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
@@ -23816,6 +24312,10 @@
       <c r="BB121" t="inlineStr"/>
       <c r="BC121" t="inlineStr"/>
       <c r="BD121" t="inlineStr"/>
+      <c r="BE121" t="inlineStr"/>
+      <c r="BF121" t="inlineStr"/>
+      <c r="BG121" t="inlineStr"/>
+      <c r="BH121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -24010,6 +24510,10 @@
       <c r="BB122" t="inlineStr"/>
       <c r="BC122" t="inlineStr"/>
       <c r="BD122" t="inlineStr"/>
+      <c r="BE122" t="inlineStr"/>
+      <c r="BF122" t="inlineStr"/>
+      <c r="BG122" t="inlineStr"/>
+      <c r="BH122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -24204,6 +24708,10 @@
       <c r="BB123" t="inlineStr"/>
       <c r="BC123" t="inlineStr"/>
       <c r="BD123" t="inlineStr"/>
+      <c r="BE123" t="inlineStr"/>
+      <c r="BF123" t="inlineStr"/>
+      <c r="BG123" t="inlineStr"/>
+      <c r="BH123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -24398,6 +24906,10 @@
       <c r="BB124" t="inlineStr"/>
       <c r="BC124" t="inlineStr"/>
       <c r="BD124" t="inlineStr"/>
+      <c r="BE124" t="inlineStr"/>
+      <c r="BF124" t="inlineStr"/>
+      <c r="BG124" t="inlineStr"/>
+      <c r="BH124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
@@ -24596,6 +25108,10 @@
       <c r="BB125" t="inlineStr"/>
       <c r="BC125" t="inlineStr"/>
       <c r="BD125" t="inlineStr"/>
+      <c r="BE125" t="inlineStr"/>
+      <c r="BF125" t="inlineStr"/>
+      <c r="BG125" t="inlineStr"/>
+      <c r="BH125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
@@ -24794,6 +25310,10 @@
       <c r="BB126" t="inlineStr"/>
       <c r="BC126" t="inlineStr"/>
       <c r="BD126" t="inlineStr"/>
+      <c r="BE126" t="inlineStr"/>
+      <c r="BF126" t="inlineStr"/>
+      <c r="BG126" t="inlineStr"/>
+      <c r="BH126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
@@ -24988,6 +25508,10 @@
       <c r="BB127" t="inlineStr"/>
       <c r="BC127" t="inlineStr"/>
       <c r="BD127" t="inlineStr"/>
+      <c r="BE127" t="inlineStr"/>
+      <c r="BF127" t="inlineStr"/>
+      <c r="BG127" t="inlineStr"/>
+      <c r="BH127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -25182,6 +25706,10 @@
       <c r="BB128" t="inlineStr"/>
       <c r="BC128" t="inlineStr"/>
       <c r="BD128" t="inlineStr"/>
+      <c r="BE128" t="inlineStr"/>
+      <c r="BF128" t="inlineStr"/>
+      <c r="BG128" t="inlineStr"/>
+      <c r="BH128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -25376,6 +25904,10 @@
       <c r="BB129" t="inlineStr"/>
       <c r="BC129" t="inlineStr"/>
       <c r="BD129" t="inlineStr"/>
+      <c r="BE129" t="inlineStr"/>
+      <c r="BF129" t="inlineStr"/>
+      <c r="BG129" t="inlineStr"/>
+      <c r="BH129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -25570,6 +26102,10 @@
       <c r="BB130" t="inlineStr"/>
       <c r="BC130" t="inlineStr"/>
       <c r="BD130" t="inlineStr"/>
+      <c r="BE130" t="inlineStr"/>
+      <c r="BF130" t="inlineStr"/>
+      <c r="BG130" t="inlineStr"/>
+      <c r="BH130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -25768,6 +26304,10 @@
       <c r="BB131" t="inlineStr"/>
       <c r="BC131" t="inlineStr"/>
       <c r="BD131" t="inlineStr"/>
+      <c r="BE131" t="inlineStr"/>
+      <c r="BF131" t="inlineStr"/>
+      <c r="BG131" t="inlineStr"/>
+      <c r="BH131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
@@ -25966,6 +26506,10 @@
       <c r="BB132" t="inlineStr"/>
       <c r="BC132" t="inlineStr"/>
       <c r="BD132" t="inlineStr"/>
+      <c r="BE132" t="inlineStr"/>
+      <c r="BF132" t="inlineStr"/>
+      <c r="BG132" t="inlineStr"/>
+      <c r="BH132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
@@ -26160,6 +26704,10 @@
       <c r="BB133" t="inlineStr"/>
       <c r="BC133" t="inlineStr"/>
       <c r="BD133" t="inlineStr"/>
+      <c r="BE133" t="inlineStr"/>
+      <c r="BF133" t="inlineStr"/>
+      <c r="BG133" t="inlineStr"/>
+      <c r="BH133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
@@ -26354,6 +26902,10 @@
       <c r="BB134" t="inlineStr"/>
       <c r="BC134" t="inlineStr"/>
       <c r="BD134" t="inlineStr"/>
+      <c r="BE134" t="inlineStr"/>
+      <c r="BF134" t="inlineStr"/>
+      <c r="BG134" t="inlineStr"/>
+      <c r="BH134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
@@ -26548,6 +27100,10 @@
       <c r="BB135" t="inlineStr"/>
       <c r="BC135" t="inlineStr"/>
       <c r="BD135" t="inlineStr"/>
+      <c r="BE135" t="inlineStr"/>
+      <c r="BF135" t="inlineStr"/>
+      <c r="BG135" t="inlineStr"/>
+      <c r="BH135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
@@ -26742,6 +27298,10 @@
       <c r="BB136" t="inlineStr"/>
       <c r="BC136" t="inlineStr"/>
       <c r="BD136" t="inlineStr"/>
+      <c r="BE136" t="inlineStr"/>
+      <c r="BF136" t="inlineStr"/>
+      <c r="BG136" t="inlineStr"/>
+      <c r="BH136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
@@ -26936,6 +27496,10 @@
       <c r="BB137" t="inlineStr"/>
       <c r="BC137" t="inlineStr"/>
       <c r="BD137" t="inlineStr"/>
+      <c r="BE137" t="inlineStr"/>
+      <c r="BF137" t="inlineStr"/>
+      <c r="BG137" t="inlineStr"/>
+      <c r="BH137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
@@ -27130,6 +27694,10 @@
       <c r="BB138" t="inlineStr"/>
       <c r="BC138" t="inlineStr"/>
       <c r="BD138" t="inlineStr"/>
+      <c r="BE138" t="inlineStr"/>
+      <c r="BF138" t="inlineStr"/>
+      <c r="BG138" t="inlineStr"/>
+      <c r="BH138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
@@ -27328,6 +27896,10 @@
       <c r="BB139" t="inlineStr"/>
       <c r="BC139" t="inlineStr"/>
       <c r="BD139" t="inlineStr"/>
+      <c r="BE139" t="inlineStr"/>
+      <c r="BF139" t="inlineStr"/>
+      <c r="BG139" t="inlineStr"/>
+      <c r="BH139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
@@ -27522,6 +28094,10 @@
       <c r="BB140" t="inlineStr"/>
       <c r="BC140" t="inlineStr"/>
       <c r="BD140" t="inlineStr"/>
+      <c r="BE140" t="inlineStr"/>
+      <c r="BF140" t="inlineStr"/>
+      <c r="BG140" t="inlineStr"/>
+      <c r="BH140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
@@ -27716,6 +28292,10 @@
       <c r="BB141" t="inlineStr"/>
       <c r="BC141" t="inlineStr"/>
       <c r="BD141" t="inlineStr"/>
+      <c r="BE141" t="inlineStr"/>
+      <c r="BF141" t="inlineStr"/>
+      <c r="BG141" t="inlineStr"/>
+      <c r="BH141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
@@ -27910,6 +28490,10 @@
       <c r="BB142" t="inlineStr"/>
       <c r="BC142" t="inlineStr"/>
       <c r="BD142" t="inlineStr"/>
+      <c r="BE142" t="inlineStr"/>
+      <c r="BF142" t="inlineStr"/>
+      <c r="BG142" t="inlineStr"/>
+      <c r="BH142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
@@ -28104,6 +28688,10 @@
       <c r="BB143" t="inlineStr"/>
       <c r="BC143" t="inlineStr"/>
       <c r="BD143" t="inlineStr"/>
+      <c r="BE143" t="inlineStr"/>
+      <c r="BF143" t="inlineStr"/>
+      <c r="BG143" t="inlineStr"/>
+      <c r="BH143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
@@ -28298,6 +28886,10 @@
       <c r="BB144" t="inlineStr"/>
       <c r="BC144" t="inlineStr"/>
       <c r="BD144" t="inlineStr"/>
+      <c r="BE144" t="inlineStr"/>
+      <c r="BF144" t="inlineStr"/>
+      <c r="BG144" t="inlineStr"/>
+      <c r="BH144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
@@ -28496,6 +29088,10 @@
       <c r="BB145" t="inlineStr"/>
       <c r="BC145" t="inlineStr"/>
       <c r="BD145" t="inlineStr"/>
+      <c r="BE145" t="inlineStr"/>
+      <c r="BF145" t="inlineStr"/>
+      <c r="BG145" t="inlineStr"/>
+      <c r="BH145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
@@ -28690,6 +29286,10 @@
       <c r="BB146" t="inlineStr"/>
       <c r="BC146" t="inlineStr"/>
       <c r="BD146" t="inlineStr"/>
+      <c r="BE146" t="inlineStr"/>
+      <c r="BF146" t="inlineStr"/>
+      <c r="BG146" t="inlineStr"/>
+      <c r="BH146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
@@ -28884,6 +29484,10 @@
       <c r="BB147" t="inlineStr"/>
       <c r="BC147" t="inlineStr"/>
       <c r="BD147" t="inlineStr"/>
+      <c r="BE147" t="inlineStr"/>
+      <c r="BF147" t="inlineStr"/>
+      <c r="BG147" t="inlineStr"/>
+      <c r="BH147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
@@ -29078,6 +29682,10 @@
       <c r="BB148" t="inlineStr"/>
       <c r="BC148" t="inlineStr"/>
       <c r="BD148" t="inlineStr"/>
+      <c r="BE148" t="inlineStr"/>
+      <c r="BF148" t="inlineStr"/>
+      <c r="BG148" t="inlineStr"/>
+      <c r="BH148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
@@ -29272,6 +29880,10 @@
       <c r="BB149" t="inlineStr"/>
       <c r="BC149" t="inlineStr"/>
       <c r="BD149" t="inlineStr"/>
+      <c r="BE149" t="inlineStr"/>
+      <c r="BF149" t="inlineStr"/>
+      <c r="BG149" t="inlineStr"/>
+      <c r="BH149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
@@ -29466,6 +30078,10 @@
       <c r="BB150" t="inlineStr"/>
       <c r="BC150" t="inlineStr"/>
       <c r="BD150" t="inlineStr"/>
+      <c r="BE150" t="inlineStr"/>
+      <c r="BF150" t="inlineStr"/>
+      <c r="BG150" t="inlineStr"/>
+      <c r="BH150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
@@ -29660,6 +30276,10 @@
       <c r="BB151" t="inlineStr"/>
       <c r="BC151" t="inlineStr"/>
       <c r="BD151" t="inlineStr"/>
+      <c r="BE151" t="inlineStr"/>
+      <c r="BF151" t="inlineStr"/>
+      <c r="BG151" t="inlineStr"/>
+      <c r="BH151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
@@ -29854,6 +30474,10 @@
       <c r="BB152" t="inlineStr"/>
       <c r="BC152" t="inlineStr"/>
       <c r="BD152" t="inlineStr"/>
+      <c r="BE152" t="inlineStr"/>
+      <c r="BF152" t="inlineStr"/>
+      <c r="BG152" t="inlineStr"/>
+      <c r="BH152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
@@ -30052,6 +30676,10 @@
       <c r="BB153" t="inlineStr"/>
       <c r="BC153" t="inlineStr"/>
       <c r="BD153" t="inlineStr"/>
+      <c r="BE153" t="inlineStr"/>
+      <c r="BF153" t="inlineStr"/>
+      <c r="BG153" t="inlineStr"/>
+      <c r="BH153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
@@ -30250,6 +30878,10 @@
       <c r="BB154" t="inlineStr"/>
       <c r="BC154" t="inlineStr"/>
       <c r="BD154" t="inlineStr"/>
+      <c r="BE154" t="inlineStr"/>
+      <c r="BF154" t="inlineStr"/>
+      <c r="BG154" t="inlineStr"/>
+      <c r="BH154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
@@ -30444,6 +31076,10 @@
       <c r="BB155" t="inlineStr"/>
       <c r="BC155" t="inlineStr"/>
       <c r="BD155" t="inlineStr"/>
+      <c r="BE155" t="inlineStr"/>
+      <c r="BF155" t="inlineStr"/>
+      <c r="BG155" t="inlineStr"/>
+      <c r="BH155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
@@ -30642,6 +31278,10 @@
       <c r="BB156" t="inlineStr"/>
       <c r="BC156" t="inlineStr"/>
       <c r="BD156" t="inlineStr"/>
+      <c r="BE156" t="inlineStr"/>
+      <c r="BF156" t="inlineStr"/>
+      <c r="BG156" t="inlineStr"/>
+      <c r="BH156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
@@ -30836,6 +31476,10 @@
       <c r="BB157" t="inlineStr"/>
       <c r="BC157" t="inlineStr"/>
       <c r="BD157" t="inlineStr"/>
+      <c r="BE157" t="inlineStr"/>
+      <c r="BF157" t="inlineStr"/>
+      <c r="BG157" t="inlineStr"/>
+      <c r="BH157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
@@ -31030,6 +31674,10 @@
       <c r="BB158" t="inlineStr"/>
       <c r="BC158" t="inlineStr"/>
       <c r="BD158" t="inlineStr"/>
+      <c r="BE158" t="inlineStr"/>
+      <c r="BF158" t="inlineStr"/>
+      <c r="BG158" t="inlineStr"/>
+      <c r="BH158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
@@ -31224,6 +31872,10 @@
       <c r="BB159" t="inlineStr"/>
       <c r="BC159" t="inlineStr"/>
       <c r="BD159" t="inlineStr"/>
+      <c r="BE159" t="inlineStr"/>
+      <c r="BF159" t="inlineStr"/>
+      <c r="BG159" t="inlineStr"/>
+      <c r="BH159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
@@ -31418,6 +32070,10 @@
       <c r="BB160" t="inlineStr"/>
       <c r="BC160" t="inlineStr"/>
       <c r="BD160" t="inlineStr"/>
+      <c r="BE160" t="inlineStr"/>
+      <c r="BF160" t="inlineStr"/>
+      <c r="BG160" t="inlineStr"/>
+      <c r="BH160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
@@ -31612,6 +32268,10 @@
       <c r="BB161" t="inlineStr"/>
       <c r="BC161" t="inlineStr"/>
       <c r="BD161" t="inlineStr"/>
+      <c r="BE161" t="inlineStr"/>
+      <c r="BF161" t="inlineStr"/>
+      <c r="BG161" t="inlineStr"/>
+      <c r="BH161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
@@ -31806,6 +32466,10 @@
       <c r="BB162" t="inlineStr"/>
       <c r="BC162" t="inlineStr"/>
       <c r="BD162" t="inlineStr"/>
+      <c r="BE162" t="inlineStr"/>
+      <c r="BF162" t="inlineStr"/>
+      <c r="BG162" t="inlineStr"/>
+      <c r="BH162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
@@ -32000,6 +32664,10 @@
       <c r="BB163" t="inlineStr"/>
       <c r="BC163" t="inlineStr"/>
       <c r="BD163" t="inlineStr"/>
+      <c r="BE163" t="inlineStr"/>
+      <c r="BF163" t="inlineStr"/>
+      <c r="BG163" t="inlineStr"/>
+      <c r="BH163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
@@ -32194,6 +32862,10 @@
       <c r="BB164" t="inlineStr"/>
       <c r="BC164" t="inlineStr"/>
       <c r="BD164" t="inlineStr"/>
+      <c r="BE164" t="inlineStr"/>
+      <c r="BF164" t="inlineStr"/>
+      <c r="BG164" t="inlineStr"/>
+      <c r="BH164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
@@ -32388,6 +33060,10 @@
       <c r="BB165" t="inlineStr"/>
       <c r="BC165" t="inlineStr"/>
       <c r="BD165" t="inlineStr"/>
+      <c r="BE165" t="inlineStr"/>
+      <c r="BF165" t="inlineStr"/>
+      <c r="BG165" t="inlineStr"/>
+      <c r="BH165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
@@ -32582,6 +33258,10 @@
       <c r="BB166" t="inlineStr"/>
       <c r="BC166" t="inlineStr"/>
       <c r="BD166" t="inlineStr"/>
+      <c r="BE166" t="inlineStr"/>
+      <c r="BF166" t="inlineStr"/>
+      <c r="BG166" t="inlineStr"/>
+      <c r="BH166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
@@ -32776,6 +33456,10 @@
       <c r="BB167" t="inlineStr"/>
       <c r="BC167" t="inlineStr"/>
       <c r="BD167" t="inlineStr"/>
+      <c r="BE167" t="inlineStr"/>
+      <c r="BF167" t="inlineStr"/>
+      <c r="BG167" t="inlineStr"/>
+      <c r="BH167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
@@ -32974,6 +33658,10 @@
       <c r="BB168" t="inlineStr"/>
       <c r="BC168" t="inlineStr"/>
       <c r="BD168" t="inlineStr"/>
+      <c r="BE168" t="inlineStr"/>
+      <c r="BF168" t="inlineStr"/>
+      <c r="BG168" t="inlineStr"/>
+      <c r="BH168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
@@ -33168,6 +33856,10 @@
       <c r="BB169" t="inlineStr"/>
       <c r="BC169" t="inlineStr"/>
       <c r="BD169" t="inlineStr"/>
+      <c r="BE169" t="inlineStr"/>
+      <c r="BF169" t="inlineStr"/>
+      <c r="BG169" t="inlineStr"/>
+      <c r="BH169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
@@ -33362,6 +34054,10 @@
       <c r="BB170" t="inlineStr"/>
       <c r="BC170" t="inlineStr"/>
       <c r="BD170" t="inlineStr"/>
+      <c r="BE170" t="inlineStr"/>
+      <c r="BF170" t="inlineStr"/>
+      <c r="BG170" t="inlineStr"/>
+      <c r="BH170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
@@ -33556,6 +34252,10 @@
       <c r="BB171" t="inlineStr"/>
       <c r="BC171" t="inlineStr"/>
       <c r="BD171" t="inlineStr"/>
+      <c r="BE171" t="inlineStr"/>
+      <c r="BF171" t="inlineStr"/>
+      <c r="BG171" t="inlineStr"/>
+      <c r="BH171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
@@ -33750,6 +34450,10 @@
       <c r="BB172" t="inlineStr"/>
       <c r="BC172" t="inlineStr"/>
       <c r="BD172" t="inlineStr"/>
+      <c r="BE172" t="inlineStr"/>
+      <c r="BF172" t="inlineStr"/>
+      <c r="BG172" t="inlineStr"/>
+      <c r="BH172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
@@ -33932,6 +34636,10 @@
       <c r="BB173" t="inlineStr"/>
       <c r="BC173" t="inlineStr"/>
       <c r="BD173" t="inlineStr"/>
+      <c r="BE173" t="inlineStr"/>
+      <c r="BF173" t="inlineStr"/>
+      <c r="BG173" t="inlineStr"/>
+      <c r="BH173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
@@ -34114,6 +34822,10 @@
       <c r="BB174" t="inlineStr"/>
       <c r="BC174" t="inlineStr"/>
       <c r="BD174" t="inlineStr"/>
+      <c r="BE174" t="inlineStr"/>
+      <c r="BF174" t="inlineStr"/>
+      <c r="BG174" t="inlineStr"/>
+      <c r="BH174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
@@ -34300,6 +35012,10 @@
       <c r="BB175" t="inlineStr"/>
       <c r="BC175" t="inlineStr"/>
       <c r="BD175" t="inlineStr"/>
+      <c r="BE175" t="inlineStr"/>
+      <c r="BF175" t="inlineStr"/>
+      <c r="BG175" t="inlineStr"/>
+      <c r="BH175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
@@ -34482,6 +35198,10 @@
       <c r="BB176" t="inlineStr"/>
       <c r="BC176" t="inlineStr"/>
       <c r="BD176" t="inlineStr"/>
+      <c r="BE176" t="inlineStr"/>
+      <c r="BF176" t="inlineStr"/>
+      <c r="BG176" t="inlineStr"/>
+      <c r="BH176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
@@ -34664,6 +35384,10 @@
       <c r="BB177" t="inlineStr"/>
       <c r="BC177" t="inlineStr"/>
       <c r="BD177" t="inlineStr"/>
+      <c r="BE177" t="inlineStr"/>
+      <c r="BF177" t="inlineStr"/>
+      <c r="BG177" t="inlineStr"/>
+      <c r="BH177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
@@ -34846,6 +35570,10 @@
       <c r="BB178" t="inlineStr"/>
       <c r="BC178" t="inlineStr"/>
       <c r="BD178" t="inlineStr"/>
+      <c r="BE178" t="inlineStr"/>
+      <c r="BF178" t="inlineStr"/>
+      <c r="BG178" t="inlineStr"/>
+      <c r="BH178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
@@ -35028,6 +35756,10 @@
       <c r="BB179" t="inlineStr"/>
       <c r="BC179" t="inlineStr"/>
       <c r="BD179" t="inlineStr"/>
+      <c r="BE179" t="inlineStr"/>
+      <c r="BF179" t="inlineStr"/>
+      <c r="BG179" t="inlineStr"/>
+      <c r="BH179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
@@ -35214,6 +35946,10 @@
       <c r="BB180" t="inlineStr"/>
       <c r="BC180" t="inlineStr"/>
       <c r="BD180" t="inlineStr"/>
+      <c r="BE180" t="inlineStr"/>
+      <c r="BF180" t="inlineStr"/>
+      <c r="BG180" t="inlineStr"/>
+      <c r="BH180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
@@ -35396,6 +36132,10 @@
       <c r="BB181" t="inlineStr"/>
       <c r="BC181" t="inlineStr"/>
       <c r="BD181" t="inlineStr"/>
+      <c r="BE181" t="inlineStr"/>
+      <c r="BF181" t="inlineStr"/>
+      <c r="BG181" t="inlineStr"/>
+      <c r="BH181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
@@ -35578,6 +36318,10 @@
       <c r="BB182" t="inlineStr"/>
       <c r="BC182" t="inlineStr"/>
       <c r="BD182" t="inlineStr"/>
+      <c r="BE182" t="inlineStr"/>
+      <c r="BF182" t="inlineStr"/>
+      <c r="BG182" t="inlineStr"/>
+      <c r="BH182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
@@ -35760,6 +36504,10 @@
       <c r="BB183" t="inlineStr"/>
       <c r="BC183" t="inlineStr"/>
       <c r="BD183" t="inlineStr"/>
+      <c r="BE183" t="inlineStr"/>
+      <c r="BF183" t="inlineStr"/>
+      <c r="BG183" t="inlineStr"/>
+      <c r="BH183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
@@ -35946,6 +36694,10 @@
       <c r="BB184" t="inlineStr"/>
       <c r="BC184" t="inlineStr"/>
       <c r="BD184" t="inlineStr"/>
+      <c r="BE184" t="inlineStr"/>
+      <c r="BF184" t="inlineStr"/>
+      <c r="BG184" t="inlineStr"/>
+      <c r="BH184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
@@ -36132,6 +36884,10 @@
       <c r="BB185" t="inlineStr"/>
       <c r="BC185" t="inlineStr"/>
       <c r="BD185" t="inlineStr"/>
+      <c r="BE185" t="inlineStr"/>
+      <c r="BF185" t="inlineStr"/>
+      <c r="BG185" t="inlineStr"/>
+      <c r="BH185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
@@ -36314,6 +37070,10 @@
       <c r="BB186" t="inlineStr"/>
       <c r="BC186" t="inlineStr"/>
       <c r="BD186" t="inlineStr"/>
+      <c r="BE186" t="inlineStr"/>
+      <c r="BF186" t="inlineStr"/>
+      <c r="BG186" t="inlineStr"/>
+      <c r="BH186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
@@ -36496,6 +37256,10 @@
       <c r="BB187" t="inlineStr"/>
       <c r="BC187" t="inlineStr"/>
       <c r="BD187" t="inlineStr"/>
+      <c r="BE187" t="inlineStr"/>
+      <c r="BF187" t="inlineStr"/>
+      <c r="BG187" t="inlineStr"/>
+      <c r="BH187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
@@ -36678,6 +37442,10 @@
       <c r="BB188" t="inlineStr"/>
       <c r="BC188" t="inlineStr"/>
       <c r="BD188" t="inlineStr"/>
+      <c r="BE188" t="inlineStr"/>
+      <c r="BF188" t="inlineStr"/>
+      <c r="BG188" t="inlineStr"/>
+      <c r="BH188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
@@ -36860,6 +37628,10 @@
       <c r="BB189" t="inlineStr"/>
       <c r="BC189" t="inlineStr"/>
       <c r="BD189" t="inlineStr"/>
+      <c r="BE189" t="inlineStr"/>
+      <c r="BF189" t="inlineStr"/>
+      <c r="BG189" t="inlineStr"/>
+      <c r="BH189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
@@ -37042,6 +37814,10 @@
       <c r="BB190" t="inlineStr"/>
       <c r="BC190" t="inlineStr"/>
       <c r="BD190" t="inlineStr"/>
+      <c r="BE190" t="inlineStr"/>
+      <c r="BF190" t="inlineStr"/>
+      <c r="BG190" t="inlineStr"/>
+      <c r="BH190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
@@ -37224,6 +38000,10 @@
       <c r="BB191" t="inlineStr"/>
       <c r="BC191" t="inlineStr"/>
       <c r="BD191" t="inlineStr"/>
+      <c r="BE191" t="inlineStr"/>
+      <c r="BF191" t="inlineStr"/>
+      <c r="BG191" t="inlineStr"/>
+      <c r="BH191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
@@ -37410,6 +38190,10 @@
       <c r="BB192" t="inlineStr"/>
       <c r="BC192" t="inlineStr"/>
       <c r="BD192" t="inlineStr"/>
+      <c r="BE192" t="inlineStr"/>
+      <c r="BF192" t="inlineStr"/>
+      <c r="BG192" t="inlineStr"/>
+      <c r="BH192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
@@ -37592,6 +38376,10 @@
       <c r="BB193" t="inlineStr"/>
       <c r="BC193" t="inlineStr"/>
       <c r="BD193" t="inlineStr"/>
+      <c r="BE193" t="inlineStr"/>
+      <c r="BF193" t="inlineStr"/>
+      <c r="BG193" t="inlineStr"/>
+      <c r="BH193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
@@ -37774,6 +38562,10 @@
       <c r="BB194" t="inlineStr"/>
       <c r="BC194" t="inlineStr"/>
       <c r="BD194" t="inlineStr"/>
+      <c r="BE194" t="inlineStr"/>
+      <c r="BF194" t="inlineStr"/>
+      <c r="BG194" t="inlineStr"/>
+      <c r="BH194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
@@ -37964,6 +38756,10 @@
       <c r="BB195" t="inlineStr"/>
       <c r="BC195" t="inlineStr"/>
       <c r="BD195" t="inlineStr"/>
+      <c r="BE195" t="inlineStr"/>
+      <c r="BF195" t="inlineStr"/>
+      <c r="BG195" t="inlineStr"/>
+      <c r="BH195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
@@ -38154,6 +38950,10 @@
       <c r="BB196" t="inlineStr"/>
       <c r="BC196" t="inlineStr"/>
       <c r="BD196" t="inlineStr"/>
+      <c r="BE196" t="inlineStr"/>
+      <c r="BF196" t="inlineStr"/>
+      <c r="BG196" t="inlineStr"/>
+      <c r="BH196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
@@ -38344,6 +39144,10 @@
       <c r="BB197" t="inlineStr"/>
       <c r="BC197" t="inlineStr"/>
       <c r="BD197" t="inlineStr"/>
+      <c r="BE197" t="inlineStr"/>
+      <c r="BF197" t="inlineStr"/>
+      <c r="BG197" t="inlineStr"/>
+      <c r="BH197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
@@ -38534,6 +39338,10 @@
       <c r="BB198" t="inlineStr"/>
       <c r="BC198" t="inlineStr"/>
       <c r="BD198" t="inlineStr"/>
+      <c r="BE198" t="inlineStr"/>
+      <c r="BF198" t="inlineStr"/>
+      <c r="BG198" t="inlineStr"/>
+      <c r="BH198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
@@ -38724,6 +39532,10 @@
       <c r="BB199" t="inlineStr"/>
       <c r="BC199" t="inlineStr"/>
       <c r="BD199" t="inlineStr"/>
+      <c r="BE199" t="inlineStr"/>
+      <c r="BF199" t="inlineStr"/>
+      <c r="BG199" t="inlineStr"/>
+      <c r="BH199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
@@ -38914,6 +39726,10 @@
       <c r="BB200" t="inlineStr"/>
       <c r="BC200" t="inlineStr"/>
       <c r="BD200" t="inlineStr"/>
+      <c r="BE200" t="inlineStr"/>
+      <c r="BF200" t="inlineStr"/>
+      <c r="BG200" t="inlineStr"/>
+      <c r="BH200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
@@ -39104,6 +39920,10 @@
       <c r="BB201" t="inlineStr"/>
       <c r="BC201" t="inlineStr"/>
       <c r="BD201" t="inlineStr"/>
+      <c r="BE201" t="inlineStr"/>
+      <c r="BF201" t="inlineStr"/>
+      <c r="BG201" t="inlineStr"/>
+      <c r="BH201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
@@ -39294,6 +40114,10 @@
       <c r="BB202" t="inlineStr"/>
       <c r="BC202" t="inlineStr"/>
       <c r="BD202" t="inlineStr"/>
+      <c r="BE202" t="inlineStr"/>
+      <c r="BF202" t="inlineStr"/>
+      <c r="BG202" t="inlineStr"/>
+      <c r="BH202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
@@ -39484,6 +40308,10 @@
       <c r="BB203" t="inlineStr"/>
       <c r="BC203" t="inlineStr"/>
       <c r="BD203" t="inlineStr"/>
+      <c r="BE203" t="inlineStr"/>
+      <c r="BF203" t="inlineStr"/>
+      <c r="BG203" t="inlineStr"/>
+      <c r="BH203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
@@ -39678,6 +40506,10 @@
       <c r="BB204" t="inlineStr"/>
       <c r="BC204" t="inlineStr"/>
       <c r="BD204" t="inlineStr"/>
+      <c r="BE204" t="inlineStr"/>
+      <c r="BF204" t="inlineStr"/>
+      <c r="BG204" t="inlineStr"/>
+      <c r="BH204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
@@ -39864,6 +40696,10 @@
       <c r="BB205" t="inlineStr"/>
       <c r="BC205" t="inlineStr"/>
       <c r="BD205" t="inlineStr"/>
+      <c r="BE205" t="inlineStr"/>
+      <c r="BF205" t="inlineStr"/>
+      <c r="BG205" t="inlineStr"/>
+      <c r="BH205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
@@ -40054,6 +40890,10 @@
       <c r="BB206" t="inlineStr"/>
       <c r="BC206" t="inlineStr"/>
       <c r="BD206" t="inlineStr"/>
+      <c r="BE206" t="inlineStr"/>
+      <c r="BF206" t="inlineStr"/>
+      <c r="BG206" t="inlineStr"/>
+      <c r="BH206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
@@ -40244,6 +41084,10 @@
       <c r="BB207" t="inlineStr"/>
       <c r="BC207" t="inlineStr"/>
       <c r="BD207" t="inlineStr"/>
+      <c r="BE207" t="inlineStr"/>
+      <c r="BF207" t="inlineStr"/>
+      <c r="BG207" t="inlineStr"/>
+      <c r="BH207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
@@ -40442,6 +41286,10 @@
       <c r="BD208" t="n">
         <v>286</v>
       </c>
+      <c r="BE208" t="inlineStr"/>
+      <c r="BF208" t="inlineStr"/>
+      <c r="BG208" t="inlineStr"/>
+      <c r="BH208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
@@ -40644,6 +41492,10 @@
       <c r="BD209" t="n">
         <v>405</v>
       </c>
+      <c r="BE209" t="inlineStr"/>
+      <c r="BF209" t="inlineStr"/>
+      <c r="BG209" t="inlineStr"/>
+      <c r="BH209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
@@ -40834,6 +41686,10 @@
       <c r="BB210" t="inlineStr"/>
       <c r="BC210" t="inlineStr"/>
       <c r="BD210" t="inlineStr"/>
+      <c r="BE210" t="inlineStr"/>
+      <c r="BF210" t="inlineStr"/>
+      <c r="BG210" t="inlineStr"/>
+      <c r="BH210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
@@ -41024,6 +41880,10 @@
       <c r="BB211" t="inlineStr"/>
       <c r="BC211" t="inlineStr"/>
       <c r="BD211" t="inlineStr"/>
+      <c r="BE211" t="inlineStr"/>
+      <c r="BF211" t="inlineStr"/>
+      <c r="BG211" t="inlineStr"/>
+      <c r="BH211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
@@ -41210,6 +42070,10 @@
       <c r="BB212" t="inlineStr"/>
       <c r="BC212" t="inlineStr"/>
       <c r="BD212" t="inlineStr"/>
+      <c r="BE212" t="inlineStr"/>
+      <c r="BF212" t="inlineStr"/>
+      <c r="BG212" t="inlineStr"/>
+      <c r="BH212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
@@ -41400,6 +42264,10 @@
       <c r="BB213" t="inlineStr"/>
       <c r="BC213" t="inlineStr"/>
       <c r="BD213" t="inlineStr"/>
+      <c r="BE213" t="inlineStr"/>
+      <c r="BF213" t="inlineStr"/>
+      <c r="BG213" t="inlineStr"/>
+      <c r="BH213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
@@ -41594,6 +42462,10 @@
       <c r="BB214" t="inlineStr"/>
       <c r="BC214" t="inlineStr"/>
       <c r="BD214" t="inlineStr"/>
+      <c r="BE214" t="inlineStr"/>
+      <c r="BF214" t="inlineStr"/>
+      <c r="BG214" t="inlineStr"/>
+      <c r="BH214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
@@ -41784,6 +42656,10 @@
       <c r="BB215" t="inlineStr"/>
       <c r="BC215" t="inlineStr"/>
       <c r="BD215" t="inlineStr"/>
+      <c r="BE215" t="inlineStr"/>
+      <c r="BF215" t="inlineStr"/>
+      <c r="BG215" t="inlineStr"/>
+      <c r="BH215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
@@ -41978,6 +42854,10 @@
       <c r="BB216" t="inlineStr"/>
       <c r="BC216" t="inlineStr"/>
       <c r="BD216" t="inlineStr"/>
+      <c r="BE216" t="inlineStr"/>
+      <c r="BF216" t="inlineStr"/>
+      <c r="BG216" t="inlineStr"/>
+      <c r="BH216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
@@ -42168,6 +43048,10 @@
       <c r="BB217" t="inlineStr"/>
       <c r="BC217" t="inlineStr"/>
       <c r="BD217" t="inlineStr"/>
+      <c r="BE217" t="inlineStr"/>
+      <c r="BF217" t="inlineStr"/>
+      <c r="BG217" t="inlineStr"/>
+      <c r="BH217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
@@ -42358,6 +43242,10 @@
       <c r="BB218" t="inlineStr"/>
       <c r="BC218" t="inlineStr"/>
       <c r="BD218" t="inlineStr"/>
+      <c r="BE218" t="inlineStr"/>
+      <c r="BF218" t="inlineStr"/>
+      <c r="BG218" t="inlineStr"/>
+      <c r="BH218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
@@ -42548,6 +43436,10 @@
       <c r="BB219" t="inlineStr"/>
       <c r="BC219" t="inlineStr"/>
       <c r="BD219" t="inlineStr"/>
+      <c r="BE219" t="inlineStr"/>
+      <c r="BF219" t="inlineStr"/>
+      <c r="BG219" t="inlineStr"/>
+      <c r="BH219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
@@ -42738,6 +43630,10 @@
       <c r="BB220" t="inlineStr"/>
       <c r="BC220" t="inlineStr"/>
       <c r="BD220" t="inlineStr"/>
+      <c r="BE220" t="inlineStr"/>
+      <c r="BF220" t="inlineStr"/>
+      <c r="BG220" t="inlineStr"/>
+      <c r="BH220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
@@ -42928,6 +43824,10 @@
       <c r="BB221" t="inlineStr"/>
       <c r="BC221" t="inlineStr"/>
       <c r="BD221" t="inlineStr"/>
+      <c r="BE221" t="inlineStr"/>
+      <c r="BF221" t="inlineStr"/>
+      <c r="BG221" t="inlineStr"/>
+      <c r="BH221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
@@ -43118,6 +44018,10 @@
       <c r="BB222" t="inlineStr"/>
       <c r="BC222" t="inlineStr"/>
       <c r="BD222" t="inlineStr"/>
+      <c r="BE222" t="inlineStr"/>
+      <c r="BF222" t="inlineStr"/>
+      <c r="BG222" t="inlineStr"/>
+      <c r="BH222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
@@ -43308,6 +44212,10 @@
       <c r="BB223" t="inlineStr"/>
       <c r="BC223" t="inlineStr"/>
       <c r="BD223" t="inlineStr"/>
+      <c r="BE223" t="inlineStr"/>
+      <c r="BF223" t="inlineStr"/>
+      <c r="BG223" t="inlineStr"/>
+      <c r="BH223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
@@ -43502,6 +44410,10 @@
       <c r="BB224" t="inlineStr"/>
       <c r="BC224" t="inlineStr"/>
       <c r="BD224" t="inlineStr"/>
+      <c r="BE224" t="inlineStr"/>
+      <c r="BF224" t="inlineStr"/>
+      <c r="BG224" t="inlineStr"/>
+      <c r="BH224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
@@ -43692,6 +44604,10 @@
       <c r="BB225" t="inlineStr"/>
       <c r="BC225" t="inlineStr"/>
       <c r="BD225" t="inlineStr"/>
+      <c r="BE225" t="inlineStr"/>
+      <c r="BF225" t="inlineStr"/>
+      <c r="BG225" t="inlineStr"/>
+      <c r="BH225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
@@ -43882,6 +44798,10 @@
       <c r="BB226" t="inlineStr"/>
       <c r="BC226" t="inlineStr"/>
       <c r="BD226" t="inlineStr"/>
+      <c r="BE226" t="inlineStr"/>
+      <c r="BF226" t="inlineStr"/>
+      <c r="BG226" t="inlineStr"/>
+      <c r="BH226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
@@ -44072,6 +44992,10 @@
       <c r="BB227" t="inlineStr"/>
       <c r="BC227" t="inlineStr"/>
       <c r="BD227" t="inlineStr"/>
+      <c r="BE227" t="inlineStr"/>
+      <c r="BF227" t="inlineStr"/>
+      <c r="BG227" t="inlineStr"/>
+      <c r="BH227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
@@ -44266,6 +45190,10 @@
       <c r="BB228" t="inlineStr"/>
       <c r="BC228" t="inlineStr"/>
       <c r="BD228" t="inlineStr"/>
+      <c r="BE228" t="inlineStr"/>
+      <c r="BF228" t="inlineStr"/>
+      <c r="BG228" t="inlineStr"/>
+      <c r="BH228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
@@ -44456,6 +45384,10 @@
       <c r="BB229" t="inlineStr"/>
       <c r="BC229" t="inlineStr"/>
       <c r="BD229" t="inlineStr"/>
+      <c r="BE229" t="inlineStr"/>
+      <c r="BF229" t="inlineStr"/>
+      <c r="BG229" t="inlineStr"/>
+      <c r="BH229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
@@ -44646,6 +45578,10 @@
       <c r="BB230" t="inlineStr"/>
       <c r="BC230" t="inlineStr"/>
       <c r="BD230" t="inlineStr"/>
+      <c r="BE230" t="inlineStr"/>
+      <c r="BF230" t="inlineStr"/>
+      <c r="BG230" t="inlineStr"/>
+      <c r="BH230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
@@ -44836,6 +45772,10 @@
       <c r="BB231" t="inlineStr"/>
       <c r="BC231" t="inlineStr"/>
       <c r="BD231" t="inlineStr"/>
+      <c r="BE231" t="inlineStr"/>
+      <c r="BF231" t="inlineStr"/>
+      <c r="BG231" t="inlineStr"/>
+      <c r="BH231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
@@ -45026,6 +45966,10 @@
       <c r="BB232" t="inlineStr"/>
       <c r="BC232" t="inlineStr"/>
       <c r="BD232" t="inlineStr"/>
+      <c r="BE232" t="inlineStr"/>
+      <c r="BF232" t="inlineStr"/>
+      <c r="BG232" t="inlineStr"/>
+      <c r="BH232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
@@ -45220,6 +46164,10 @@
       <c r="BB233" t="inlineStr"/>
       <c r="BC233" t="inlineStr"/>
       <c r="BD233" t="inlineStr"/>
+      <c r="BE233" t="inlineStr"/>
+      <c r="BF233" t="inlineStr"/>
+      <c r="BG233" t="inlineStr"/>
+      <c r="BH233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
@@ -45410,6 +46358,10 @@
       <c r="BB234" t="inlineStr"/>
       <c r="BC234" t="inlineStr"/>
       <c r="BD234" t="inlineStr"/>
+      <c r="BE234" t="inlineStr"/>
+      <c r="BF234" t="inlineStr"/>
+      <c r="BG234" t="inlineStr"/>
+      <c r="BH234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
@@ -45600,6 +46552,10 @@
       <c r="BB235" t="inlineStr"/>
       <c r="BC235" t="inlineStr"/>
       <c r="BD235" t="inlineStr"/>
+      <c r="BE235" t="inlineStr"/>
+      <c r="BF235" t="inlineStr"/>
+      <c r="BG235" t="inlineStr"/>
+      <c r="BH235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
@@ -45790,6 +46746,10 @@
       <c r="BB236" t="inlineStr"/>
       <c r="BC236" t="inlineStr"/>
       <c r="BD236" t="inlineStr"/>
+      <c r="BE236" t="inlineStr"/>
+      <c r="BF236" t="inlineStr"/>
+      <c r="BG236" t="inlineStr"/>
+      <c r="BH236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
@@ -45980,6 +46940,10 @@
       <c r="BB237" t="inlineStr"/>
       <c r="BC237" t="inlineStr"/>
       <c r="BD237" t="inlineStr"/>
+      <c r="BE237" t="inlineStr"/>
+      <c r="BF237" t="inlineStr"/>
+      <c r="BG237" t="inlineStr"/>
+      <c r="BH237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
@@ -46170,6 +47134,10 @@
       <c r="BB238" t="inlineStr"/>
       <c r="BC238" t="inlineStr"/>
       <c r="BD238" t="inlineStr"/>
+      <c r="BE238" t="inlineStr"/>
+      <c r="BF238" t="inlineStr"/>
+      <c r="BG238" t="inlineStr"/>
+      <c r="BH238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
@@ -46360,6 +47328,10 @@
       <c r="BB239" t="inlineStr"/>
       <c r="BC239" t="inlineStr"/>
       <c r="BD239" t="inlineStr"/>
+      <c r="BE239" t="inlineStr"/>
+      <c r="BF239" t="inlineStr"/>
+      <c r="BG239" t="inlineStr"/>
+      <c r="BH239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
@@ -46550,6 +47522,10 @@
       <c r="BB240" t="inlineStr"/>
       <c r="BC240" t="inlineStr"/>
       <c r="BD240" t="inlineStr"/>
+      <c r="BE240" t="inlineStr"/>
+      <c r="BF240" t="inlineStr"/>
+      <c r="BG240" t="inlineStr"/>
+      <c r="BH240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
@@ -46740,6 +47716,10 @@
       <c r="BB241" t="inlineStr"/>
       <c r="BC241" t="inlineStr"/>
       <c r="BD241" t="inlineStr"/>
+      <c r="BE241" t="inlineStr"/>
+      <c r="BF241" t="inlineStr"/>
+      <c r="BG241" t="inlineStr"/>
+      <c r="BH241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
@@ -46930,6 +47910,10 @@
       <c r="BB242" t="inlineStr"/>
       <c r="BC242" t="inlineStr"/>
       <c r="BD242" t="inlineStr"/>
+      <c r="BE242" t="inlineStr"/>
+      <c r="BF242" t="inlineStr"/>
+      <c r="BG242" t="inlineStr"/>
+      <c r="BH242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
@@ -47120,6 +48104,10 @@
       <c r="BB243" t="inlineStr"/>
       <c r="BC243" t="inlineStr"/>
       <c r="BD243" t="inlineStr"/>
+      <c r="BE243" t="inlineStr"/>
+      <c r="BF243" t="inlineStr"/>
+      <c r="BG243" t="inlineStr"/>
+      <c r="BH243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
@@ -47310,6 +48298,10 @@
       <c r="BB244" t="inlineStr"/>
       <c r="BC244" t="inlineStr"/>
       <c r="BD244" t="inlineStr"/>
+      <c r="BE244" t="inlineStr"/>
+      <c r="BF244" t="inlineStr"/>
+      <c r="BG244" t="inlineStr"/>
+      <c r="BH244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
@@ -47500,6 +48492,10 @@
       <c r="BB245" t="inlineStr"/>
       <c r="BC245" t="inlineStr"/>
       <c r="BD245" t="inlineStr"/>
+      <c r="BE245" t="inlineStr"/>
+      <c r="BF245" t="inlineStr"/>
+      <c r="BG245" t="inlineStr"/>
+      <c r="BH245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
@@ -47690,6 +48686,10 @@
       <c r="BB246" t="inlineStr"/>
       <c r="BC246" t="inlineStr"/>
       <c r="BD246" t="inlineStr"/>
+      <c r="BE246" t="inlineStr"/>
+      <c r="BF246" t="inlineStr"/>
+      <c r="BG246" t="inlineStr"/>
+      <c r="BH246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
@@ -47880,6 +48880,10 @@
       <c r="BB247" t="inlineStr"/>
       <c r="BC247" t="inlineStr"/>
       <c r="BD247" t="inlineStr"/>
+      <c r="BE247" t="inlineStr"/>
+      <c r="BF247" t="inlineStr"/>
+      <c r="BG247" t="inlineStr"/>
+      <c r="BH247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
@@ -48070,6 +49074,10 @@
       <c r="BB248" t="inlineStr"/>
       <c r="BC248" t="inlineStr"/>
       <c r="BD248" t="inlineStr"/>
+      <c r="BE248" t="inlineStr"/>
+      <c r="BF248" t="inlineStr"/>
+      <c r="BG248" t="inlineStr"/>
+      <c r="BH248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
@@ -48260,6 +49268,10 @@
       <c r="BB249" t="inlineStr"/>
       <c r="BC249" t="inlineStr"/>
       <c r="BD249" t="inlineStr"/>
+      <c r="BE249" t="inlineStr"/>
+      <c r="BF249" t="inlineStr"/>
+      <c r="BG249" t="inlineStr"/>
+      <c r="BH249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
@@ -48451,6 +49463,10 @@
       <c r="BB250" t="inlineStr"/>
       <c r="BC250" t="inlineStr"/>
       <c r="BD250" t="inlineStr"/>
+      <c r="BE250" t="inlineStr"/>
+      <c r="BF250" t="inlineStr"/>
+      <c r="BG250" t="inlineStr"/>
+      <c r="BH250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
@@ -48641,6 +49657,10 @@
       <c r="BB251" t="inlineStr"/>
       <c r="BC251" t="inlineStr"/>
       <c r="BD251" t="inlineStr"/>
+      <c r="BE251" t="inlineStr"/>
+      <c r="BF251" t="inlineStr"/>
+      <c r="BG251" t="inlineStr"/>
+      <c r="BH251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
@@ -48836,6 +49856,10 @@
       <c r="BB252" t="inlineStr"/>
       <c r="BC252" t="inlineStr"/>
       <c r="BD252" t="inlineStr"/>
+      <c r="BE252" t="inlineStr"/>
+      <c r="BF252" t="inlineStr"/>
+      <c r="BG252" t="inlineStr"/>
+      <c r="BH252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
@@ -49027,6 +50051,10 @@
       <c r="BB253" t="inlineStr"/>
       <c r="BC253" t="inlineStr"/>
       <c r="BD253" t="inlineStr"/>
+      <c r="BE253" t="inlineStr"/>
+      <c r="BF253" t="inlineStr"/>
+      <c r="BG253" t="inlineStr"/>
+      <c r="BH253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
@@ -49225,6 +50253,10 @@
       <c r="BB254" t="inlineStr"/>
       <c r="BC254" t="inlineStr"/>
       <c r="BD254" t="inlineStr"/>
+      <c r="BE254" t="inlineStr"/>
+      <c r="BF254" t="inlineStr"/>
+      <c r="BG254" t="inlineStr"/>
+      <c r="BH254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
@@ -49419,6 +50451,10 @@
       <c r="BB255" t="inlineStr"/>
       <c r="BC255" t="inlineStr"/>
       <c r="BD255" t="inlineStr"/>
+      <c r="BE255" t="inlineStr"/>
+      <c r="BF255" t="inlineStr"/>
+      <c r="BG255" t="inlineStr"/>
+      <c r="BH255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
@@ -49613,6 +50649,10 @@
       <c r="BB256" t="inlineStr"/>
       <c r="BC256" t="inlineStr"/>
       <c r="BD256" t="inlineStr"/>
+      <c r="BE256" t="inlineStr"/>
+      <c r="BF256" t="inlineStr"/>
+      <c r="BG256" t="inlineStr"/>
+      <c r="BH256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
@@ -49807,6 +50847,10 @@
       <c r="BB257" t="inlineStr"/>
       <c r="BC257" t="inlineStr"/>
       <c r="BD257" t="inlineStr"/>
+      <c r="BE257" t="inlineStr"/>
+      <c r="BF257" t="inlineStr"/>
+      <c r="BG257" t="inlineStr"/>
+      <c r="BH257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
@@ -50001,6 +51045,10 @@
       <c r="BB258" t="inlineStr"/>
       <c r="BC258" t="inlineStr"/>
       <c r="BD258" t="inlineStr"/>
+      <c r="BE258" t="inlineStr"/>
+      <c r="BF258" t="inlineStr"/>
+      <c r="BG258" t="inlineStr"/>
+      <c r="BH258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
@@ -50195,6 +51243,10 @@
       <c r="BB259" t="inlineStr"/>
       <c r="BC259" t="inlineStr"/>
       <c r="BD259" t="inlineStr"/>
+      <c r="BE259" t="inlineStr"/>
+      <c r="BF259" t="inlineStr"/>
+      <c r="BG259" t="inlineStr"/>
+      <c r="BH259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
@@ -50389,6 +51441,10 @@
       <c r="BB260" t="inlineStr"/>
       <c r="BC260" t="inlineStr"/>
       <c r="BD260" t="inlineStr"/>
+      <c r="BE260" t="inlineStr"/>
+      <c r="BF260" t="inlineStr"/>
+      <c r="BG260" t="inlineStr"/>
+      <c r="BH260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
@@ -50583,6 +51639,10 @@
       <c r="BB261" t="inlineStr"/>
       <c r="BC261" t="inlineStr"/>
       <c r="BD261" t="inlineStr"/>
+      <c r="BE261" t="inlineStr"/>
+      <c r="BF261" t="inlineStr"/>
+      <c r="BG261" t="inlineStr"/>
+      <c r="BH261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
@@ -50777,6 +51837,10 @@
       <c r="BB262" t="inlineStr"/>
       <c r="BC262" t="inlineStr"/>
       <c r="BD262" t="inlineStr"/>
+      <c r="BE262" t="inlineStr"/>
+      <c r="BF262" t="inlineStr"/>
+      <c r="BG262" t="inlineStr"/>
+      <c r="BH262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
@@ -50971,6 +52035,10 @@
       <c r="BB263" t="inlineStr"/>
       <c r="BC263" t="inlineStr"/>
       <c r="BD263" t="inlineStr"/>
+      <c r="BE263" t="inlineStr"/>
+      <c r="BF263" t="inlineStr"/>
+      <c r="BG263" t="inlineStr"/>
+      <c r="BH263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
@@ -51161,6 +52229,10 @@
       <c r="BB264" t="inlineStr"/>
       <c r="BC264" t="inlineStr"/>
       <c r="BD264" t="inlineStr"/>
+      <c r="BE264" t="inlineStr"/>
+      <c r="BF264" t="inlineStr"/>
+      <c r="BG264" t="inlineStr"/>
+      <c r="BH264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
@@ -51355,6 +52427,10 @@
       <c r="BB265" t="inlineStr"/>
       <c r="BC265" t="inlineStr"/>
       <c r="BD265" t="inlineStr"/>
+      <c r="BE265" t="inlineStr"/>
+      <c r="BF265" t="inlineStr"/>
+      <c r="BG265" t="inlineStr"/>
+      <c r="BH265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
@@ -51549,6 +52625,10 @@
       <c r="BB266" t="inlineStr"/>
       <c r="BC266" t="inlineStr"/>
       <c r="BD266" t="inlineStr"/>
+      <c r="BE266" t="inlineStr"/>
+      <c r="BF266" t="inlineStr"/>
+      <c r="BG266" t="inlineStr"/>
+      <c r="BH266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
@@ -51743,6 +52823,10 @@
       <c r="BB267" t="inlineStr"/>
       <c r="BC267" t="inlineStr"/>
       <c r="BD267" t="inlineStr"/>
+      <c r="BE267" t="inlineStr"/>
+      <c r="BF267" t="inlineStr"/>
+      <c r="BG267" t="inlineStr"/>
+      <c r="BH267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
@@ -51937,6 +53021,10 @@
       <c r="BB268" t="inlineStr"/>
       <c r="BC268" t="inlineStr"/>
       <c r="BD268" t="inlineStr"/>
+      <c r="BE268" t="inlineStr"/>
+      <c r="BF268" t="inlineStr"/>
+      <c r="BG268" t="inlineStr"/>
+      <c r="BH268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
@@ -52131,6 +53219,10 @@
       <c r="BB269" t="inlineStr"/>
       <c r="BC269" t="inlineStr"/>
       <c r="BD269" t="inlineStr"/>
+      <c r="BE269" t="inlineStr"/>
+      <c r="BF269" t="inlineStr"/>
+      <c r="BG269" t="inlineStr"/>
+      <c r="BH269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
@@ -52325,6 +53417,10 @@
       <c r="BB270" t="inlineStr"/>
       <c r="BC270" t="inlineStr"/>
       <c r="BD270" t="inlineStr"/>
+      <c r="BE270" t="inlineStr"/>
+      <c r="BF270" t="inlineStr"/>
+      <c r="BG270" t="inlineStr"/>
+      <c r="BH270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
@@ -52519,6 +53615,10 @@
       <c r="BB271" t="inlineStr"/>
       <c r="BC271" t="inlineStr"/>
       <c r="BD271" t="inlineStr"/>
+      <c r="BE271" t="inlineStr"/>
+      <c r="BF271" t="inlineStr"/>
+      <c r="BG271" t="inlineStr"/>
+      <c r="BH271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
@@ -52713,6 +53813,10 @@
       <c r="BB272" t="inlineStr"/>
       <c r="BC272" t="inlineStr"/>
       <c r="BD272" t="inlineStr"/>
+      <c r="BE272" t="inlineStr"/>
+      <c r="BF272" t="inlineStr"/>
+      <c r="BG272" t="inlineStr"/>
+      <c r="BH272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
@@ -52907,6 +54011,10 @@
       <c r="BB273" t="inlineStr"/>
       <c r="BC273" t="inlineStr"/>
       <c r="BD273" t="inlineStr"/>
+      <c r="BE273" t="inlineStr"/>
+      <c r="BF273" t="inlineStr"/>
+      <c r="BG273" t="inlineStr"/>
+      <c r="BH273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
@@ -53101,6 +54209,10 @@
       <c r="BB274" t="inlineStr"/>
       <c r="BC274" t="inlineStr"/>
       <c r="BD274" t="inlineStr"/>
+      <c r="BE274" t="inlineStr"/>
+      <c r="BF274" t="inlineStr"/>
+      <c r="BG274" t="inlineStr"/>
+      <c r="BH274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
@@ -53295,6 +54407,10 @@
       <c r="BB275" t="inlineStr"/>
       <c r="BC275" t="inlineStr"/>
       <c r="BD275" t="inlineStr"/>
+      <c r="BE275" t="inlineStr"/>
+      <c r="BF275" t="inlineStr"/>
+      <c r="BG275" t="inlineStr"/>
+      <c r="BH275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
@@ -53489,6 +54605,10 @@
       <c r="BB276" t="inlineStr"/>
       <c r="BC276" t="inlineStr"/>
       <c r="BD276" t="inlineStr"/>
+      <c r="BE276" t="inlineStr"/>
+      <c r="BF276" t="inlineStr"/>
+      <c r="BG276" t="inlineStr"/>
+      <c r="BH276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
@@ -53687,6 +54807,10 @@
       <c r="BB277" t="inlineStr"/>
       <c r="BC277" t="inlineStr"/>
       <c r="BD277" t="inlineStr"/>
+      <c r="BE277" t="inlineStr"/>
+      <c r="BF277" t="inlineStr"/>
+      <c r="BG277" t="inlineStr"/>
+      <c r="BH277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
@@ -53881,6 +55005,10 @@
       <c r="BB278" t="inlineStr"/>
       <c r="BC278" t="inlineStr"/>
       <c r="BD278" t="inlineStr"/>
+      <c r="BE278" t="inlineStr"/>
+      <c r="BF278" t="inlineStr"/>
+      <c r="BG278" t="inlineStr"/>
+      <c r="BH278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
@@ -54075,6 +55203,10 @@
       <c r="BB279" t="inlineStr"/>
       <c r="BC279" t="inlineStr"/>
       <c r="BD279" t="inlineStr"/>
+      <c r="BE279" t="inlineStr"/>
+      <c r="BF279" t="inlineStr"/>
+      <c r="BG279" t="inlineStr"/>
+      <c r="BH279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
@@ -54269,6 +55401,10 @@
       <c r="BB280" t="inlineStr"/>
       <c r="BC280" t="inlineStr"/>
       <c r="BD280" t="inlineStr"/>
+      <c r="BE280" t="inlineStr"/>
+      <c r="BF280" t="inlineStr"/>
+      <c r="BG280" t="inlineStr"/>
+      <c r="BH280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
@@ -54463,6 +55599,10 @@
       <c r="BB281" t="inlineStr"/>
       <c r="BC281" t="inlineStr"/>
       <c r="BD281" t="inlineStr"/>
+      <c r="BE281" t="inlineStr"/>
+      <c r="BF281" t="inlineStr"/>
+      <c r="BG281" t="inlineStr"/>
+      <c r="BH281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
@@ -54661,6 +55801,10 @@
       <c r="BB282" t="inlineStr"/>
       <c r="BC282" t="inlineStr"/>
       <c r="BD282" t="inlineStr"/>
+      <c r="BE282" t="inlineStr"/>
+      <c r="BF282" t="inlineStr"/>
+      <c r="BG282" t="inlineStr"/>
+      <c r="BH282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
@@ -54855,6 +55999,10 @@
       <c r="BB283" t="inlineStr"/>
       <c r="BC283" t="inlineStr"/>
       <c r="BD283" t="inlineStr"/>
+      <c r="BE283" t="inlineStr"/>
+      <c r="BF283" t="inlineStr"/>
+      <c r="BG283" t="inlineStr"/>
+      <c r="BH283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
@@ -55049,6 +56197,10 @@
       <c r="BB284" t="inlineStr"/>
       <c r="BC284" t="inlineStr"/>
       <c r="BD284" t="inlineStr"/>
+      <c r="BE284" t="inlineStr"/>
+      <c r="BF284" t="inlineStr"/>
+      <c r="BG284" t="inlineStr"/>
+      <c r="BH284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
@@ -55243,6 +56395,10 @@
       <c r="BB285" t="inlineStr"/>
       <c r="BC285" t="inlineStr"/>
       <c r="BD285" t="inlineStr"/>
+      <c r="BE285" t="inlineStr"/>
+      <c r="BF285" t="inlineStr"/>
+      <c r="BG285" t="inlineStr"/>
+      <c r="BH285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
@@ -55441,6 +56597,10 @@
       <c r="BB286" t="inlineStr"/>
       <c r="BC286" t="inlineStr"/>
       <c r="BD286" t="inlineStr"/>
+      <c r="BE286" t="inlineStr"/>
+      <c r="BF286" t="inlineStr"/>
+      <c r="BG286" t="inlineStr"/>
+      <c r="BH286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
@@ -55635,6 +56795,10 @@
       <c r="BB287" t="inlineStr"/>
       <c r="BC287" t="inlineStr"/>
       <c r="BD287" t="inlineStr"/>
+      <c r="BE287" t="inlineStr"/>
+      <c r="BF287" t="inlineStr"/>
+      <c r="BG287" t="inlineStr"/>
+      <c r="BH287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
@@ -55829,6 +56993,10 @@
       <c r="BB288" t="inlineStr"/>
       <c r="BC288" t="inlineStr"/>
       <c r="BD288" t="inlineStr"/>
+      <c r="BE288" t="inlineStr"/>
+      <c r="BF288" t="inlineStr"/>
+      <c r="BG288" t="inlineStr"/>
+      <c r="BH288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
@@ -56023,6 +57191,10 @@
       <c r="BB289" t="inlineStr"/>
       <c r="BC289" t="inlineStr"/>
       <c r="BD289" t="inlineStr"/>
+      <c r="BE289" t="inlineStr"/>
+      <c r="BF289" t="inlineStr"/>
+      <c r="BG289" t="inlineStr"/>
+      <c r="BH289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
@@ -56217,6 +57389,10 @@
       <c r="BB290" t="inlineStr"/>
       <c r="BC290" t="inlineStr"/>
       <c r="BD290" t="inlineStr"/>
+      <c r="BE290" t="inlineStr"/>
+      <c r="BF290" t="inlineStr"/>
+      <c r="BG290" t="inlineStr"/>
+      <c r="BH290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
@@ -56411,6 +57587,10 @@
       <c r="BB291" t="inlineStr"/>
       <c r="BC291" t="inlineStr"/>
       <c r="BD291" t="inlineStr"/>
+      <c r="BE291" t="inlineStr"/>
+      <c r="BF291" t="inlineStr"/>
+      <c r="BG291" t="inlineStr"/>
+      <c r="BH291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
@@ -56609,6 +57789,10 @@
       <c r="BB292" t="inlineStr"/>
       <c r="BC292" t="inlineStr"/>
       <c r="BD292" t="inlineStr"/>
+      <c r="BE292" t="inlineStr"/>
+      <c r="BF292" t="inlineStr"/>
+      <c r="BG292" t="inlineStr"/>
+      <c r="BH292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
@@ -56807,6 +57991,10 @@
       <c r="BB293" t="inlineStr"/>
       <c r="BC293" t="inlineStr"/>
       <c r="BD293" t="inlineStr"/>
+      <c r="BE293" t="inlineStr"/>
+      <c r="BF293" t="inlineStr"/>
+      <c r="BG293" t="inlineStr"/>
+      <c r="BH293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
@@ -57005,6 +58193,10 @@
       <c r="BB294" t="inlineStr"/>
       <c r="BC294" t="inlineStr"/>
       <c r="BD294" t="inlineStr"/>
+      <c r="BE294" t="inlineStr"/>
+      <c r="BF294" t="inlineStr"/>
+      <c r="BG294" t="inlineStr"/>
+      <c r="BH294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
@@ -57203,6 +58395,10 @@
       <c r="BB295" t="inlineStr"/>
       <c r="BC295" t="inlineStr"/>
       <c r="BD295" t="inlineStr"/>
+      <c r="BE295" t="inlineStr"/>
+      <c r="BF295" t="inlineStr"/>
+      <c r="BG295" t="inlineStr"/>
+      <c r="BH295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
@@ -57397,6 +58593,10 @@
       <c r="BB296" t="inlineStr"/>
       <c r="BC296" t="inlineStr"/>
       <c r="BD296" t="inlineStr"/>
+      <c r="BE296" t="inlineStr"/>
+      <c r="BF296" t="inlineStr"/>
+      <c r="BG296" t="inlineStr"/>
+      <c r="BH296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
@@ -57591,6 +58791,10 @@
       <c r="BB297" t="inlineStr"/>
       <c r="BC297" t="inlineStr"/>
       <c r="BD297" t="inlineStr"/>
+      <c r="BE297" t="inlineStr"/>
+      <c r="BF297" t="inlineStr"/>
+      <c r="BG297" t="inlineStr"/>
+      <c r="BH297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
@@ -57785,6 +58989,10 @@
       <c r="BB298" t="inlineStr"/>
       <c r="BC298" t="inlineStr"/>
       <c r="BD298" t="inlineStr"/>
+      <c r="BE298" t="inlineStr"/>
+      <c r="BF298" t="inlineStr"/>
+      <c r="BG298" t="inlineStr"/>
+      <c r="BH298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
@@ -57979,6 +59187,10 @@
       <c r="BB299" t="inlineStr"/>
       <c r="BC299" t="inlineStr"/>
       <c r="BD299" t="inlineStr"/>
+      <c r="BE299" t="inlineStr"/>
+      <c r="BF299" t="inlineStr"/>
+      <c r="BG299" t="inlineStr"/>
+      <c r="BH299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
@@ -58173,6 +59385,10 @@
       <c r="BB300" t="inlineStr"/>
       <c r="BC300" t="inlineStr"/>
       <c r="BD300" t="inlineStr"/>
+      <c r="BE300" t="inlineStr"/>
+      <c r="BF300" t="inlineStr"/>
+      <c r="BG300" t="inlineStr"/>
+      <c r="BH300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
@@ -58371,6 +59587,10 @@
       <c r="BB301" t="inlineStr"/>
       <c r="BC301" t="inlineStr"/>
       <c r="BD301" t="inlineStr"/>
+      <c r="BE301" t="inlineStr"/>
+      <c r="BF301" t="inlineStr"/>
+      <c r="BG301" t="inlineStr"/>
+      <c r="BH301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
@@ -58565,6 +59785,10 @@
       <c r="BB302" t="inlineStr"/>
       <c r="BC302" t="inlineStr"/>
       <c r="BD302" t="inlineStr"/>
+      <c r="BE302" t="inlineStr"/>
+      <c r="BF302" t="inlineStr"/>
+      <c r="BG302" t="inlineStr"/>
+      <c r="BH302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
@@ -58763,6 +59987,10 @@
       <c r="BB303" t="inlineStr"/>
       <c r="BC303" t="inlineStr"/>
       <c r="BD303" t="inlineStr"/>
+      <c r="BE303" t="inlineStr"/>
+      <c r="BF303" t="inlineStr"/>
+      <c r="BG303" t="inlineStr"/>
+      <c r="BH303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
@@ -58957,6 +60185,10 @@
       <c r="BB304" t="inlineStr"/>
       <c r="BC304" t="inlineStr"/>
       <c r="BD304" t="inlineStr"/>
+      <c r="BE304" t="inlineStr"/>
+      <c r="BF304" t="inlineStr"/>
+      <c r="BG304" t="inlineStr"/>
+      <c r="BH304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
@@ -59151,6 +60383,10 @@
       <c r="BB305" t="inlineStr"/>
       <c r="BC305" t="inlineStr"/>
       <c r="BD305" t="inlineStr"/>
+      <c r="BE305" t="inlineStr"/>
+      <c r="BF305" t="inlineStr"/>
+      <c r="BG305" t="inlineStr"/>
+      <c r="BH305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
@@ -59345,6 +60581,10 @@
       <c r="BB306" t="inlineStr"/>
       <c r="BC306" t="inlineStr"/>
       <c r="BD306" t="inlineStr"/>
+      <c r="BE306" t="inlineStr"/>
+      <c r="BF306" t="inlineStr"/>
+      <c r="BG306" t="inlineStr"/>
+      <c r="BH306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
@@ -59543,6 +60783,10 @@
       <c r="BB307" t="inlineStr"/>
       <c r="BC307" t="inlineStr"/>
       <c r="BD307" t="inlineStr"/>
+      <c r="BE307" t="inlineStr"/>
+      <c r="BF307" t="inlineStr"/>
+      <c r="BG307" t="inlineStr"/>
+      <c r="BH307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
@@ -59737,6 +60981,10 @@
       <c r="BB308" t="inlineStr"/>
       <c r="BC308" t="inlineStr"/>
       <c r="BD308" t="inlineStr"/>
+      <c r="BE308" t="inlineStr"/>
+      <c r="BF308" t="inlineStr"/>
+      <c r="BG308" t="inlineStr"/>
+      <c r="BH308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
@@ -59935,6 +61183,10 @@
       <c r="BB309" t="inlineStr"/>
       <c r="BC309" t="inlineStr"/>
       <c r="BD309" t="inlineStr"/>
+      <c r="BE309" t="inlineStr"/>
+      <c r="BF309" t="inlineStr"/>
+      <c r="BG309" t="inlineStr"/>
+      <c r="BH309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
@@ -60129,6 +61381,10 @@
       <c r="BB310" t="inlineStr"/>
       <c r="BC310" t="inlineStr"/>
       <c r="BD310" t="inlineStr"/>
+      <c r="BE310" t="inlineStr"/>
+      <c r="BF310" t="inlineStr"/>
+      <c r="BG310" t="inlineStr"/>
+      <c r="BH310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
@@ -60323,6 +61579,10 @@
       <c r="BB311" t="inlineStr"/>
       <c r="BC311" t="inlineStr"/>
       <c r="BD311" t="inlineStr"/>
+      <c r="BE311" t="inlineStr"/>
+      <c r="BF311" t="inlineStr"/>
+      <c r="BG311" t="inlineStr"/>
+      <c r="BH311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
@@ -60517,6 +61777,10 @@
       <c r="BB312" t="inlineStr"/>
       <c r="BC312" t="inlineStr"/>
       <c r="BD312" t="inlineStr"/>
+      <c r="BE312" t="inlineStr"/>
+      <c r="BF312" t="inlineStr"/>
+      <c r="BG312" t="inlineStr"/>
+      <c r="BH312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
@@ -60711,6 +61975,10 @@
       <c r="BB313" t="inlineStr"/>
       <c r="BC313" t="inlineStr"/>
       <c r="BD313" t="inlineStr"/>
+      <c r="BE313" t="inlineStr"/>
+      <c r="BF313" t="inlineStr"/>
+      <c r="BG313" t="inlineStr"/>
+      <c r="BH313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
@@ -60905,6 +62173,10 @@
       <c r="BB314" t="inlineStr"/>
       <c r="BC314" t="inlineStr"/>
       <c r="BD314" t="inlineStr"/>
+      <c r="BE314" t="inlineStr"/>
+      <c r="BF314" t="inlineStr"/>
+      <c r="BG314" t="inlineStr"/>
+      <c r="BH314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
@@ -61099,6 +62371,10 @@
       <c r="BB315" t="inlineStr"/>
       <c r="BC315" t="inlineStr"/>
       <c r="BD315" t="inlineStr"/>
+      <c r="BE315" t="inlineStr"/>
+      <c r="BF315" t="inlineStr"/>
+      <c r="BG315" t="inlineStr"/>
+      <c r="BH315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
@@ -61293,6 +62569,10 @@
       <c r="BB316" t="inlineStr"/>
       <c r="BC316" t="inlineStr"/>
       <c r="BD316" t="inlineStr"/>
+      <c r="BE316" t="inlineStr"/>
+      <c r="BF316" t="inlineStr"/>
+      <c r="BG316" t="inlineStr"/>
+      <c r="BH316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
@@ -61487,6 +62767,10 @@
       <c r="BB317" t="inlineStr"/>
       <c r="BC317" t="inlineStr"/>
       <c r="BD317" t="inlineStr"/>
+      <c r="BE317" t="inlineStr"/>
+      <c r="BF317" t="inlineStr"/>
+      <c r="BG317" t="inlineStr"/>
+      <c r="BH317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
@@ -61681,6 +62965,10 @@
       <c r="BB318" t="inlineStr"/>
       <c r="BC318" t="inlineStr"/>
       <c r="BD318" t="inlineStr"/>
+      <c r="BE318" t="inlineStr"/>
+      <c r="BF318" t="inlineStr"/>
+      <c r="BG318" t="inlineStr"/>
+      <c r="BH318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
@@ -61875,6 +63163,10 @@
       <c r="BB319" t="inlineStr"/>
       <c r="BC319" t="inlineStr"/>
       <c r="BD319" t="inlineStr"/>
+      <c r="BE319" t="inlineStr"/>
+      <c r="BF319" t="inlineStr"/>
+      <c r="BG319" t="inlineStr"/>
+      <c r="BH319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
@@ -62069,6 +63361,10 @@
       <c r="BB320" t="inlineStr"/>
       <c r="BC320" t="inlineStr"/>
       <c r="BD320" t="inlineStr"/>
+      <c r="BE320" t="inlineStr"/>
+      <c r="BF320" t="inlineStr"/>
+      <c r="BG320" t="inlineStr"/>
+      <c r="BH320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
@@ -62263,6 +63559,10 @@
       <c r="BB321" t="inlineStr"/>
       <c r="BC321" t="inlineStr"/>
       <c r="BD321" t="inlineStr"/>
+      <c r="BE321" t="inlineStr"/>
+      <c r="BF321" t="inlineStr"/>
+      <c r="BG321" t="inlineStr"/>
+      <c r="BH321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
@@ -62461,6 +63761,10 @@
       <c r="BB322" t="inlineStr"/>
       <c r="BC322" t="inlineStr"/>
       <c r="BD322" t="inlineStr"/>
+      <c r="BE322" t="inlineStr"/>
+      <c r="BF322" t="inlineStr"/>
+      <c r="BG322" t="inlineStr"/>
+      <c r="BH322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
@@ -62655,6 +63959,10 @@
       <c r="BB323" t="inlineStr"/>
       <c r="BC323" t="inlineStr"/>
       <c r="BD323" t="inlineStr"/>
+      <c r="BE323" t="inlineStr"/>
+      <c r="BF323" t="inlineStr"/>
+      <c r="BG323" t="inlineStr"/>
+      <c r="BH323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
@@ -62853,6 +64161,10 @@
       <c r="BB324" t="inlineStr"/>
       <c r="BC324" t="inlineStr"/>
       <c r="BD324" t="inlineStr"/>
+      <c r="BE324" t="inlineStr"/>
+      <c r="BF324" t="inlineStr"/>
+      <c r="BG324" t="inlineStr"/>
+      <c r="BH324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
@@ -63047,6 +64359,10 @@
       <c r="BB325" t="inlineStr"/>
       <c r="BC325" t="inlineStr"/>
       <c r="BD325" t="inlineStr"/>
+      <c r="BE325" t="inlineStr"/>
+      <c r="BF325" t="inlineStr"/>
+      <c r="BG325" t="inlineStr"/>
+      <c r="BH325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
@@ -63241,6 +64557,10 @@
       <c r="BB326" t="inlineStr"/>
       <c r="BC326" t="inlineStr"/>
       <c r="BD326" t="inlineStr"/>
+      <c r="BE326" t="inlineStr"/>
+      <c r="BF326" t="inlineStr"/>
+      <c r="BG326" t="inlineStr"/>
+      <c r="BH326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
@@ -63439,6 +64759,10 @@
       <c r="BB327" t="inlineStr"/>
       <c r="BC327" t="inlineStr"/>
       <c r="BD327" t="inlineStr"/>
+      <c r="BE327" t="inlineStr"/>
+      <c r="BF327" t="inlineStr"/>
+      <c r="BG327" t="inlineStr"/>
+      <c r="BH327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
@@ -63633,6 +64957,10 @@
       <c r="BB328" t="inlineStr"/>
       <c r="BC328" t="inlineStr"/>
       <c r="BD328" t="inlineStr"/>
+      <c r="BE328" t="inlineStr"/>
+      <c r="BF328" t="inlineStr"/>
+      <c r="BG328" t="inlineStr"/>
+      <c r="BH328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
@@ -63827,6 +65155,10 @@
       <c r="BB329" t="inlineStr"/>
       <c r="BC329" t="inlineStr"/>
       <c r="BD329" t="inlineStr"/>
+      <c r="BE329" t="inlineStr"/>
+      <c r="BF329" t="inlineStr"/>
+      <c r="BG329" t="inlineStr"/>
+      <c r="BH329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
@@ -64021,6 +65353,10 @@
       <c r="BB330" t="inlineStr"/>
       <c r="BC330" t="inlineStr"/>
       <c r="BD330" t="inlineStr"/>
+      <c r="BE330" t="inlineStr"/>
+      <c r="BF330" t="inlineStr"/>
+      <c r="BG330" t="inlineStr"/>
+      <c r="BH330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
@@ -64219,6 +65555,10 @@
       <c r="BB331" t="inlineStr"/>
       <c r="BC331" t="inlineStr"/>
       <c r="BD331" t="inlineStr"/>
+      <c r="BE331" t="inlineStr"/>
+      <c r="BF331" t="inlineStr"/>
+      <c r="BG331" t="inlineStr"/>
+      <c r="BH331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
@@ -64413,6 +65753,10 @@
       <c r="BB332" t="inlineStr"/>
       <c r="BC332" t="inlineStr"/>
       <c r="BD332" t="inlineStr"/>
+      <c r="BE332" t="inlineStr"/>
+      <c r="BF332" t="inlineStr"/>
+      <c r="BG332" t="inlineStr"/>
+      <c r="BH332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
@@ -64607,6 +65951,10 @@
       <c r="BB333" t="inlineStr"/>
       <c r="BC333" t="inlineStr"/>
       <c r="BD333" t="inlineStr"/>
+      <c r="BE333" t="inlineStr"/>
+      <c r="BF333" t="inlineStr"/>
+      <c r="BG333" t="inlineStr"/>
+      <c r="BH333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
@@ -64801,6 +66149,10 @@
       <c r="BB334" t="inlineStr"/>
       <c r="BC334" t="inlineStr"/>
       <c r="BD334" t="inlineStr"/>
+      <c r="BE334" t="inlineStr"/>
+      <c r="BF334" t="inlineStr"/>
+      <c r="BG334" t="inlineStr"/>
+      <c r="BH334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
@@ -64995,6 +66347,10 @@
       <c r="BB335" t="inlineStr"/>
       <c r="BC335" t="inlineStr"/>
       <c r="BD335" t="inlineStr"/>
+      <c r="BE335" t="inlineStr"/>
+      <c r="BF335" t="inlineStr"/>
+      <c r="BG335" t="inlineStr"/>
+      <c r="BH335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
@@ -65189,6 +66545,10 @@
       <c r="BB336" t="inlineStr"/>
       <c r="BC336" t="inlineStr"/>
       <c r="BD336" t="inlineStr"/>
+      <c r="BE336" t="inlineStr"/>
+      <c r="BF336" t="inlineStr"/>
+      <c r="BG336" t="inlineStr"/>
+      <c r="BH336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
@@ -65387,6 +66747,10 @@
       <c r="BB337" t="inlineStr"/>
       <c r="BC337" t="inlineStr"/>
       <c r="BD337" t="inlineStr"/>
+      <c r="BE337" t="inlineStr"/>
+      <c r="BF337" t="inlineStr"/>
+      <c r="BG337" t="inlineStr"/>
+      <c r="BH337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
@@ -65581,6 +66945,10 @@
       <c r="BB338" t="inlineStr"/>
       <c r="BC338" t="inlineStr"/>
       <c r="BD338" t="inlineStr"/>
+      <c r="BE338" t="inlineStr"/>
+      <c r="BF338" t="inlineStr"/>
+      <c r="BG338" t="inlineStr"/>
+      <c r="BH338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
@@ -65775,6 +67143,10 @@
       <c r="BB339" t="inlineStr"/>
       <c r="BC339" t="inlineStr"/>
       <c r="BD339" t="inlineStr"/>
+      <c r="BE339" t="inlineStr"/>
+      <c r="BF339" t="inlineStr"/>
+      <c r="BG339" t="inlineStr"/>
+      <c r="BH339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
@@ -65969,6 +67341,10 @@
       <c r="BB340" t="inlineStr"/>
       <c r="BC340" t="inlineStr"/>
       <c r="BD340" t="inlineStr"/>
+      <c r="BE340" t="inlineStr"/>
+      <c r="BF340" t="inlineStr"/>
+      <c r="BG340" t="inlineStr"/>
+      <c r="BH340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="1" t="inlineStr">
@@ -66163,6 +67539,10 @@
       <c r="BB341" t="inlineStr"/>
       <c r="BC341" t="inlineStr"/>
       <c r="BD341" t="inlineStr"/>
+      <c r="BE341" t="inlineStr"/>
+      <c r="BF341" t="inlineStr"/>
+      <c r="BG341" t="inlineStr"/>
+      <c r="BH341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="1" t="inlineStr">
@@ -66357,6 +67737,10 @@
       <c r="BB342" t="inlineStr"/>
       <c r="BC342" t="inlineStr"/>
       <c r="BD342" t="inlineStr"/>
+      <c r="BE342" t="inlineStr"/>
+      <c r="BF342" t="inlineStr"/>
+      <c r="BG342" t="inlineStr"/>
+      <c r="BH342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="1" t="inlineStr">
@@ -66551,6 +67935,10 @@
       <c r="BB343" t="inlineStr"/>
       <c r="BC343" t="inlineStr"/>
       <c r="BD343" t="inlineStr"/>
+      <c r="BE343" t="inlineStr"/>
+      <c r="BF343" t="inlineStr"/>
+      <c r="BG343" t="inlineStr"/>
+      <c r="BH343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="1" t="inlineStr">
@@ -66749,6 +68137,10 @@
       <c r="BB344" t="inlineStr"/>
       <c r="BC344" t="inlineStr"/>
       <c r="BD344" t="inlineStr"/>
+      <c r="BE344" t="inlineStr"/>
+      <c r="BF344" t="inlineStr"/>
+      <c r="BG344" t="inlineStr"/>
+      <c r="BH344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="1" t="inlineStr">
@@ -66943,6 +68335,10 @@
       <c r="BB345" t="inlineStr"/>
       <c r="BC345" t="inlineStr"/>
       <c r="BD345" t="inlineStr"/>
+      <c r="BE345" t="inlineStr"/>
+      <c r="BF345" t="inlineStr"/>
+      <c r="BG345" t="inlineStr"/>
+      <c r="BH345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="1" t="inlineStr">
@@ -67141,6 +68537,10 @@
       <c r="BB346" t="inlineStr"/>
       <c r="BC346" t="inlineStr"/>
       <c r="BD346" t="inlineStr"/>
+      <c r="BE346" t="inlineStr"/>
+      <c r="BF346" t="inlineStr"/>
+      <c r="BG346" t="inlineStr"/>
+      <c r="BH346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="1" t="inlineStr">
@@ -67335,6 +68735,10 @@
       <c r="BB347" t="inlineStr"/>
       <c r="BC347" t="inlineStr"/>
       <c r="BD347" t="inlineStr"/>
+      <c r="BE347" t="inlineStr"/>
+      <c r="BF347" t="inlineStr"/>
+      <c r="BG347" t="inlineStr"/>
+      <c r="BH347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="1" t="inlineStr">
@@ -67529,6 +68933,10 @@
       <c r="BB348" t="inlineStr"/>
       <c r="BC348" t="inlineStr"/>
       <c r="BD348" t="inlineStr"/>
+      <c r="BE348" t="inlineStr"/>
+      <c r="BF348" t="inlineStr"/>
+      <c r="BG348" t="inlineStr"/>
+      <c r="BH348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="1" t="inlineStr">
@@ -67723,6 +69131,10 @@
       <c r="BB349" t="inlineStr"/>
       <c r="BC349" t="inlineStr"/>
       <c r="BD349" t="inlineStr"/>
+      <c r="BE349" t="inlineStr"/>
+      <c r="BF349" t="inlineStr"/>
+      <c r="BG349" t="inlineStr"/>
+      <c r="BH349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="1" t="inlineStr">
@@ -67917,6 +69329,10 @@
       <c r="BB350" t="inlineStr"/>
       <c r="BC350" t="inlineStr"/>
       <c r="BD350" t="inlineStr"/>
+      <c r="BE350" t="inlineStr"/>
+      <c r="BF350" t="inlineStr"/>
+      <c r="BG350" t="inlineStr"/>
+      <c r="BH350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="1" t="inlineStr">
@@ -68111,6 +69527,10 @@
       <c r="BB351" t="inlineStr"/>
       <c r="BC351" t="inlineStr"/>
       <c r="BD351" t="inlineStr"/>
+      <c r="BE351" t="inlineStr"/>
+      <c r="BF351" t="inlineStr"/>
+      <c r="BG351" t="inlineStr"/>
+      <c r="BH351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="1" t="inlineStr">
@@ -68305,6 +69725,10 @@
       <c r="BB352" t="inlineStr"/>
       <c r="BC352" t="inlineStr"/>
       <c r="BD352" t="inlineStr"/>
+      <c r="BE352" t="inlineStr"/>
+      <c r="BF352" t="inlineStr"/>
+      <c r="BG352" t="inlineStr"/>
+      <c r="BH352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="1" t="inlineStr">
@@ -68499,6 +69923,10 @@
       <c r="BB353" t="inlineStr"/>
       <c r="BC353" t="inlineStr"/>
       <c r="BD353" t="inlineStr"/>
+      <c r="BE353" t="inlineStr"/>
+      <c r="BF353" t="inlineStr"/>
+      <c r="BG353" t="inlineStr"/>
+      <c r="BH353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="1" t="inlineStr">
@@ -68693,6 +70121,10 @@
       <c r="BB354" t="inlineStr"/>
       <c r="BC354" t="inlineStr"/>
       <c r="BD354" t="inlineStr"/>
+      <c r="BE354" t="inlineStr"/>
+      <c r="BF354" t="inlineStr"/>
+      <c r="BG354" t="inlineStr"/>
+      <c r="BH354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="1" t="inlineStr">
@@ -68887,6 +70319,10 @@
       <c r="BB355" t="inlineStr"/>
       <c r="BC355" t="inlineStr"/>
       <c r="BD355" t="inlineStr"/>
+      <c r="BE355" t="inlineStr"/>
+      <c r="BF355" t="inlineStr"/>
+      <c r="BG355" t="inlineStr"/>
+      <c r="BH355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="1" t="inlineStr">
@@ -69081,6 +70517,10 @@
       <c r="BB356" t="inlineStr"/>
       <c r="BC356" t="inlineStr"/>
       <c r="BD356" t="inlineStr"/>
+      <c r="BE356" t="inlineStr"/>
+      <c r="BF356" t="inlineStr"/>
+      <c r="BG356" t="inlineStr"/>
+      <c r="BH356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="1" t="inlineStr">
@@ -69275,6 +70715,10 @@
       <c r="BB357" t="inlineStr"/>
       <c r="BC357" t="inlineStr"/>
       <c r="BD357" t="inlineStr"/>
+      <c r="BE357" t="inlineStr"/>
+      <c r="BF357" t="inlineStr"/>
+      <c r="BG357" t="inlineStr"/>
+      <c r="BH357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="1" t="inlineStr">
@@ -69473,6 +70917,10 @@
       <c r="BB358" t="inlineStr"/>
       <c r="BC358" t="inlineStr"/>
       <c r="BD358" t="inlineStr"/>
+      <c r="BE358" t="inlineStr"/>
+      <c r="BF358" t="inlineStr"/>
+      <c r="BG358" t="inlineStr"/>
+      <c r="BH358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="1" t="inlineStr">
@@ -69667,6 +71115,10 @@
       <c r="BB359" t="inlineStr"/>
       <c r="BC359" t="inlineStr"/>
       <c r="BD359" t="inlineStr"/>
+      <c r="BE359" t="inlineStr"/>
+      <c r="BF359" t="inlineStr"/>
+      <c r="BG359" t="inlineStr"/>
+      <c r="BH359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="1" t="inlineStr">
@@ -69865,6 +71317,10 @@
       <c r="BB360" t="inlineStr"/>
       <c r="BC360" t="inlineStr"/>
       <c r="BD360" t="inlineStr"/>
+      <c r="BE360" t="inlineStr"/>
+      <c r="BF360" t="inlineStr"/>
+      <c r="BG360" t="inlineStr"/>
+      <c r="BH360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="1" t="inlineStr">
@@ -70059,6 +71515,10 @@
       <c r="BB361" t="inlineStr"/>
       <c r="BC361" t="inlineStr"/>
       <c r="BD361" t="inlineStr"/>
+      <c r="BE361" t="inlineStr"/>
+      <c r="BF361" t="inlineStr"/>
+      <c r="BG361" t="inlineStr"/>
+      <c r="BH361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="1" t="inlineStr">
@@ -70253,6 +71713,10 @@
       <c r="BB362" t="inlineStr"/>
       <c r="BC362" t="inlineStr"/>
       <c r="BD362" t="inlineStr"/>
+      <c r="BE362" t="inlineStr"/>
+      <c r="BF362" t="inlineStr"/>
+      <c r="BG362" t="inlineStr"/>
+      <c r="BH362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" s="1" t="inlineStr">
@@ -70447,6 +71911,10 @@
       <c r="BB363" t="inlineStr"/>
       <c r="BC363" t="inlineStr"/>
       <c r="BD363" t="inlineStr"/>
+      <c r="BE363" t="inlineStr"/>
+      <c r="BF363" t="inlineStr"/>
+      <c r="BG363" t="inlineStr"/>
+      <c r="BH363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="1" t="inlineStr">
@@ -70641,6 +72109,10 @@
       <c r="BB364" t="inlineStr"/>
       <c r="BC364" t="inlineStr"/>
       <c r="BD364" t="inlineStr"/>
+      <c r="BE364" t="inlineStr"/>
+      <c r="BF364" t="inlineStr"/>
+      <c r="BG364" t="inlineStr"/>
+      <c r="BH364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="1" t="inlineStr">
@@ -70835,6 +72307,10 @@
       <c r="BB365" t="inlineStr"/>
       <c r="BC365" t="inlineStr"/>
       <c r="BD365" t="inlineStr"/>
+      <c r="BE365" t="inlineStr"/>
+      <c r="BF365" t="inlineStr"/>
+      <c r="BG365" t="inlineStr"/>
+      <c r="BH365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="1" t="inlineStr">
@@ -71029,6 +72505,10 @@
       <c r="BB366" t="inlineStr"/>
       <c r="BC366" t="inlineStr"/>
       <c r="BD366" t="inlineStr"/>
+      <c r="BE366" t="inlineStr"/>
+      <c r="BF366" t="inlineStr"/>
+      <c r="BG366" t="inlineStr"/>
+      <c r="BH366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="1" t="inlineStr">
@@ -71223,6 +72703,10 @@
       <c r="BB367" t="inlineStr"/>
       <c r="BC367" t="inlineStr"/>
       <c r="BD367" t="inlineStr"/>
+      <c r="BE367" t="inlineStr"/>
+      <c r="BF367" t="inlineStr"/>
+      <c r="BG367" t="inlineStr"/>
+      <c r="BH367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="1" t="inlineStr">
@@ -71413,6 +72897,10 @@
       <c r="BB368" t="inlineStr"/>
       <c r="BC368" t="inlineStr"/>
       <c r="BD368" t="inlineStr"/>
+      <c r="BE368" t="inlineStr"/>
+      <c r="BF368" t="inlineStr"/>
+      <c r="BG368" t="inlineStr"/>
+      <c r="BH368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="1" t="inlineStr">
@@ -71607,6 +73095,10 @@
       <c r="BB369" t="inlineStr"/>
       <c r="BC369" t="inlineStr"/>
       <c r="BD369" t="inlineStr"/>
+      <c r="BE369" t="inlineStr"/>
+      <c r="BF369" t="inlineStr"/>
+      <c r="BG369" t="inlineStr"/>
+      <c r="BH369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="1" t="inlineStr">
@@ -71797,6 +73289,10 @@
       <c r="BB370" t="inlineStr"/>
       <c r="BC370" t="inlineStr"/>
       <c r="BD370" t="inlineStr"/>
+      <c r="BE370" t="inlineStr"/>
+      <c r="BF370" t="inlineStr"/>
+      <c r="BG370" t="inlineStr"/>
+      <c r="BH370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="1" t="inlineStr">
@@ -71995,6 +73491,10 @@
       <c r="BB371" t="inlineStr"/>
       <c r="BC371" t="inlineStr"/>
       <c r="BD371" t="inlineStr"/>
+      <c r="BE371" t="inlineStr"/>
+      <c r="BF371" t="inlineStr"/>
+      <c r="BG371" t="inlineStr"/>
+      <c r="BH371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="1" t="inlineStr">
@@ -72189,6 +73689,10 @@
       <c r="BB372" t="inlineStr"/>
       <c r="BC372" t="inlineStr"/>
       <c r="BD372" t="inlineStr"/>
+      <c r="BE372" t="inlineStr"/>
+      <c r="BF372" t="inlineStr"/>
+      <c r="BG372" t="inlineStr"/>
+      <c r="BH372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="1" t="inlineStr">
@@ -72383,6 +73887,10 @@
       <c r="BB373" t="inlineStr"/>
       <c r="BC373" t="inlineStr"/>
       <c r="BD373" t="inlineStr"/>
+      <c r="BE373" t="inlineStr"/>
+      <c r="BF373" t="inlineStr"/>
+      <c r="BG373" t="inlineStr"/>
+      <c r="BH373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="1" t="inlineStr">
@@ -72577,6 +74085,10 @@
       <c r="BB374" t="inlineStr"/>
       <c r="BC374" t="inlineStr"/>
       <c r="BD374" t="inlineStr"/>
+      <c r="BE374" t="inlineStr"/>
+      <c r="BF374" t="inlineStr"/>
+      <c r="BG374" t="inlineStr"/>
+      <c r="BH374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="1" t="inlineStr">
@@ -72771,6 +74283,10 @@
       <c r="BB375" t="inlineStr"/>
       <c r="BC375" t="inlineStr"/>
       <c r="BD375" t="inlineStr"/>
+      <c r="BE375" t="inlineStr"/>
+      <c r="BF375" t="inlineStr"/>
+      <c r="BG375" t="inlineStr"/>
+      <c r="BH375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="1" t="inlineStr">
@@ -72965,6 +74481,10 @@
       <c r="BB376" t="inlineStr"/>
       <c r="BC376" t="inlineStr"/>
       <c r="BD376" t="inlineStr"/>
+      <c r="BE376" t="inlineStr"/>
+      <c r="BF376" t="inlineStr"/>
+      <c r="BG376" t="inlineStr"/>
+      <c r="BH376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="1" t="inlineStr">
@@ -73160,6 +74680,10 @@
       <c r="BB377" t="inlineStr"/>
       <c r="BC377" t="inlineStr"/>
       <c r="BD377" t="inlineStr"/>
+      <c r="BE377" t="inlineStr"/>
+      <c r="BF377" t="inlineStr"/>
+      <c r="BG377" t="inlineStr"/>
+      <c r="BH377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="1" t="inlineStr">
@@ -73350,6 +74874,10 @@
       <c r="BB378" t="inlineStr"/>
       <c r="BC378" t="inlineStr"/>
       <c r="BD378" t="inlineStr"/>
+      <c r="BE378" t="inlineStr"/>
+      <c r="BF378" t="inlineStr"/>
+      <c r="BG378" t="inlineStr"/>
+      <c r="BH378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="1" t="inlineStr">
@@ -73536,6 +75064,10 @@
       <c r="BB379" t="inlineStr"/>
       <c r="BC379" t="inlineStr"/>
       <c r="BD379" t="inlineStr"/>
+      <c r="BE379" t="inlineStr"/>
+      <c r="BF379" t="inlineStr"/>
+      <c r="BG379" t="inlineStr"/>
+      <c r="BH379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="1" t="inlineStr">
@@ -73722,6 +75254,10 @@
       <c r="BB380" t="inlineStr"/>
       <c r="BC380" t="inlineStr"/>
       <c r="BD380" t="inlineStr"/>
+      <c r="BE380" t="inlineStr"/>
+      <c r="BF380" t="inlineStr"/>
+      <c r="BG380" t="inlineStr"/>
+      <c r="BH380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="1" t="inlineStr">
@@ -73908,6 +75444,10 @@
       <c r="BB381" t="inlineStr"/>
       <c r="BC381" t="inlineStr"/>
       <c r="BD381" t="inlineStr"/>
+      <c r="BE381" t="inlineStr"/>
+      <c r="BF381" t="inlineStr"/>
+      <c r="BG381" t="inlineStr"/>
+      <c r="BH381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="1" t="inlineStr">
@@ -74094,6 +75634,10 @@
       <c r="BB382" t="inlineStr"/>
       <c r="BC382" t="inlineStr"/>
       <c r="BD382" t="inlineStr"/>
+      <c r="BE382" t="inlineStr"/>
+      <c r="BF382" t="inlineStr"/>
+      <c r="BG382" t="inlineStr"/>
+      <c r="BH382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="1" t="inlineStr">
@@ -74280,6 +75824,10 @@
       <c r="BB383" t="inlineStr"/>
       <c r="BC383" t="inlineStr"/>
       <c r="BD383" t="inlineStr"/>
+      <c r="BE383" t="inlineStr"/>
+      <c r="BF383" t="inlineStr"/>
+      <c r="BG383" t="inlineStr"/>
+      <c r="BH383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="1" t="inlineStr">
@@ -74466,6 +76014,10 @@
       <c r="BB384" t="inlineStr"/>
       <c r="BC384" t="inlineStr"/>
       <c r="BD384" t="inlineStr"/>
+      <c r="BE384" t="inlineStr"/>
+      <c r="BF384" t="inlineStr"/>
+      <c r="BG384" t="inlineStr"/>
+      <c r="BH384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="1" t="inlineStr">
@@ -74648,6 +76200,10 @@
       <c r="BB385" t="inlineStr"/>
       <c r="BC385" t="inlineStr"/>
       <c r="BD385" t="inlineStr"/>
+      <c r="BE385" t="inlineStr"/>
+      <c r="BF385" t="inlineStr"/>
+      <c r="BG385" t="inlineStr"/>
+      <c r="BH385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="1" t="inlineStr">
@@ -74830,6 +76386,10 @@
       <c r="BB386" t="inlineStr"/>
       <c r="BC386" t="inlineStr"/>
       <c r="BD386" t="inlineStr"/>
+      <c r="BE386" t="inlineStr"/>
+      <c r="BF386" t="inlineStr"/>
+      <c r="BG386" t="inlineStr"/>
+      <c r="BH386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="1" t="inlineStr">
@@ -75012,6 +76572,10 @@
       <c r="BB387" t="inlineStr"/>
       <c r="BC387" t="inlineStr"/>
       <c r="BD387" t="inlineStr"/>
+      <c r="BE387" t="inlineStr"/>
+      <c r="BF387" t="inlineStr"/>
+      <c r="BG387" t="inlineStr"/>
+      <c r="BH387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="1" t="inlineStr">
@@ -75198,6 +76762,10 @@
       <c r="BB388" t="inlineStr"/>
       <c r="BC388" t="inlineStr"/>
       <c r="BD388" t="inlineStr"/>
+      <c r="BE388" t="inlineStr"/>
+      <c r="BF388" t="inlineStr"/>
+      <c r="BG388" t="inlineStr"/>
+      <c r="BH388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="1" t="inlineStr">
@@ -75384,6 +76952,10 @@
       <c r="BB389" t="inlineStr"/>
       <c r="BC389" t="inlineStr"/>
       <c r="BD389" t="inlineStr"/>
+      <c r="BE389" t="inlineStr"/>
+      <c r="BF389" t="inlineStr"/>
+      <c r="BG389" t="inlineStr"/>
+      <c r="BH389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="1" t="inlineStr">
@@ -75574,6 +77146,10 @@
       <c r="BB390" t="inlineStr"/>
       <c r="BC390" t="inlineStr"/>
       <c r="BD390" t="inlineStr"/>
+      <c r="BE390" t="inlineStr"/>
+      <c r="BF390" t="inlineStr"/>
+      <c r="BG390" t="inlineStr"/>
+      <c r="BH390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="1" t="inlineStr">
@@ -75760,6 +77336,10 @@
       <c r="BB391" t="inlineStr"/>
       <c r="BC391" t="inlineStr"/>
       <c r="BD391" t="inlineStr"/>
+      <c r="BE391" t="inlineStr"/>
+      <c r="BF391" t="inlineStr"/>
+      <c r="BG391" t="inlineStr"/>
+      <c r="BH391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="1" t="inlineStr">
@@ -75950,6 +77530,10 @@
       <c r="BB392" t="inlineStr"/>
       <c r="BC392" t="inlineStr"/>
       <c r="BD392" t="inlineStr"/>
+      <c r="BE392" t="inlineStr"/>
+      <c r="BF392" t="inlineStr"/>
+      <c r="BG392" t="inlineStr"/>
+      <c r="BH392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="1" t="inlineStr">
@@ -76136,6 +77720,10 @@
       <c r="BB393" t="inlineStr"/>
       <c r="BC393" t="inlineStr"/>
       <c r="BD393" t="inlineStr"/>
+      <c r="BE393" t="inlineStr"/>
+      <c r="BF393" t="inlineStr"/>
+      <c r="BG393" t="inlineStr"/>
+      <c r="BH393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="1" t="inlineStr">
@@ -76318,6 +77906,10 @@
       <c r="BB394" t="inlineStr"/>
       <c r="BC394" t="inlineStr"/>
       <c r="BD394" t="inlineStr"/>
+      <c r="BE394" t="inlineStr"/>
+      <c r="BF394" t="inlineStr"/>
+      <c r="BG394" t="inlineStr"/>
+      <c r="BH394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="1" t="inlineStr">
@@ -76500,6 +78092,10 @@
       <c r="BB395" t="inlineStr"/>
       <c r="BC395" t="inlineStr"/>
       <c r="BD395" t="inlineStr"/>
+      <c r="BE395" t="inlineStr"/>
+      <c r="BF395" t="inlineStr"/>
+      <c r="BG395" t="inlineStr"/>
+      <c r="BH395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="1" t="inlineStr">
@@ -76682,6 +78278,10 @@
       <c r="BB396" t="inlineStr"/>
       <c r="BC396" t="inlineStr"/>
       <c r="BD396" t="inlineStr"/>
+      <c r="BE396" t="inlineStr"/>
+      <c r="BF396" t="inlineStr"/>
+      <c r="BG396" t="inlineStr"/>
+      <c r="BH396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="1" t="inlineStr">
@@ -76864,6 +78464,10 @@
       <c r="BB397" t="inlineStr"/>
       <c r="BC397" t="inlineStr"/>
       <c r="BD397" t="inlineStr"/>
+      <c r="BE397" t="inlineStr"/>
+      <c r="BF397" t="inlineStr"/>
+      <c r="BG397" t="inlineStr"/>
+      <c r="BH397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="1" t="inlineStr">
@@ -77046,6 +78650,10 @@
       <c r="BB398" t="inlineStr"/>
       <c r="BC398" t="inlineStr"/>
       <c r="BD398" t="inlineStr"/>
+      <c r="BE398" t="inlineStr"/>
+      <c r="BF398" t="inlineStr"/>
+      <c r="BG398" t="inlineStr"/>
+      <c r="BH398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="1" t="inlineStr">
@@ -77080,15 +78688,11 @@
           <t>15 810</t>
         </is>
       </c>
-      <c r="G399" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H399" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G399" t="n">
+        <v>0</v>
+      </c>
+      <c r="H399" t="n">
+        <v>0</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
@@ -77122,115 +78726,71 @@
           <t>32%</t>
         </is>
       </c>
-      <c r="Q399" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R399" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S399" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T399" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U399" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V399" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W399" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X399" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y399" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Z399" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA399" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB399" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC399" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD399" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE399" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF399" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG399" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH399" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI399" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ399" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AK399" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL399" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q399" t="n">
+        <v>13</v>
+      </c>
+      <c r="R399" t="n">
+        <v>10</v>
+      </c>
+      <c r="S399" t="n">
+        <v>1</v>
+      </c>
+      <c r="T399" t="n">
+        <v>5</v>
+      </c>
+      <c r="U399" t="n">
+        <v>9</v>
+      </c>
+      <c r="V399" t="n">
+        <v>3</v>
+      </c>
+      <c r="W399" t="n">
+        <v>3</v>
+      </c>
+      <c r="X399" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y399" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z399" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA399" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB399" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC399" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD399" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE399" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF399" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG399" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH399" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI399" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ399" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK399" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL399" t="n">
+        <v>2</v>
       </c>
       <c r="AM399" t="inlineStr">
         <is>
@@ -77276,6 +78836,10 @@
       <c r="BB399" t="inlineStr"/>
       <c r="BC399" t="inlineStr"/>
       <c r="BD399" t="inlineStr"/>
+      <c r="BE399" t="inlineStr"/>
+      <c r="BF399" t="inlineStr"/>
+      <c r="BG399" t="inlineStr"/>
+      <c r="BH399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="1" t="inlineStr">
@@ -77310,15 +78874,11 @@
           <t>11 300</t>
         </is>
       </c>
-      <c r="G400" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H400" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G400" t="n">
+        <v>0</v>
+      </c>
+      <c r="H400" t="n">
+        <v>1</v>
       </c>
       <c r="I400" t="inlineStr">
         <is>
@@ -77352,115 +78912,71 @@
           <t>35%</t>
         </is>
       </c>
-      <c r="Q400" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R400" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S400" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T400" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U400" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V400" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W400" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X400" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y400" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Z400" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA400" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB400" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC400" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD400" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE400" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AF400" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG400" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH400" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI400" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ400" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AK400" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AL400" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q400" t="n">
+        <v>9</v>
+      </c>
+      <c r="R400" t="n">
+        <v>11</v>
+      </c>
+      <c r="S400" t="n">
+        <v>3</v>
+      </c>
+      <c r="T400" t="n">
+        <v>3</v>
+      </c>
+      <c r="U400" t="n">
+        <v>3</v>
+      </c>
+      <c r="V400" t="n">
+        <v>5</v>
+      </c>
+      <c r="W400" t="n">
+        <v>3</v>
+      </c>
+      <c r="X400" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y400" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z400" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA400" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB400" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC400" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD400" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE400" t="n">
+        <v>31</v>
+      </c>
+      <c r="AF400" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG400" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH400" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI400" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ400" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK400" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL400" t="n">
+        <v>3</v>
       </c>
       <c r="AM400" t="inlineStr">
         <is>
@@ -77506,6 +79022,10 @@
       <c r="BB400" t="inlineStr"/>
       <c r="BC400" t="inlineStr"/>
       <c r="BD400" t="inlineStr"/>
+      <c r="BE400" t="inlineStr"/>
+      <c r="BF400" t="inlineStr"/>
+      <c r="BG400" t="inlineStr"/>
+      <c r="BH400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" s="1" t="inlineStr">
@@ -77540,15 +79060,11 @@
           <t>18 036</t>
         </is>
       </c>
-      <c r="G401" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H401" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G401" t="n">
+        <v>1</v>
+      </c>
+      <c r="H401" t="n">
+        <v>0</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
@@ -77582,115 +79098,71 @@
           <t>37%</t>
         </is>
       </c>
-      <c r="Q401" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R401" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S401" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T401" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U401" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V401" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W401" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X401" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y401" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Z401" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA401" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB401" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC401" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD401" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE401" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="AF401" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG401" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH401" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI401" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ401" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK401" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL401" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q401" t="n">
+        <v>18</v>
+      </c>
+      <c r="R401" t="n">
+        <v>8</v>
+      </c>
+      <c r="S401" t="n">
+        <v>5</v>
+      </c>
+      <c r="T401" t="n">
+        <v>2</v>
+      </c>
+      <c r="U401" t="n">
+        <v>10</v>
+      </c>
+      <c r="V401" t="n">
+        <v>3</v>
+      </c>
+      <c r="W401" t="n">
+        <v>3</v>
+      </c>
+      <c r="X401" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y401" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z401" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA401" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB401" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC401" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD401" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE401" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF401" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG401" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH401" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI401" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ401" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK401" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL401" t="n">
+        <v>2</v>
       </c>
       <c r="AM401" t="inlineStr">
         <is>
@@ -77726,15 +79198,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU401" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV401" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AU401" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV401" t="n">
+        <v>1</v>
       </c>
       <c r="AW401" t="inlineStr"/>
       <c r="AX401" t="inlineStr"/>
@@ -77744,6 +79212,10 @@
       <c r="BB401" t="inlineStr"/>
       <c r="BC401" t="inlineStr"/>
       <c r="BD401" t="inlineStr"/>
+      <c r="BE401" t="inlineStr"/>
+      <c r="BF401" t="inlineStr"/>
+      <c r="BG401" t="inlineStr"/>
+      <c r="BH401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="1" t="inlineStr">
@@ -77778,15 +79250,11 @@
           <t>19 426</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H402" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G402" t="n">
+        <v>3</v>
+      </c>
+      <c r="H402" t="n">
+        <v>2</v>
       </c>
       <c r="I402" t="inlineStr">
         <is>
@@ -77820,115 +79288,71 @@
           <t>39%</t>
         </is>
       </c>
-      <c r="Q402" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R402" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S402" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T402" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U402" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V402" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W402" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X402" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y402" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z402" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AA402" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB402" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC402" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD402" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE402" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF402" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG402" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH402" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI402" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ402" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AK402" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL402" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q402" t="n">
+        <v>24</v>
+      </c>
+      <c r="R402" t="n">
+        <v>8</v>
+      </c>
+      <c r="S402" t="n">
+        <v>10</v>
+      </c>
+      <c r="T402" t="n">
+        <v>5</v>
+      </c>
+      <c r="U402" t="n">
+        <v>11</v>
+      </c>
+      <c r="V402" t="n">
+        <v>3</v>
+      </c>
+      <c r="W402" t="n">
+        <v>3</v>
+      </c>
+      <c r="X402" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y402" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z402" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA402" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB402" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC402" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD402" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE402" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF402" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG402" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH402" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI402" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ402" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK402" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL402" t="n">
+        <v>3</v>
       </c>
       <c r="AM402" t="inlineStr">
         <is>
@@ -77964,15 +79388,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU402" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV402" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AU402" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV402" t="n">
+        <v>2</v>
       </c>
       <c r="AW402" t="inlineStr"/>
       <c r="AX402" t="inlineStr"/>
@@ -77982,6 +79402,10 @@
       <c r="BB402" t="inlineStr"/>
       <c r="BC402" t="inlineStr"/>
       <c r="BD402" t="inlineStr"/>
+      <c r="BE402" t="inlineStr"/>
+      <c r="BF402" t="inlineStr"/>
+      <c r="BG402" t="inlineStr"/>
+      <c r="BH402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="1" t="inlineStr">
@@ -78016,15 +79440,11 @@
           <t>20 680</t>
         </is>
       </c>
-      <c r="G403" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H403" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G403" t="n">
+        <v>1</v>
+      </c>
+      <c r="H403" t="n">
+        <v>0</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
@@ -78058,115 +79478,71 @@
           <t>49%</t>
         </is>
       </c>
-      <c r="Q403" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R403" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S403" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T403" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U403" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V403" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W403" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X403" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y403" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="Z403" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA403" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB403" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC403" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD403" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AE403" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AF403" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG403" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH403" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI403" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AJ403" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK403" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL403" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q403" t="n">
+        <v>16</v>
+      </c>
+      <c r="R403" t="n">
+        <v>6</v>
+      </c>
+      <c r="S403" t="n">
+        <v>2</v>
+      </c>
+      <c r="T403" t="n">
+        <v>2</v>
+      </c>
+      <c r="U403" t="n">
+        <v>11</v>
+      </c>
+      <c r="V403" t="n">
+        <v>3</v>
+      </c>
+      <c r="W403" t="n">
+        <v>3</v>
+      </c>
+      <c r="X403" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y403" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z403" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA403" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB403" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC403" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD403" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE403" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF403" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG403" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH403" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI403" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ403" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK403" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL403" t="n">
+        <v>4</v>
       </c>
       <c r="AM403" t="inlineStr">
         <is>
@@ -78212,6 +79588,10 @@
       <c r="BB403" t="inlineStr"/>
       <c r="BC403" t="inlineStr"/>
       <c r="BD403" t="inlineStr"/>
+      <c r="BE403" t="inlineStr"/>
+      <c r="BF403" t="inlineStr"/>
+      <c r="BG403" t="inlineStr"/>
+      <c r="BH403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="1" t="inlineStr">
@@ -78246,15 +79626,11 @@
           <t>5 722</t>
         </is>
       </c>
-      <c r="G404" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H404" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G404" t="n">
+        <v>2</v>
+      </c>
+      <c r="H404" t="n">
+        <v>2</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
@@ -78288,115 +79664,71 @@
           <t>39%</t>
         </is>
       </c>
-      <c r="Q404" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R404" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S404" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T404" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U404" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V404" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W404" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X404" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y404" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z404" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA404" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB404" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC404" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD404" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE404" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AF404" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG404" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH404" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI404" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ404" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK404" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL404" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q404" t="n">
+        <v>9</v>
+      </c>
+      <c r="R404" t="n">
+        <v>5</v>
+      </c>
+      <c r="S404" t="n">
+        <v>2</v>
+      </c>
+      <c r="T404" t="n">
+        <v>2</v>
+      </c>
+      <c r="U404" t="n">
+        <v>5</v>
+      </c>
+      <c r="V404" t="n">
+        <v>2</v>
+      </c>
+      <c r="W404" t="n">
+        <v>2</v>
+      </c>
+      <c r="X404" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y404" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z404" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA404" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB404" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC404" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD404" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE404" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF404" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG404" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH404" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI404" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ404" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK404" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL404" t="n">
+        <v>5</v>
       </c>
       <c r="AM404" t="inlineStr">
         <is>
@@ -78442,6 +79774,10 @@
       <c r="BB404" t="inlineStr"/>
       <c r="BC404" t="inlineStr"/>
       <c r="BD404" t="inlineStr"/>
+      <c r="BE404" t="inlineStr"/>
+      <c r="BF404" t="inlineStr"/>
+      <c r="BG404" t="inlineStr"/>
+      <c r="BH404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="1" t="inlineStr">
@@ -78476,15 +79812,11 @@
           <t>11 507</t>
         </is>
       </c>
-      <c r="G405" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H405" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G405" t="n">
+        <v>2</v>
+      </c>
+      <c r="H405" t="n">
+        <v>2</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
@@ -78518,115 +79850,71 @@
           <t>57%</t>
         </is>
       </c>
-      <c r="Q405" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R405" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S405" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T405" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U405" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V405" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W405" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X405" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y405" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z405" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AA405" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB405" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC405" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD405" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE405" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF405" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AG405" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH405" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI405" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AJ405" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK405" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL405" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q405" t="n">
+        <v>16</v>
+      </c>
+      <c r="R405" t="n">
+        <v>13</v>
+      </c>
+      <c r="S405" t="n">
+        <v>9</v>
+      </c>
+      <c r="T405" t="n">
+        <v>7</v>
+      </c>
+      <c r="U405" t="n">
+        <v>5</v>
+      </c>
+      <c r="V405" t="n">
+        <v>4</v>
+      </c>
+      <c r="W405" t="n">
+        <v>2</v>
+      </c>
+      <c r="X405" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y405" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z405" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA405" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB405" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC405" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD405" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE405" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF405" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG405" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH405" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI405" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ405" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK405" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL405" t="n">
+        <v>0</v>
       </c>
       <c r="AM405" t="inlineStr">
         <is>
@@ -78672,6 +79960,10 @@
       <c r="BB405" t="inlineStr"/>
       <c r="BC405" t="inlineStr"/>
       <c r="BD405" t="inlineStr"/>
+      <c r="BE405" t="inlineStr"/>
+      <c r="BF405" t="inlineStr"/>
+      <c r="BG405" t="inlineStr"/>
+      <c r="BH405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="1" t="inlineStr">
@@ -78706,15 +79998,11 @@
           <t>5 097</t>
         </is>
       </c>
-      <c r="G406" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H406" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G406" t="n">
+        <v>1</v>
+      </c>
+      <c r="H406" t="n">
+        <v>0</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
@@ -78748,115 +80036,71 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="Q406" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R406" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S406" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T406" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U406" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V406" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W406" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X406" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y406" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z406" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AA406" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB406" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC406" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD406" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE406" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AF406" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AG406" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH406" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI406" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AJ406" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AK406" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL406" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q406" t="n">
+        <v>16</v>
+      </c>
+      <c r="R406" t="n">
+        <v>14</v>
+      </c>
+      <c r="S406" t="n">
+        <v>7</v>
+      </c>
+      <c r="T406" t="n">
+        <v>3</v>
+      </c>
+      <c r="U406" t="n">
+        <v>4</v>
+      </c>
+      <c r="V406" t="n">
+        <v>8</v>
+      </c>
+      <c r="W406" t="n">
+        <v>5</v>
+      </c>
+      <c r="X406" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y406" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z406" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA406" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB406" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC406" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD406" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE406" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF406" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG406" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH406" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI406" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ406" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK406" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL406" t="n">
+        <v>0</v>
       </c>
       <c r="AM406" t="inlineStr">
         <is>
@@ -78902,6 +80146,10 @@
       <c r="BB406" t="inlineStr"/>
       <c r="BC406" t="inlineStr"/>
       <c r="BD406" t="inlineStr"/>
+      <c r="BE406" t="inlineStr"/>
+      <c r="BF406" t="inlineStr"/>
+      <c r="BG406" t="inlineStr"/>
+      <c r="BH406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="1" t="inlineStr">
@@ -78936,15 +80184,11 @@
           <t>6 223</t>
         </is>
       </c>
-      <c r="G407" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H407" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G407" t="n">
+        <v>0</v>
+      </c>
+      <c r="H407" t="n">
+        <v>1</v>
       </c>
       <c r="I407" t="inlineStr">
         <is>
@@ -78978,115 +80222,71 @@
           <t>59%</t>
         </is>
       </c>
-      <c r="Q407" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R407" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S407" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T407" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U407" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V407" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W407" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X407" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y407" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z407" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA407" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB407" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC407" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD407" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE407" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AF407" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AG407" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH407" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI407" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ407" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AK407" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL407" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q407" t="n">
+        <v>7</v>
+      </c>
+      <c r="R407" t="n">
+        <v>5</v>
+      </c>
+      <c r="S407" t="n">
+        <v>1</v>
+      </c>
+      <c r="T407" t="n">
+        <v>2</v>
+      </c>
+      <c r="U407" t="n">
+        <v>2</v>
+      </c>
+      <c r="V407" t="n">
+        <v>2</v>
+      </c>
+      <c r="W407" t="n">
+        <v>4</v>
+      </c>
+      <c r="X407" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y407" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z407" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA407" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB407" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC407" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD407" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE407" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF407" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG407" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH407" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI407" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ407" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK407" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL407" t="n">
+        <v>0</v>
       </c>
       <c r="AM407" t="inlineStr">
         <is>
@@ -79132,6 +80332,10 @@
       <c r="BB407" t="inlineStr"/>
       <c r="BC407" t="inlineStr"/>
       <c r="BD407" t="inlineStr"/>
+      <c r="BE407" t="inlineStr"/>
+      <c r="BF407" t="inlineStr"/>
+      <c r="BG407" t="inlineStr"/>
+      <c r="BH407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="1" t="inlineStr">
@@ -79166,15 +80370,11 @@
           <t>15 155</t>
         </is>
       </c>
-      <c r="G408" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H408" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G408" t="n">
+        <v>2</v>
+      </c>
+      <c r="H408" t="n">
+        <v>3</v>
       </c>
       <c r="I408" t="inlineStr">
         <is>
@@ -79208,115 +80408,71 @@
           <t>67%</t>
         </is>
       </c>
-      <c r="Q408" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R408" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="S408" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T408" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="U408" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V408" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W408" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X408" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y408" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Z408" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA408" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB408" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC408" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD408" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AE408" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF408" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AG408" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH408" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI408" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ408" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK408" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL408" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q408" t="n">
+        <v>9</v>
+      </c>
+      <c r="R408" t="n">
+        <v>18</v>
+      </c>
+      <c r="S408" t="n">
+        <v>2</v>
+      </c>
+      <c r="T408" t="n">
+        <v>10</v>
+      </c>
+      <c r="U408" t="n">
+        <v>3</v>
+      </c>
+      <c r="V408" t="n">
+        <v>4</v>
+      </c>
+      <c r="W408" t="n">
+        <v>4</v>
+      </c>
+      <c r="X408" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y408" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z408" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA408" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB408" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC408" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD408" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE408" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF408" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG408" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH408" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI408" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ408" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK408" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL408" t="n">
+        <v>3</v>
       </c>
       <c r="AM408" t="inlineStr">
         <is>
@@ -79352,15 +80508,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU408" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AV408" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AU408" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV408" t="n">
+        <v>0</v>
       </c>
       <c r="AW408" t="inlineStr"/>
       <c r="AX408" t="inlineStr"/>
@@ -79370,6 +80522,10 @@
       <c r="BB408" t="inlineStr"/>
       <c r="BC408" t="inlineStr"/>
       <c r="BD408" t="inlineStr"/>
+      <c r="BE408" t="inlineStr"/>
+      <c r="BF408" t="inlineStr"/>
+      <c r="BG408" t="inlineStr"/>
+      <c r="BH408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="1" t="inlineStr">
@@ -79386,15 +80542,11 @@
       <c r="D409" t="inlineStr"/>
       <c r="E409" t="inlineStr"/>
       <c r="F409" t="inlineStr"/>
-      <c r="G409" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H409" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G409" t="n">
+        <v>4</v>
+      </c>
+      <c r="H409" t="n">
+        <v>0</v>
       </c>
       <c r="I409" t="inlineStr">
         <is>
@@ -79471,6 +80623,10 @@
       <c r="BB409" t="inlineStr"/>
       <c r="BC409" t="inlineStr"/>
       <c r="BD409" t="inlineStr"/>
+      <c r="BE409" t="inlineStr"/>
+      <c r="BF409" t="inlineStr"/>
+      <c r="BG409" t="inlineStr"/>
+      <c r="BH409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="1" t="inlineStr">
@@ -79487,15 +80643,11 @@
       <c r="D410" t="inlineStr"/>
       <c r="E410" t="inlineStr"/>
       <c r="F410" t="inlineStr"/>
-      <c r="G410" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H410" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G410" t="n">
+        <v>2</v>
+      </c>
+      <c r="H410" t="n">
+        <v>1</v>
       </c>
       <c r="I410" t="inlineStr">
         <is>
@@ -79572,6 +80724,10 @@
       <c r="BB410" t="inlineStr"/>
       <c r="BC410" t="inlineStr"/>
       <c r="BD410" t="inlineStr"/>
+      <c r="BE410" t="inlineStr"/>
+      <c r="BF410" t="inlineStr"/>
+      <c r="BG410" t="inlineStr"/>
+      <c r="BH410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="1" t="inlineStr">
@@ -79588,15 +80744,11 @@
       <c r="D411" t="inlineStr"/>
       <c r="E411" t="inlineStr"/>
       <c r="F411" t="inlineStr"/>
-      <c r="G411" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H411" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G411" t="n">
+        <v>4</v>
+      </c>
+      <c r="H411" t="n">
+        <v>0</v>
       </c>
       <c r="I411" t="inlineStr">
         <is>
@@ -79673,6 +80825,10 @@
       <c r="BB411" t="inlineStr"/>
       <c r="BC411" t="inlineStr"/>
       <c r="BD411" t="inlineStr"/>
+      <c r="BE411" t="inlineStr"/>
+      <c r="BF411" t="inlineStr"/>
+      <c r="BG411" t="inlineStr"/>
+      <c r="BH411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="1" t="inlineStr">
@@ -79689,15 +80845,11 @@
       <c r="D412" t="inlineStr"/>
       <c r="E412" t="inlineStr"/>
       <c r="F412" t="inlineStr"/>
-      <c r="G412" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H412" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G412" t="n">
+        <v>1</v>
+      </c>
+      <c r="H412" t="n">
+        <v>3</v>
       </c>
       <c r="I412" t="inlineStr">
         <is>
@@ -79774,6 +80926,10 @@
       <c r="BB412" t="inlineStr"/>
       <c r="BC412" t="inlineStr"/>
       <c r="BD412" t="inlineStr"/>
+      <c r="BE412" t="inlineStr"/>
+      <c r="BF412" t="inlineStr"/>
+      <c r="BG412" t="inlineStr"/>
+      <c r="BH412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="1" t="inlineStr">
@@ -79790,15 +80946,11 @@
       <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr"/>
       <c r="F413" t="inlineStr"/>
-      <c r="G413" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H413" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G413" t="n">
+        <v>1</v>
+      </c>
+      <c r="H413" t="n">
+        <v>0</v>
       </c>
       <c r="I413" t="inlineStr">
         <is>
@@ -79875,6 +81027,10 @@
       <c r="BB413" t="inlineStr"/>
       <c r="BC413" t="inlineStr"/>
       <c r="BD413" t="inlineStr"/>
+      <c r="BE413" t="inlineStr"/>
+      <c r="BF413" t="inlineStr"/>
+      <c r="BG413" t="inlineStr"/>
+      <c r="BH413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="1" t="inlineStr">
@@ -79891,15 +81047,11 @@
       <c r="D414" t="inlineStr"/>
       <c r="E414" t="inlineStr"/>
       <c r="F414" t="inlineStr"/>
-      <c r="G414" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H414" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G414" t="n">
+        <v>2</v>
+      </c>
+      <c r="H414" t="n">
+        <v>0</v>
       </c>
       <c r="I414" t="inlineStr">
         <is>
@@ -79976,6 +81128,10 @@
       <c r="BB414" t="inlineStr"/>
       <c r="BC414" t="inlineStr"/>
       <c r="BD414" t="inlineStr"/>
+      <c r="BE414" t="inlineStr"/>
+      <c r="BF414" t="inlineStr"/>
+      <c r="BG414" t="inlineStr"/>
+      <c r="BH414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" s="1" t="inlineStr">
@@ -79992,15 +81148,11 @@
       <c r="D415" t="inlineStr"/>
       <c r="E415" t="inlineStr"/>
       <c r="F415" t="inlineStr"/>
-      <c r="G415" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H415" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G415" t="n">
+        <v>1</v>
+      </c>
+      <c r="H415" t="n">
+        <v>2</v>
       </c>
       <c r="I415" t="inlineStr">
         <is>
@@ -80077,6 +81229,10 @@
       <c r="BB415" t="inlineStr"/>
       <c r="BC415" t="inlineStr"/>
       <c r="BD415" t="inlineStr"/>
+      <c r="BE415" t="inlineStr"/>
+      <c r="BF415" t="inlineStr"/>
+      <c r="BG415" t="inlineStr"/>
+      <c r="BH415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="1" t="inlineStr">
@@ -80093,15 +81249,11 @@
       <c r="D416" t="inlineStr"/>
       <c r="E416" t="inlineStr"/>
       <c r="F416" t="inlineStr"/>
-      <c r="G416" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H416" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G416" t="n">
+        <v>4</v>
+      </c>
+      <c r="H416" t="n">
+        <v>2</v>
       </c>
       <c r="I416" t="inlineStr">
         <is>
@@ -80178,6 +81330,10 @@
       <c r="BB416" t="inlineStr"/>
       <c r="BC416" t="inlineStr"/>
       <c r="BD416" t="inlineStr"/>
+      <c r="BE416" t="inlineStr"/>
+      <c r="BF416" t="inlineStr"/>
+      <c r="BG416" t="inlineStr"/>
+      <c r="BH416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="1" t="inlineStr">
@@ -80194,15 +81350,11 @@
       <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr"/>
       <c r="F417" t="inlineStr"/>
-      <c r="G417" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H417" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G417" t="n">
+        <v>0</v>
+      </c>
+      <c r="H417" t="n">
+        <v>1</v>
       </c>
       <c r="I417" t="inlineStr">
         <is>
@@ -80279,6 +81431,10 @@
       <c r="BB417" t="inlineStr"/>
       <c r="BC417" t="inlineStr"/>
       <c r="BD417" t="inlineStr"/>
+      <c r="BE417" t="inlineStr"/>
+      <c r="BF417" t="inlineStr"/>
+      <c r="BG417" t="inlineStr"/>
+      <c r="BH417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="1" t="inlineStr">
@@ -80295,15 +81451,11 @@
       <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr"/>
       <c r="F418" t="inlineStr"/>
-      <c r="G418" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H418" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G418" t="n">
+        <v>2</v>
+      </c>
+      <c r="H418" t="n">
+        <v>1</v>
       </c>
       <c r="I418" t="inlineStr">
         <is>
@@ -80380,6 +81532,2534 @@
       <c r="BB418" t="inlineStr"/>
       <c r="BC418" t="inlineStr"/>
       <c r="BD418" t="inlineStr"/>
+      <c r="BE418" t="inlineStr"/>
+      <c r="BF418" t="inlineStr"/>
+      <c r="BG418" t="inlineStr"/>
+      <c r="BH418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>h2NyhKup</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>19.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Grado C. S.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Montilivi
+ (Girona)</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>14 624</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>12 602</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T419" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V419" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W419" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X419" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y419" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z419" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA419" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB419" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC419" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD419" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE419" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF419" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG419" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH419" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI419" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ419" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK419" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL419" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM419" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="AN419" t="inlineStr">
+        <is>
+          <t>michel</t>
+        </is>
+      </c>
+      <c r="AO419" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="AP419" t="inlineStr">
+        <is>
+          <t>alguacil imanol</t>
+        </is>
+      </c>
+      <c r="AQ419" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR419" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS419" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT419" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU419" t="inlineStr"/>
+      <c r="AV419" t="inlineStr"/>
+      <c r="AW419" t="inlineStr"/>
+      <c r="AX419" t="inlineStr"/>
+      <c r="AY419" t="inlineStr"/>
+      <c r="AZ419" t="inlineStr"/>
+      <c r="BA419" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="BB419" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="BC419" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="BD419" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="BE419" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="BF419" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BG419" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BH419" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
+        <is>
+          <t>ll7vCuXF</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>19.10.2024 11:15</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Ruiz A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>23 516</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>21 045</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T420" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V420" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W420" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X420" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y420" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z420" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA420" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB420" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC420" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD420" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE420" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF420" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG420" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH420" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI420" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ420" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK420" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL420" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM420" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="AN420" t="inlineStr">
+        <is>
+          <t>moreno vicente</t>
+        </is>
+      </c>
+      <c r="AO420" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="AP420" t="inlineStr">
+        <is>
+          <t>pellegrini manuel</t>
+        </is>
+      </c>
+      <c r="AQ420" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR420" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS420" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT420" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU420" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV420" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AW420" t="inlineStr"/>
+      <c r="AX420" t="inlineStr"/>
+      <c r="AY420" t="inlineStr"/>
+      <c r="AZ420" t="inlineStr"/>
+      <c r="BA420" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="BB420" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="BC420" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="BD420" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="BE420" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BF420" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BG420" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BH420" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="1" t="inlineStr">
+        <is>
+          <t>YNHbsZ6C</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>19.10.2024 09:00</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Busquets Ferrer M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Estadio San Mamés
+ (Bilbao)</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>53 331</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>46 713</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T421" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V421" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W421" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X421" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y421" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Z421" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA421" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB421" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC421" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD421" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE421" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF421" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AG421" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH421" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI421" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ421" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AK421" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL421" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM421" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="AN421" t="inlineStr">
+        <is>
+          <t>valverde tejedor ernesto</t>
+        </is>
+      </c>
+      <c r="AO421" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="AP421" t="inlineStr">
+        <is>
+          <t>gonzalez manolo</t>
+        </is>
+      </c>
+      <c r="AQ421" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR421" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS421" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT421" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU421" t="inlineStr"/>
+      <c r="AV421" t="inlineStr"/>
+      <c r="AW421" t="inlineStr"/>
+      <c r="AX421" t="inlineStr"/>
+      <c r="AY421" t="inlineStr"/>
+      <c r="AZ421" t="inlineStr"/>
+      <c r="BA421" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="BB421" t="inlineStr">
+        <is>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="BC421" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="BD421" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="BE421" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BF421" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BG421" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BH421" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="1" t="inlineStr">
+        <is>
+          <t>Gz9WD123</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>18.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Lopez M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Estadio Mendizorrotza
+ (Vitoria-Gasteiz)</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>19 840</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>16 904</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T422" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V422" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W422" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X422" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y422" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z422" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA422" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB422" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC422" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD422" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE422" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF422" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG422" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH422" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI422" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ422" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK422" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AL422" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM422" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="AN422" t="inlineStr">
+        <is>
+          <t>garcia luis</t>
+        </is>
+      </c>
+      <c r="AO422" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="AP422" t="inlineStr">
+        <is>
+          <t>pezzolano paulo</t>
+        </is>
+      </c>
+      <c r="AQ422" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR422" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS422" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT422" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU422" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV422" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW422" t="inlineStr"/>
+      <c r="AX422" t="inlineStr"/>
+      <c r="AY422" t="inlineStr"/>
+      <c r="AZ422" t="inlineStr"/>
+      <c r="BA422" t="inlineStr">
+        <is>
+          <t>418</t>
+        </is>
+      </c>
+      <c r="BB422" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="BC422" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="BD422" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="BE422" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BF422" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BG422" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BH422" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="1" t="inlineStr">
+        <is>
+          <t>KhgxuOqK</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>19.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Sanchez A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Castalia
+ (Castellón de la Plana)</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>15 500</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>12 905</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>Castellon</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr"/>
+      <c r="N423" t="inlineStr"/>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T423" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U423" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V423" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W423" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X423" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y423" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z423" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA423" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB423" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC423" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD423" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE423" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF423" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AG423" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH423" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI423" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ423" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK423" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL423" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM423" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="AN423" t="inlineStr">
+        <is>
+          <t>schreuder dick</t>
+        </is>
+      </c>
+      <c r="AO423" t="inlineStr">
+        <is>
+          <t>fiZxGYJ3</t>
+        </is>
+      </c>
+      <c r="AP423" t="inlineStr">
+        <is>
+          <t>calero julian</t>
+        </is>
+      </c>
+      <c r="AQ423" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR423" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS423" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT423" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU423" t="inlineStr"/>
+      <c r="AV423" t="inlineStr"/>
+      <c r="AW423" t="inlineStr"/>
+      <c r="AX423" t="inlineStr"/>
+      <c r="AY423" t="inlineStr"/>
+      <c r="AZ423" t="inlineStr"/>
+      <c r="BA423" t="inlineStr"/>
+      <c r="BB423" t="inlineStr"/>
+      <c r="BC423" t="inlineStr"/>
+      <c r="BD423" t="inlineStr"/>
+      <c r="BE423" t="inlineStr"/>
+      <c r="BF423" t="inlineStr"/>
+      <c r="BG423" t="inlineStr"/>
+      <c r="BH423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="1" t="inlineStr">
+        <is>
+          <t>fZPXTcyJ</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>19.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Gonzalez Esteban J. A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Los Cármenes
+ (Granada)</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>22 524</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>16 582</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>Granada CF</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>Tenerife</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr"/>
+      <c r="N424" t="inlineStr"/>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="T424" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U424" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V424" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W424" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X424" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y424" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z424" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA424" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB424" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC424" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD424" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE424" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AF424" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG424" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH424" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI424" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ424" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK424" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL424" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM424" t="inlineStr">
+        <is>
+          <t>K0UZov8F</t>
+        </is>
+      </c>
+      <c r="AN424" t="inlineStr">
+        <is>
+          <t>escriba fran</t>
+        </is>
+      </c>
+      <c r="AO424" t="inlineStr">
+        <is>
+          <t>CYND5rZG</t>
+        </is>
+      </c>
+      <c r="AP424" t="inlineStr">
+        <is>
+          <t>mel pepe</t>
+        </is>
+      </c>
+      <c r="AQ424" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR424" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS424" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT424" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU424" t="inlineStr"/>
+      <c r="AV424" t="inlineStr"/>
+      <c r="AW424" t="inlineStr"/>
+      <c r="AX424" t="inlineStr"/>
+      <c r="AY424" t="inlineStr"/>
+      <c r="AZ424" t="inlineStr"/>
+      <c r="BA424" t="inlineStr"/>
+      <c r="BB424" t="inlineStr"/>
+      <c r="BC424" t="inlineStr"/>
+      <c r="BD424" t="inlineStr"/>
+      <c r="BE424" t="inlineStr"/>
+      <c r="BF424" t="inlineStr"/>
+      <c r="BG424" t="inlineStr"/>
+      <c r="BH424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="1" t="inlineStr">
+        <is>
+          <t>URv8Z17s</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>19.10.2024 11:15</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Galech I.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Riazor
+ (La Coruña)</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>34 889</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>21 198</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>Dep. La Coruna</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>Eldense</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr"/>
+      <c r="N425" t="inlineStr"/>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T425" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V425" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W425" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X425" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y425" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z425" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA425" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AB425" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC425" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD425" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE425" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF425" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG425" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH425" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI425" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ425" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK425" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL425" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM425" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="AN425" t="inlineStr">
+        <is>
+          <t>idiakez imanol</t>
+        </is>
+      </c>
+      <c r="AO425" t="inlineStr">
+        <is>
+          <t>hh4xt2Df</t>
+        </is>
+      </c>
+      <c r="AP425" t="inlineStr">
+        <is>
+          <t>ponz daniel</t>
+        </is>
+      </c>
+      <c r="AQ425" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR425" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS425" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT425" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU425" t="inlineStr"/>
+      <c r="AV425" t="inlineStr"/>
+      <c r="AW425" t="inlineStr"/>
+      <c r="AX425" t="inlineStr"/>
+      <c r="AY425" t="inlineStr"/>
+      <c r="AZ425" t="inlineStr"/>
+      <c r="BA425" t="inlineStr"/>
+      <c r="BB425" t="inlineStr"/>
+      <c r="BC425" t="inlineStr"/>
+      <c r="BD425" t="inlineStr"/>
+      <c r="BE425" t="inlineStr"/>
+      <c r="BF425" t="inlineStr"/>
+      <c r="BG425" t="inlineStr"/>
+      <c r="BH425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="1" t="inlineStr">
+        <is>
+          <t>KCHJi1TP</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>19.10.2024 11:15</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Sesma Espinosa M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Estadio La Rosaleda
+ (Málaga)</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>30 044</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>26 074</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>R. Oviedo</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr"/>
+      <c r="N426" t="inlineStr"/>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T426" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V426" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W426" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X426" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y426" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z426" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA426" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB426" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC426" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD426" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE426" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF426" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AG426" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH426" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI426" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ426" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AK426" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL426" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM426" t="inlineStr">
+        <is>
+          <t>tjXr7SAp</t>
+        </is>
+      </c>
+      <c r="AN426" t="inlineStr">
+        <is>
+          <t>garcia sergio</t>
+        </is>
+      </c>
+      <c r="AO426" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="AP426" t="inlineStr">
+        <is>
+          <t>calleja javier</t>
+        </is>
+      </c>
+      <c r="AQ426" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR426" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS426" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT426" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU426" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV426" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AW426" t="inlineStr"/>
+      <c r="AX426" t="inlineStr"/>
+      <c r="AY426" t="inlineStr"/>
+      <c r="AZ426" t="inlineStr"/>
+      <c r="BA426" t="inlineStr"/>
+      <c r="BB426" t="inlineStr"/>
+      <c r="BC426" t="inlineStr"/>
+      <c r="BD426" t="inlineStr"/>
+      <c r="BE426" t="inlineStr"/>
+      <c r="BF426" t="inlineStr"/>
+      <c r="BG426" t="inlineStr"/>
+      <c r="BH426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="1" t="inlineStr">
+        <is>
+          <t>CAdbpJLa</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>18.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Perez M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Arcángel
+ (Córdoba)</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>21 822</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>15 636</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>Cordoba</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>FC Cartagena SAD</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr"/>
+      <c r="N427" t="inlineStr"/>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T427" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U427" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V427" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W427" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X427" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y427" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z427" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA427" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB427" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC427" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD427" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE427" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF427" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AG427" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH427" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI427" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ427" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK427" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL427" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM427" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="AN427" t="inlineStr">
+        <is>
+          <t>ania ivan</t>
+        </is>
+      </c>
+      <c r="AO427" t="inlineStr">
+        <is>
+          <t>hlQINAie</t>
+        </is>
+      </c>
+      <c r="AP427" t="inlineStr">
+        <is>
+          <t>jandro</t>
+        </is>
+      </c>
+      <c r="AQ427" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR427" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS427" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT427" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU427" t="inlineStr"/>
+      <c r="AV427" t="inlineStr"/>
+      <c r="AW427" t="inlineStr"/>
+      <c r="AX427" t="inlineStr"/>
+      <c r="AY427" t="inlineStr"/>
+      <c r="AZ427" t="inlineStr"/>
+      <c r="BA427" t="inlineStr"/>
+      <c r="BB427" t="inlineStr"/>
+      <c r="BC427" t="inlineStr"/>
+      <c r="BD427" t="inlineStr"/>
+      <c r="BE427" t="inlineStr"/>
+      <c r="BF427" t="inlineStr"/>
+      <c r="BG427" t="inlineStr"/>
+      <c r="BH427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>d2d7HTod</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>14.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>De La Fuente Ramos O.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Estadio El Molinón
+ (Gijón)</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>29 029</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>19 940</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>Gijon</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>Castellon</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr"/>
+      <c r="N428" t="inlineStr"/>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T428" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U428" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V428" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W428" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X428" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y428" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Z428" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA428" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB428" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC428" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD428" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE428" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AF428" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG428" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH428" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI428" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ428" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK428" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL428" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM428" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="AN428" t="inlineStr">
+        <is>
+          <t>albes ruben</t>
+        </is>
+      </c>
+      <c r="AO428" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="AP428" t="inlineStr">
+        <is>
+          <t>schreuder dick</t>
+        </is>
+      </c>
+      <c r="AQ428" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR428" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS428" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT428" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU428" t="inlineStr"/>
+      <c r="AV428" t="inlineStr"/>
+      <c r="AW428" t="inlineStr"/>
+      <c r="AX428" t="inlineStr"/>
+      <c r="AY428" t="inlineStr"/>
+      <c r="AZ428" t="inlineStr"/>
+      <c r="BA428" t="inlineStr"/>
+      <c r="BB428" t="inlineStr"/>
+      <c r="BC428" t="inlineStr"/>
+      <c r="BD428" t="inlineStr"/>
+      <c r="BE428" t="inlineStr"/>
+      <c r="BF428" t="inlineStr"/>
+      <c r="BG428" t="inlineStr"/>
+      <c r="BH428" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH428"/>
+  <dimension ref="A1:BH440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81570,15 +81570,11 @@
           <t>12 602</t>
         </is>
       </c>
-      <c r="G419" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H419" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G419" t="n">
+        <v>0</v>
+      </c>
+      <c r="H419" t="n">
+        <v>1</v>
       </c>
       <c r="I419" t="inlineStr">
         <is>
@@ -81600,15 +81596,11 @@
           <t>Real Sociedad</t>
         </is>
       </c>
-      <c r="M419" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="N419" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
+      <c r="M419" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N419" t="n">
+        <v>1.94</v>
       </c>
       <c r="O419" t="inlineStr">
         <is>
@@ -81620,115 +81612,71 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q419" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R419" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S419" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T419" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U419" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V419" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W419" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X419" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y419" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z419" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA419" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB419" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC419" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD419" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE419" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AF419" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG419" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH419" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI419" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ419" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK419" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL419" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q419" t="n">
+        <v>8</v>
+      </c>
+      <c r="R419" t="n">
+        <v>14</v>
+      </c>
+      <c r="S419" t="n">
+        <v>3</v>
+      </c>
+      <c r="T419" t="n">
+        <v>4</v>
+      </c>
+      <c r="U419" t="n">
+        <v>4</v>
+      </c>
+      <c r="V419" t="n">
+        <v>6</v>
+      </c>
+      <c r="W419" t="n">
+        <v>1</v>
+      </c>
+      <c r="X419" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y419" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z419" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA419" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB419" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC419" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD419" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE419" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF419" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG419" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH419" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI419" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ419" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK419" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL419" t="n">
+        <v>1</v>
       </c>
       <c r="AM419" t="inlineStr">
         <is>
@@ -81770,45 +81718,29 @@
       <c r="AX419" t="inlineStr"/>
       <c r="AY419" t="inlineStr"/>
       <c r="AZ419" t="inlineStr"/>
-      <c r="BA419" t="inlineStr">
-        <is>
-          <t>428</t>
-        </is>
-      </c>
-      <c r="BB419" t="inlineStr">
-        <is>
-          <t>498</t>
-        </is>
-      </c>
-      <c r="BC419" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="BD419" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="BE419" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="BF419" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BG419" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BH419" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="BA419" t="n">
+        <v>428</v>
+      </c>
+      <c r="BB419" t="n">
+        <v>498</v>
+      </c>
+      <c r="BC419" t="n">
+        <v>369</v>
+      </c>
+      <c r="BD419" t="n">
+        <v>442</v>
+      </c>
+      <c r="BE419" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF419" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG419" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH419" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="420">
@@ -81844,15 +81776,11 @@
           <t>21 045</t>
         </is>
       </c>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H420" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G420" t="n">
+        <v>1</v>
+      </c>
+      <c r="H420" t="n">
+        <v>2</v>
       </c>
       <c r="I420" t="inlineStr">
         <is>
@@ -81874,15 +81802,11 @@
           <t>Betis</t>
         </is>
       </c>
-      <c r="M420" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="N420" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
+      <c r="M420" t="n">
+        <v>2</v>
+      </c>
+      <c r="N420" t="n">
+        <v>2.49</v>
       </c>
       <c r="O420" t="inlineStr">
         <is>
@@ -81894,115 +81818,71 @@
           <t>46%</t>
         </is>
       </c>
-      <c r="Q420" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R420" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S420" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T420" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U420" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V420" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W420" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X420" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y420" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z420" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA420" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AB420" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC420" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD420" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE420" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AF420" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG420" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH420" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI420" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ420" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AK420" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL420" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q420" t="n">
+        <v>19</v>
+      </c>
+      <c r="R420" t="n">
+        <v>11</v>
+      </c>
+      <c r="S420" t="n">
+        <v>6</v>
+      </c>
+      <c r="T420" t="n">
+        <v>7</v>
+      </c>
+      <c r="U420" t="n">
+        <v>7</v>
+      </c>
+      <c r="V420" t="n">
+        <v>3</v>
+      </c>
+      <c r="W420" t="n">
+        <v>6</v>
+      </c>
+      <c r="X420" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y420" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z420" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA420" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB420" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC420" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD420" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE420" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF420" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG420" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH420" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI420" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ420" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK420" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL420" t="n">
+        <v>1</v>
       </c>
       <c r="AM420" t="inlineStr">
         <is>
@@ -82038,59 +81918,39 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU420" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV420" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AU420" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV420" t="n">
+        <v>1</v>
       </c>
       <c r="AW420" t="inlineStr"/>
       <c r="AX420" t="inlineStr"/>
       <c r="AY420" t="inlineStr"/>
       <c r="AZ420" t="inlineStr"/>
-      <c r="BA420" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="BB420" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="BC420" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="BD420" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="BE420" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BF420" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BG420" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BH420" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="BA420" t="n">
+        <v>373</v>
+      </c>
+      <c r="BB420" t="n">
+        <v>322</v>
+      </c>
+      <c r="BC420" t="n">
+        <v>289</v>
+      </c>
+      <c r="BD420" t="n">
+        <v>238</v>
+      </c>
+      <c r="BE420" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF420" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG420" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH420" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="421">
@@ -82126,15 +81986,11 @@
           <t>46 713</t>
         </is>
       </c>
-      <c r="G421" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H421" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G421" t="n">
+        <v>4</v>
+      </c>
+      <c r="H421" t="n">
+        <v>1</v>
       </c>
       <c r="I421" t="inlineStr">
         <is>
@@ -82156,15 +82012,11 @@
           <t>Espanyol</t>
         </is>
       </c>
-      <c r="M421" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="N421" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
+      <c r="M421" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N421" t="n">
+        <v>0.27</v>
       </c>
       <c r="O421" t="inlineStr">
         <is>
@@ -82176,115 +82028,71 @@
           <t>43%</t>
         </is>
       </c>
-      <c r="Q421" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R421" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S421" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T421" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U421" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V421" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W421" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X421" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y421" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Z421" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA421" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB421" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC421" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD421" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE421" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF421" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AG421" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH421" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI421" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ421" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AK421" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL421" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q421" t="n">
+        <v>10</v>
+      </c>
+      <c r="R421" t="n">
+        <v>5</v>
+      </c>
+      <c r="S421" t="n">
+        <v>6</v>
+      </c>
+      <c r="T421" t="n">
+        <v>2</v>
+      </c>
+      <c r="U421" t="n">
+        <v>4</v>
+      </c>
+      <c r="V421" t="n">
+        <v>2</v>
+      </c>
+      <c r="W421" t="n">
+        <v>0</v>
+      </c>
+      <c r="X421" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y421" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z421" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA421" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB421" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC421" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD421" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE421" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF421" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG421" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH421" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI421" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ421" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK421" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL421" t="n">
+        <v>3</v>
       </c>
       <c r="AM421" t="inlineStr">
         <is>
@@ -82326,45 +82134,29 @@
       <c r="AX421" t="inlineStr"/>
       <c r="AY421" t="inlineStr"/>
       <c r="AZ421" t="inlineStr"/>
-      <c r="BA421" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="BB421" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="BC421" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="BD421" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="BE421" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BF421" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="BG421" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BH421" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="BA421" t="n">
+        <v>480</v>
+      </c>
+      <c r="BB421" t="n">
+        <v>349</v>
+      </c>
+      <c r="BC421" t="n">
+        <v>400</v>
+      </c>
+      <c r="BD421" t="n">
+        <v>275</v>
+      </c>
+      <c r="BE421" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF421" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG421" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH421" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="422">
@@ -82400,15 +82192,11 @@
           <t>16 904</t>
         </is>
       </c>
-      <c r="G422" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H422" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G422" t="n">
+        <v>2</v>
+      </c>
+      <c r="H422" t="n">
+        <v>3</v>
       </c>
       <c r="I422" t="inlineStr">
         <is>
@@ -82430,15 +82218,11 @@
           <t>Valladolid</t>
         </is>
       </c>
-      <c r="M422" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="N422" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="M422" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N422" t="n">
+        <v>2.5</v>
       </c>
       <c r="O422" t="inlineStr">
         <is>
@@ -82450,115 +82234,71 @@
           <t>38%</t>
         </is>
       </c>
-      <c r="Q422" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R422" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S422" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T422" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U422" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V422" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W422" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X422" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y422" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z422" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA422" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB422" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC422" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD422" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE422" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF422" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AG422" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH422" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI422" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AJ422" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK422" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AL422" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q422" t="n">
+        <v>10</v>
+      </c>
+      <c r="R422" t="n">
+        <v>12</v>
+      </c>
+      <c r="S422" t="n">
+        <v>4</v>
+      </c>
+      <c r="T422" t="n">
+        <v>4</v>
+      </c>
+      <c r="U422" t="n">
+        <v>3</v>
+      </c>
+      <c r="V422" t="n">
+        <v>5</v>
+      </c>
+      <c r="W422" t="n">
+        <v>3</v>
+      </c>
+      <c r="X422" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y422" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z422" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA422" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB422" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC422" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD422" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE422" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF422" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG422" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH422" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI422" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ422" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK422" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL422" t="n">
+        <v>2</v>
       </c>
       <c r="AM422" t="inlineStr">
         <is>
@@ -82594,59 +82334,39 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU422" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AV422" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AU422" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV422" t="n">
+        <v>0</v>
       </c>
       <c r="AW422" t="inlineStr"/>
       <c r="AX422" t="inlineStr"/>
       <c r="AY422" t="inlineStr"/>
       <c r="AZ422" t="inlineStr"/>
-      <c r="BA422" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="BB422" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="BC422" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="BD422" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="BE422" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BF422" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BG422" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BH422" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="BA422" t="n">
+        <v>418</v>
+      </c>
+      <c r="BB422" t="n">
+        <v>247</v>
+      </c>
+      <c r="BC422" t="n">
+        <v>325</v>
+      </c>
+      <c r="BD422" t="n">
+        <v>166</v>
+      </c>
+      <c r="BE422" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF422" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG422" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH422" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="423">
@@ -82682,15 +82402,11 @@
           <t>12 905</t>
         </is>
       </c>
-      <c r="G423" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H423" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G423" t="n">
+        <v>2</v>
+      </c>
+      <c r="H423" t="n">
+        <v>0</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
@@ -82724,115 +82440,71 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q423" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R423" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S423" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T423" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U423" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V423" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W423" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X423" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y423" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z423" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA423" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB423" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC423" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD423" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE423" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AF423" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AG423" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH423" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI423" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ423" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK423" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL423" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q423" t="n">
+        <v>15</v>
+      </c>
+      <c r="R423" t="n">
+        <v>12</v>
+      </c>
+      <c r="S423" t="n">
+        <v>5</v>
+      </c>
+      <c r="T423" t="n">
+        <v>4</v>
+      </c>
+      <c r="U423" t="n">
+        <v>7</v>
+      </c>
+      <c r="V423" t="n">
+        <v>6</v>
+      </c>
+      <c r="W423" t="n">
+        <v>3</v>
+      </c>
+      <c r="X423" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y423" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z423" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA423" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB423" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC423" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD423" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE423" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF423" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG423" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH423" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI423" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ423" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK423" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL423" t="n">
+        <v>3</v>
       </c>
       <c r="AM423" t="inlineStr">
         <is>
@@ -82916,15 +82588,11 @@
           <t>16 582</t>
         </is>
       </c>
-      <c r="G424" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H424" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G424" t="n">
+        <v>4</v>
+      </c>
+      <c r="H424" t="n">
+        <v>0</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
@@ -82958,115 +82626,71 @@
           <t>39%</t>
         </is>
       </c>
-      <c r="Q424" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R424" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S424" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="T424" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U424" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V424" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W424" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X424" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y424" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z424" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA424" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB424" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC424" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD424" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE424" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AF424" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG424" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH424" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI424" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ424" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK424" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL424" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q424" t="n">
+        <v>18</v>
+      </c>
+      <c r="R424" t="n">
+        <v>6</v>
+      </c>
+      <c r="S424" t="n">
+        <v>12</v>
+      </c>
+      <c r="T424" t="n">
+        <v>0</v>
+      </c>
+      <c r="U424" t="n">
+        <v>3</v>
+      </c>
+      <c r="V424" t="n">
+        <v>4</v>
+      </c>
+      <c r="W424" t="n">
+        <v>3</v>
+      </c>
+      <c r="X424" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y424" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z424" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA424" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB424" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC424" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD424" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE424" t="n">
+        <v>33</v>
+      </c>
+      <c r="AF424" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG424" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH424" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI424" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ424" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK424" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL424" t="n">
+        <v>2</v>
       </c>
       <c r="AM424" t="inlineStr">
         <is>
@@ -83150,15 +82774,11 @@
           <t>21 198</t>
         </is>
       </c>
-      <c r="G425" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H425" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G425" t="n">
+        <v>1</v>
+      </c>
+      <c r="H425" t="n">
+        <v>1</v>
       </c>
       <c r="I425" t="inlineStr">
         <is>
@@ -83192,115 +82812,71 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="Q425" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R425" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S425" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T425" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U425" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V425" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W425" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="X425" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y425" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z425" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA425" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AB425" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC425" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD425" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE425" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AF425" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG425" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH425" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AI425" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ425" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK425" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL425" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="Q425" t="n">
+        <v>26</v>
+      </c>
+      <c r="R425" t="n">
+        <v>6</v>
+      </c>
+      <c r="S425" t="n">
+        <v>7</v>
+      </c>
+      <c r="T425" t="n">
+        <v>2</v>
+      </c>
+      <c r="U425" t="n">
+        <v>9</v>
+      </c>
+      <c r="V425" t="n">
+        <v>3</v>
+      </c>
+      <c r="W425" t="n">
+        <v>10</v>
+      </c>
+      <c r="X425" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y425" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z425" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA425" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB425" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC425" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD425" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE425" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF425" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG425" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH425" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI425" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ425" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK425" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL425" t="n">
+        <v>4</v>
       </c>
       <c r="AM425" t="inlineStr">
         <is>
@@ -83384,15 +82960,11 @@
           <t>26 074</t>
         </is>
       </c>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H426" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G426" t="n">
+        <v>0</v>
+      </c>
+      <c r="H426" t="n">
+        <v>0</v>
       </c>
       <c r="I426" t="inlineStr">
         <is>
@@ -83426,115 +82998,71 @@
           <t>49%</t>
         </is>
       </c>
-      <c r="Q426" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R426" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S426" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T426" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U426" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="V426" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W426" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X426" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y426" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z426" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA426" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB426" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AC426" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD426" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE426" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AF426" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AG426" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AH426" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI426" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ426" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AK426" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL426" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q426" t="n">
+        <v>12</v>
+      </c>
+      <c r="R426" t="n">
+        <v>20</v>
+      </c>
+      <c r="S426" t="n">
+        <v>4</v>
+      </c>
+      <c r="T426" t="n">
+        <v>7</v>
+      </c>
+      <c r="U426" t="n">
+        <v>3</v>
+      </c>
+      <c r="V426" t="n">
+        <v>8</v>
+      </c>
+      <c r="W426" t="n">
+        <v>5</v>
+      </c>
+      <c r="X426" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y426" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z426" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA426" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB426" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC426" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD426" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE426" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF426" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG426" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH426" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI426" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ426" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK426" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL426" t="n">
+        <v>2</v>
       </c>
       <c r="AM426" t="inlineStr">
         <is>
@@ -83570,15 +83098,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU426" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV426" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AU426" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV426" t="n">
+        <v>1</v>
       </c>
       <c r="AW426" t="inlineStr"/>
       <c r="AX426" t="inlineStr"/>
@@ -83626,15 +83150,11 @@
           <t>15 636</t>
         </is>
       </c>
-      <c r="G427" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H427" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G427" t="n">
+        <v>2</v>
+      </c>
+      <c r="H427" t="n">
+        <v>1</v>
       </c>
       <c r="I427" t="inlineStr">
         <is>
@@ -83668,115 +83188,71 @@
           <t>40%</t>
         </is>
       </c>
-      <c r="Q427" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R427" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S427" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T427" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U427" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V427" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W427" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X427" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y427" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z427" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA427" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB427" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC427" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD427" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AE427" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AF427" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AG427" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH427" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI427" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ427" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK427" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL427" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q427" t="n">
+        <v>21</v>
+      </c>
+      <c r="R427" t="n">
+        <v>6</v>
+      </c>
+      <c r="S427" t="n">
+        <v>7</v>
+      </c>
+      <c r="T427" t="n">
+        <v>3</v>
+      </c>
+      <c r="U427" t="n">
+        <v>10</v>
+      </c>
+      <c r="V427" t="n">
+        <v>3</v>
+      </c>
+      <c r="W427" t="n">
+        <v>4</v>
+      </c>
+      <c r="X427" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y427" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z427" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA427" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB427" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC427" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD427" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE427" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF427" t="n">
+        <v>31</v>
+      </c>
+      <c r="AG427" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH427" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI427" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ427" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK427" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL427" t="n">
+        <v>3</v>
       </c>
       <c r="AM427" t="inlineStr">
         <is>
@@ -83860,15 +83336,11 @@
           <t>19 940</t>
         </is>
       </c>
-      <c r="G428" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H428" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G428" t="n">
+        <v>2</v>
+      </c>
+      <c r="H428" t="n">
+        <v>1</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -83902,115 +83374,71 @@
           <t>45%</t>
         </is>
       </c>
-      <c r="Q428" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="R428" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S428" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T428" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U428" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V428" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W428" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X428" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y428" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z428" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA428" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB428" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC428" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD428" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE428" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="AF428" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AG428" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH428" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AI428" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ428" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK428" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL428" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q428" t="n">
+        <v>19</v>
+      </c>
+      <c r="R428" t="n">
+        <v>11</v>
+      </c>
+      <c r="S428" t="n">
+        <v>9</v>
+      </c>
+      <c r="T428" t="n">
+        <v>1</v>
+      </c>
+      <c r="U428" t="n">
+        <v>7</v>
+      </c>
+      <c r="V428" t="n">
+        <v>6</v>
+      </c>
+      <c r="W428" t="n">
+        <v>3</v>
+      </c>
+      <c r="X428" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y428" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z428" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA428" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB428" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC428" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD428" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE428" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF428" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG428" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH428" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI428" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ428" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK428" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL428" t="n">
+        <v>2</v>
       </c>
       <c r="AM428" t="inlineStr">
         <is>
@@ -84061,6 +83489,2482 @@
       <c r="BG428" t="inlineStr"/>
       <c r="BH428" t="inlineStr"/>
     </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2Xrca2mA</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>20.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Bengoetxea R.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Estadi Olímpic Lluís Companys
+ (Barcelona)</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>55 926</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>47 848</t>
+        </is>
+      </c>
+      <c r="G429" t="n">
+        <v>5</v>
+      </c>
+      <c r="H429" t="n">
+        <v>1</v>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="M429" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="N429" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="Q429" t="n">
+        <v>21</v>
+      </c>
+      <c r="R429" t="n">
+        <v>7</v>
+      </c>
+      <c r="S429" t="n">
+        <v>9</v>
+      </c>
+      <c r="T429" t="n">
+        <v>1</v>
+      </c>
+      <c r="U429" t="n">
+        <v>8</v>
+      </c>
+      <c r="V429" t="n">
+        <v>2</v>
+      </c>
+      <c r="W429" t="n">
+        <v>4</v>
+      </c>
+      <c r="X429" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y429" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z429" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA429" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB429" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC429" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD429" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE429" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF429" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG429" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH429" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI429" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ429" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK429" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL429" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM429" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="AN429" t="inlineStr">
+        <is>
+          <t>flick hans dieter</t>
+        </is>
+      </c>
+      <c r="AO429" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="AP429" t="inlineStr">
+        <is>
+          <t>pimienta francisco</t>
+        </is>
+      </c>
+      <c r="AQ429" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR429" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS429" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT429" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU429" t="inlineStr"/>
+      <c r="AV429" t="inlineStr"/>
+      <c r="AW429" t="inlineStr"/>
+      <c r="AX429" t="inlineStr"/>
+      <c r="AY429" t="inlineStr"/>
+      <c r="AZ429" t="inlineStr"/>
+      <c r="BA429" t="n">
+        <v>614</v>
+      </c>
+      <c r="BB429" t="n">
+        <v>296</v>
+      </c>
+      <c r="BC429" t="n">
+        <v>558</v>
+      </c>
+      <c r="BD429" t="n">
+        <v>235</v>
+      </c>
+      <c r="BE429" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF429" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG429" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH429" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>f1xuAJ1S</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>20.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Garcia V.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Estadio de la Ceramica
+ (Villarreal)</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>23 000</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>19 355</t>
+        </is>
+      </c>
+      <c r="G430" t="n">
+        <v>1</v>
+      </c>
+      <c r="H430" t="n">
+        <v>1</v>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="M430" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="N430" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q430" t="n">
+        <v>10</v>
+      </c>
+      <c r="R430" t="n">
+        <v>21</v>
+      </c>
+      <c r="S430" t="n">
+        <v>4</v>
+      </c>
+      <c r="T430" t="n">
+        <v>4</v>
+      </c>
+      <c r="U430" t="n">
+        <v>5</v>
+      </c>
+      <c r="V430" t="n">
+        <v>7</v>
+      </c>
+      <c r="W430" t="n">
+        <v>1</v>
+      </c>
+      <c r="X430" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y430" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z430" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA430" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB430" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC430" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD430" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE430" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF430" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG430" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH430" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI430" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ430" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK430" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL430" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM430" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="AN430" t="inlineStr">
+        <is>
+          <t>marcelino</t>
+        </is>
+      </c>
+      <c r="AO430" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="AP430" t="inlineStr">
+        <is>
+          <t>bordalas pepe</t>
+        </is>
+      </c>
+      <c r="AQ430" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR430" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS430" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT430" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU430" t="inlineStr"/>
+      <c r="AV430" t="inlineStr"/>
+      <c r="AW430" t="inlineStr"/>
+      <c r="AX430" t="inlineStr"/>
+      <c r="AY430" t="inlineStr"/>
+      <c r="AZ430" t="inlineStr"/>
+      <c r="BA430" t="n">
+        <v>367</v>
+      </c>
+      <c r="BB430" t="n">
+        <v>268</v>
+      </c>
+      <c r="BC430" t="n">
+        <v>273</v>
+      </c>
+      <c r="BD430" t="n">
+        <v>194</v>
+      </c>
+      <c r="BE430" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF430" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG430" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH430" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>65kl1OIc</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>20.10.2024 11:15</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Munuera Montero J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Metropolitano Stadium
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>70 460</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>60 122</t>
+        </is>
+      </c>
+      <c r="G431" t="n">
+        <v>3</v>
+      </c>
+      <c r="H431" t="n">
+        <v>1</v>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="M431" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="N431" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="Q431" t="n">
+        <v>24</v>
+      </c>
+      <c r="R431" t="n">
+        <v>5</v>
+      </c>
+      <c r="S431" t="n">
+        <v>9</v>
+      </c>
+      <c r="T431" t="n">
+        <v>2</v>
+      </c>
+      <c r="U431" t="n">
+        <v>8</v>
+      </c>
+      <c r="V431" t="n">
+        <v>1</v>
+      </c>
+      <c r="W431" t="n">
+        <v>7</v>
+      </c>
+      <c r="X431" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y431" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z431" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA431" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB431" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC431" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD431" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE431" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF431" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG431" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH431" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI431" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ431" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK431" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL431" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM431" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="AN431" t="inlineStr">
+        <is>
+          <t>simeone diego</t>
+        </is>
+      </c>
+      <c r="AO431" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="AP431" t="inlineStr">
+        <is>
+          <t>jimenez borja</t>
+        </is>
+      </c>
+      <c r="AQ431" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR431" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS431" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT431" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU431" t="inlineStr"/>
+      <c r="AV431" t="inlineStr"/>
+      <c r="AW431" t="inlineStr"/>
+      <c r="AX431" t="inlineStr"/>
+      <c r="AY431" t="inlineStr"/>
+      <c r="AZ431" t="inlineStr"/>
+      <c r="BA431" t="n">
+        <v>568</v>
+      </c>
+      <c r="BB431" t="n">
+        <v>342</v>
+      </c>
+      <c r="BC431" t="n">
+        <v>485</v>
+      </c>
+      <c r="BD431" t="n">
+        <v>260</v>
+      </c>
+      <c r="BE431" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF431" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG431" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH431" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>0SQqjbAd</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>20.10.2024 09:00</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Rojas J. A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Estadi Mallorca Son Moix
+ (Palma de Mallorca)</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>26 020</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>18 316</t>
+        </is>
+      </c>
+      <c r="G432" t="n">
+        <v>1</v>
+      </c>
+      <c r="H432" t="n">
+        <v>0</v>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="M432" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N432" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q432" t="n">
+        <v>19</v>
+      </c>
+      <c r="R432" t="n">
+        <v>10</v>
+      </c>
+      <c r="S432" t="n">
+        <v>5</v>
+      </c>
+      <c r="T432" t="n">
+        <v>2</v>
+      </c>
+      <c r="U432" t="n">
+        <v>10</v>
+      </c>
+      <c r="V432" t="n">
+        <v>7</v>
+      </c>
+      <c r="W432" t="n">
+        <v>4</v>
+      </c>
+      <c r="X432" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y432" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z432" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA432" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB432" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC432" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD432" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE432" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF432" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG432" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH432" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI432" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ432" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK432" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL432" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM432" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="AN432" t="inlineStr">
+        <is>
+          <t>arrasate jagoba</t>
+        </is>
+      </c>
+      <c r="AO432" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="AP432" t="inlineStr">
+        <is>
+          <t>perez inigo</t>
+        </is>
+      </c>
+      <c r="AQ432" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR432" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS432" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT432" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU432" t="inlineStr"/>
+      <c r="AV432" t="inlineStr"/>
+      <c r="AW432" t="inlineStr"/>
+      <c r="AX432" t="inlineStr"/>
+      <c r="AY432" t="inlineStr"/>
+      <c r="AZ432" t="inlineStr"/>
+      <c r="BA432" t="n">
+        <v>367</v>
+      </c>
+      <c r="BB432" t="n">
+        <v>371</v>
+      </c>
+      <c r="BC432" t="n">
+        <v>279</v>
+      </c>
+      <c r="BD432" t="n">
+        <v>279</v>
+      </c>
+      <c r="BE432" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF432" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG432" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH432" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>8Uo5ctIM</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>19.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Hernandez A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Estadio de Balaídos
+ (Vigo)</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>24 791</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>24 445</t>
+        </is>
+      </c>
+      <c r="G433" t="n">
+        <v>1</v>
+      </c>
+      <c r="H433" t="n">
+        <v>2</v>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="M433" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="N433" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q433" t="n">
+        <v>13</v>
+      </c>
+      <c r="R433" t="n">
+        <v>10</v>
+      </c>
+      <c r="S433" t="n">
+        <v>5</v>
+      </c>
+      <c r="T433" t="n">
+        <v>3</v>
+      </c>
+      <c r="U433" t="n">
+        <v>4</v>
+      </c>
+      <c r="V433" t="n">
+        <v>5</v>
+      </c>
+      <c r="W433" t="n">
+        <v>4</v>
+      </c>
+      <c r="X433" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y433" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z433" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA433" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB433" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC433" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD433" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE433" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF433" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG433" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH433" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI433" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ433" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK433" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL433" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM433" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="AN433" t="inlineStr">
+        <is>
+          <t>giraldez claudio</t>
+        </is>
+      </c>
+      <c r="AO433" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="AP433" t="inlineStr">
+        <is>
+          <t>ancelotti carlo</t>
+        </is>
+      </c>
+      <c r="AQ433" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR433" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS433" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT433" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU433" t="inlineStr"/>
+      <c r="AV433" t="inlineStr"/>
+      <c r="AW433" t="inlineStr"/>
+      <c r="AX433" t="inlineStr"/>
+      <c r="AY433" t="inlineStr"/>
+      <c r="AZ433" t="inlineStr"/>
+      <c r="BA433" t="n">
+        <v>530</v>
+      </c>
+      <c r="BB433" t="n">
+        <v>608</v>
+      </c>
+      <c r="BC433" t="n">
+        <v>460</v>
+      </c>
+      <c r="BD433" t="n">
+        <v>541</v>
+      </c>
+      <c r="BE433" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF433" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG433" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH433" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>QgYGXuxf</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>20.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Orellana M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Estadio Manuel Martínez Valero
+ (Elche)</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>31 388</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>17 421</t>
+        </is>
+      </c>
+      <c r="G434" t="n">
+        <v>2</v>
+      </c>
+      <c r="H434" t="n">
+        <v>1</v>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>Gijon</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr"/>
+      <c r="N434" t="inlineStr"/>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q434" t="n">
+        <v>12</v>
+      </c>
+      <c r="R434" t="n">
+        <v>9</v>
+      </c>
+      <c r="S434" t="n">
+        <v>4</v>
+      </c>
+      <c r="T434" t="n">
+        <v>2</v>
+      </c>
+      <c r="U434" t="n">
+        <v>5</v>
+      </c>
+      <c r="V434" t="n">
+        <v>5</v>
+      </c>
+      <c r="W434" t="n">
+        <v>3</v>
+      </c>
+      <c r="X434" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y434" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z434" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA434" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB434" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC434" t="inlineStr"/>
+      <c r="AD434" t="inlineStr"/>
+      <c r="AE434" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF434" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG434" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH434" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI434" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ434" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK434" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL434" t="n">
+        <v>7</v>
+      </c>
+      <c r="AM434" t="inlineStr">
+        <is>
+          <t>zT9gi7i9</t>
+        </is>
+      </c>
+      <c r="AN434" t="inlineStr">
+        <is>
+          <t>sarabia eder</t>
+        </is>
+      </c>
+      <c r="AO434" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="AP434" t="inlineStr">
+        <is>
+          <t>albes ruben</t>
+        </is>
+      </c>
+      <c r="AQ434" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR434" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS434" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT434" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU434" t="inlineStr"/>
+      <c r="AV434" t="inlineStr"/>
+      <c r="AW434" t="inlineStr"/>
+      <c r="AX434" t="inlineStr"/>
+      <c r="AY434" t="inlineStr"/>
+      <c r="AZ434" t="inlineStr"/>
+      <c r="BA434" t="inlineStr"/>
+      <c r="BB434" t="inlineStr"/>
+      <c r="BC434" t="inlineStr"/>
+      <c r="BD434" t="inlineStr"/>
+      <c r="BE434" t="inlineStr"/>
+      <c r="BF434" t="inlineStr"/>
+      <c r="BG434" t="inlineStr"/>
+      <c r="BH434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>4pgjnuim</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>20.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Muresan S.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>La Romareda
+ (Zaragoza)</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>33 608</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>20 814</t>
+        </is>
+      </c>
+      <c r="G435" t="n">
+        <v>1</v>
+      </c>
+      <c r="H435" t="n">
+        <v>2</v>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>Almeria</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr"/>
+      <c r="N435" t="inlineStr"/>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q435" t="n">
+        <v>15</v>
+      </c>
+      <c r="R435" t="n">
+        <v>13</v>
+      </c>
+      <c r="S435" t="n">
+        <v>3</v>
+      </c>
+      <c r="T435" t="n">
+        <v>5</v>
+      </c>
+      <c r="U435" t="n">
+        <v>7</v>
+      </c>
+      <c r="V435" t="n">
+        <v>3</v>
+      </c>
+      <c r="W435" t="n">
+        <v>5</v>
+      </c>
+      <c r="X435" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y435" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z435" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA435" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB435" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC435" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD435" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE435" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF435" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG435" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH435" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI435" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ435" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK435" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL435" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM435" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="AN435" t="inlineStr">
+        <is>
+          <t>fernandez braulio victor</t>
+        </is>
+      </c>
+      <c r="AO435" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="AP435" t="inlineStr">
+        <is>
+          <t>rubi joan</t>
+        </is>
+      </c>
+      <c r="AQ435" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR435" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS435" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT435" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU435" t="inlineStr"/>
+      <c r="AV435" t="inlineStr"/>
+      <c r="AW435" t="inlineStr"/>
+      <c r="AX435" t="inlineStr"/>
+      <c r="AY435" t="inlineStr"/>
+      <c r="AZ435" t="inlineStr"/>
+      <c r="BA435" t="inlineStr"/>
+      <c r="BB435" t="inlineStr"/>
+      <c r="BC435" t="inlineStr"/>
+      <c r="BD435" t="inlineStr"/>
+      <c r="BE435" t="inlineStr"/>
+      <c r="BF435" t="inlineStr"/>
+      <c r="BG435" t="inlineStr"/>
+      <c r="BH435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>b7WOVJ66</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>20.10.2024 11:15</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Gonzalez Diaz M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Estadio Municipal da Malata
+ (Ferrol)</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>10 450</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>6 732</t>
+        </is>
+      </c>
+      <c r="G436" t="n">
+        <v>0</v>
+      </c>
+      <c r="H436" t="n">
+        <v>0</v>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>Racing Club Ferrol</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr"/>
+      <c r="N436" t="inlineStr"/>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q436" t="n">
+        <v>13</v>
+      </c>
+      <c r="R436" t="n">
+        <v>10</v>
+      </c>
+      <c r="S436" t="n">
+        <v>4</v>
+      </c>
+      <c r="T436" t="n">
+        <v>2</v>
+      </c>
+      <c r="U436" t="n">
+        <v>7</v>
+      </c>
+      <c r="V436" t="n">
+        <v>7</v>
+      </c>
+      <c r="W436" t="n">
+        <v>2</v>
+      </c>
+      <c r="X436" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y436" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z436" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA436" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB436" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC436" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD436" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE436" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF436" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG436" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH436" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI436" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ436" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK436" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL436" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM436" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="AN436" t="inlineStr">
+        <is>
+          <t>parralo cristobal</t>
+        </is>
+      </c>
+      <c r="AO436" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="AP436" t="inlineStr">
+        <is>
+          <t>hidalgo antonio</t>
+        </is>
+      </c>
+      <c r="AQ436" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR436" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT436" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU436" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV436" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW436" t="inlineStr"/>
+      <c r="AX436" t="inlineStr"/>
+      <c r="AY436" t="inlineStr"/>
+      <c r="AZ436" t="inlineStr"/>
+      <c r="BA436" t="inlineStr"/>
+      <c r="BB436" t="inlineStr"/>
+      <c r="BC436" t="inlineStr"/>
+      <c r="BD436" t="inlineStr"/>
+      <c r="BE436" t="inlineStr"/>
+      <c r="BF436" t="inlineStr"/>
+      <c r="BG436" t="inlineStr"/>
+      <c r="BH436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>vcGkHKiD</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>20.10.2024 09:00</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Monescillo D.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Mirandilla
+ (Cadiz)</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>20 776</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>15 545</t>
+        </is>
+      </c>
+      <c r="G437" t="n">
+        <v>0</v>
+      </c>
+      <c r="H437" t="n">
+        <v>1</v>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>Cadiz CF</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr"/>
+      <c r="N437" t="inlineStr"/>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q437" t="n">
+        <v>16</v>
+      </c>
+      <c r="R437" t="n">
+        <v>14</v>
+      </c>
+      <c r="S437" t="n">
+        <v>4</v>
+      </c>
+      <c r="T437" t="n">
+        <v>2</v>
+      </c>
+      <c r="U437" t="n">
+        <v>6</v>
+      </c>
+      <c r="V437" t="n">
+        <v>5</v>
+      </c>
+      <c r="W437" t="n">
+        <v>6</v>
+      </c>
+      <c r="X437" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y437" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z437" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA437" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB437" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC437" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD437" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE437" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF437" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG437" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH437" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI437" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ437" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK437" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL437" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM437" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="AN437" t="inlineStr">
+        <is>
+          <t>lopez paco</t>
+        </is>
+      </c>
+      <c r="AO437" t="inlineStr">
+        <is>
+          <t>rak12p9n</t>
+        </is>
+      </c>
+      <c r="AP437" t="inlineStr">
+        <is>
+          <t>lopez jose</t>
+        </is>
+      </c>
+      <c r="AQ437" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR437" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT437" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU437" t="inlineStr"/>
+      <c r="AV437" t="inlineStr"/>
+      <c r="AW437" t="inlineStr"/>
+      <c r="AX437" t="inlineStr"/>
+      <c r="AY437" t="inlineStr"/>
+      <c r="AZ437" t="inlineStr"/>
+      <c r="BA437" t="inlineStr"/>
+      <c r="BB437" t="inlineStr"/>
+      <c r="BC437" t="inlineStr"/>
+      <c r="BD437" t="inlineStr"/>
+      <c r="BE437" t="inlineStr"/>
+      <c r="BF437" t="inlineStr"/>
+      <c r="BG437" t="inlineStr"/>
+      <c r="BH437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>8xj7rcjC</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>19.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Fuentes Molina A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Anduva
+ (Miranda de Ebro)</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>5 759</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>3 770</t>
+        </is>
+      </c>
+      <c r="G438" t="n">
+        <v>1</v>
+      </c>
+      <c r="H438" t="n">
+        <v>0</v>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>Eibar</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr"/>
+      <c r="N438" t="inlineStr"/>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q438" t="n">
+        <v>8</v>
+      </c>
+      <c r="R438" t="n">
+        <v>7</v>
+      </c>
+      <c r="S438" t="n">
+        <v>3</v>
+      </c>
+      <c r="T438" t="n">
+        <v>2</v>
+      </c>
+      <c r="U438" t="n">
+        <v>3</v>
+      </c>
+      <c r="V438" t="n">
+        <v>4</v>
+      </c>
+      <c r="W438" t="n">
+        <v>2</v>
+      </c>
+      <c r="X438" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y438" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z438" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA438" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB438" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC438" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD438" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE438" t="n">
+        <v>35</v>
+      </c>
+      <c r="AF438" t="n">
+        <v>35</v>
+      </c>
+      <c r="AG438" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH438" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI438" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ438" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK438" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL438" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM438" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="AN438" t="inlineStr">
+        <is>
+          <t>lisci alessio</t>
+        </is>
+      </c>
+      <c r="AO438" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="AP438" t="inlineStr">
+        <is>
+          <t>etxeberria joseba</t>
+        </is>
+      </c>
+      <c r="AQ438" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR438" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT438" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV438" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW438" t="inlineStr"/>
+      <c r="AX438" t="inlineStr"/>
+      <c r="AY438" t="inlineStr"/>
+      <c r="AZ438" t="inlineStr"/>
+      <c r="BA438" t="inlineStr"/>
+      <c r="BB438" t="inlineStr"/>
+      <c r="BC438" t="inlineStr"/>
+      <c r="BD438" t="inlineStr"/>
+      <c r="BE438" t="inlineStr"/>
+      <c r="BF438" t="inlineStr"/>
+      <c r="BG438" t="inlineStr"/>
+      <c r="BH438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>QqTA4cPk</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>21.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Gil Manzano J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla
+ (Valencia)</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>49 430</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V439" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W439" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X439" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y439" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z439" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA439" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AB439" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC439" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD439" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE439" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AF439" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG439" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH439" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI439" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ439" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK439" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL439" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AM439" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="AN439" t="inlineStr">
+        <is>
+          <t>baraja ruben</t>
+        </is>
+      </c>
+      <c r="AO439" t="inlineStr">
+        <is>
+          <t>tI57YghG</t>
+        </is>
+      </c>
+      <c r="AP439" t="inlineStr">
+        <is>
+          <t>martinez diego</t>
+        </is>
+      </c>
+      <c r="AQ439" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR439" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT439" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU439" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV439" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW439" t="inlineStr"/>
+      <c r="AX439" t="inlineStr"/>
+      <c r="AY439" t="inlineStr"/>
+      <c r="AZ439" t="inlineStr"/>
+      <c r="BA439" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="BB439" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="BC439" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="BD439" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="BE439" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BF439" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BG439" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BH439" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="inlineStr">
+        <is>
+          <t>WWCsJtN0</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>21.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Muniz Munoz C.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Estadio Carlos Belmonte
+ (Albacete)</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>17 524</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>9 041</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>Burgos CF</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr"/>
+      <c r="N440" t="inlineStr"/>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V440" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W440" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X440" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y440" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z440" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA440" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB440" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC440" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD440" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE440" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF440" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AG440" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH440" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI440" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ440" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK440" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL440" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM440" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="AN440" t="inlineStr">
+        <is>
+          <t>gonzalez alberto</t>
+        </is>
+      </c>
+      <c r="AO440" t="inlineStr">
+        <is>
+          <t>l6JQtDqc</t>
+        </is>
+      </c>
+      <c r="AP440" t="inlineStr">
+        <is>
+          <t>bolo</t>
+        </is>
+      </c>
+      <c r="AQ440" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR440" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT440" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU440" t="inlineStr"/>
+      <c r="AV440" t="inlineStr"/>
+      <c r="AW440" t="inlineStr"/>
+      <c r="AX440" t="inlineStr"/>
+      <c r="AY440" t="inlineStr"/>
+      <c r="AZ440" t="inlineStr"/>
+      <c r="BA440" t="inlineStr"/>
+      <c r="BB440" t="inlineStr"/>
+      <c r="BC440" t="inlineStr"/>
+      <c r="BD440" t="inlineStr"/>
+      <c r="BE440" t="inlineStr"/>
+      <c r="BF440" t="inlineStr"/>
+      <c r="BG440" t="inlineStr"/>
+      <c r="BH440" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH440"/>
+  <dimension ref="A1:BH448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85482,15 +85482,11 @@
         </is>
       </c>
       <c r="F439" t="inlineStr"/>
-      <c r="G439" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H439" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G439" t="n">
+        <v>2</v>
+      </c>
+      <c r="H439" t="n">
+        <v>3</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
@@ -85512,15 +85508,11 @@
           <t>Las Palmas</t>
         </is>
       </c>
-      <c r="M439" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="N439" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
+      <c r="M439" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N439" t="n">
+        <v>1.14</v>
       </c>
       <c r="O439" t="inlineStr">
         <is>
@@ -85532,115 +85524,71 @@
           <t>53%</t>
         </is>
       </c>
-      <c r="Q439" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R439" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S439" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T439" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="U439" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V439" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W439" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X439" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y439" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z439" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA439" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AB439" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC439" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD439" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE439" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AF439" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AG439" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH439" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI439" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ439" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK439" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL439" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="Q439" t="n">
+        <v>14</v>
+      </c>
+      <c r="R439" t="n">
+        <v>11</v>
+      </c>
+      <c r="S439" t="n">
+        <v>7</v>
+      </c>
+      <c r="T439" t="n">
+        <v>6</v>
+      </c>
+      <c r="U439" t="n">
+        <v>4</v>
+      </c>
+      <c r="V439" t="n">
+        <v>2</v>
+      </c>
+      <c r="W439" t="n">
+        <v>3</v>
+      </c>
+      <c r="X439" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y439" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z439" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA439" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB439" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC439" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD439" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE439" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF439" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG439" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH439" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI439" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ439" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK439" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL439" t="n">
+        <v>9</v>
       </c>
       <c r="AM439" t="inlineStr">
         <is>
@@ -85676,59 +85624,39 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU439" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AV439" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AU439" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV439" t="n">
+        <v>0</v>
       </c>
       <c r="AW439" t="inlineStr"/>
       <c r="AX439" t="inlineStr"/>
       <c r="AY439" t="inlineStr"/>
       <c r="AZ439" t="inlineStr"/>
-      <c r="BA439" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="BB439" t="inlineStr">
-        <is>
-          <t>490</t>
-        </is>
-      </c>
-      <c r="BC439" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="BD439" t="inlineStr">
-        <is>
-          <t>399</t>
-        </is>
-      </c>
-      <c r="BE439" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BF439" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BG439" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BH439" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="BA439" t="n">
+        <v>410</v>
+      </c>
+      <c r="BB439" t="n">
+        <v>490</v>
+      </c>
+      <c r="BC439" t="n">
+        <v>318</v>
+      </c>
+      <c r="BD439" t="n">
+        <v>399</v>
+      </c>
+      <c r="BE439" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF439" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG439" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH439" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="440">
@@ -85764,15 +85692,11 @@
           <t>9 041</t>
         </is>
       </c>
-      <c r="G440" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H440" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G440" t="n">
+        <v>2</v>
+      </c>
+      <c r="H440" t="n">
+        <v>0</v>
       </c>
       <c r="I440" t="inlineStr">
         <is>
@@ -85806,115 +85730,71 @@
           <t>60%</t>
         </is>
       </c>
-      <c r="Q440" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R440" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S440" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T440" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U440" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V440" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W440" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X440" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y440" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z440" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA440" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB440" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC440" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD440" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE440" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AF440" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AG440" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH440" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI440" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ440" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK440" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL440" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q440" t="n">
+        <v>18</v>
+      </c>
+      <c r="R440" t="n">
+        <v>9</v>
+      </c>
+      <c r="S440" t="n">
+        <v>10</v>
+      </c>
+      <c r="T440" t="n">
+        <v>3</v>
+      </c>
+      <c r="U440" t="n">
+        <v>6</v>
+      </c>
+      <c r="V440" t="n">
+        <v>4</v>
+      </c>
+      <c r="W440" t="n">
+        <v>2</v>
+      </c>
+      <c r="X440" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y440" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z440" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA440" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB440" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC440" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD440" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE440" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF440" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG440" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH440" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI440" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ440" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL440" t="n">
+        <v>1</v>
       </c>
       <c r="AM440" t="inlineStr">
         <is>
@@ -85965,6 +85845,1886 @@
       <c r="BG440" t="inlineStr"/>
       <c r="BH440" t="inlineStr"/>
     </row>
+    <row r="441">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>67jtezzI</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>24.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Barrera R.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Power Horse Stadium
+ (Almería)</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>17 400</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>Almeria</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr"/>
+      <c r="N441" t="inlineStr"/>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V441" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W441" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X441" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y441" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z441" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AA441" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB441" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC441" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD441" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE441" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF441" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG441" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH441" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI441" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AJ441" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK441" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL441" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM441" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="AN441" t="inlineStr">
+        <is>
+          <t>rubi joan</t>
+        </is>
+      </c>
+      <c r="AO441" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="AP441" t="inlineStr">
+        <is>
+          <t>gonzalez alberto</t>
+        </is>
+      </c>
+      <c r="AQ441" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR441" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT441" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU441" t="inlineStr"/>
+      <c r="AV441" t="inlineStr"/>
+      <c r="AW441" t="inlineStr"/>
+      <c r="AX441" t="inlineStr"/>
+      <c r="AY441" t="inlineStr"/>
+      <c r="AZ441" t="inlineStr"/>
+      <c r="BA441" t="inlineStr"/>
+      <c r="BB441" t="inlineStr"/>
+      <c r="BC441" t="inlineStr"/>
+      <c r="BD441" t="inlineStr"/>
+      <c r="BE441" t="inlineStr"/>
+      <c r="BF441" t="inlineStr"/>
+      <c r="BG441" t="inlineStr"/>
+      <c r="BH441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="inlineStr">
+        <is>
+          <t>CpD7BeKb</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>24.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Sanchez Lopez R.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Estadi Ciutat de València
+ (Valencia)</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>26 354</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>Dep. La Coruna</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr"/>
+      <c r="N442" t="inlineStr"/>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V442" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W442" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X442" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y442" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z442" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA442" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB442" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC442" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD442" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE442" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF442" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG442" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH442" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI442" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ442" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK442" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL442" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM442" t="inlineStr">
+        <is>
+          <t>fiZxGYJ3</t>
+        </is>
+      </c>
+      <c r="AN442" t="inlineStr">
+        <is>
+          <t>calero julian</t>
+        </is>
+      </c>
+      <c r="AO442" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="AP442" t="inlineStr">
+        <is>
+          <t>idiakez imanol</t>
+        </is>
+      </c>
+      <c r="AQ442" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR442" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS442" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT442" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU442" t="inlineStr"/>
+      <c r="AV442" t="inlineStr"/>
+      <c r="AW442" t="inlineStr"/>
+      <c r="AX442" t="inlineStr"/>
+      <c r="AY442" t="inlineStr"/>
+      <c r="AZ442" t="inlineStr"/>
+      <c r="BA442" t="inlineStr"/>
+      <c r="BB442" t="inlineStr"/>
+      <c r="BC442" t="inlineStr"/>
+      <c r="BD442" t="inlineStr"/>
+      <c r="BE442" t="inlineStr"/>
+      <c r="BF442" t="inlineStr"/>
+      <c r="BG442" t="inlineStr"/>
+      <c r="BH442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="inlineStr">
+        <is>
+          <t>U1eH0v6t</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>23.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>De La Fuente Ramos O.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Estadio Municipal Cartagonova
+ (Cartagena)</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>13 745</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>5 637</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>FC Cartagena SAD</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr"/>
+      <c r="N443" t="inlineStr"/>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V443" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="W443" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X443" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y443" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z443" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA443" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB443" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC443" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD443" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE443" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF443" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG443" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH443" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI443" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ443" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AK443" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL443" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM443" t="inlineStr">
+        <is>
+          <t>hlQINAie</t>
+        </is>
+      </c>
+      <c r="AN443" t="inlineStr">
+        <is>
+          <t>jandro</t>
+        </is>
+      </c>
+      <c r="AO443" t="inlineStr">
+        <is>
+          <t>zT9gi7i9</t>
+        </is>
+      </c>
+      <c r="AP443" t="inlineStr">
+        <is>
+          <t>sarabia eder</t>
+        </is>
+      </c>
+      <c r="AQ443" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR443" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT443" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU443" t="inlineStr"/>
+      <c r="AV443" t="inlineStr"/>
+      <c r="AW443" t="inlineStr"/>
+      <c r="AX443" t="inlineStr"/>
+      <c r="AY443" t="inlineStr"/>
+      <c r="AZ443" t="inlineStr"/>
+      <c r="BA443" t="inlineStr"/>
+      <c r="BB443" t="inlineStr"/>
+      <c r="BC443" t="inlineStr"/>
+      <c r="BD443" t="inlineStr"/>
+      <c r="BE443" t="inlineStr"/>
+      <c r="BF443" t="inlineStr"/>
+      <c r="BG443" t="inlineStr"/>
+      <c r="BH443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="inlineStr">
+        <is>
+          <t>GIJbDHkn</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>23.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Mallo E.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Estadio El Sardinero
+ (Santander)</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>22 222</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>16 036</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>Cordoba</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr"/>
+      <c r="N444" t="inlineStr"/>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V444" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W444" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X444" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y444" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="Z444" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AA444" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB444" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC444" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AD444" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE444" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AF444" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG444" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH444" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI444" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ444" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK444" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL444" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM444" t="inlineStr">
+        <is>
+          <t>rak12p9n</t>
+        </is>
+      </c>
+      <c r="AN444" t="inlineStr">
+        <is>
+          <t>lopez jose</t>
+        </is>
+      </c>
+      <c r="AO444" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="AP444" t="inlineStr">
+        <is>
+          <t>ania ivan</t>
+        </is>
+      </c>
+      <c r="AQ444" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR444" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT444" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU444" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV444" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AW444" t="inlineStr"/>
+      <c r="AX444" t="inlineStr"/>
+      <c r="AY444" t="inlineStr"/>
+      <c r="AZ444" t="inlineStr"/>
+      <c r="BA444" t="inlineStr"/>
+      <c r="BB444" t="inlineStr"/>
+      <c r="BC444" t="inlineStr"/>
+      <c r="BD444" t="inlineStr"/>
+      <c r="BE444" t="inlineStr"/>
+      <c r="BF444" t="inlineStr"/>
+      <c r="BG444" t="inlineStr"/>
+      <c r="BH444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="inlineStr">
+        <is>
+          <t>06qkgE4U</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>23.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Lax Franco S.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Ipurua
+ (Eibar)</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>8 164</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>5 100</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>Eibar</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>Cadiz CF</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr"/>
+      <c r="N445" t="inlineStr"/>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T445" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V445" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W445" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X445" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y445" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z445" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AA445" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB445" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC445" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD445" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE445" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AF445" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG445" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH445" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI445" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AJ445" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK445" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL445" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM445" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="AN445" t="inlineStr">
+        <is>
+          <t>etxeberria joseba</t>
+        </is>
+      </c>
+      <c r="AO445" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="AP445" t="inlineStr">
+        <is>
+          <t>lopez paco</t>
+        </is>
+      </c>
+      <c r="AQ445" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR445" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT445" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU445" t="inlineStr"/>
+      <c r="AV445" t="inlineStr"/>
+      <c r="AW445" t="inlineStr"/>
+      <c r="AX445" t="inlineStr"/>
+      <c r="AY445" t="inlineStr"/>
+      <c r="AZ445" t="inlineStr"/>
+      <c r="BA445" t="inlineStr"/>
+      <c r="BB445" t="inlineStr"/>
+      <c r="BC445" t="inlineStr"/>
+      <c r="BD445" t="inlineStr"/>
+      <c r="BE445" t="inlineStr"/>
+      <c r="BF445" t="inlineStr"/>
+      <c r="BG445" t="inlineStr"/>
+      <c r="BH445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="inlineStr">
+        <is>
+          <t>bsmYdd55</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>23.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Monescillo D.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Pepico Amat
+ (Elda)</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>4 038</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>4 158</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>Eldense</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr"/>
+      <c r="N446" t="inlineStr"/>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T446" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V446" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W446" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X446" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y446" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z446" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA446" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB446" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC446" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD446" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE446" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AF446" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG446" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH446" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI446" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ446" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK446" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL446" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM446" t="inlineStr">
+        <is>
+          <t>hh4xt2Df</t>
+        </is>
+      </c>
+      <c r="AN446" t="inlineStr">
+        <is>
+          <t>ponz daniel</t>
+        </is>
+      </c>
+      <c r="AO446" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="AP446" t="inlineStr">
+        <is>
+          <t>fernandez braulio victor</t>
+        </is>
+      </c>
+      <c r="AQ446" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR446" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT446" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU446" t="inlineStr"/>
+      <c r="AV446" t="inlineStr"/>
+      <c r="AW446" t="inlineStr"/>
+      <c r="AX446" t="inlineStr"/>
+      <c r="AY446" t="inlineStr"/>
+      <c r="AZ446" t="inlineStr"/>
+      <c r="BA446" t="inlineStr"/>
+      <c r="BB446" t="inlineStr"/>
+      <c r="BC446" t="inlineStr"/>
+      <c r="BD446" t="inlineStr"/>
+      <c r="BE446" t="inlineStr"/>
+      <c r="BF446" t="inlineStr"/>
+      <c r="BG446" t="inlineStr"/>
+      <c r="BH446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="inlineStr">
+        <is>
+          <t>xSbPbIzg</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>22.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>De Aza M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Castalia
+ (Castellón de la Plana)</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>15 500</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>9 431</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>Castellon</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>Granada CF</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr"/>
+      <c r="N447" t="inlineStr"/>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T447" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V447" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W447" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X447" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y447" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z447" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA447" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB447" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC447" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AD447" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE447" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF447" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG447" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH447" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI447" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ447" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK447" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL447" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AM447" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="AN447" t="inlineStr">
+        <is>
+          <t>schreuder dick</t>
+        </is>
+      </c>
+      <c r="AO447" t="inlineStr">
+        <is>
+          <t>K0UZov8F</t>
+        </is>
+      </c>
+      <c r="AP447" t="inlineStr">
+        <is>
+          <t>escriba fran</t>
+        </is>
+      </c>
+      <c r="AQ447" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR447" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT447" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU447" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV447" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AW447" t="inlineStr"/>
+      <c r="AX447" t="inlineStr"/>
+      <c r="AY447" t="inlineStr"/>
+      <c r="AZ447" t="inlineStr"/>
+      <c r="BA447" t="inlineStr"/>
+      <c r="BB447" t="inlineStr"/>
+      <c r="BC447" t="inlineStr"/>
+      <c r="BD447" t="inlineStr"/>
+      <c r="BE447" t="inlineStr"/>
+      <c r="BF447" t="inlineStr"/>
+      <c r="BG447" t="inlineStr"/>
+      <c r="BH447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="inlineStr">
+        <is>
+          <t>QFRek53d</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>22.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Moreno A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Carlos Tartiere
+ (Oviedo)</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>30 500</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>16 275</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>R. Oviedo</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr"/>
+      <c r="N448" t="inlineStr"/>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T448" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V448" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W448" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X448" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y448" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z448" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA448" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB448" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC448" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD448" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE448" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF448" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG448" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH448" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI448" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ448" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK448" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL448" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM448" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="AN448" t="inlineStr">
+        <is>
+          <t>calleja javier</t>
+        </is>
+      </c>
+      <c r="AO448" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="AP448" t="inlineStr">
+        <is>
+          <t>lisci alessio</t>
+        </is>
+      </c>
+      <c r="AQ448" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR448" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS448" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT448" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU448" t="inlineStr"/>
+      <c r="AV448" t="inlineStr"/>
+      <c r="AW448" t="inlineStr"/>
+      <c r="AX448" t="inlineStr"/>
+      <c r="AY448" t="inlineStr"/>
+      <c r="AZ448" t="inlineStr"/>
+      <c r="BA448" t="inlineStr"/>
+      <c r="BB448" t="inlineStr"/>
+      <c r="BC448" t="inlineStr"/>
+      <c r="BD448" t="inlineStr"/>
+      <c r="BE448" t="inlineStr"/>
+      <c r="BF448" t="inlineStr"/>
+      <c r="BG448" t="inlineStr"/>
+      <c r="BH448" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH448"/>
+  <dimension ref="A1:BH472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85874,15 +85874,11 @@
         </is>
       </c>
       <c r="F441" t="inlineStr"/>
-      <c r="G441" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H441" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G441" t="n">
+        <v>3</v>
+      </c>
+      <c r="H441" t="n">
+        <v>1</v>
       </c>
       <c r="I441" t="inlineStr">
         <is>
@@ -85916,115 +85912,71 @@
           <t>45%</t>
         </is>
       </c>
-      <c r="Q441" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R441" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="S441" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T441" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="U441" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="V441" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W441" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X441" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y441" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Z441" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AA441" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB441" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC441" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD441" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE441" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF441" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG441" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AH441" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI441" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AJ441" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK441" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL441" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q441" t="n">
+        <v>25</v>
+      </c>
+      <c r="R441" t="n">
+        <v>15</v>
+      </c>
+      <c r="S441" t="n">
+        <v>8</v>
+      </c>
+      <c r="T441" t="n">
+        <v>7</v>
+      </c>
+      <c r="U441" t="n">
+        <v>11</v>
+      </c>
+      <c r="V441" t="n">
+        <v>7</v>
+      </c>
+      <c r="W441" t="n">
+        <v>6</v>
+      </c>
+      <c r="X441" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y441" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z441" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA441" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB441" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC441" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD441" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE441" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF441" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG441" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH441" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI441" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ441" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK441" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL441" t="n">
+        <v>0</v>
       </c>
       <c r="AM441" t="inlineStr">
         <is>
@@ -86104,15 +86056,11 @@
         </is>
       </c>
       <c r="F442" t="inlineStr"/>
-      <c r="G442" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H442" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G442" t="n">
+        <v>2</v>
+      </c>
+      <c r="H442" t="n">
+        <v>1</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
@@ -86146,115 +86094,71 @@
           <t>57%</t>
         </is>
       </c>
-      <c r="Q442" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R442" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="S442" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="T442" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U442" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V442" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W442" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X442" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y442" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z442" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA442" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB442" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC442" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD442" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE442" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF442" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG442" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH442" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI442" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ442" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AK442" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL442" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q442" t="n">
+        <v>14</v>
+      </c>
+      <c r="R442" t="n">
+        <v>14</v>
+      </c>
+      <c r="S442" t="n">
+        <v>6</v>
+      </c>
+      <c r="T442" t="n">
+        <v>3</v>
+      </c>
+      <c r="U442" t="n">
+        <v>7</v>
+      </c>
+      <c r="V442" t="n">
+        <v>8</v>
+      </c>
+      <c r="W442" t="n">
+        <v>1</v>
+      </c>
+      <c r="X442" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y442" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z442" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA442" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB442" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC442" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD442" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE442" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF442" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG442" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH442" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI442" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ442" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK442" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL442" t="n">
+        <v>2</v>
       </c>
       <c r="AM442" t="inlineStr">
         <is>
@@ -86338,15 +86242,11 @@
           <t>5 637</t>
         </is>
       </c>
-      <c r="G443" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H443" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G443" t="n">
+        <v>0</v>
+      </c>
+      <c r="H443" t="n">
+        <v>0</v>
       </c>
       <c r="I443" t="inlineStr">
         <is>
@@ -86380,115 +86280,71 @@
           <t>76%</t>
         </is>
       </c>
-      <c r="Q443" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R443" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S443" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T443" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U443" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V443" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="W443" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X443" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y443" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="Z443" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA443" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB443" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC443" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD443" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE443" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF443" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG443" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH443" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI443" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ443" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AK443" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL443" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Q443" t="n">
+        <v>6</v>
+      </c>
+      <c r="R443" t="n">
+        <v>16</v>
+      </c>
+      <c r="S443" t="n">
+        <v>2</v>
+      </c>
+      <c r="T443" t="n">
+        <v>3</v>
+      </c>
+      <c r="U443" t="n">
+        <v>4</v>
+      </c>
+      <c r="V443" t="n">
+        <v>12</v>
+      </c>
+      <c r="W443" t="n">
+        <v>0</v>
+      </c>
+      <c r="X443" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y443" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z443" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA443" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB443" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC443" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE443" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF443" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG443" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH443" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI443" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ443" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK443" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL443" t="n">
+        <v>0</v>
       </c>
       <c r="AM443" t="inlineStr">
         <is>
@@ -86572,15 +86428,11 @@
           <t>16 036</t>
         </is>
       </c>
-      <c r="G444" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H444" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G444" t="n">
+        <v>2</v>
+      </c>
+      <c r="H444" t="n">
+        <v>0</v>
       </c>
       <c r="I444" t="inlineStr">
         <is>
@@ -86614,115 +86466,71 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="Q444" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R444" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S444" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T444" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U444" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V444" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W444" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X444" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y444" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="Z444" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AA444" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB444" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC444" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AD444" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AE444" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AF444" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AG444" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH444" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI444" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ444" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK444" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL444" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q444" t="n">
+        <v>20</v>
+      </c>
+      <c r="R444" t="n">
+        <v>13</v>
+      </c>
+      <c r="S444" t="n">
+        <v>7</v>
+      </c>
+      <c r="T444" t="n">
+        <v>4</v>
+      </c>
+      <c r="U444" t="n">
+        <v>5</v>
+      </c>
+      <c r="V444" t="n">
+        <v>8</v>
+      </c>
+      <c r="W444" t="n">
+        <v>8</v>
+      </c>
+      <c r="X444" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y444" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z444" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA444" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB444" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC444" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD444" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE444" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF444" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG444" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH444" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI444" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ444" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK444" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL444" t="n">
+        <v>5</v>
       </c>
       <c r="AM444" t="inlineStr">
         <is>
@@ -86758,15 +86566,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU444" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV444" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AU444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV444" t="n">
+        <v>1</v>
       </c>
       <c r="AW444" t="inlineStr"/>
       <c r="AX444" t="inlineStr"/>
@@ -86814,15 +86618,11 @@
           <t>5 100</t>
         </is>
       </c>
-      <c r="G445" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H445" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G445" t="n">
+        <v>1</v>
+      </c>
+      <c r="H445" t="n">
+        <v>0</v>
       </c>
       <c r="I445" t="inlineStr">
         <is>
@@ -86856,115 +86656,71 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="Q445" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R445" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="S445" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T445" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U445" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V445" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W445" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X445" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y445" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z445" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AA445" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB445" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC445" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD445" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE445" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AF445" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG445" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH445" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI445" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AJ445" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK445" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL445" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="Q445" t="n">
+        <v>11</v>
+      </c>
+      <c r="R445" t="n">
+        <v>12</v>
+      </c>
+      <c r="S445" t="n">
+        <v>4</v>
+      </c>
+      <c r="T445" t="n">
+        <v>4</v>
+      </c>
+      <c r="U445" t="n">
+        <v>4</v>
+      </c>
+      <c r="V445" t="n">
+        <v>1</v>
+      </c>
+      <c r="W445" t="n">
+        <v>3</v>
+      </c>
+      <c r="X445" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y445" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z445" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA445" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB445" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC445" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE445" t="n">
+        <v>33</v>
+      </c>
+      <c r="AF445" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG445" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH445" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI445" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ445" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK445" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL445" t="n">
+        <v>5</v>
       </c>
       <c r="AM445" t="inlineStr">
         <is>
@@ -87048,15 +86804,11 @@
           <t>4 158</t>
         </is>
       </c>
-      <c r="G446" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H446" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G446" t="n">
+        <v>2</v>
+      </c>
+      <c r="H446" t="n">
+        <v>3</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
@@ -87090,115 +86842,71 @@
           <t>47%</t>
         </is>
       </c>
-      <c r="Q446" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R446" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="S446" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T446" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U446" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="V446" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W446" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X446" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y446" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z446" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA446" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB446" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC446" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD446" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE446" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF446" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG446" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH446" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI446" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ446" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK446" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL446" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q446" t="n">
+        <v>21</v>
+      </c>
+      <c r="R446" t="n">
+        <v>9</v>
+      </c>
+      <c r="S446" t="n">
+        <v>7</v>
+      </c>
+      <c r="T446" t="n">
+        <v>4</v>
+      </c>
+      <c r="U446" t="n">
+        <v>8</v>
+      </c>
+      <c r="V446" t="n">
+        <v>3</v>
+      </c>
+      <c r="W446" t="n">
+        <v>6</v>
+      </c>
+      <c r="X446" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y446" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z446" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA446" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB446" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC446" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD446" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE446" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF446" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG446" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH446" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI446" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ446" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK446" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL446" t="n">
+        <v>3</v>
       </c>
       <c r="AM446" t="inlineStr">
         <is>
@@ -87282,15 +86990,11 @@
           <t>9 431</t>
         </is>
       </c>
-      <c r="G447" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H447" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G447" t="n">
+        <v>2</v>
+      </c>
+      <c r="H447" t="n">
+        <v>3</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
@@ -87324,115 +87028,71 @@
           <t>38%</t>
         </is>
       </c>
-      <c r="Q447" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R447" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S447" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T447" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U447" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V447" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W447" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X447" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y447" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="Z447" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AA447" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB447" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC447" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AD447" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE447" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AF447" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG447" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH447" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI447" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ447" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK447" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL447" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="Q447" t="n">
+        <v>11</v>
+      </c>
+      <c r="R447" t="n">
+        <v>11</v>
+      </c>
+      <c r="S447" t="n">
+        <v>4</v>
+      </c>
+      <c r="T447" t="n">
+        <v>5</v>
+      </c>
+      <c r="U447" t="n">
+        <v>4</v>
+      </c>
+      <c r="V447" t="n">
+        <v>3</v>
+      </c>
+      <c r="W447" t="n">
+        <v>3</v>
+      </c>
+      <c r="X447" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y447" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z447" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA447" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB447" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC447" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD447" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE447" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF447" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG447" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH447" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI447" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ447" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK447" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL447" t="n">
+        <v>6</v>
       </c>
       <c r="AM447" t="inlineStr">
         <is>
@@ -87468,15 +87128,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU447" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV447" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="AU447" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV447" t="n">
+        <v>1</v>
       </c>
       <c r="AW447" t="inlineStr"/>
       <c r="AX447" t="inlineStr"/>
@@ -87524,15 +87180,11 @@
           <t>16 275</t>
         </is>
       </c>
-      <c r="G448" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H448" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G448" t="n">
+        <v>4</v>
+      </c>
+      <c r="H448" t="n">
+        <v>1</v>
       </c>
       <c r="I448" t="inlineStr">
         <is>
@@ -87566,115 +87218,71 @@
           <t>48%</t>
         </is>
       </c>
-      <c r="Q448" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R448" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="S448" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="T448" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U448" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V448" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W448" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X448" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y448" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z448" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA448" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB448" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC448" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD448" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE448" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AF448" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG448" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH448" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AI448" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ448" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AK448" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL448" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="Q448" t="n">
+        <v>16</v>
+      </c>
+      <c r="R448" t="n">
+        <v>5</v>
+      </c>
+      <c r="S448" t="n">
+        <v>8</v>
+      </c>
+      <c r="T448" t="n">
+        <v>2</v>
+      </c>
+      <c r="U448" t="n">
+        <v>5</v>
+      </c>
+      <c r="V448" t="n">
+        <v>2</v>
+      </c>
+      <c r="W448" t="n">
+        <v>3</v>
+      </c>
+      <c r="X448" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y448" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z448" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA448" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB448" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC448" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD448" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE448" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF448" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG448" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH448" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI448" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ448" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK448" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL448" t="n">
+        <v>3</v>
       </c>
       <c r="AM448" t="inlineStr">
         <is>
@@ -87725,6 +87333,4818 @@
       <c r="BG448" t="inlineStr"/>
       <c r="BH448" t="inlineStr"/>
     </row>
+    <row r="449">
+      <c r="A449" s="1" t="inlineStr">
+        <is>
+          <t>4zlpJdvq</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>26.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Sanchez J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Estadio Santiago Bernabéu
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>83 186</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>78 192</t>
+        </is>
+      </c>
+      <c r="G449" t="n">
+        <v>0</v>
+      </c>
+      <c r="H449" t="n">
+        <v>4</v>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="M449" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="N449" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q449" t="n">
+        <v>9</v>
+      </c>
+      <c r="R449" t="n">
+        <v>15</v>
+      </c>
+      <c r="S449" t="n">
+        <v>4</v>
+      </c>
+      <c r="T449" t="n">
+        <v>7</v>
+      </c>
+      <c r="U449" t="n">
+        <v>4</v>
+      </c>
+      <c r="V449" t="n">
+        <v>7</v>
+      </c>
+      <c r="W449" t="n">
+        <v>1</v>
+      </c>
+      <c r="X449" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y449" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z449" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA449" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB449" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC449" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD449" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE449" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF449" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG449" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH449" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI449" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ449" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK449" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL449" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM449" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="AN449" t="inlineStr">
+        <is>
+          <t>ancelotti carlo</t>
+        </is>
+      </c>
+      <c r="AO449" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="AP449" t="inlineStr">
+        <is>
+          <t>flick hans dieter</t>
+        </is>
+      </c>
+      <c r="AQ449" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR449" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS449" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT449" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU449" t="inlineStr"/>
+      <c r="AV449" t="inlineStr"/>
+      <c r="AW449" t="inlineStr"/>
+      <c r="AX449" t="inlineStr"/>
+      <c r="AY449" t="inlineStr"/>
+      <c r="AZ449" t="inlineStr"/>
+      <c r="BA449" t="n">
+        <v>311</v>
+      </c>
+      <c r="BB449" t="n">
+        <v>452</v>
+      </c>
+      <c r="BC449" t="n">
+        <v>244</v>
+      </c>
+      <c r="BD449" t="n">
+        <v>380</v>
+      </c>
+      <c r="BE449" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF449" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG449" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH449" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="inlineStr">
+        <is>
+          <t>8Sp1FEw8</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>26.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Quintero A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Estadio de Gran Canaria
+ (Las Palmas)</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>32 392</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>21 506</t>
+        </is>
+      </c>
+      <c r="G450" t="n">
+        <v>1</v>
+      </c>
+      <c r="H450" t="n">
+        <v>0</v>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="M450" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="N450" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q450" t="n">
+        <v>12</v>
+      </c>
+      <c r="R450" t="n">
+        <v>8</v>
+      </c>
+      <c r="S450" t="n">
+        <v>3</v>
+      </c>
+      <c r="T450" t="n">
+        <v>3</v>
+      </c>
+      <c r="U450" t="n">
+        <v>7</v>
+      </c>
+      <c r="V450" t="n">
+        <v>2</v>
+      </c>
+      <c r="W450" t="n">
+        <v>2</v>
+      </c>
+      <c r="X450" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y450" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z450" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA450" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB450" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC450" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD450" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE450" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF450" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG450" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH450" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI450" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ450" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK450" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL450" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM450" t="inlineStr">
+        <is>
+          <t>tI57YghG</t>
+        </is>
+      </c>
+      <c r="AN450" t="inlineStr">
+        <is>
+          <t>martinez diego</t>
+        </is>
+      </c>
+      <c r="AO450" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="AP450" t="inlineStr">
+        <is>
+          <t>michel</t>
+        </is>
+      </c>
+      <c r="AQ450" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR450" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS450" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT450" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU450" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV450" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW450" t="inlineStr"/>
+      <c r="AX450" t="inlineStr"/>
+      <c r="AY450" t="inlineStr"/>
+      <c r="AZ450" t="inlineStr"/>
+      <c r="BA450" t="n">
+        <v>369</v>
+      </c>
+      <c r="BB450" t="n">
+        <v>474</v>
+      </c>
+      <c r="BC450" t="n">
+        <v>300</v>
+      </c>
+      <c r="BD450" t="n">
+        <v>401</v>
+      </c>
+      <c r="BE450" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF450" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG450" t="n">
+        <v>16</v>
+      </c>
+      <c r="BH450" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="inlineStr">
+        <is>
+          <t>dhkQFrkl</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>26.10.2024 11:15</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Vega A. C.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Campo de Futbol de Vallecas
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>14 708</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>13 010</t>
+        </is>
+      </c>
+      <c r="G451" t="n">
+        <v>1</v>
+      </c>
+      <c r="H451" t="n">
+        <v>0</v>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="M451" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="N451" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q451" t="n">
+        <v>16</v>
+      </c>
+      <c r="R451" t="n">
+        <v>15</v>
+      </c>
+      <c r="S451" t="n">
+        <v>4</v>
+      </c>
+      <c r="T451" t="n">
+        <v>7</v>
+      </c>
+      <c r="U451" t="n">
+        <v>10</v>
+      </c>
+      <c r="V451" t="n">
+        <v>5</v>
+      </c>
+      <c r="W451" t="n">
+        <v>2</v>
+      </c>
+      <c r="X451" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y451" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z451" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA451" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB451" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC451" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD451" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE451" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF451" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG451" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH451" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI451" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ451" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK451" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL451" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM451" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="AN451" t="inlineStr">
+        <is>
+          <t>perez inigo</t>
+        </is>
+      </c>
+      <c r="AO451" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="AP451" t="inlineStr">
+        <is>
+          <t>garcia luis</t>
+        </is>
+      </c>
+      <c r="AQ451" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR451" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS451" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT451" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU451" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV451" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW451" t="inlineStr"/>
+      <c r="AX451" t="inlineStr"/>
+      <c r="AY451" t="inlineStr"/>
+      <c r="AZ451" t="inlineStr"/>
+      <c r="BA451" t="n">
+        <v>371</v>
+      </c>
+      <c r="BB451" t="n">
+        <v>373</v>
+      </c>
+      <c r="BC451" t="n">
+        <v>299</v>
+      </c>
+      <c r="BD451" t="n">
+        <v>284</v>
+      </c>
+      <c r="BE451" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF451" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG451" t="n">
+        <v>9</v>
+      </c>
+      <c r="BH451" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>x88gL4RQ</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>26.10.2024 09:00</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Maeso F.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Estadio José Zorrilla
+ (Valladolid)</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>27 618</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>20 170</t>
+        </is>
+      </c>
+      <c r="G452" t="n">
+        <v>1</v>
+      </c>
+      <c r="H452" t="n">
+        <v>2</v>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="M452" t="n">
+        <v>1</v>
+      </c>
+      <c r="N452" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q452" t="n">
+        <v>7</v>
+      </c>
+      <c r="R452" t="n">
+        <v>21</v>
+      </c>
+      <c r="S452" t="n">
+        <v>3</v>
+      </c>
+      <c r="T452" t="n">
+        <v>9</v>
+      </c>
+      <c r="U452" t="n">
+        <v>4</v>
+      </c>
+      <c r="V452" t="n">
+        <v>8</v>
+      </c>
+      <c r="W452" t="n">
+        <v>0</v>
+      </c>
+      <c r="X452" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y452" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z452" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA452" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB452" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC452" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD452" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE452" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF452" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG452" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH452" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI452" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ452" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK452" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL452" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM452" t="inlineStr">
+        <is>
+          <t>naiTF0T9</t>
+        </is>
+      </c>
+      <c r="AN452" t="inlineStr">
+        <is>
+          <t>speranza camilo</t>
+        </is>
+      </c>
+      <c r="AO452" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="AP452" t="inlineStr">
+        <is>
+          <t>marcelino</t>
+        </is>
+      </c>
+      <c r="AQ452" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR452" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS452" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT452" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU452" t="inlineStr"/>
+      <c r="AV452" t="inlineStr"/>
+      <c r="AW452" t="inlineStr"/>
+      <c r="AX452" t="inlineStr"/>
+      <c r="AY452" t="inlineStr"/>
+      <c r="AZ452" t="inlineStr"/>
+      <c r="BA452" t="n">
+        <v>412</v>
+      </c>
+      <c r="BB452" t="n">
+        <v>511</v>
+      </c>
+      <c r="BC452" t="n">
+        <v>354</v>
+      </c>
+      <c r="BD452" t="n">
+        <v>448</v>
+      </c>
+      <c r="BE452" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF452" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG452" t="n">
+        <v>6</v>
+      </c>
+      <c r="BH452" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="inlineStr">
+        <is>
+          <t>vymauDyP</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>25.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Ortiz M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>RCDE Stadium
+ (Cornella de Llobregat)</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>40 000</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>23 656</t>
+        </is>
+      </c>
+      <c r="G453" t="n">
+        <v>0</v>
+      </c>
+      <c r="H453" t="n">
+        <v>2</v>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="M453" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N453" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q453" t="n">
+        <v>16</v>
+      </c>
+      <c r="R453" t="n">
+        <v>6</v>
+      </c>
+      <c r="S453" t="n">
+        <v>1</v>
+      </c>
+      <c r="T453" t="n">
+        <v>3</v>
+      </c>
+      <c r="U453" t="n">
+        <v>11</v>
+      </c>
+      <c r="V453" t="n">
+        <v>1</v>
+      </c>
+      <c r="W453" t="n">
+        <v>4</v>
+      </c>
+      <c r="X453" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y453" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z453" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA453" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB453" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC453" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD453" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE453" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF453" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG453" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH453" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI453" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ453" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK453" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL453" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM453" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="AN453" t="inlineStr">
+        <is>
+          <t>gonzalez manolo</t>
+        </is>
+      </c>
+      <c r="AO453" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="AP453" t="inlineStr">
+        <is>
+          <t>pimienta francisco</t>
+        </is>
+      </c>
+      <c r="AQ453" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR453" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS453" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT453" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU453" t="inlineStr"/>
+      <c r="AV453" t="inlineStr"/>
+      <c r="AW453" t="inlineStr"/>
+      <c r="AX453" t="inlineStr"/>
+      <c r="AY453" t="inlineStr"/>
+      <c r="AZ453" t="inlineStr"/>
+      <c r="BA453" t="n">
+        <v>312</v>
+      </c>
+      <c r="BB453" t="n">
+        <v>479</v>
+      </c>
+      <c r="BC453" t="n">
+        <v>237</v>
+      </c>
+      <c r="BD453" t="n">
+        <v>395</v>
+      </c>
+      <c r="BE453" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF453" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG453" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH453" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="inlineStr">
+        <is>
+          <t>A31a9QfS</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>26.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Muniz Munoz C.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Arcángel
+ (Córdoba)</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>21 822</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>13 453</t>
+        </is>
+      </c>
+      <c r="G454" t="n">
+        <v>2</v>
+      </c>
+      <c r="H454" t="n">
+        <v>0</v>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>Cordoba</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>Eldense</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr"/>
+      <c r="N454" t="inlineStr"/>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q454" t="n">
+        <v>18</v>
+      </c>
+      <c r="R454" t="n">
+        <v>7</v>
+      </c>
+      <c r="S454" t="n">
+        <v>10</v>
+      </c>
+      <c r="T454" t="n">
+        <v>3</v>
+      </c>
+      <c r="U454" t="n">
+        <v>5</v>
+      </c>
+      <c r="V454" t="n">
+        <v>3</v>
+      </c>
+      <c r="W454" t="n">
+        <v>3</v>
+      </c>
+      <c r="X454" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y454" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z454" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA454" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB454" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC454" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD454" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE454" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF454" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG454" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH454" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI454" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ454" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK454" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL454" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM454" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="AN454" t="inlineStr">
+        <is>
+          <t>ania ivan</t>
+        </is>
+      </c>
+      <c r="AO454" t="inlineStr">
+        <is>
+          <t>hh4xt2Df</t>
+        </is>
+      </c>
+      <c r="AP454" t="inlineStr">
+        <is>
+          <t>ponz daniel</t>
+        </is>
+      </c>
+      <c r="AQ454" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR454" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS454" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT454" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU454" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV454" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW454" t="inlineStr"/>
+      <c r="AX454" t="inlineStr"/>
+      <c r="AY454" t="inlineStr"/>
+      <c r="AZ454" t="inlineStr"/>
+      <c r="BA454" t="inlineStr"/>
+      <c r="BB454" t="inlineStr"/>
+      <c r="BC454" t="inlineStr"/>
+      <c r="BD454" t="inlineStr"/>
+      <c r="BE454" t="inlineStr"/>
+      <c r="BF454" t="inlineStr"/>
+      <c r="BG454" t="inlineStr"/>
+      <c r="BH454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="inlineStr">
+        <is>
+          <t>YFoDELW7</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>26.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Orellana M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>La Romareda
+ (Zaragoza)</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>33 608</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>20 017</t>
+        </is>
+      </c>
+      <c r="G455" t="n">
+        <v>1</v>
+      </c>
+      <c r="H455" t="n">
+        <v>2</v>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>Castellon</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr"/>
+      <c r="N455" t="inlineStr"/>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q455" t="n">
+        <v>10</v>
+      </c>
+      <c r="R455" t="n">
+        <v>13</v>
+      </c>
+      <c r="S455" t="n">
+        <v>4</v>
+      </c>
+      <c r="T455" t="n">
+        <v>4</v>
+      </c>
+      <c r="U455" t="n">
+        <v>4</v>
+      </c>
+      <c r="V455" t="n">
+        <v>3</v>
+      </c>
+      <c r="W455" t="n">
+        <v>2</v>
+      </c>
+      <c r="X455" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y455" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z455" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA455" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB455" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC455" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD455" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE455" t="n">
+        <v>37</v>
+      </c>
+      <c r="AF455" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG455" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH455" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI455" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ455" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK455" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL455" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM455" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="AN455" t="inlineStr">
+        <is>
+          <t>fernandez braulio victor</t>
+        </is>
+      </c>
+      <c r="AO455" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="AP455" t="inlineStr">
+        <is>
+          <t>schreuder dick</t>
+        </is>
+      </c>
+      <c r="AQ455" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR455" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS455" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT455" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU455" t="inlineStr"/>
+      <c r="AV455" t="inlineStr"/>
+      <c r="AW455" t="inlineStr"/>
+      <c r="AX455" t="inlineStr"/>
+      <c r="AY455" t="inlineStr"/>
+      <c r="AZ455" t="inlineStr"/>
+      <c r="BA455" t="inlineStr"/>
+      <c r="BB455" t="inlineStr"/>
+      <c r="BC455" t="inlineStr"/>
+      <c r="BD455" t="inlineStr"/>
+      <c r="BE455" t="inlineStr"/>
+      <c r="BF455" t="inlineStr"/>
+      <c r="BG455" t="inlineStr"/>
+      <c r="BH455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="inlineStr">
+        <is>
+          <t>Ey8jBnQF</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>26.10.2024 11:15</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Galech I.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Mirandilla
+ (Cadiz)</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>20 776</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>13 899</t>
+        </is>
+      </c>
+      <c r="G456" t="n">
+        <v>2</v>
+      </c>
+      <c r="H456" t="n">
+        <v>0</v>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>Cadiz CF</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>R. Oviedo</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr"/>
+      <c r="N456" t="inlineStr"/>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q456" t="n">
+        <v>11</v>
+      </c>
+      <c r="R456" t="n">
+        <v>4</v>
+      </c>
+      <c r="S456" t="n">
+        <v>5</v>
+      </c>
+      <c r="T456" t="n">
+        <v>1</v>
+      </c>
+      <c r="U456" t="n">
+        <v>4</v>
+      </c>
+      <c r="V456" t="n">
+        <v>2</v>
+      </c>
+      <c r="W456" t="n">
+        <v>2</v>
+      </c>
+      <c r="X456" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y456" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z456" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA456" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB456" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC456" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD456" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE456" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF456" t="n">
+        <v>31</v>
+      </c>
+      <c r="AG456" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH456" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI456" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ456" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK456" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL456" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM456" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="AN456" t="inlineStr">
+        <is>
+          <t>lopez paco</t>
+        </is>
+      </c>
+      <c r="AO456" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="AP456" t="inlineStr">
+        <is>
+          <t>calleja javier</t>
+        </is>
+      </c>
+      <c r="AQ456" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR456" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS456" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT456" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU456" t="inlineStr"/>
+      <c r="AV456" t="inlineStr"/>
+      <c r="AW456" t="inlineStr"/>
+      <c r="AX456" t="inlineStr"/>
+      <c r="AY456" t="inlineStr"/>
+      <c r="AZ456" t="inlineStr"/>
+      <c r="BA456" t="inlineStr"/>
+      <c r="BB456" t="inlineStr"/>
+      <c r="BC456" t="inlineStr"/>
+      <c r="BD456" t="inlineStr"/>
+      <c r="BE456" t="inlineStr"/>
+      <c r="BF456" t="inlineStr"/>
+      <c r="BG456" t="inlineStr"/>
+      <c r="BH456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="inlineStr">
+        <is>
+          <t>Qkr5Gs2e</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>26.10.2024 11:15</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Gonzalez Diaz M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Anduva
+ (Miranda de Ebro)</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>5 759</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>2 700</t>
+        </is>
+      </c>
+      <c r="G457" t="n">
+        <v>3</v>
+      </c>
+      <c r="H457" t="n">
+        <v>1</v>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>FC Cartagena SAD</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr"/>
+      <c r="N457" t="inlineStr"/>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="Q457" t="n">
+        <v>12</v>
+      </c>
+      <c r="R457" t="n">
+        <v>11</v>
+      </c>
+      <c r="S457" t="n">
+        <v>6</v>
+      </c>
+      <c r="T457" t="n">
+        <v>5</v>
+      </c>
+      <c r="U457" t="n">
+        <v>3</v>
+      </c>
+      <c r="V457" t="n">
+        <v>3</v>
+      </c>
+      <c r="W457" t="n">
+        <v>3</v>
+      </c>
+      <c r="X457" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y457" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z457" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA457" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB457" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC457" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD457" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE457" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF457" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG457" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH457" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI457" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ457" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK457" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL457" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM457" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="AN457" t="inlineStr">
+        <is>
+          <t>lisci alessio</t>
+        </is>
+      </c>
+      <c r="AO457" t="inlineStr">
+        <is>
+          <t>hlQINAie</t>
+        </is>
+      </c>
+      <c r="AP457" t="inlineStr">
+        <is>
+          <t>jandro</t>
+        </is>
+      </c>
+      <c r="AQ457" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR457" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS457" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT457" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU457" t="inlineStr"/>
+      <c r="AV457" t="inlineStr"/>
+      <c r="AW457" t="inlineStr"/>
+      <c r="AX457" t="inlineStr"/>
+      <c r="AY457" t="inlineStr"/>
+      <c r="AZ457" t="inlineStr"/>
+      <c r="BA457" t="inlineStr"/>
+      <c r="BB457" t="inlineStr"/>
+      <c r="BC457" t="inlineStr"/>
+      <c r="BD457" t="inlineStr"/>
+      <c r="BE457" t="inlineStr"/>
+      <c r="BF457" t="inlineStr"/>
+      <c r="BG457" t="inlineStr"/>
+      <c r="BH457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="inlineStr">
+        <is>
+          <t>tjlFtyLO</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>24.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Guzman Mansilla J. L.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Estadio El Plantío
+ (Burgos)</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>12 194</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>8 053</t>
+        </is>
+      </c>
+      <c r="G458" t="n">
+        <v>1</v>
+      </c>
+      <c r="H458" t="n">
+        <v>1</v>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>Burgos CF</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>Racing Club Ferrol</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr"/>
+      <c r="N458" t="inlineStr"/>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q458" t="n">
+        <v>15</v>
+      </c>
+      <c r="R458" t="n">
+        <v>11</v>
+      </c>
+      <c r="S458" t="n">
+        <v>2</v>
+      </c>
+      <c r="T458" t="n">
+        <v>1</v>
+      </c>
+      <c r="U458" t="n">
+        <v>10</v>
+      </c>
+      <c r="V458" t="n">
+        <v>2</v>
+      </c>
+      <c r="W458" t="n">
+        <v>3</v>
+      </c>
+      <c r="X458" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y458" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z458" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA458" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB458" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC458" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD458" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE458" t="n">
+        <v>41</v>
+      </c>
+      <c r="AF458" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG458" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH458" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI458" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ458" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK458" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL458" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM458" t="inlineStr">
+        <is>
+          <t>l6JQtDqc</t>
+        </is>
+      </c>
+      <c r="AN458" t="inlineStr">
+        <is>
+          <t>bolo</t>
+        </is>
+      </c>
+      <c r="AO458" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="AP458" t="inlineStr">
+        <is>
+          <t>parralo cristobal</t>
+        </is>
+      </c>
+      <c r="AQ458" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR458" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS458" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT458" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU458" t="inlineStr"/>
+      <c r="AV458" t="inlineStr"/>
+      <c r="AW458" t="inlineStr"/>
+      <c r="AX458" t="inlineStr"/>
+      <c r="AY458" t="inlineStr"/>
+      <c r="AZ458" t="inlineStr"/>
+      <c r="BA458" t="inlineStr"/>
+      <c r="BB458" t="inlineStr"/>
+      <c r="BC458" t="inlineStr"/>
+      <c r="BD458" t="inlineStr"/>
+      <c r="BE458" t="inlineStr"/>
+      <c r="BF458" t="inlineStr"/>
+      <c r="BG458" t="inlineStr"/>
+      <c r="BH458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="inlineStr">
+        <is>
+          <t>KAGF9ZlB</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>24.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Fuentes Molina A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Estadio El Molinón
+ (Gijón)</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>29 029</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>18 690</t>
+        </is>
+      </c>
+      <c r="G459" t="n">
+        <v>2</v>
+      </c>
+      <c r="H459" t="n">
+        <v>1</v>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>Gijon</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr"/>
+      <c r="N459" t="inlineStr"/>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="Q459" t="n">
+        <v>15</v>
+      </c>
+      <c r="R459" t="n">
+        <v>10</v>
+      </c>
+      <c r="S459" t="n">
+        <v>5</v>
+      </c>
+      <c r="T459" t="n">
+        <v>4</v>
+      </c>
+      <c r="U459" t="n">
+        <v>3</v>
+      </c>
+      <c r="V459" t="n">
+        <v>4</v>
+      </c>
+      <c r="W459" t="n">
+        <v>7</v>
+      </c>
+      <c r="X459" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y459" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z459" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA459" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB459" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC459" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD459" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE459" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF459" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG459" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH459" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI459" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ459" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK459" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL459" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM459" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="AN459" t="inlineStr">
+        <is>
+          <t>albes ruben</t>
+        </is>
+      </c>
+      <c r="AO459" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="AP459" t="inlineStr">
+        <is>
+          <t>hidalgo antonio</t>
+        </is>
+      </c>
+      <c r="AQ459" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR459" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS459" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT459" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU459" t="inlineStr"/>
+      <c r="AV459" t="inlineStr"/>
+      <c r="AW459" t="inlineStr"/>
+      <c r="AX459" t="inlineStr"/>
+      <c r="AY459" t="inlineStr"/>
+      <c r="AZ459" t="inlineStr"/>
+      <c r="BA459" t="inlineStr"/>
+      <c r="BB459" t="inlineStr"/>
+      <c r="BC459" t="inlineStr"/>
+      <c r="BD459" t="inlineStr"/>
+      <c r="BE459" t="inlineStr"/>
+      <c r="BF459" t="inlineStr"/>
+      <c r="BG459" t="inlineStr"/>
+      <c r="BH459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="inlineStr">
+        <is>
+          <t>vaTmiRYq</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>24.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Reig S. A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Estadio Heliodoro Rodríguez López
+ (Santa Cruz de Tenerife)</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>22 824</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>13 121</t>
+        </is>
+      </c>
+      <c r="G460" t="n">
+        <v>0</v>
+      </c>
+      <c r="H460" t="n">
+        <v>0</v>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>Tenerife</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr"/>
+      <c r="N460" t="inlineStr"/>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q460" t="n">
+        <v>14</v>
+      </c>
+      <c r="R460" t="n">
+        <v>5</v>
+      </c>
+      <c r="S460" t="n">
+        <v>4</v>
+      </c>
+      <c r="T460" t="n">
+        <v>1</v>
+      </c>
+      <c r="U460" t="n">
+        <v>5</v>
+      </c>
+      <c r="V460" t="n">
+        <v>3</v>
+      </c>
+      <c r="W460" t="n">
+        <v>5</v>
+      </c>
+      <c r="X460" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y460" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z460" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA460" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB460" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC460" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD460" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE460" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF460" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG460" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH460" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI460" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ460" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK460" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL460" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM460" t="inlineStr">
+        <is>
+          <t>CYND5rZG</t>
+        </is>
+      </c>
+      <c r="AN460" t="inlineStr">
+        <is>
+          <t>mel pepe</t>
+        </is>
+      </c>
+      <c r="AO460" t="inlineStr">
+        <is>
+          <t>tjXr7SAp</t>
+        </is>
+      </c>
+      <c r="AP460" t="inlineStr">
+        <is>
+          <t>garcia sergio</t>
+        </is>
+      </c>
+      <c r="AQ460" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR460" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS460" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT460" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU460" t="inlineStr"/>
+      <c r="AV460" t="inlineStr"/>
+      <c r="AW460" t="inlineStr"/>
+      <c r="AX460" t="inlineStr"/>
+      <c r="AY460" t="inlineStr"/>
+      <c r="AZ460" t="inlineStr"/>
+      <c r="BA460" t="inlineStr"/>
+      <c r="BB460" t="inlineStr"/>
+      <c r="BC460" t="inlineStr"/>
+      <c r="BD460" t="inlineStr"/>
+      <c r="BE460" t="inlineStr"/>
+      <c r="BF460" t="inlineStr"/>
+      <c r="BG460" t="inlineStr"/>
+      <c r="BH460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="inlineStr">
+        <is>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>27.10.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Pulido J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Reale Arena
+ (San Sebastian)</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>40 000</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>31 729</t>
+        </is>
+      </c>
+      <c r="G461" t="n">
+        <v>0</v>
+      </c>
+      <c r="H461" t="n">
+        <v>2</v>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="M461" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="N461" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="Q461" t="n">
+        <v>19</v>
+      </c>
+      <c r="R461" t="n">
+        <v>10</v>
+      </c>
+      <c r="S461" t="n">
+        <v>9</v>
+      </c>
+      <c r="T461" t="n">
+        <v>4</v>
+      </c>
+      <c r="U461" t="n">
+        <v>8</v>
+      </c>
+      <c r="V461" t="n">
+        <v>4</v>
+      </c>
+      <c r="W461" t="n">
+        <v>2</v>
+      </c>
+      <c r="X461" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y461" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z461" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA461" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB461" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC461" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD461" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE461" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF461" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG461" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH461" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI461" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ461" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK461" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL461" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM461" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="AN461" t="inlineStr">
+        <is>
+          <t>alguacil imanol</t>
+        </is>
+      </c>
+      <c r="AO461" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="AP461" t="inlineStr">
+        <is>
+          <t>moreno vicente</t>
+        </is>
+      </c>
+      <c r="AQ461" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR461" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS461" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT461" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU461" t="inlineStr"/>
+      <c r="AV461" t="inlineStr"/>
+      <c r="AW461" t="inlineStr"/>
+      <c r="AX461" t="inlineStr"/>
+      <c r="AY461" t="inlineStr"/>
+      <c r="AZ461" t="inlineStr"/>
+      <c r="BA461" t="n">
+        <v>583</v>
+      </c>
+      <c r="BB461" t="n">
+        <v>200</v>
+      </c>
+      <c r="BC461" t="n">
+        <v>514</v>
+      </c>
+      <c r="BD461" t="n">
+        <v>128</v>
+      </c>
+      <c r="BE461" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF461" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG461" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH461" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="inlineStr">
+        <is>
+          <t>842EOIGL</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>27.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Gil Manzano J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Estadio Benito Villamarín
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>60 721</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>52 621</t>
+        </is>
+      </c>
+      <c r="G462" t="n">
+        <v>1</v>
+      </c>
+      <c r="H462" t="n">
+        <v>0</v>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="M462" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="N462" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q462" t="n">
+        <v>24</v>
+      </c>
+      <c r="R462" t="n">
+        <v>10</v>
+      </c>
+      <c r="S462" t="n">
+        <v>3</v>
+      </c>
+      <c r="T462" t="n">
+        <v>3</v>
+      </c>
+      <c r="U462" t="n">
+        <v>17</v>
+      </c>
+      <c r="V462" t="n">
+        <v>4</v>
+      </c>
+      <c r="W462" t="n">
+        <v>4</v>
+      </c>
+      <c r="X462" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y462" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z462" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA462" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB462" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC462" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD462" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE462" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF462" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG462" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH462" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI462" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ462" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK462" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL462" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM462" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="AN462" t="inlineStr">
+        <is>
+          <t>pellegrini manuel</t>
+        </is>
+      </c>
+      <c r="AO462" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="AP462" t="inlineStr">
+        <is>
+          <t>simeone diego</t>
+        </is>
+      </c>
+      <c r="AQ462" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR462" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS462" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT462" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU462" t="inlineStr"/>
+      <c r="AV462" t="inlineStr"/>
+      <c r="AW462" t="inlineStr"/>
+      <c r="AX462" t="inlineStr"/>
+      <c r="AY462" t="inlineStr"/>
+      <c r="AZ462" t="inlineStr"/>
+      <c r="BA462" t="n">
+        <v>378</v>
+      </c>
+      <c r="BB462" t="n">
+        <v>530</v>
+      </c>
+      <c r="BC462" t="n">
+        <v>296</v>
+      </c>
+      <c r="BD462" t="n">
+        <v>411</v>
+      </c>
+      <c r="BE462" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF462" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG462" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH462" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>naHJ2yf2</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>27.10.2024 12:15</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Cuadra G.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Coliseum
+ (Getafe)</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>16 500</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>12 412</t>
+        </is>
+      </c>
+      <c r="G463" t="n">
+        <v>1</v>
+      </c>
+      <c r="H463" t="n">
+        <v>1</v>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="M463" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="N463" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="Q463" t="n">
+        <v>15</v>
+      </c>
+      <c r="R463" t="n">
+        <v>2</v>
+      </c>
+      <c r="S463" t="n">
+        <v>4</v>
+      </c>
+      <c r="T463" t="n">
+        <v>1</v>
+      </c>
+      <c r="U463" t="n">
+        <v>7</v>
+      </c>
+      <c r="V463" t="n">
+        <v>0</v>
+      </c>
+      <c r="W463" t="n">
+        <v>4</v>
+      </c>
+      <c r="X463" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y463" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z463" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA463" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB463" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC463" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD463" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE463" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF463" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG463" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH463" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI463" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ463" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK463" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL463" t="n">
+        <v>7</v>
+      </c>
+      <c r="AM463" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="AN463" t="inlineStr">
+        <is>
+          <t>bordalas pepe</t>
+        </is>
+      </c>
+      <c r="AO463" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="AP463" t="inlineStr">
+        <is>
+          <t>baraja ruben</t>
+        </is>
+      </c>
+      <c r="AQ463" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR463" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS463" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT463" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU463" t="inlineStr"/>
+      <c r="AV463" t="inlineStr"/>
+      <c r="AW463" t="inlineStr"/>
+      <c r="AX463" t="inlineStr"/>
+      <c r="AY463" t="inlineStr"/>
+      <c r="AZ463" t="inlineStr"/>
+      <c r="BA463" t="n">
+        <v>389</v>
+      </c>
+      <c r="BB463" t="n">
+        <v>230</v>
+      </c>
+      <c r="BC463" t="n">
+        <v>301</v>
+      </c>
+      <c r="BD463" t="n">
+        <v>122</v>
+      </c>
+      <c r="BE463" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF463" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG463" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH463" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="inlineStr">
+        <is>
+          <t>02sgHz9e</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>27.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Lopez M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Butarque
+ (Leganes)</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>12 454</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>11 358</t>
+        </is>
+      </c>
+      <c r="G464" t="n">
+        <v>3</v>
+      </c>
+      <c r="H464" t="n">
+        <v>0</v>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="M464" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="N464" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q464" t="n">
+        <v>7</v>
+      </c>
+      <c r="R464" t="n">
+        <v>18</v>
+      </c>
+      <c r="S464" t="n">
+        <v>4</v>
+      </c>
+      <c r="T464" t="n">
+        <v>5</v>
+      </c>
+      <c r="U464" t="n">
+        <v>2</v>
+      </c>
+      <c r="V464" t="n">
+        <v>6</v>
+      </c>
+      <c r="W464" t="n">
+        <v>1</v>
+      </c>
+      <c r="X464" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y464" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z464" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA464" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB464" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC464" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD464" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE464" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF464" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG464" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH464" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI464" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ464" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK464" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL464" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM464" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="AN464" t="inlineStr">
+        <is>
+          <t>jimenez borja</t>
+        </is>
+      </c>
+      <c r="AO464" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="AP464" t="inlineStr">
+        <is>
+          <t>giraldez claudio</t>
+        </is>
+      </c>
+      <c r="AQ464" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR464" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS464" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT464" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU464" t="inlineStr"/>
+      <c r="AV464" t="inlineStr"/>
+      <c r="AW464" t="inlineStr"/>
+      <c r="AX464" t="inlineStr"/>
+      <c r="AY464" t="inlineStr"/>
+      <c r="AZ464" t="inlineStr"/>
+      <c r="BA464" t="n">
+        <v>364</v>
+      </c>
+      <c r="BB464" t="n">
+        <v>588</v>
+      </c>
+      <c r="BC464" t="n">
+        <v>276</v>
+      </c>
+      <c r="BD464" t="n">
+        <v>493</v>
+      </c>
+      <c r="BE464" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF464" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG464" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH464" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="inlineStr">
+        <is>
+          <t>EkmPPou9</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>27.10.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Palencia Caballero D.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Los Cármenes
+ (Granada)</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>22 524</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>12 871</t>
+        </is>
+      </c>
+      <c r="G465" t="n">
+        <v>1</v>
+      </c>
+      <c r="H465" t="n">
+        <v>2</v>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>Granada CF</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr"/>
+      <c r="N465" t="inlineStr"/>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q465" t="n">
+        <v>18</v>
+      </c>
+      <c r="R465" t="n">
+        <v>13</v>
+      </c>
+      <c r="S465" t="n">
+        <v>5</v>
+      </c>
+      <c r="T465" t="n">
+        <v>9</v>
+      </c>
+      <c r="U465" t="n">
+        <v>4</v>
+      </c>
+      <c r="V465" t="n">
+        <v>3</v>
+      </c>
+      <c r="W465" t="n">
+        <v>9</v>
+      </c>
+      <c r="X465" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y465" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z465" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA465" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB465" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC465" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD465" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE465" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF465" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG465" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH465" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI465" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ465" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK465" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL465" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM465" t="inlineStr">
+        <is>
+          <t>K0UZov8F</t>
+        </is>
+      </c>
+      <c r="AN465" t="inlineStr">
+        <is>
+          <t>escriba fran</t>
+        </is>
+      </c>
+      <c r="AO465" t="inlineStr">
+        <is>
+          <t>fiZxGYJ3</t>
+        </is>
+      </c>
+      <c r="AP465" t="inlineStr">
+        <is>
+          <t>calero julian</t>
+        </is>
+      </c>
+      <c r="AQ465" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR465" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS465" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT465" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU465" t="inlineStr"/>
+      <c r="AV465" t="inlineStr"/>
+      <c r="AW465" t="inlineStr"/>
+      <c r="AX465" t="inlineStr"/>
+      <c r="AY465" t="inlineStr"/>
+      <c r="AZ465" t="inlineStr"/>
+      <c r="BA465" t="inlineStr"/>
+      <c r="BB465" t="inlineStr"/>
+      <c r="BC465" t="inlineStr"/>
+      <c r="BD465" t="inlineStr"/>
+      <c r="BE465" t="inlineStr"/>
+      <c r="BF465" t="inlineStr"/>
+      <c r="BG465" t="inlineStr"/>
+      <c r="BH465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="inlineStr">
+        <is>
+          <t>tO9rD8e3</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>27.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Sanchez A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Estadio Carlos Belmonte
+ (Albacete)</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>17 524</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>7 305</t>
+        </is>
+      </c>
+      <c r="G466" t="n">
+        <v>3</v>
+      </c>
+      <c r="H466" t="n">
+        <v>3</v>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>Gijon</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr"/>
+      <c r="N466" t="inlineStr"/>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q466" t="n">
+        <v>25</v>
+      </c>
+      <c r="R466" t="n">
+        <v>11</v>
+      </c>
+      <c r="S466" t="n">
+        <v>12</v>
+      </c>
+      <c r="T466" t="n">
+        <v>7</v>
+      </c>
+      <c r="U466" t="n">
+        <v>9</v>
+      </c>
+      <c r="V466" t="n">
+        <v>2</v>
+      </c>
+      <c r="W466" t="n">
+        <v>4</v>
+      </c>
+      <c r="X466" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y466" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z466" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA466" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB466" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC466" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD466" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE466" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF466" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG466" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH466" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI466" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ466" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK466" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL466" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM466" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="AN466" t="inlineStr">
+        <is>
+          <t>gonzalez alberto</t>
+        </is>
+      </c>
+      <c r="AO466" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="AP466" t="inlineStr">
+        <is>
+          <t>albes ruben</t>
+        </is>
+      </c>
+      <c r="AQ466" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR466" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS466" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT466" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU466" t="inlineStr"/>
+      <c r="AV466" t="inlineStr"/>
+      <c r="AW466" t="inlineStr"/>
+      <c r="AX466" t="inlineStr"/>
+      <c r="AY466" t="inlineStr"/>
+      <c r="AZ466" t="inlineStr"/>
+      <c r="BA466" t="inlineStr"/>
+      <c r="BB466" t="inlineStr"/>
+      <c r="BC466" t="inlineStr"/>
+      <c r="BD466" t="inlineStr"/>
+      <c r="BE466" t="inlineStr"/>
+      <c r="BF466" t="inlineStr"/>
+      <c r="BG466" t="inlineStr"/>
+      <c r="BH466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="inlineStr">
+        <is>
+          <t>AHtYNP9L</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>27.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Monescillo D.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Estadio El Alcoraz
+ (Huesca)</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>9 100</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>5 223</t>
+        </is>
+      </c>
+      <c r="G467" t="n">
+        <v>2</v>
+      </c>
+      <c r="H467" t="n">
+        <v>2</v>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>Almeria</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr"/>
+      <c r="N467" t="inlineStr"/>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="Q467" t="n">
+        <v>9</v>
+      </c>
+      <c r="R467" t="n">
+        <v>25</v>
+      </c>
+      <c r="S467" t="n">
+        <v>3</v>
+      </c>
+      <c r="T467" t="n">
+        <v>5</v>
+      </c>
+      <c r="U467" t="n">
+        <v>4</v>
+      </c>
+      <c r="V467" t="n">
+        <v>13</v>
+      </c>
+      <c r="W467" t="n">
+        <v>2</v>
+      </c>
+      <c r="X467" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y467" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z467" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA467" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB467" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC467" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD467" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE467" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF467" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG467" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH467" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI467" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ467" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK467" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL467" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM467" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="AN467" t="inlineStr">
+        <is>
+          <t>hidalgo antonio</t>
+        </is>
+      </c>
+      <c r="AO467" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="AP467" t="inlineStr">
+        <is>
+          <t>rubi joan</t>
+        </is>
+      </c>
+      <c r="AQ467" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR467" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS467" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT467" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU467" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV467" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW467" t="inlineStr"/>
+      <c r="AX467" t="inlineStr"/>
+      <c r="AY467" t="inlineStr"/>
+      <c r="AZ467" t="inlineStr"/>
+      <c r="BA467" t="inlineStr"/>
+      <c r="BB467" t="inlineStr"/>
+      <c r="BC467" t="inlineStr"/>
+      <c r="BD467" t="inlineStr"/>
+      <c r="BE467" t="inlineStr"/>
+      <c r="BF467" t="inlineStr"/>
+      <c r="BG467" t="inlineStr"/>
+      <c r="BH467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="inlineStr">
+        <is>
+          <t>QT6U34Ik</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>27.10.2024 12:15</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Gonzalez Esteban J. A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Riazor
+ (La Coruña)</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>34 889</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>22 978</t>
+        </is>
+      </c>
+      <c r="G468" t="n">
+        <v>1</v>
+      </c>
+      <c r="H468" t="n">
+        <v>2</v>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>Dep. La Coruna</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr"/>
+      <c r="N468" t="inlineStr"/>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q468" t="n">
+        <v>16</v>
+      </c>
+      <c r="R468" t="n">
+        <v>12</v>
+      </c>
+      <c r="S468" t="n">
+        <v>3</v>
+      </c>
+      <c r="T468" t="n">
+        <v>7</v>
+      </c>
+      <c r="U468" t="n">
+        <v>10</v>
+      </c>
+      <c r="V468" t="n">
+        <v>3</v>
+      </c>
+      <c r="W468" t="n">
+        <v>3</v>
+      </c>
+      <c r="X468" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y468" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z468" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA468" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB468" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC468" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD468" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE468" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF468" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG468" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH468" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI468" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ468" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK468" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL468" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM468" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="AN468" t="inlineStr">
+        <is>
+          <t>idiakez imanol</t>
+        </is>
+      </c>
+      <c r="AO468" t="inlineStr">
+        <is>
+          <t>rak12p9n</t>
+        </is>
+      </c>
+      <c r="AP468" t="inlineStr">
+        <is>
+          <t>lopez jose</t>
+        </is>
+      </c>
+      <c r="AQ468" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR468" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS468" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT468" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU468" t="inlineStr"/>
+      <c r="AV468" t="inlineStr"/>
+      <c r="AW468" t="inlineStr"/>
+      <c r="AX468" t="inlineStr"/>
+      <c r="AY468" t="inlineStr"/>
+      <c r="AZ468" t="inlineStr"/>
+      <c r="BA468" t="inlineStr"/>
+      <c r="BB468" t="inlineStr"/>
+      <c r="BC468" t="inlineStr"/>
+      <c r="BD468" t="inlineStr"/>
+      <c r="BE468" t="inlineStr"/>
+      <c r="BF468" t="inlineStr"/>
+      <c r="BG468" t="inlineStr"/>
+      <c r="BH468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="inlineStr">
+        <is>
+          <t>6mS3I3Xr</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>27.10.2024 12:15</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Sesma Espinosa M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Estadio Manuel Martínez Valero
+ (Elche)</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>31 388</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>9 708</t>
+        </is>
+      </c>
+      <c r="G469" t="n">
+        <v>1</v>
+      </c>
+      <c r="H469" t="n">
+        <v>0</v>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>Burgos CF</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr"/>
+      <c r="N469" t="inlineStr"/>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q469" t="n">
+        <v>21</v>
+      </c>
+      <c r="R469" t="n">
+        <v>6</v>
+      </c>
+      <c r="S469" t="n">
+        <v>9</v>
+      </c>
+      <c r="T469" t="n">
+        <v>3</v>
+      </c>
+      <c r="U469" t="n">
+        <v>4</v>
+      </c>
+      <c r="V469" t="n">
+        <v>2</v>
+      </c>
+      <c r="W469" t="n">
+        <v>8</v>
+      </c>
+      <c r="X469" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y469" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z469" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA469" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB469" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC469" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD469" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE469" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF469" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG469" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH469" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI469" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ469" t="n">
+        <v>11</v>
+      </c>
+      <c r="AK469" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL469" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM469" t="inlineStr">
+        <is>
+          <t>zT9gi7i9</t>
+        </is>
+      </c>
+      <c r="AN469" t="inlineStr">
+        <is>
+          <t>sarabia eder</t>
+        </is>
+      </c>
+      <c r="AO469" t="inlineStr">
+        <is>
+          <t>l6JQtDqc</t>
+        </is>
+      </c>
+      <c r="AP469" t="inlineStr">
+        <is>
+          <t>bolo</t>
+        </is>
+      </c>
+      <c r="AQ469" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR469" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS469" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT469" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU469" t="inlineStr"/>
+      <c r="AV469" t="inlineStr"/>
+      <c r="AW469" t="inlineStr"/>
+      <c r="AX469" t="inlineStr"/>
+      <c r="AY469" t="inlineStr"/>
+      <c r="AZ469" t="inlineStr"/>
+      <c r="BA469" t="inlineStr"/>
+      <c r="BB469" t="inlineStr"/>
+      <c r="BC469" t="inlineStr"/>
+      <c r="BD469" t="inlineStr"/>
+      <c r="BE469" t="inlineStr"/>
+      <c r="BF469" t="inlineStr"/>
+      <c r="BG469" t="inlineStr"/>
+      <c r="BH469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="inlineStr">
+        <is>
+          <t>EBOaxPOE</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>27.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Perez M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Estadio La Rosaleda
+ (Málaga)</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>30 044</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>24 008</t>
+        </is>
+      </c>
+      <c r="G470" t="n">
+        <v>1</v>
+      </c>
+      <c r="H470" t="n">
+        <v>0</v>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>Eibar</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr"/>
+      <c r="N470" t="inlineStr"/>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="Q470" t="n">
+        <v>10</v>
+      </c>
+      <c r="R470" t="n">
+        <v>16</v>
+      </c>
+      <c r="S470" t="n">
+        <v>5</v>
+      </c>
+      <c r="T470" t="n">
+        <v>5</v>
+      </c>
+      <c r="U470" t="n">
+        <v>4</v>
+      </c>
+      <c r="V470" t="n">
+        <v>5</v>
+      </c>
+      <c r="W470" t="n">
+        <v>1</v>
+      </c>
+      <c r="X470" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y470" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z470" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA470" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB470" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC470" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD470" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE470" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF470" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG470" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH470" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI470" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ470" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK470" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL470" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM470" t="inlineStr">
+        <is>
+          <t>tjXr7SAp</t>
+        </is>
+      </c>
+      <c r="AN470" t="inlineStr">
+        <is>
+          <t>garcia sergio</t>
+        </is>
+      </c>
+      <c r="AO470" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="AP470" t="inlineStr">
+        <is>
+          <t>etxeberria joseba</t>
+        </is>
+      </c>
+      <c r="AQ470" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR470" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS470" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT470" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU470" t="inlineStr"/>
+      <c r="AV470" t="inlineStr"/>
+      <c r="AW470" t="inlineStr"/>
+      <c r="AX470" t="inlineStr"/>
+      <c r="AY470" t="inlineStr"/>
+      <c r="AZ470" t="inlineStr"/>
+      <c r="BA470" t="inlineStr"/>
+      <c r="BB470" t="inlineStr"/>
+      <c r="BC470" t="inlineStr"/>
+      <c r="BD470" t="inlineStr"/>
+      <c r="BE470" t="inlineStr"/>
+      <c r="BF470" t="inlineStr"/>
+      <c r="BG470" t="inlineStr"/>
+      <c r="BH470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="inlineStr">
+        <is>
+          <t>E595Qvn9</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>28.10.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Munuera J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Estadi Mallorca Son Moix
+ (Palma de Mallorca)</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>26 020</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>19 797</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S471" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T471" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U471" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V471" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="W471" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X471" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y471" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z471" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA471" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB471" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AC471" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD471" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE471" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AF471" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG471" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH471" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI471" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ471" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK471" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AL471" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM471" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="AN471" t="inlineStr">
+        <is>
+          <t>arrasate jagoba</t>
+        </is>
+      </c>
+      <c r="AO471" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="AP471" t="inlineStr">
+        <is>
+          <t>valverde tejedor ernesto</t>
+        </is>
+      </c>
+      <c r="AQ471" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR471" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS471" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT471" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU471" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV471" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW471" t="inlineStr"/>
+      <c r="AX471" t="inlineStr"/>
+      <c r="AY471" t="inlineStr"/>
+      <c r="AZ471" t="inlineStr"/>
+      <c r="BA471" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="BB471" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="BC471" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="BD471" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="BE471" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BF471" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="BG471" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="BH471" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="inlineStr">
+        <is>
+          <t>nqew2rm2</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>28.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Muresan S.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Estadio Municipal da Malata
+ (Ferrol)</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>10 450</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>6 001</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>Racing Club Ferrol</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>Tenerife</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr"/>
+      <c r="N472" t="inlineStr"/>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T472" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U472" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V472" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W472" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X472" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y472" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Z472" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA472" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB472" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC472" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD472" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE472" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AF472" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AG472" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH472" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI472" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ472" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AK472" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL472" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM472" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="AN472" t="inlineStr">
+        <is>
+          <t>parralo cristobal</t>
+        </is>
+      </c>
+      <c r="AO472" t="inlineStr">
+        <is>
+          <t>CYND5rZG</t>
+        </is>
+      </c>
+      <c r="AP472" t="inlineStr">
+        <is>
+          <t>mel pepe</t>
+        </is>
+      </c>
+      <c r="AQ472" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR472" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS472" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT472" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU472" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AV472" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AW472" t="inlineStr"/>
+      <c r="AX472" t="inlineStr"/>
+      <c r="AY472" t="inlineStr"/>
+      <c r="AZ472" t="inlineStr"/>
+      <c r="BA472" t="inlineStr"/>
+      <c r="BB472" t="inlineStr"/>
+      <c r="BC472" t="inlineStr"/>
+      <c r="BD472" t="inlineStr"/>
+      <c r="BE472" t="inlineStr"/>
+      <c r="BF472" t="inlineStr"/>
+      <c r="BG472" t="inlineStr"/>
+      <c r="BH472" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH472"/>
+  <dimension ref="A1:BH520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91654,15 +91654,11 @@
           <t>19 797</t>
         </is>
       </c>
-      <c r="G471" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H471" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G471" t="n">
+        <v>0</v>
+      </c>
+      <c r="H471" t="n">
+        <v>0</v>
       </c>
       <c r="I471" t="inlineStr">
         <is>
@@ -91684,15 +91680,11 @@
           <t>Ath Bilbao</t>
         </is>
       </c>
-      <c r="M471" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="N471" t="inlineStr">
-        <is>
-          <t>0.59</t>
-        </is>
+      <c r="M471" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="N471" t="n">
+        <v>0.59</v>
       </c>
       <c r="O471" t="inlineStr">
         <is>
@@ -91704,115 +91696,71 @@
           <t>67%</t>
         </is>
       </c>
-      <c r="Q471" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R471" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S471" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T471" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="U471" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V471" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="W471" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X471" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y471" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z471" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA471" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB471" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AC471" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD471" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE471" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AF471" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG471" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH471" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI471" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AJ471" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK471" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AL471" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="Q471" t="n">
+        <v>4</v>
+      </c>
+      <c r="R471" t="n">
+        <v>20</v>
+      </c>
+      <c r="S471" t="n">
+        <v>1</v>
+      </c>
+      <c r="T471" t="n">
+        <v>1</v>
+      </c>
+      <c r="U471" t="n">
+        <v>2</v>
+      </c>
+      <c r="V471" t="n">
+        <v>11</v>
+      </c>
+      <c r="W471" t="n">
+        <v>1</v>
+      </c>
+      <c r="X471" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y471" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z471" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA471" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB471" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC471" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD471" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE471" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF471" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG471" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH471" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI471" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ471" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK471" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL471" t="n">
+        <v>1</v>
       </c>
       <c r="AM471" t="inlineStr">
         <is>
@@ -91848,59 +91796,39 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU471" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AV471" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AU471" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV471" t="n">
+        <v>0</v>
       </c>
       <c r="AW471" t="inlineStr"/>
       <c r="AX471" t="inlineStr"/>
       <c r="AY471" t="inlineStr"/>
       <c r="AZ471" t="inlineStr"/>
-      <c r="BA471" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="BB471" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="BC471" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="BD471" t="inlineStr">
-        <is>
-          <t>455</t>
-        </is>
-      </c>
-      <c r="BE471" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="BF471" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BG471" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="BH471" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="BA471" t="n">
+        <v>274</v>
+      </c>
+      <c r="BB471" t="n">
+        <v>535</v>
+      </c>
+      <c r="BC471" t="n">
+        <v>193</v>
+      </c>
+      <c r="BD471" t="n">
+        <v>455</v>
+      </c>
+      <c r="BE471" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF471" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG471" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH471" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="472">
@@ -91936,15 +91864,11 @@
           <t>6 001</t>
         </is>
       </c>
-      <c r="G472" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H472" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G472" t="n">
+        <v>1</v>
+      </c>
+      <c r="H472" t="n">
+        <v>1</v>
       </c>
       <c r="I472" t="inlineStr">
         <is>
@@ -91978,115 +91902,71 @@
           <t>36%</t>
         </is>
       </c>
-      <c r="Q472" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R472" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S472" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T472" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U472" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="V472" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="W472" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X472" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y472" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Z472" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA472" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AB472" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC472" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD472" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE472" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="AF472" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AG472" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH472" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI472" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ472" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AK472" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL472" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="Q472" t="n">
+        <v>8</v>
+      </c>
+      <c r="R472" t="n">
+        <v>10</v>
+      </c>
+      <c r="S472" t="n">
+        <v>4</v>
+      </c>
+      <c r="T472" t="n">
+        <v>5</v>
+      </c>
+      <c r="U472" t="n">
+        <v>2</v>
+      </c>
+      <c r="V472" t="n">
+        <v>3</v>
+      </c>
+      <c r="W472" t="n">
+        <v>2</v>
+      </c>
+      <c r="X472" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y472" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z472" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA472" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB472" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC472" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD472" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE472" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF472" t="n">
+        <v>25</v>
+      </c>
+      <c r="AG472" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH472" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI472" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ472" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK472" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL472" t="n">
+        <v>2</v>
       </c>
       <c r="AM472" t="inlineStr">
         <is>
@@ -92122,15 +92002,11 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU472" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AV472" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AU472" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV472" t="n">
+        <v>0</v>
       </c>
       <c r="AW472" t="inlineStr"/>
       <c r="AX472" t="inlineStr"/>
@@ -92145,6 +92021,5410 @@
       <c r="BG472" t="inlineStr"/>
       <c r="BH472" t="inlineStr"/>
     </row>
+    <row r="473">
+      <c r="A473" s="1" t="inlineStr">
+        <is>
+          <t>G0EJ1qlU</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>31.10.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>La Molineta
+ (Alfaro)</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>2 500</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr"/>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>4vSPUg3d</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>Alfaro</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>Tenerife
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr"/>
+      <c r="N473" t="inlineStr"/>
+      <c r="O473" t="inlineStr"/>
+      <c r="P473" t="inlineStr"/>
+      <c r="Q473" t="inlineStr"/>
+      <c r="R473" t="inlineStr"/>
+      <c r="S473" t="inlineStr"/>
+      <c r="T473" t="inlineStr"/>
+      <c r="U473" t="inlineStr"/>
+      <c r="V473" t="inlineStr"/>
+      <c r="W473" t="inlineStr"/>
+      <c r="X473" t="inlineStr"/>
+      <c r="Y473" t="inlineStr"/>
+      <c r="Z473" t="inlineStr"/>
+      <c r="AA473" t="inlineStr"/>
+      <c r="AB473" t="inlineStr"/>
+      <c r="AC473" t="inlineStr"/>
+      <c r="AD473" t="inlineStr"/>
+      <c r="AE473" t="inlineStr"/>
+      <c r="AF473" t="inlineStr"/>
+      <c r="AG473" t="inlineStr"/>
+      <c r="AH473" t="inlineStr"/>
+      <c r="AI473" t="inlineStr"/>
+      <c r="AJ473" t="inlineStr"/>
+      <c r="AK473" t="inlineStr"/>
+      <c r="AL473" t="inlineStr"/>
+      <c r="AM473" t="inlineStr"/>
+      <c r="AN473" t="inlineStr"/>
+      <c r="AO473" t="inlineStr"/>
+      <c r="AP473" t="inlineStr"/>
+      <c r="AQ473" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR473" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS473" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT473" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU473" t="inlineStr"/>
+      <c r="AV473" t="inlineStr"/>
+      <c r="AW473" t="inlineStr"/>
+      <c r="AX473" t="inlineStr"/>
+      <c r="AY473" t="inlineStr"/>
+      <c r="AZ473" t="inlineStr"/>
+      <c r="BA473" t="inlineStr"/>
+      <c r="BB473" t="inlineStr"/>
+      <c r="BC473" t="inlineStr"/>
+      <c r="BD473" t="inlineStr"/>
+      <c r="BE473" t="inlineStr"/>
+      <c r="BF473" t="inlineStr"/>
+      <c r="BG473" t="inlineStr"/>
+      <c r="BH473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>K8uZCRtP</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>31.10.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Estadio Municipal Francisco Muñoz Pérez
+ (Estepona)</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>3 800</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr"/>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>l2GKzvhb</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+CD Estepona</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr"/>
+      <c r="N474" t="inlineStr"/>
+      <c r="O474" t="inlineStr"/>
+      <c r="P474" t="inlineStr"/>
+      <c r="Q474" t="inlineStr"/>
+      <c r="R474" t="inlineStr"/>
+      <c r="S474" t="inlineStr"/>
+      <c r="T474" t="inlineStr"/>
+      <c r="U474" t="inlineStr"/>
+      <c r="V474" t="inlineStr"/>
+      <c r="W474" t="inlineStr"/>
+      <c r="X474" t="inlineStr"/>
+      <c r="Y474" t="inlineStr"/>
+      <c r="Z474" t="inlineStr"/>
+      <c r="AA474" t="inlineStr"/>
+      <c r="AB474" t="inlineStr"/>
+      <c r="AC474" t="inlineStr"/>
+      <c r="AD474" t="inlineStr"/>
+      <c r="AE474" t="inlineStr"/>
+      <c r="AF474" t="inlineStr"/>
+      <c r="AG474" t="inlineStr"/>
+      <c r="AH474" t="inlineStr"/>
+      <c r="AI474" t="inlineStr"/>
+      <c r="AJ474" t="inlineStr"/>
+      <c r="AK474" t="inlineStr"/>
+      <c r="AL474" t="inlineStr"/>
+      <c r="AM474" t="inlineStr"/>
+      <c r="AN474" t="inlineStr"/>
+      <c r="AO474" t="inlineStr"/>
+      <c r="AP474" t="inlineStr"/>
+      <c r="AQ474" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR474" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS474" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT474" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU474" t="inlineStr"/>
+      <c r="AV474" t="inlineStr"/>
+      <c r="AW474" t="inlineStr"/>
+      <c r="AX474" t="inlineStr"/>
+      <c r="AY474" t="inlineStr"/>
+      <c r="AZ474" t="inlineStr"/>
+      <c r="BA474" t="inlineStr"/>
+      <c r="BB474" t="inlineStr"/>
+      <c r="BC474" t="inlineStr"/>
+      <c r="BD474" t="inlineStr"/>
+      <c r="BE474" t="inlineStr"/>
+      <c r="BF474" t="inlineStr"/>
+      <c r="BG474" t="inlineStr"/>
+      <c r="BH474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="inlineStr">
+        <is>
+          <t>QZBZmK7d</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>31.10.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Estadio Municipal Juan Guerrero El Lobo
+ (Cuarte de Huerva)</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr"/>
+      <c r="F475" t="inlineStr"/>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>QgTbFMxi</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>Cuarte</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>Racing Club Ferrol
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr"/>
+      <c r="N475" t="inlineStr"/>
+      <c r="O475" t="inlineStr"/>
+      <c r="P475" t="inlineStr"/>
+      <c r="Q475" t="inlineStr"/>
+      <c r="R475" t="inlineStr"/>
+      <c r="S475" t="inlineStr"/>
+      <c r="T475" t="inlineStr"/>
+      <c r="U475" t="inlineStr"/>
+      <c r="V475" t="inlineStr"/>
+      <c r="W475" t="inlineStr"/>
+      <c r="X475" t="inlineStr"/>
+      <c r="Y475" t="inlineStr"/>
+      <c r="Z475" t="inlineStr"/>
+      <c r="AA475" t="inlineStr"/>
+      <c r="AB475" t="inlineStr"/>
+      <c r="AC475" t="inlineStr"/>
+      <c r="AD475" t="inlineStr"/>
+      <c r="AE475" t="inlineStr"/>
+      <c r="AF475" t="inlineStr"/>
+      <c r="AG475" t="inlineStr"/>
+      <c r="AH475" t="inlineStr"/>
+      <c r="AI475" t="inlineStr"/>
+      <c r="AJ475" t="inlineStr"/>
+      <c r="AK475" t="inlineStr"/>
+      <c r="AL475" t="inlineStr"/>
+      <c r="AM475" t="inlineStr"/>
+      <c r="AN475" t="inlineStr"/>
+      <c r="AO475" t="inlineStr"/>
+      <c r="AP475" t="inlineStr"/>
+      <c r="AQ475" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR475" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS475" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT475" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU475" t="inlineStr"/>
+      <c r="AV475" t="inlineStr"/>
+      <c r="AW475" t="inlineStr"/>
+      <c r="AX475" t="inlineStr"/>
+      <c r="AY475" t="inlineStr"/>
+      <c r="AZ475" t="inlineStr"/>
+      <c r="BA475" t="inlineStr"/>
+      <c r="BB475" t="inlineStr"/>
+      <c r="BC475" t="inlineStr"/>
+      <c r="BD475" t="inlineStr"/>
+      <c r="BE475" t="inlineStr"/>
+      <c r="BF475" t="inlineStr"/>
+      <c r="BG475" t="inlineStr"/>
+      <c r="BH475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="inlineStr">
+        <is>
+          <t>GraCJHdl</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>31.10.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Estadio Francisco de la Hera
+ (Almendralejo)</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>11 580</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr"/>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>lYt2HNv2</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>Gevora</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>Betis
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr"/>
+      <c r="N476" t="inlineStr"/>
+      <c r="O476" t="inlineStr"/>
+      <c r="P476" t="inlineStr"/>
+      <c r="Q476" t="inlineStr"/>
+      <c r="R476" t="inlineStr"/>
+      <c r="S476" t="inlineStr"/>
+      <c r="T476" t="inlineStr"/>
+      <c r="U476" t="inlineStr"/>
+      <c r="V476" t="inlineStr"/>
+      <c r="W476" t="inlineStr"/>
+      <c r="X476" t="inlineStr"/>
+      <c r="Y476" t="inlineStr"/>
+      <c r="Z476" t="inlineStr"/>
+      <c r="AA476" t="inlineStr"/>
+      <c r="AB476" t="inlineStr"/>
+      <c r="AC476" t="inlineStr"/>
+      <c r="AD476" t="inlineStr"/>
+      <c r="AE476" t="inlineStr"/>
+      <c r="AF476" t="inlineStr"/>
+      <c r="AG476" t="inlineStr"/>
+      <c r="AH476" t="inlineStr"/>
+      <c r="AI476" t="inlineStr"/>
+      <c r="AJ476" t="inlineStr"/>
+      <c r="AK476" t="inlineStr"/>
+      <c r="AL476" t="inlineStr"/>
+      <c r="AM476" t="inlineStr"/>
+      <c r="AN476" t="inlineStr"/>
+      <c r="AO476" t="inlineStr"/>
+      <c r="AP476" t="inlineStr"/>
+      <c r="AQ476" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR476" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS476" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT476" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU476" t="inlineStr"/>
+      <c r="AV476" t="inlineStr"/>
+      <c r="AW476" t="inlineStr"/>
+      <c r="AX476" t="inlineStr"/>
+      <c r="AY476" t="inlineStr"/>
+      <c r="AZ476" t="inlineStr"/>
+      <c r="BA476" t="inlineStr"/>
+      <c r="BB476" t="inlineStr"/>
+      <c r="BC476" t="inlineStr"/>
+      <c r="BD476" t="inlineStr"/>
+      <c r="BE476" t="inlineStr"/>
+      <c r="BF476" t="inlineStr"/>
+      <c r="BG476" t="inlineStr"/>
+      <c r="BH476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="inlineStr">
+        <is>
+          <t>fR1YQYGr</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>31.10.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Estadio Pepe Quimaran
+ (Posada de Llanera)</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>1 000</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr"/>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>YXwLruOR</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>Llanera</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>O6FowKBc</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>Cultural Leonesa
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr"/>
+      <c r="N477" t="inlineStr"/>
+      <c r="O477" t="inlineStr"/>
+      <c r="P477" t="inlineStr"/>
+      <c r="Q477" t="inlineStr"/>
+      <c r="R477" t="inlineStr"/>
+      <c r="S477" t="inlineStr"/>
+      <c r="T477" t="inlineStr"/>
+      <c r="U477" t="inlineStr"/>
+      <c r="V477" t="inlineStr"/>
+      <c r="W477" t="inlineStr"/>
+      <c r="X477" t="inlineStr"/>
+      <c r="Y477" t="inlineStr"/>
+      <c r="Z477" t="inlineStr"/>
+      <c r="AA477" t="inlineStr"/>
+      <c r="AB477" t="inlineStr"/>
+      <c r="AC477" t="inlineStr"/>
+      <c r="AD477" t="inlineStr"/>
+      <c r="AE477" t="inlineStr"/>
+      <c r="AF477" t="inlineStr"/>
+      <c r="AG477" t="inlineStr"/>
+      <c r="AH477" t="inlineStr"/>
+      <c r="AI477" t="inlineStr"/>
+      <c r="AJ477" t="inlineStr"/>
+      <c r="AK477" t="inlineStr"/>
+      <c r="AL477" t="inlineStr"/>
+      <c r="AM477" t="inlineStr"/>
+      <c r="AN477" t="inlineStr"/>
+      <c r="AO477" t="inlineStr"/>
+      <c r="AP477" t="inlineStr"/>
+      <c r="AQ477" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR477" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS477" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT477" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU477" t="inlineStr"/>
+      <c r="AV477" t="inlineStr"/>
+      <c r="AW477" t="inlineStr"/>
+      <c r="AX477" t="inlineStr"/>
+      <c r="AY477" t="inlineStr"/>
+      <c r="AZ477" t="inlineStr"/>
+      <c r="BA477" t="inlineStr"/>
+      <c r="BB477" t="inlineStr"/>
+      <c r="BC477" t="inlineStr"/>
+      <c r="BD477" t="inlineStr"/>
+      <c r="BE477" t="inlineStr"/>
+      <c r="BF477" t="inlineStr"/>
+      <c r="BG477" t="inlineStr"/>
+      <c r="BH477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="inlineStr">
+        <is>
+          <t>4rI4FQ1U</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>31.10.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Campo de fútbol Isidro Calderón
+ (Monzón)</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr"/>
+      <c r="F478" t="inlineStr"/>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>6mKmGJct</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>Ontinena</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>Las Palmas
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr"/>
+      <c r="N478" t="inlineStr"/>
+      <c r="O478" t="inlineStr"/>
+      <c r="P478" t="inlineStr"/>
+      <c r="Q478" t="inlineStr"/>
+      <c r="R478" t="inlineStr"/>
+      <c r="S478" t="inlineStr"/>
+      <c r="T478" t="inlineStr"/>
+      <c r="U478" t="inlineStr"/>
+      <c r="V478" t="inlineStr"/>
+      <c r="W478" t="inlineStr"/>
+      <c r="X478" t="inlineStr"/>
+      <c r="Y478" t="inlineStr"/>
+      <c r="Z478" t="inlineStr"/>
+      <c r="AA478" t="inlineStr"/>
+      <c r="AB478" t="inlineStr"/>
+      <c r="AC478" t="inlineStr"/>
+      <c r="AD478" t="inlineStr"/>
+      <c r="AE478" t="inlineStr"/>
+      <c r="AF478" t="inlineStr"/>
+      <c r="AG478" t="inlineStr"/>
+      <c r="AH478" t="inlineStr"/>
+      <c r="AI478" t="inlineStr"/>
+      <c r="AJ478" t="inlineStr"/>
+      <c r="AK478" t="inlineStr"/>
+      <c r="AL478" t="inlineStr"/>
+      <c r="AM478" t="inlineStr"/>
+      <c r="AN478" t="inlineStr"/>
+      <c r="AO478" t="inlineStr"/>
+      <c r="AP478" t="inlineStr"/>
+      <c r="AQ478" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR478" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS478" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT478" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU478" t="inlineStr"/>
+      <c r="AV478" t="inlineStr"/>
+      <c r="AW478" t="inlineStr"/>
+      <c r="AX478" t="inlineStr"/>
+      <c r="AY478" t="inlineStr"/>
+      <c r="AZ478" t="inlineStr"/>
+      <c r="BA478" t="inlineStr"/>
+      <c r="BB478" t="inlineStr"/>
+      <c r="BC478" t="inlineStr"/>
+      <c r="BD478" t="inlineStr"/>
+      <c r="BE478" t="inlineStr"/>
+      <c r="BF478" t="inlineStr"/>
+      <c r="BG478" t="inlineStr"/>
+      <c r="BH478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="inlineStr">
+        <is>
+          <t>OSUPZTaD</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>31.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Estadio Vicente Sanz
+ (Don Benito)</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr"/>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>UV0LgBv7</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>Don Benito</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>O6ucWgAa</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>Andorra
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr"/>
+      <c r="N479" t="inlineStr"/>
+      <c r="O479" t="inlineStr"/>
+      <c r="P479" t="inlineStr"/>
+      <c r="Q479" t="inlineStr"/>
+      <c r="R479" t="inlineStr"/>
+      <c r="S479" t="inlineStr"/>
+      <c r="T479" t="inlineStr"/>
+      <c r="U479" t="inlineStr"/>
+      <c r="V479" t="inlineStr"/>
+      <c r="W479" t="inlineStr"/>
+      <c r="X479" t="inlineStr"/>
+      <c r="Y479" t="inlineStr"/>
+      <c r="Z479" t="inlineStr"/>
+      <c r="AA479" t="inlineStr"/>
+      <c r="AB479" t="inlineStr"/>
+      <c r="AC479" t="inlineStr"/>
+      <c r="AD479" t="inlineStr"/>
+      <c r="AE479" t="inlineStr"/>
+      <c r="AF479" t="inlineStr"/>
+      <c r="AG479" t="inlineStr"/>
+      <c r="AH479" t="inlineStr"/>
+      <c r="AI479" t="inlineStr"/>
+      <c r="AJ479" t="inlineStr"/>
+      <c r="AK479" t="inlineStr"/>
+      <c r="AL479" t="inlineStr"/>
+      <c r="AM479" t="inlineStr"/>
+      <c r="AN479" t="inlineStr"/>
+      <c r="AO479" t="inlineStr"/>
+      <c r="AP479" t="inlineStr"/>
+      <c r="AQ479" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR479" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS479" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT479" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU479" t="inlineStr"/>
+      <c r="AV479" t="inlineStr"/>
+      <c r="AW479" t="inlineStr"/>
+      <c r="AX479" t="inlineStr"/>
+      <c r="AY479" t="inlineStr"/>
+      <c r="AZ479" t="inlineStr"/>
+      <c r="BA479" t="inlineStr"/>
+      <c r="BB479" t="inlineStr"/>
+      <c r="BC479" t="inlineStr"/>
+      <c r="BD479" t="inlineStr"/>
+      <c r="BE479" t="inlineStr"/>
+      <c r="BF479" t="inlineStr"/>
+      <c r="BG479" t="inlineStr"/>
+      <c r="BH479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="inlineStr">
+        <is>
+          <t>S0NREmCC</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>31.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Estadio Adolfo Suárez
+ (Avila)</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>6 000</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr"/>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>Q3CdYV39</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Real Avila</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>R. Oviedo</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr"/>
+      <c r="N480" t="inlineStr"/>
+      <c r="O480" t="inlineStr"/>
+      <c r="P480" t="inlineStr"/>
+      <c r="Q480" t="inlineStr"/>
+      <c r="R480" t="inlineStr"/>
+      <c r="S480" t="inlineStr"/>
+      <c r="T480" t="inlineStr"/>
+      <c r="U480" t="inlineStr"/>
+      <c r="V480" t="inlineStr"/>
+      <c r="W480" t="inlineStr"/>
+      <c r="X480" t="inlineStr"/>
+      <c r="Y480" t="inlineStr"/>
+      <c r="Z480" t="inlineStr"/>
+      <c r="AA480" t="inlineStr"/>
+      <c r="AB480" t="inlineStr"/>
+      <c r="AC480" t="inlineStr"/>
+      <c r="AD480" t="inlineStr"/>
+      <c r="AE480" t="inlineStr"/>
+      <c r="AF480" t="inlineStr"/>
+      <c r="AG480" t="inlineStr"/>
+      <c r="AH480" t="inlineStr"/>
+      <c r="AI480" t="inlineStr"/>
+      <c r="AJ480" t="inlineStr"/>
+      <c r="AK480" t="inlineStr"/>
+      <c r="AL480" t="inlineStr"/>
+      <c r="AM480" t="inlineStr"/>
+      <c r="AN480" t="inlineStr"/>
+      <c r="AO480" t="inlineStr"/>
+      <c r="AP480" t="inlineStr"/>
+      <c r="AQ480" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR480" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS480" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT480" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU480" t="inlineStr"/>
+      <c r="AV480" t="inlineStr"/>
+      <c r="AW480" t="inlineStr"/>
+      <c r="AX480" t="inlineStr"/>
+      <c r="AY480" t="inlineStr"/>
+      <c r="AZ480" t="inlineStr"/>
+      <c r="BA480" t="inlineStr"/>
+      <c r="BB480" t="inlineStr"/>
+      <c r="BC480" t="inlineStr"/>
+      <c r="BD480" t="inlineStr"/>
+      <c r="BE480" t="inlineStr"/>
+      <c r="BF480" t="inlineStr"/>
+      <c r="BG480" t="inlineStr"/>
+      <c r="BH480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="inlineStr">
+        <is>
+          <t>jZMBcXiK</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>31.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Pabellón Ciudad de Tudela
+ (Tudela)</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>1 200</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr"/>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>jVd9kPdO</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>Tudelano</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>v91i4Lwr</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>Deportiva Minera
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr"/>
+      <c r="N481" t="inlineStr"/>
+      <c r="O481" t="inlineStr"/>
+      <c r="P481" t="inlineStr"/>
+      <c r="Q481" t="inlineStr"/>
+      <c r="R481" t="inlineStr"/>
+      <c r="S481" t="inlineStr"/>
+      <c r="T481" t="inlineStr"/>
+      <c r="U481" t="inlineStr"/>
+      <c r="V481" t="inlineStr"/>
+      <c r="W481" t="inlineStr"/>
+      <c r="X481" t="inlineStr"/>
+      <c r="Y481" t="inlineStr"/>
+      <c r="Z481" t="inlineStr"/>
+      <c r="AA481" t="inlineStr"/>
+      <c r="AB481" t="inlineStr"/>
+      <c r="AC481" t="inlineStr"/>
+      <c r="AD481" t="inlineStr"/>
+      <c r="AE481" t="inlineStr"/>
+      <c r="AF481" t="inlineStr"/>
+      <c r="AG481" t="inlineStr"/>
+      <c r="AH481" t="inlineStr"/>
+      <c r="AI481" t="inlineStr"/>
+      <c r="AJ481" t="inlineStr"/>
+      <c r="AK481" t="inlineStr"/>
+      <c r="AL481" t="inlineStr"/>
+      <c r="AM481" t="inlineStr"/>
+      <c r="AN481" t="inlineStr"/>
+      <c r="AO481" t="inlineStr"/>
+      <c r="AP481" t="inlineStr"/>
+      <c r="AQ481" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR481" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS481" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT481" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU481" t="inlineStr"/>
+      <c r="AV481" t="inlineStr"/>
+      <c r="AW481" t="inlineStr"/>
+      <c r="AX481" t="inlineStr"/>
+      <c r="AY481" t="inlineStr"/>
+      <c r="AZ481" t="inlineStr"/>
+      <c r="BA481" t="inlineStr"/>
+      <c r="BB481" t="inlineStr"/>
+      <c r="BC481" t="inlineStr"/>
+      <c r="BD481" t="inlineStr"/>
+      <c r="BE481" t="inlineStr"/>
+      <c r="BF481" t="inlineStr"/>
+      <c r="BG481" t="inlineStr"/>
+      <c r="BH481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="inlineStr">
+        <is>
+          <t>tOyaCZ1k</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>31.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Deportes
+ (Barbastro)</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr"/>
+      <c r="F482" t="inlineStr"/>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>xKtKvMa3</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Barbastro</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>pfuJWA0r</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>Amorebieta</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr"/>
+      <c r="N482" t="inlineStr"/>
+      <c r="O482" t="inlineStr"/>
+      <c r="P482" t="inlineStr"/>
+      <c r="Q482" t="inlineStr"/>
+      <c r="R482" t="inlineStr"/>
+      <c r="S482" t="inlineStr"/>
+      <c r="T482" t="inlineStr"/>
+      <c r="U482" t="inlineStr"/>
+      <c r="V482" t="inlineStr"/>
+      <c r="W482" t="inlineStr"/>
+      <c r="X482" t="inlineStr"/>
+      <c r="Y482" t="inlineStr"/>
+      <c r="Z482" t="inlineStr"/>
+      <c r="AA482" t="inlineStr"/>
+      <c r="AB482" t="inlineStr"/>
+      <c r="AC482" t="inlineStr"/>
+      <c r="AD482" t="inlineStr"/>
+      <c r="AE482" t="inlineStr"/>
+      <c r="AF482" t="inlineStr"/>
+      <c r="AG482" t="inlineStr"/>
+      <c r="AH482" t="inlineStr"/>
+      <c r="AI482" t="inlineStr"/>
+      <c r="AJ482" t="inlineStr"/>
+      <c r="AK482" t="inlineStr"/>
+      <c r="AL482" t="inlineStr"/>
+      <c r="AM482" t="inlineStr"/>
+      <c r="AN482" t="inlineStr"/>
+      <c r="AO482" t="inlineStr"/>
+      <c r="AP482" t="inlineStr"/>
+      <c r="AQ482" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR482" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS482" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT482" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU482" t="inlineStr"/>
+      <c r="AV482" t="inlineStr"/>
+      <c r="AW482" t="inlineStr"/>
+      <c r="AX482" t="inlineStr"/>
+      <c r="AY482" t="inlineStr"/>
+      <c r="AZ482" t="inlineStr"/>
+      <c r="BA482" t="inlineStr"/>
+      <c r="BB482" t="inlineStr"/>
+      <c r="BC482" t="inlineStr"/>
+      <c r="BD482" t="inlineStr"/>
+      <c r="BE482" t="inlineStr"/>
+      <c r="BF482" t="inlineStr"/>
+      <c r="BG482" t="inlineStr"/>
+      <c r="BH482" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="inlineStr">
+        <is>
+          <t>8z7vNj3t</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>31.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr"/>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Campo de Fútbol de Monte
+ (Monte)</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr"/>
+      <c r="F483" t="inlineStr"/>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>0AcMabDa</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>San Tirso</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>Espanyol
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr"/>
+      <c r="N483" t="inlineStr"/>
+      <c r="O483" t="inlineStr"/>
+      <c r="P483" t="inlineStr"/>
+      <c r="Q483" t="inlineStr"/>
+      <c r="R483" t="inlineStr"/>
+      <c r="S483" t="inlineStr"/>
+      <c r="T483" t="inlineStr"/>
+      <c r="U483" t="inlineStr"/>
+      <c r="V483" t="inlineStr"/>
+      <c r="W483" t="inlineStr"/>
+      <c r="X483" t="inlineStr"/>
+      <c r="Y483" t="inlineStr"/>
+      <c r="Z483" t="inlineStr"/>
+      <c r="AA483" t="inlineStr"/>
+      <c r="AB483" t="inlineStr"/>
+      <c r="AC483" t="inlineStr"/>
+      <c r="AD483" t="inlineStr"/>
+      <c r="AE483" t="inlineStr"/>
+      <c r="AF483" t="inlineStr"/>
+      <c r="AG483" t="inlineStr"/>
+      <c r="AH483" t="inlineStr"/>
+      <c r="AI483" t="inlineStr"/>
+      <c r="AJ483" t="inlineStr"/>
+      <c r="AK483" t="inlineStr"/>
+      <c r="AL483" t="inlineStr"/>
+      <c r="AM483" t="inlineStr"/>
+      <c r="AN483" t="inlineStr"/>
+      <c r="AO483" t="inlineStr"/>
+      <c r="AP483" t="inlineStr"/>
+      <c r="AQ483" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR483" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS483" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT483" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU483" t="inlineStr"/>
+      <c r="AV483" t="inlineStr"/>
+      <c r="AW483" t="inlineStr"/>
+      <c r="AX483" t="inlineStr"/>
+      <c r="AY483" t="inlineStr"/>
+      <c r="AZ483" t="inlineStr"/>
+      <c r="BA483" t="inlineStr"/>
+      <c r="BB483" t="inlineStr"/>
+      <c r="BC483" t="inlineStr"/>
+      <c r="BD483" t="inlineStr"/>
+      <c r="BE483" t="inlineStr"/>
+      <c r="BF483" t="inlineStr"/>
+      <c r="BG483" t="inlineStr"/>
+      <c r="BH483" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="inlineStr">
+        <is>
+          <t>dbIuPwZQ</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>31.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr"/>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Estadio Hipòlit Planàs
+ (Vic)</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr"/>
+      <c r="F484" t="inlineStr"/>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>SGQrDLqm</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>UE Vic</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>Atl. Madrid
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr"/>
+      <c r="N484" t="inlineStr"/>
+      <c r="O484" t="inlineStr"/>
+      <c r="P484" t="inlineStr"/>
+      <c r="Q484" t="inlineStr"/>
+      <c r="R484" t="inlineStr"/>
+      <c r="S484" t="inlineStr"/>
+      <c r="T484" t="inlineStr"/>
+      <c r="U484" t="inlineStr"/>
+      <c r="V484" t="inlineStr"/>
+      <c r="W484" t="inlineStr"/>
+      <c r="X484" t="inlineStr"/>
+      <c r="Y484" t="inlineStr"/>
+      <c r="Z484" t="inlineStr"/>
+      <c r="AA484" t="inlineStr"/>
+      <c r="AB484" t="inlineStr"/>
+      <c r="AC484" t="inlineStr"/>
+      <c r="AD484" t="inlineStr"/>
+      <c r="AE484" t="inlineStr"/>
+      <c r="AF484" t="inlineStr"/>
+      <c r="AG484" t="inlineStr"/>
+      <c r="AH484" t="inlineStr"/>
+      <c r="AI484" t="inlineStr"/>
+      <c r="AJ484" t="inlineStr"/>
+      <c r="AK484" t="inlineStr"/>
+      <c r="AL484" t="inlineStr"/>
+      <c r="AM484" t="inlineStr"/>
+      <c r="AN484" t="inlineStr"/>
+      <c r="AO484" t="inlineStr"/>
+      <c r="AP484" t="inlineStr"/>
+      <c r="AQ484" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR484" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS484" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT484" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU484" t="inlineStr"/>
+      <c r="AV484" t="inlineStr"/>
+      <c r="AW484" t="inlineStr"/>
+      <c r="AX484" t="inlineStr"/>
+      <c r="AY484" t="inlineStr"/>
+      <c r="AZ484" t="inlineStr"/>
+      <c r="BA484" t="inlineStr"/>
+      <c r="BB484" t="inlineStr"/>
+      <c r="BC484" t="inlineStr"/>
+      <c r="BD484" t="inlineStr"/>
+      <c r="BE484" t="inlineStr"/>
+      <c r="BF484" t="inlineStr"/>
+      <c r="BG484" t="inlineStr"/>
+      <c r="BH484" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="inlineStr">
+        <is>
+          <t>8WGS5hTs</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>30.10.2024 17:30</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr"/>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Campo Municipal de El Paso
+ (El Paso)</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr"/>
+      <c r="F485" t="inlineStr"/>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>lMqF1cA8</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>Atl. Paso</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>Eldense
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr"/>
+      <c r="N485" t="inlineStr"/>
+      <c r="O485" t="inlineStr"/>
+      <c r="P485" t="inlineStr"/>
+      <c r="Q485" t="inlineStr"/>
+      <c r="R485" t="inlineStr"/>
+      <c r="S485" t="inlineStr"/>
+      <c r="T485" t="inlineStr"/>
+      <c r="U485" t="inlineStr"/>
+      <c r="V485" t="inlineStr"/>
+      <c r="W485" t="inlineStr"/>
+      <c r="X485" t="inlineStr"/>
+      <c r="Y485" t="inlineStr"/>
+      <c r="Z485" t="inlineStr"/>
+      <c r="AA485" t="inlineStr"/>
+      <c r="AB485" t="inlineStr"/>
+      <c r="AC485" t="inlineStr"/>
+      <c r="AD485" t="inlineStr"/>
+      <c r="AE485" t="inlineStr"/>
+      <c r="AF485" t="inlineStr"/>
+      <c r="AG485" t="inlineStr"/>
+      <c r="AH485" t="inlineStr"/>
+      <c r="AI485" t="inlineStr"/>
+      <c r="AJ485" t="inlineStr"/>
+      <c r="AK485" t="inlineStr"/>
+      <c r="AL485" t="inlineStr"/>
+      <c r="AM485" t="inlineStr"/>
+      <c r="AN485" t="inlineStr"/>
+      <c r="AO485" t="inlineStr"/>
+      <c r="AP485" t="inlineStr"/>
+      <c r="AQ485" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR485" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS485" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT485" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU485" t="inlineStr"/>
+      <c r="AV485" t="inlineStr"/>
+      <c r="AW485" t="inlineStr"/>
+      <c r="AX485" t="inlineStr"/>
+      <c r="AY485" t="inlineStr"/>
+      <c r="AZ485" t="inlineStr"/>
+      <c r="BA485" t="inlineStr"/>
+      <c r="BB485" t="inlineStr"/>
+      <c r="BC485" t="inlineStr"/>
+      <c r="BD485" t="inlineStr"/>
+      <c r="BE485" t="inlineStr"/>
+      <c r="BF485" t="inlineStr"/>
+      <c r="BG485" t="inlineStr"/>
+      <c r="BH485" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="inlineStr">
+        <is>
+          <t>Kh3g99kt</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>30.10.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr"/>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Estadio El Rubial
+ (Águilas)</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>4 000</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr"/>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>jaHVSovI</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>Aguilas FC</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>Castellon
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr"/>
+      <c r="N486" t="inlineStr"/>
+      <c r="O486" t="inlineStr"/>
+      <c r="P486" t="inlineStr"/>
+      <c r="Q486" t="inlineStr"/>
+      <c r="R486" t="inlineStr"/>
+      <c r="S486" t="inlineStr"/>
+      <c r="T486" t="inlineStr"/>
+      <c r="U486" t="inlineStr"/>
+      <c r="V486" t="inlineStr"/>
+      <c r="W486" t="inlineStr"/>
+      <c r="X486" t="inlineStr"/>
+      <c r="Y486" t="inlineStr"/>
+      <c r="Z486" t="inlineStr"/>
+      <c r="AA486" t="inlineStr"/>
+      <c r="AB486" t="inlineStr"/>
+      <c r="AC486" t="inlineStr"/>
+      <c r="AD486" t="inlineStr"/>
+      <c r="AE486" t="inlineStr"/>
+      <c r="AF486" t="inlineStr"/>
+      <c r="AG486" t="inlineStr"/>
+      <c r="AH486" t="inlineStr"/>
+      <c r="AI486" t="inlineStr"/>
+      <c r="AJ486" t="inlineStr"/>
+      <c r="AK486" t="inlineStr"/>
+      <c r="AL486" t="inlineStr"/>
+      <c r="AM486" t="inlineStr"/>
+      <c r="AN486" t="inlineStr"/>
+      <c r="AO486" t="inlineStr"/>
+      <c r="AP486" t="inlineStr"/>
+      <c r="AQ486" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR486" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS486" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT486" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU486" t="inlineStr"/>
+      <c r="AV486" t="inlineStr"/>
+      <c r="AW486" t="inlineStr"/>
+      <c r="AX486" t="inlineStr"/>
+      <c r="AY486" t="inlineStr"/>
+      <c r="AZ486" t="inlineStr"/>
+      <c r="BA486" t="inlineStr"/>
+      <c r="BB486" t="inlineStr"/>
+      <c r="BC486" t="inlineStr"/>
+      <c r="BD486" t="inlineStr"/>
+      <c r="BE486" t="inlineStr"/>
+      <c r="BF486" t="inlineStr"/>
+      <c r="BG486" t="inlineStr"/>
+      <c r="BH486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="inlineStr">
+        <is>
+          <t>GzRen7Wi</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>30.10.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Estadio Francisco de la Hera
+ (Almendralejo)</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>11 580</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr"/>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>AqFWmrmE</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>CD Extremadura</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>Girona
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr"/>
+      <c r="N487" t="inlineStr"/>
+      <c r="O487" t="inlineStr"/>
+      <c r="P487" t="inlineStr"/>
+      <c r="Q487" t="inlineStr"/>
+      <c r="R487" t="inlineStr"/>
+      <c r="S487" t="inlineStr"/>
+      <c r="T487" t="inlineStr"/>
+      <c r="U487" t="inlineStr"/>
+      <c r="V487" t="inlineStr"/>
+      <c r="W487" t="inlineStr"/>
+      <c r="X487" t="inlineStr"/>
+      <c r="Y487" t="inlineStr"/>
+      <c r="Z487" t="inlineStr"/>
+      <c r="AA487" t="inlineStr"/>
+      <c r="AB487" t="inlineStr"/>
+      <c r="AC487" t="inlineStr"/>
+      <c r="AD487" t="inlineStr"/>
+      <c r="AE487" t="inlineStr"/>
+      <c r="AF487" t="inlineStr"/>
+      <c r="AG487" t="inlineStr"/>
+      <c r="AH487" t="inlineStr"/>
+      <c r="AI487" t="inlineStr"/>
+      <c r="AJ487" t="inlineStr"/>
+      <c r="AK487" t="inlineStr"/>
+      <c r="AL487" t="inlineStr"/>
+      <c r="AM487" t="inlineStr"/>
+      <c r="AN487" t="inlineStr"/>
+      <c r="AO487" t="inlineStr"/>
+      <c r="AP487" t="inlineStr"/>
+      <c r="AQ487" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR487" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS487" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT487" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU487" t="inlineStr"/>
+      <c r="AV487" t="inlineStr"/>
+      <c r="AW487" t="inlineStr"/>
+      <c r="AX487" t="inlineStr"/>
+      <c r="AY487" t="inlineStr"/>
+      <c r="AZ487" t="inlineStr"/>
+      <c r="BA487" t="inlineStr"/>
+      <c r="BB487" t="inlineStr"/>
+      <c r="BC487" t="inlineStr"/>
+      <c r="BD487" t="inlineStr"/>
+      <c r="BE487" t="inlineStr"/>
+      <c r="BF487" t="inlineStr"/>
+      <c r="BG487" t="inlineStr"/>
+      <c r="BH487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>bLVAIVCm</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>30.10.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Estadio Municipal Nuevo Matapiñonera
+ (San Sebastián de los Reyes)</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>3 000</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr"/>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>b3GVm8Ia</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>San Sebastian Reyes</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>Almeria
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr"/>
+      <c r="N488" t="inlineStr"/>
+      <c r="O488" t="inlineStr"/>
+      <c r="P488" t="inlineStr"/>
+      <c r="Q488" t="inlineStr"/>
+      <c r="R488" t="inlineStr"/>
+      <c r="S488" t="inlineStr"/>
+      <c r="T488" t="inlineStr"/>
+      <c r="U488" t="inlineStr"/>
+      <c r="V488" t="inlineStr"/>
+      <c r="W488" t="inlineStr"/>
+      <c r="X488" t="inlineStr"/>
+      <c r="Y488" t="inlineStr"/>
+      <c r="Z488" t="inlineStr"/>
+      <c r="AA488" t="inlineStr"/>
+      <c r="AB488" t="inlineStr"/>
+      <c r="AC488" t="inlineStr"/>
+      <c r="AD488" t="inlineStr"/>
+      <c r="AE488" t="inlineStr"/>
+      <c r="AF488" t="inlineStr"/>
+      <c r="AG488" t="inlineStr"/>
+      <c r="AH488" t="inlineStr"/>
+      <c r="AI488" t="inlineStr"/>
+      <c r="AJ488" t="inlineStr"/>
+      <c r="AK488" t="inlineStr"/>
+      <c r="AL488" t="inlineStr"/>
+      <c r="AM488" t="inlineStr"/>
+      <c r="AN488" t="inlineStr"/>
+      <c r="AO488" t="inlineStr"/>
+      <c r="AP488" t="inlineStr"/>
+      <c r="AQ488" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR488" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS488" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT488" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU488" t="inlineStr"/>
+      <c r="AV488" t="inlineStr"/>
+      <c r="AW488" t="inlineStr"/>
+      <c r="AX488" t="inlineStr"/>
+      <c r="AY488" t="inlineStr"/>
+      <c r="AZ488" t="inlineStr"/>
+      <c r="BA488" t="inlineStr"/>
+      <c r="BB488" t="inlineStr"/>
+      <c r="BC488" t="inlineStr"/>
+      <c r="BD488" t="inlineStr"/>
+      <c r="BE488" t="inlineStr"/>
+      <c r="BF488" t="inlineStr"/>
+      <c r="BG488" t="inlineStr"/>
+      <c r="BH488" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>xGbeJ825</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>30.10.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Estadio Municipal Antonio Naranjo
+ (San Pedro Alcantara)</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>5 000</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr"/>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>8WJ5ilVD</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>UD San Pedro</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>Celta Vigo
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr"/>
+      <c r="N489" t="inlineStr"/>
+      <c r="O489" t="inlineStr"/>
+      <c r="P489" t="inlineStr"/>
+      <c r="Q489" t="inlineStr"/>
+      <c r="R489" t="inlineStr"/>
+      <c r="S489" t="inlineStr"/>
+      <c r="T489" t="inlineStr"/>
+      <c r="U489" t="inlineStr"/>
+      <c r="V489" t="inlineStr"/>
+      <c r="W489" t="inlineStr"/>
+      <c r="X489" t="inlineStr"/>
+      <c r="Y489" t="inlineStr"/>
+      <c r="Z489" t="inlineStr"/>
+      <c r="AA489" t="inlineStr"/>
+      <c r="AB489" t="inlineStr"/>
+      <c r="AC489" t="inlineStr"/>
+      <c r="AD489" t="inlineStr"/>
+      <c r="AE489" t="inlineStr"/>
+      <c r="AF489" t="inlineStr"/>
+      <c r="AG489" t="inlineStr"/>
+      <c r="AH489" t="inlineStr"/>
+      <c r="AI489" t="inlineStr"/>
+      <c r="AJ489" t="inlineStr"/>
+      <c r="AK489" t="inlineStr"/>
+      <c r="AL489" t="inlineStr"/>
+      <c r="AM489" t="inlineStr"/>
+      <c r="AN489" t="inlineStr"/>
+      <c r="AO489" t="inlineStr"/>
+      <c r="AP489" t="inlineStr"/>
+      <c r="AQ489" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR489" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS489" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT489" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU489" t="inlineStr"/>
+      <c r="AV489" t="inlineStr"/>
+      <c r="AW489" t="inlineStr"/>
+      <c r="AX489" t="inlineStr"/>
+      <c r="AY489" t="inlineStr"/>
+      <c r="AZ489" t="inlineStr"/>
+      <c r="BA489" t="inlineStr"/>
+      <c r="BB489" t="inlineStr"/>
+      <c r="BC489" t="inlineStr"/>
+      <c r="BD489" t="inlineStr"/>
+      <c r="BE489" t="inlineStr"/>
+      <c r="BF489" t="inlineStr"/>
+      <c r="BG489" t="inlineStr"/>
+      <c r="BH489" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>QBB2WfgL</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Estadio Principe Felipe
+ (Cáceres)</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr"/>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>EXTWwqkE</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Cacereno</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>IyihVeQK</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>Gimnastica Segoviana</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr"/>
+      <c r="N490" t="inlineStr"/>
+      <c r="O490" t="inlineStr"/>
+      <c r="P490" t="inlineStr"/>
+      <c r="Q490" t="inlineStr"/>
+      <c r="R490" t="inlineStr"/>
+      <c r="S490" t="inlineStr"/>
+      <c r="T490" t="inlineStr"/>
+      <c r="U490" t="inlineStr"/>
+      <c r="V490" t="inlineStr"/>
+      <c r="W490" t="inlineStr"/>
+      <c r="X490" t="inlineStr"/>
+      <c r="Y490" t="inlineStr"/>
+      <c r="Z490" t="inlineStr"/>
+      <c r="AA490" t="inlineStr"/>
+      <c r="AB490" t="inlineStr"/>
+      <c r="AC490" t="inlineStr"/>
+      <c r="AD490" t="inlineStr"/>
+      <c r="AE490" t="inlineStr"/>
+      <c r="AF490" t="inlineStr"/>
+      <c r="AG490" t="inlineStr"/>
+      <c r="AH490" t="inlineStr"/>
+      <c r="AI490" t="inlineStr"/>
+      <c r="AJ490" t="inlineStr"/>
+      <c r="AK490" t="inlineStr"/>
+      <c r="AL490" t="inlineStr"/>
+      <c r="AM490" t="inlineStr"/>
+      <c r="AN490" t="inlineStr"/>
+      <c r="AO490" t="inlineStr"/>
+      <c r="AP490" t="inlineStr"/>
+      <c r="AQ490" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR490" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS490" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT490" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU490" t="inlineStr"/>
+      <c r="AV490" t="inlineStr"/>
+      <c r="AW490" t="inlineStr"/>
+      <c r="AX490" t="inlineStr"/>
+      <c r="AY490" t="inlineStr"/>
+      <c r="AZ490" t="inlineStr"/>
+      <c r="BA490" t="inlineStr"/>
+      <c r="BB490" t="inlineStr"/>
+      <c r="BC490" t="inlineStr"/>
+      <c r="BD490" t="inlineStr"/>
+      <c r="BE490" t="inlineStr"/>
+      <c r="BF490" t="inlineStr"/>
+      <c r="BG490" t="inlineStr"/>
+      <c r="BH490" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>dbbI35JH</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Estadio La Isla
+ (Coria)</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>2 000</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr"/>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>2mbZcDGG</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>CD Coria</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>Elche
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr"/>
+      <c r="N491" t="inlineStr"/>
+      <c r="O491" t="inlineStr"/>
+      <c r="P491" t="inlineStr"/>
+      <c r="Q491" t="inlineStr"/>
+      <c r="R491" t="inlineStr"/>
+      <c r="S491" t="inlineStr"/>
+      <c r="T491" t="inlineStr"/>
+      <c r="U491" t="inlineStr"/>
+      <c r="V491" t="inlineStr"/>
+      <c r="W491" t="inlineStr"/>
+      <c r="X491" t="inlineStr"/>
+      <c r="Y491" t="inlineStr"/>
+      <c r="Z491" t="inlineStr"/>
+      <c r="AA491" t="inlineStr"/>
+      <c r="AB491" t="inlineStr"/>
+      <c r="AC491" t="inlineStr"/>
+      <c r="AD491" t="inlineStr"/>
+      <c r="AE491" t="inlineStr"/>
+      <c r="AF491" t="inlineStr"/>
+      <c r="AG491" t="inlineStr"/>
+      <c r="AH491" t="inlineStr"/>
+      <c r="AI491" t="inlineStr"/>
+      <c r="AJ491" t="inlineStr"/>
+      <c r="AK491" t="inlineStr"/>
+      <c r="AL491" t="inlineStr"/>
+      <c r="AM491" t="inlineStr"/>
+      <c r="AN491" t="inlineStr"/>
+      <c r="AO491" t="inlineStr"/>
+      <c r="AP491" t="inlineStr"/>
+      <c r="AQ491" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR491" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS491" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT491" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU491" t="inlineStr"/>
+      <c r="AV491" t="inlineStr"/>
+      <c r="AW491" t="inlineStr"/>
+      <c r="AX491" t="inlineStr"/>
+      <c r="AY491" t="inlineStr"/>
+      <c r="AZ491" t="inlineStr"/>
+      <c r="BA491" t="inlineStr"/>
+      <c r="BB491" t="inlineStr"/>
+      <c r="BC491" t="inlineStr"/>
+      <c r="BD491" t="inlineStr"/>
+      <c r="BE491" t="inlineStr"/>
+      <c r="BF491" t="inlineStr"/>
+      <c r="BG491" t="inlineStr"/>
+      <c r="BH491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>GtjsPCoe</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Estadio La Fuensanta
+ (Cuenca)</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr"/>
+      <c r="F492" t="inlineStr"/>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>W4EcOeMI</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Conquense</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>rNW6jqw0</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>UD Ibiza</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr"/>
+      <c r="N492" t="inlineStr"/>
+      <c r="O492" t="inlineStr"/>
+      <c r="P492" t="inlineStr"/>
+      <c r="Q492" t="inlineStr"/>
+      <c r="R492" t="inlineStr"/>
+      <c r="S492" t="inlineStr"/>
+      <c r="T492" t="inlineStr"/>
+      <c r="U492" t="inlineStr"/>
+      <c r="V492" t="inlineStr"/>
+      <c r="W492" t="inlineStr"/>
+      <c r="X492" t="inlineStr"/>
+      <c r="Y492" t="inlineStr"/>
+      <c r="Z492" t="inlineStr"/>
+      <c r="AA492" t="inlineStr"/>
+      <c r="AB492" t="inlineStr"/>
+      <c r="AC492" t="inlineStr"/>
+      <c r="AD492" t="inlineStr"/>
+      <c r="AE492" t="inlineStr"/>
+      <c r="AF492" t="inlineStr"/>
+      <c r="AG492" t="inlineStr"/>
+      <c r="AH492" t="inlineStr"/>
+      <c r="AI492" t="inlineStr"/>
+      <c r="AJ492" t="inlineStr"/>
+      <c r="AK492" t="inlineStr"/>
+      <c r="AL492" t="inlineStr"/>
+      <c r="AM492" t="inlineStr"/>
+      <c r="AN492" t="inlineStr"/>
+      <c r="AO492" t="inlineStr"/>
+      <c r="AP492" t="inlineStr"/>
+      <c r="AQ492" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR492" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS492" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT492" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU492" t="inlineStr"/>
+      <c r="AV492" t="inlineStr"/>
+      <c r="AW492" t="inlineStr"/>
+      <c r="AX492" t="inlineStr"/>
+      <c r="AY492" t="inlineStr"/>
+      <c r="AZ492" t="inlineStr"/>
+      <c r="BA492" t="inlineStr"/>
+      <c r="BB492" t="inlineStr"/>
+      <c r="BC492" t="inlineStr"/>
+      <c r="BD492" t="inlineStr"/>
+      <c r="BE492" t="inlineStr"/>
+      <c r="BF492" t="inlineStr"/>
+      <c r="BG492" t="inlineStr"/>
+      <c r="BH492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>4bAy4Wcf</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Nou Estadi Municipal de Palamos
+ (Palamos)</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>3 724</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr"/>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>zgXOPZmr</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>Badalona Futur</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>Huesca
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr"/>
+      <c r="N493" t="inlineStr"/>
+      <c r="O493" t="inlineStr"/>
+      <c r="P493" t="inlineStr"/>
+      <c r="Q493" t="inlineStr"/>
+      <c r="R493" t="inlineStr"/>
+      <c r="S493" t="inlineStr"/>
+      <c r="T493" t="inlineStr"/>
+      <c r="U493" t="inlineStr"/>
+      <c r="V493" t="inlineStr"/>
+      <c r="W493" t="inlineStr"/>
+      <c r="X493" t="inlineStr"/>
+      <c r="Y493" t="inlineStr"/>
+      <c r="Z493" t="inlineStr"/>
+      <c r="AA493" t="inlineStr"/>
+      <c r="AB493" t="inlineStr"/>
+      <c r="AC493" t="inlineStr"/>
+      <c r="AD493" t="inlineStr"/>
+      <c r="AE493" t="inlineStr"/>
+      <c r="AF493" t="inlineStr"/>
+      <c r="AG493" t="inlineStr"/>
+      <c r="AH493" t="inlineStr"/>
+      <c r="AI493" t="inlineStr"/>
+      <c r="AJ493" t="inlineStr"/>
+      <c r="AK493" t="inlineStr"/>
+      <c r="AL493" t="inlineStr"/>
+      <c r="AM493" t="inlineStr"/>
+      <c r="AN493" t="inlineStr"/>
+      <c r="AO493" t="inlineStr"/>
+      <c r="AP493" t="inlineStr"/>
+      <c r="AQ493" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR493" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS493" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT493" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU493" t="inlineStr"/>
+      <c r="AV493" t="inlineStr"/>
+      <c r="AW493" t="inlineStr"/>
+      <c r="AX493" t="inlineStr"/>
+      <c r="AY493" t="inlineStr"/>
+      <c r="AZ493" t="inlineStr"/>
+      <c r="BA493" t="inlineStr"/>
+      <c r="BB493" t="inlineStr"/>
+      <c r="BC493" t="inlineStr"/>
+      <c r="BD493" t="inlineStr"/>
+      <c r="BE493" t="inlineStr"/>
+      <c r="BF493" t="inlineStr"/>
+      <c r="BG493" t="inlineStr"/>
+      <c r="BH493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>U7IQktwp</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr"/>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Estadio San Francisco Javier
+ (Aguilar de Campoo)</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>1 000</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr"/>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>vVUbHs5o</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>Cortes</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>Granada CF
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr"/>
+      <c r="N494" t="inlineStr"/>
+      <c r="O494" t="inlineStr"/>
+      <c r="P494" t="inlineStr"/>
+      <c r="Q494" t="inlineStr"/>
+      <c r="R494" t="inlineStr"/>
+      <c r="S494" t="inlineStr"/>
+      <c r="T494" t="inlineStr"/>
+      <c r="U494" t="inlineStr"/>
+      <c r="V494" t="inlineStr"/>
+      <c r="W494" t="inlineStr"/>
+      <c r="X494" t="inlineStr"/>
+      <c r="Y494" t="inlineStr"/>
+      <c r="Z494" t="inlineStr"/>
+      <c r="AA494" t="inlineStr"/>
+      <c r="AB494" t="inlineStr"/>
+      <c r="AC494" t="inlineStr"/>
+      <c r="AD494" t="inlineStr"/>
+      <c r="AE494" t="inlineStr"/>
+      <c r="AF494" t="inlineStr"/>
+      <c r="AG494" t="inlineStr"/>
+      <c r="AH494" t="inlineStr"/>
+      <c r="AI494" t="inlineStr"/>
+      <c r="AJ494" t="inlineStr"/>
+      <c r="AK494" t="inlineStr"/>
+      <c r="AL494" t="inlineStr"/>
+      <c r="AM494" t="inlineStr"/>
+      <c r="AN494" t="inlineStr"/>
+      <c r="AO494" t="inlineStr"/>
+      <c r="AP494" t="inlineStr"/>
+      <c r="AQ494" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR494" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS494" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT494" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU494" t="inlineStr"/>
+      <c r="AV494" t="inlineStr"/>
+      <c r="AW494" t="inlineStr"/>
+      <c r="AX494" t="inlineStr"/>
+      <c r="AY494" t="inlineStr"/>
+      <c r="AZ494" t="inlineStr"/>
+      <c r="BA494" t="inlineStr"/>
+      <c r="BB494" t="inlineStr"/>
+      <c r="BC494" t="inlineStr"/>
+      <c r="BD494" t="inlineStr"/>
+      <c r="BE494" t="inlineStr"/>
+      <c r="BF494" t="inlineStr"/>
+      <c r="BG494" t="inlineStr"/>
+      <c r="BH494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>fmw9wC0l</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Estadio Eusebio Arce
+ (Escobedo)</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>2 000</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr"/>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>d8zuVWbh</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>Escobedo</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>0UFPgH6a</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>Ponferradina
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr"/>
+      <c r="N495" t="inlineStr"/>
+      <c r="O495" t="inlineStr"/>
+      <c r="P495" t="inlineStr"/>
+      <c r="Q495" t="inlineStr"/>
+      <c r="R495" t="inlineStr"/>
+      <c r="S495" t="inlineStr"/>
+      <c r="T495" t="inlineStr"/>
+      <c r="U495" t="inlineStr"/>
+      <c r="V495" t="inlineStr"/>
+      <c r="W495" t="inlineStr"/>
+      <c r="X495" t="inlineStr"/>
+      <c r="Y495" t="inlineStr"/>
+      <c r="Z495" t="inlineStr"/>
+      <c r="AA495" t="inlineStr"/>
+      <c r="AB495" t="inlineStr"/>
+      <c r="AC495" t="inlineStr"/>
+      <c r="AD495" t="inlineStr"/>
+      <c r="AE495" t="inlineStr"/>
+      <c r="AF495" t="inlineStr"/>
+      <c r="AG495" t="inlineStr"/>
+      <c r="AH495" t="inlineStr"/>
+      <c r="AI495" t="inlineStr"/>
+      <c r="AJ495" t="inlineStr"/>
+      <c r="AK495" t="inlineStr"/>
+      <c r="AL495" t="inlineStr"/>
+      <c r="AM495" t="inlineStr"/>
+      <c r="AN495" t="inlineStr"/>
+      <c r="AO495" t="inlineStr"/>
+      <c r="AP495" t="inlineStr"/>
+      <c r="AQ495" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR495" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS495" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT495" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU495" t="inlineStr"/>
+      <c r="AV495" t="inlineStr"/>
+      <c r="AW495" t="inlineStr"/>
+      <c r="AX495" t="inlineStr"/>
+      <c r="AY495" t="inlineStr"/>
+      <c r="AZ495" t="inlineStr"/>
+      <c r="BA495" t="inlineStr"/>
+      <c r="BB495" t="inlineStr"/>
+      <c r="BC495" t="inlineStr"/>
+      <c r="BD495" t="inlineStr"/>
+      <c r="BE495" t="inlineStr"/>
+      <c r="BF495" t="inlineStr"/>
+      <c r="BG495" t="inlineStr"/>
+      <c r="BH495" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>vFyxof8E</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Estadio San Lorenzo
+ (Laredo)</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr"/>
+      <c r="F496" t="inlineStr"/>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>SStPzDHM</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>Laredo</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>bwkt7cPq</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>Yeclano
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M496" t="inlineStr"/>
+      <c r="N496" t="inlineStr"/>
+      <c r="O496" t="inlineStr"/>
+      <c r="P496" t="inlineStr"/>
+      <c r="Q496" t="inlineStr"/>
+      <c r="R496" t="inlineStr"/>
+      <c r="S496" t="inlineStr"/>
+      <c r="T496" t="inlineStr"/>
+      <c r="U496" t="inlineStr"/>
+      <c r="V496" t="inlineStr"/>
+      <c r="W496" t="inlineStr"/>
+      <c r="X496" t="inlineStr"/>
+      <c r="Y496" t="inlineStr"/>
+      <c r="Z496" t="inlineStr"/>
+      <c r="AA496" t="inlineStr"/>
+      <c r="AB496" t="inlineStr"/>
+      <c r="AC496" t="inlineStr"/>
+      <c r="AD496" t="inlineStr"/>
+      <c r="AE496" t="inlineStr"/>
+      <c r="AF496" t="inlineStr"/>
+      <c r="AG496" t="inlineStr"/>
+      <c r="AH496" t="inlineStr"/>
+      <c r="AI496" t="inlineStr"/>
+      <c r="AJ496" t="inlineStr"/>
+      <c r="AK496" t="inlineStr"/>
+      <c r="AL496" t="inlineStr"/>
+      <c r="AM496" t="inlineStr"/>
+      <c r="AN496" t="inlineStr"/>
+      <c r="AO496" t="inlineStr"/>
+      <c r="AP496" t="inlineStr"/>
+      <c r="AQ496" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR496" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS496" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT496" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU496" t="inlineStr"/>
+      <c r="AV496" t="inlineStr"/>
+      <c r="AW496" t="inlineStr"/>
+      <c r="AX496" t="inlineStr"/>
+      <c r="AY496" t="inlineStr"/>
+      <c r="AZ496" t="inlineStr"/>
+      <c r="BA496" t="inlineStr"/>
+      <c r="BB496" t="inlineStr"/>
+      <c r="BC496" t="inlineStr"/>
+      <c r="BD496" t="inlineStr"/>
+      <c r="BE496" t="inlineStr"/>
+      <c r="BF496" t="inlineStr"/>
+      <c r="BG496" t="inlineStr"/>
+      <c r="BH496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>SEGkjkpf</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr"/>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Camp d'Esports
+ (Lleida)</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>13 500</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr"/>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>f9Ugc7VJ</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>Lleida</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>fBqFQex0</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>Barakaldo
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr"/>
+      <c r="N497" t="inlineStr"/>
+      <c r="O497" t="inlineStr"/>
+      <c r="P497" t="inlineStr"/>
+      <c r="Q497" t="inlineStr"/>
+      <c r="R497" t="inlineStr"/>
+      <c r="S497" t="inlineStr"/>
+      <c r="T497" t="inlineStr"/>
+      <c r="U497" t="inlineStr"/>
+      <c r="V497" t="inlineStr"/>
+      <c r="W497" t="inlineStr"/>
+      <c r="X497" t="inlineStr"/>
+      <c r="Y497" t="inlineStr"/>
+      <c r="Z497" t="inlineStr"/>
+      <c r="AA497" t="inlineStr"/>
+      <c r="AB497" t="inlineStr"/>
+      <c r="AC497" t="inlineStr"/>
+      <c r="AD497" t="inlineStr"/>
+      <c r="AE497" t="inlineStr"/>
+      <c r="AF497" t="inlineStr"/>
+      <c r="AG497" t="inlineStr"/>
+      <c r="AH497" t="inlineStr"/>
+      <c r="AI497" t="inlineStr"/>
+      <c r="AJ497" t="inlineStr"/>
+      <c r="AK497" t="inlineStr"/>
+      <c r="AL497" t="inlineStr"/>
+      <c r="AM497" t="inlineStr"/>
+      <c r="AN497" t="inlineStr"/>
+      <c r="AO497" t="inlineStr"/>
+      <c r="AP497" t="inlineStr"/>
+      <c r="AQ497" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR497" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS497" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT497" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU497" t="inlineStr"/>
+      <c r="AV497" t="inlineStr"/>
+      <c r="AW497" t="inlineStr"/>
+      <c r="AX497" t="inlineStr"/>
+      <c r="AY497" t="inlineStr"/>
+      <c r="AZ497" t="inlineStr"/>
+      <c r="BA497" t="inlineStr"/>
+      <c r="BB497" t="inlineStr"/>
+      <c r="BC497" t="inlineStr"/>
+      <c r="BD497" t="inlineStr"/>
+      <c r="BE497" t="inlineStr"/>
+      <c r="BF497" t="inlineStr"/>
+      <c r="BG497" t="inlineStr"/>
+      <c r="BH497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>vykvOikQ</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Nuevo Estadio Los Pajaritos
+ (Soria)</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>8 261</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr"/>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>I7HizxOs</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>Numancia</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>Gijon
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr"/>
+      <c r="N498" t="inlineStr"/>
+      <c r="O498" t="inlineStr"/>
+      <c r="P498" t="inlineStr"/>
+      <c r="Q498" t="inlineStr"/>
+      <c r="R498" t="inlineStr"/>
+      <c r="S498" t="inlineStr"/>
+      <c r="T498" t="inlineStr"/>
+      <c r="U498" t="inlineStr"/>
+      <c r="V498" t="inlineStr"/>
+      <c r="W498" t="inlineStr"/>
+      <c r="X498" t="inlineStr"/>
+      <c r="Y498" t="inlineStr"/>
+      <c r="Z498" t="inlineStr"/>
+      <c r="AA498" t="inlineStr"/>
+      <c r="AB498" t="inlineStr"/>
+      <c r="AC498" t="inlineStr"/>
+      <c r="AD498" t="inlineStr"/>
+      <c r="AE498" t="inlineStr"/>
+      <c r="AF498" t="inlineStr"/>
+      <c r="AG498" t="inlineStr"/>
+      <c r="AH498" t="inlineStr"/>
+      <c r="AI498" t="inlineStr"/>
+      <c r="AJ498" t="inlineStr"/>
+      <c r="AK498" t="inlineStr"/>
+      <c r="AL498" t="inlineStr"/>
+      <c r="AM498" t="inlineStr"/>
+      <c r="AN498" t="inlineStr"/>
+      <c r="AO498" t="inlineStr"/>
+      <c r="AP498" t="inlineStr"/>
+      <c r="AQ498" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR498" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS498" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT498" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU498" t="inlineStr"/>
+      <c r="AV498" t="inlineStr"/>
+      <c r="AW498" t="inlineStr"/>
+      <c r="AX498" t="inlineStr"/>
+      <c r="AY498" t="inlineStr"/>
+      <c r="AZ498" t="inlineStr"/>
+      <c r="BA498" t="inlineStr"/>
+      <c r="BB498" t="inlineStr"/>
+      <c r="BC498" t="inlineStr"/>
+      <c r="BD498" t="inlineStr"/>
+      <c r="BE498" t="inlineStr"/>
+      <c r="BF498" t="inlineStr"/>
+      <c r="BG498" t="inlineStr"/>
+      <c r="BH498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2DtHyjV0</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Guijuelo
+ (Guijuelo)</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>2 000</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr"/>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>8OiWNQkh</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Salamanca</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>0ranWp9D</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>Alcorcon</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr"/>
+      <c r="N499" t="inlineStr"/>
+      <c r="O499" t="inlineStr"/>
+      <c r="P499" t="inlineStr"/>
+      <c r="Q499" t="inlineStr"/>
+      <c r="R499" t="inlineStr"/>
+      <c r="S499" t="inlineStr"/>
+      <c r="T499" t="inlineStr"/>
+      <c r="U499" t="inlineStr"/>
+      <c r="V499" t="inlineStr"/>
+      <c r="W499" t="inlineStr"/>
+      <c r="X499" t="inlineStr"/>
+      <c r="Y499" t="inlineStr"/>
+      <c r="Z499" t="inlineStr"/>
+      <c r="AA499" t="inlineStr"/>
+      <c r="AB499" t="inlineStr"/>
+      <c r="AC499" t="inlineStr"/>
+      <c r="AD499" t="inlineStr"/>
+      <c r="AE499" t="inlineStr"/>
+      <c r="AF499" t="inlineStr"/>
+      <c r="AG499" t="inlineStr"/>
+      <c r="AH499" t="inlineStr"/>
+      <c r="AI499" t="inlineStr"/>
+      <c r="AJ499" t="inlineStr"/>
+      <c r="AK499" t="inlineStr"/>
+      <c r="AL499" t="inlineStr"/>
+      <c r="AM499" t="inlineStr"/>
+      <c r="AN499" t="inlineStr"/>
+      <c r="AO499" t="inlineStr"/>
+      <c r="AP499" t="inlineStr"/>
+      <c r="AQ499" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR499" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS499" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT499" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU499" t="inlineStr"/>
+      <c r="AV499" t="inlineStr"/>
+      <c r="AW499" t="inlineStr"/>
+      <c r="AX499" t="inlineStr"/>
+      <c r="AY499" t="inlineStr"/>
+      <c r="AZ499" t="inlineStr"/>
+      <c r="BA499" t="inlineStr"/>
+      <c r="BB499" t="inlineStr"/>
+      <c r="BC499" t="inlineStr"/>
+      <c r="BD499" t="inlineStr"/>
+      <c r="BE499" t="inlineStr"/>
+      <c r="BF499" t="inlineStr"/>
+      <c r="BG499" t="inlineStr"/>
+      <c r="BH499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>C0VdBE5K</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Camp Municipal Narcís Sala
+ (Barcelona)</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>6 563</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr"/>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>rkPfzpO6</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Sant Andreu</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr"/>
+      <c r="N500" t="inlineStr"/>
+      <c r="O500" t="inlineStr"/>
+      <c r="P500" t="inlineStr"/>
+      <c r="Q500" t="inlineStr"/>
+      <c r="R500" t="inlineStr"/>
+      <c r="S500" t="inlineStr"/>
+      <c r="T500" t="inlineStr"/>
+      <c r="U500" t="inlineStr"/>
+      <c r="V500" t="inlineStr"/>
+      <c r="W500" t="inlineStr"/>
+      <c r="X500" t="inlineStr"/>
+      <c r="Y500" t="inlineStr"/>
+      <c r="Z500" t="inlineStr"/>
+      <c r="AA500" t="inlineStr"/>
+      <c r="AB500" t="inlineStr"/>
+      <c r="AC500" t="inlineStr"/>
+      <c r="AD500" t="inlineStr"/>
+      <c r="AE500" t="inlineStr"/>
+      <c r="AF500" t="inlineStr"/>
+      <c r="AG500" t="inlineStr"/>
+      <c r="AH500" t="inlineStr"/>
+      <c r="AI500" t="inlineStr"/>
+      <c r="AJ500" t="inlineStr"/>
+      <c r="AK500" t="inlineStr"/>
+      <c r="AL500" t="inlineStr"/>
+      <c r="AM500" t="inlineStr"/>
+      <c r="AN500" t="inlineStr"/>
+      <c r="AO500" t="inlineStr"/>
+      <c r="AP500" t="inlineStr"/>
+      <c r="AQ500" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR500" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS500" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT500" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU500" t="inlineStr"/>
+      <c r="AV500" t="inlineStr"/>
+      <c r="AW500" t="inlineStr"/>
+      <c r="AX500" t="inlineStr"/>
+      <c r="AY500" t="inlineStr"/>
+      <c r="AZ500" t="inlineStr"/>
+      <c r="BA500" t="inlineStr"/>
+      <c r="BB500" t="inlineStr"/>
+      <c r="BC500" t="inlineStr"/>
+      <c r="BD500" t="inlineStr"/>
+      <c r="BE500" t="inlineStr"/>
+      <c r="BF500" t="inlineStr"/>
+      <c r="BG500" t="inlineStr"/>
+      <c r="BH500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>CSZqqYxR</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Nuevo Estadio Municipal
+ (Lucena)</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr"/>
+      <c r="F501" t="inlineStr"/>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>AB8XRSBQ</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>Torremolinos</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>pGGsv0di</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>Zamora
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr"/>
+      <c r="N501" t="inlineStr"/>
+      <c r="O501" t="inlineStr"/>
+      <c r="P501" t="inlineStr"/>
+      <c r="Q501" t="inlineStr"/>
+      <c r="R501" t="inlineStr"/>
+      <c r="S501" t="inlineStr"/>
+      <c r="T501" t="inlineStr"/>
+      <c r="U501" t="inlineStr"/>
+      <c r="V501" t="inlineStr"/>
+      <c r="W501" t="inlineStr"/>
+      <c r="X501" t="inlineStr"/>
+      <c r="Y501" t="inlineStr"/>
+      <c r="Z501" t="inlineStr"/>
+      <c r="AA501" t="inlineStr"/>
+      <c r="AB501" t="inlineStr"/>
+      <c r="AC501" t="inlineStr"/>
+      <c r="AD501" t="inlineStr"/>
+      <c r="AE501" t="inlineStr"/>
+      <c r="AF501" t="inlineStr"/>
+      <c r="AG501" t="inlineStr"/>
+      <c r="AH501" t="inlineStr"/>
+      <c r="AI501" t="inlineStr"/>
+      <c r="AJ501" t="inlineStr"/>
+      <c r="AK501" t="inlineStr"/>
+      <c r="AL501" t="inlineStr"/>
+      <c r="AM501" t="inlineStr"/>
+      <c r="AN501" t="inlineStr"/>
+      <c r="AO501" t="inlineStr"/>
+      <c r="AP501" t="inlineStr"/>
+      <c r="AQ501" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR501" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS501" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT501" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU501" t="inlineStr"/>
+      <c r="AV501" t="inlineStr"/>
+      <c r="AW501" t="inlineStr"/>
+      <c r="AX501" t="inlineStr"/>
+      <c r="AY501" t="inlineStr"/>
+      <c r="AZ501" t="inlineStr"/>
+      <c r="BA501" t="inlineStr"/>
+      <c r="BB501" t="inlineStr"/>
+      <c r="BC501" t="inlineStr"/>
+      <c r="BD501" t="inlineStr"/>
+      <c r="BE501" t="inlineStr"/>
+      <c r="BF501" t="inlineStr"/>
+      <c r="BG501" t="inlineStr"/>
+      <c r="BH501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="inlineStr">
+        <is>
+          <t>SI617mKh</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Estadio Las Gaunas
+ (Logroño)</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>16 000</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr"/>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>G2DnUxNN</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+UD Logrones</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>Eibar</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr"/>
+      <c r="N502" t="inlineStr"/>
+      <c r="O502" t="inlineStr"/>
+      <c r="P502" t="inlineStr"/>
+      <c r="Q502" t="inlineStr"/>
+      <c r="R502" t="inlineStr"/>
+      <c r="S502" t="inlineStr"/>
+      <c r="T502" t="inlineStr"/>
+      <c r="U502" t="inlineStr"/>
+      <c r="V502" t="inlineStr"/>
+      <c r="W502" t="inlineStr"/>
+      <c r="X502" t="inlineStr"/>
+      <c r="Y502" t="inlineStr"/>
+      <c r="Z502" t="inlineStr"/>
+      <c r="AA502" t="inlineStr"/>
+      <c r="AB502" t="inlineStr"/>
+      <c r="AC502" t="inlineStr"/>
+      <c r="AD502" t="inlineStr"/>
+      <c r="AE502" t="inlineStr"/>
+      <c r="AF502" t="inlineStr"/>
+      <c r="AG502" t="inlineStr"/>
+      <c r="AH502" t="inlineStr"/>
+      <c r="AI502" t="inlineStr"/>
+      <c r="AJ502" t="inlineStr"/>
+      <c r="AK502" t="inlineStr"/>
+      <c r="AL502" t="inlineStr"/>
+      <c r="AM502" t="inlineStr"/>
+      <c r="AN502" t="inlineStr"/>
+      <c r="AO502" t="inlineStr"/>
+      <c r="AP502" t="inlineStr"/>
+      <c r="AQ502" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR502" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS502" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT502" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU502" t="inlineStr"/>
+      <c r="AV502" t="inlineStr"/>
+      <c r="AW502" t="inlineStr"/>
+      <c r="AX502" t="inlineStr"/>
+      <c r="AY502" t="inlineStr"/>
+      <c r="AZ502" t="inlineStr"/>
+      <c r="BA502" t="inlineStr"/>
+      <c r="BB502" t="inlineStr"/>
+      <c r="BC502" t="inlineStr"/>
+      <c r="BD502" t="inlineStr"/>
+      <c r="BE502" t="inlineStr"/>
+      <c r="BF502" t="inlineStr"/>
+      <c r="BG502" t="inlineStr"/>
+      <c r="BH502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="inlineStr">
+        <is>
+          <t>UqIgYGO8</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Santa Ana
+ (Torrelavega)</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr"/>
+      <c r="F503" t="inlineStr"/>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>MoTP7drL</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>Utebo FC</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>fmE1l44l</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>Unionistas
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr"/>
+      <c r="N503" t="inlineStr"/>
+      <c r="O503" t="inlineStr"/>
+      <c r="P503" t="inlineStr"/>
+      <c r="Q503" t="inlineStr"/>
+      <c r="R503" t="inlineStr"/>
+      <c r="S503" t="inlineStr"/>
+      <c r="T503" t="inlineStr"/>
+      <c r="U503" t="inlineStr"/>
+      <c r="V503" t="inlineStr"/>
+      <c r="W503" t="inlineStr"/>
+      <c r="X503" t="inlineStr"/>
+      <c r="Y503" t="inlineStr"/>
+      <c r="Z503" t="inlineStr"/>
+      <c r="AA503" t="inlineStr"/>
+      <c r="AB503" t="inlineStr"/>
+      <c r="AC503" t="inlineStr"/>
+      <c r="AD503" t="inlineStr"/>
+      <c r="AE503" t="inlineStr"/>
+      <c r="AF503" t="inlineStr"/>
+      <c r="AG503" t="inlineStr"/>
+      <c r="AH503" t="inlineStr"/>
+      <c r="AI503" t="inlineStr"/>
+      <c r="AJ503" t="inlineStr"/>
+      <c r="AK503" t="inlineStr"/>
+      <c r="AL503" t="inlineStr"/>
+      <c r="AM503" t="inlineStr"/>
+      <c r="AN503" t="inlineStr"/>
+      <c r="AO503" t="inlineStr"/>
+      <c r="AP503" t="inlineStr"/>
+      <c r="AQ503" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR503" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS503" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT503" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU503" t="inlineStr"/>
+      <c r="AV503" t="inlineStr"/>
+      <c r="AW503" t="inlineStr"/>
+      <c r="AX503" t="inlineStr"/>
+      <c r="AY503" t="inlineStr"/>
+      <c r="AZ503" t="inlineStr"/>
+      <c r="BA503" t="inlineStr"/>
+      <c r="BB503" t="inlineStr"/>
+      <c r="BC503" t="inlineStr"/>
+      <c r="BD503" t="inlineStr"/>
+      <c r="BE503" t="inlineStr"/>
+      <c r="BF503" t="inlineStr"/>
+      <c r="BG503" t="inlineStr"/>
+      <c r="BH503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="inlineStr">
+        <is>
+          <t>bPRfe2FM</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>30.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr"/>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Loinaz
+ (Beasain)</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr"/>
+      <c r="F504" t="inlineStr"/>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>bsKMYEn7</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>Beasain</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>FC Cartagena SAD
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr"/>
+      <c r="N504" t="inlineStr"/>
+      <c r="O504" t="inlineStr"/>
+      <c r="P504" t="inlineStr"/>
+      <c r="Q504" t="inlineStr"/>
+      <c r="R504" t="inlineStr"/>
+      <c r="S504" t="inlineStr"/>
+      <c r="T504" t="inlineStr"/>
+      <c r="U504" t="inlineStr"/>
+      <c r="V504" t="inlineStr"/>
+      <c r="W504" t="inlineStr"/>
+      <c r="X504" t="inlineStr"/>
+      <c r="Y504" t="inlineStr"/>
+      <c r="Z504" t="inlineStr"/>
+      <c r="AA504" t="inlineStr"/>
+      <c r="AB504" t="inlineStr"/>
+      <c r="AC504" t="inlineStr"/>
+      <c r="AD504" t="inlineStr"/>
+      <c r="AE504" t="inlineStr"/>
+      <c r="AF504" t="inlineStr"/>
+      <c r="AG504" t="inlineStr"/>
+      <c r="AH504" t="inlineStr"/>
+      <c r="AI504" t="inlineStr"/>
+      <c r="AJ504" t="inlineStr"/>
+      <c r="AK504" t="inlineStr"/>
+      <c r="AL504" t="inlineStr"/>
+      <c r="AM504" t="inlineStr"/>
+      <c r="AN504" t="inlineStr"/>
+      <c r="AO504" t="inlineStr"/>
+      <c r="AP504" t="inlineStr"/>
+      <c r="AQ504" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR504" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS504" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT504" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU504" t="inlineStr"/>
+      <c r="AV504" t="inlineStr"/>
+      <c r="AW504" t="inlineStr"/>
+      <c r="AX504" t="inlineStr"/>
+      <c r="AY504" t="inlineStr"/>
+      <c r="AZ504" t="inlineStr"/>
+      <c r="BA504" t="inlineStr"/>
+      <c r="BB504" t="inlineStr"/>
+      <c r="BC504" t="inlineStr"/>
+      <c r="BD504" t="inlineStr"/>
+      <c r="BE504" t="inlineStr"/>
+      <c r="BF504" t="inlineStr"/>
+      <c r="BG504" t="inlineStr"/>
+      <c r="BH504" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="inlineStr">
+        <is>
+          <t>pvyUHevS</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>30.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Campo Municipal de As Eiroas
+ (Carballo)</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>5 000</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr"/>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>r5x6yql2</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>Bergantinos</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>fw2i3K6O</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>Marbella
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr"/>
+      <c r="N505" t="inlineStr"/>
+      <c r="O505" t="inlineStr"/>
+      <c r="P505" t="inlineStr"/>
+      <c r="Q505" t="inlineStr"/>
+      <c r="R505" t="inlineStr"/>
+      <c r="S505" t="inlineStr"/>
+      <c r="T505" t="inlineStr"/>
+      <c r="U505" t="inlineStr"/>
+      <c r="V505" t="inlineStr"/>
+      <c r="W505" t="inlineStr"/>
+      <c r="X505" t="inlineStr"/>
+      <c r="Y505" t="inlineStr"/>
+      <c r="Z505" t="inlineStr"/>
+      <c r="AA505" t="inlineStr"/>
+      <c r="AB505" t="inlineStr"/>
+      <c r="AC505" t="inlineStr"/>
+      <c r="AD505" t="inlineStr"/>
+      <c r="AE505" t="inlineStr"/>
+      <c r="AF505" t="inlineStr"/>
+      <c r="AG505" t="inlineStr"/>
+      <c r="AH505" t="inlineStr"/>
+      <c r="AI505" t="inlineStr"/>
+      <c r="AJ505" t="inlineStr"/>
+      <c r="AK505" t="inlineStr"/>
+      <c r="AL505" t="inlineStr"/>
+      <c r="AM505" t="inlineStr"/>
+      <c r="AN505" t="inlineStr"/>
+      <c r="AO505" t="inlineStr"/>
+      <c r="AP505" t="inlineStr"/>
+      <c r="AQ505" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR505" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS505" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT505" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU505" t="inlineStr"/>
+      <c r="AV505" t="inlineStr"/>
+      <c r="AW505" t="inlineStr"/>
+      <c r="AX505" t="inlineStr"/>
+      <c r="AY505" t="inlineStr"/>
+      <c r="AZ505" t="inlineStr"/>
+      <c r="BA505" t="inlineStr"/>
+      <c r="BB505" t="inlineStr"/>
+      <c r="BC505" t="inlineStr"/>
+      <c r="BD505" t="inlineStr"/>
+      <c r="BE505" t="inlineStr"/>
+      <c r="BF505" t="inlineStr"/>
+      <c r="BG505" t="inlineStr"/>
+      <c r="BH505" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="inlineStr">
+        <is>
+          <t>CODq2AS6</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>30.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr"/>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Estadio El Soto
+ (Mostoles)</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr"/>
+      <c r="F506" t="inlineStr"/>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>tvOLKCtq</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>CD Mostoles</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>Burgos CF
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M506" t="inlineStr"/>
+      <c r="N506" t="inlineStr"/>
+      <c r="O506" t="inlineStr"/>
+      <c r="P506" t="inlineStr"/>
+      <c r="Q506" t="inlineStr"/>
+      <c r="R506" t="inlineStr"/>
+      <c r="S506" t="inlineStr"/>
+      <c r="T506" t="inlineStr"/>
+      <c r="U506" t="inlineStr"/>
+      <c r="V506" t="inlineStr"/>
+      <c r="W506" t="inlineStr"/>
+      <c r="X506" t="inlineStr"/>
+      <c r="Y506" t="inlineStr"/>
+      <c r="Z506" t="inlineStr"/>
+      <c r="AA506" t="inlineStr"/>
+      <c r="AB506" t="inlineStr"/>
+      <c r="AC506" t="inlineStr"/>
+      <c r="AD506" t="inlineStr"/>
+      <c r="AE506" t="inlineStr"/>
+      <c r="AF506" t="inlineStr"/>
+      <c r="AG506" t="inlineStr"/>
+      <c r="AH506" t="inlineStr"/>
+      <c r="AI506" t="inlineStr"/>
+      <c r="AJ506" t="inlineStr"/>
+      <c r="AK506" t="inlineStr"/>
+      <c r="AL506" t="inlineStr"/>
+      <c r="AM506" t="inlineStr"/>
+      <c r="AN506" t="inlineStr"/>
+      <c r="AO506" t="inlineStr"/>
+      <c r="AP506" t="inlineStr"/>
+      <c r="AQ506" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR506" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS506" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT506" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU506" t="inlineStr"/>
+      <c r="AV506" t="inlineStr"/>
+      <c r="AW506" t="inlineStr"/>
+      <c r="AX506" t="inlineStr"/>
+      <c r="AY506" t="inlineStr"/>
+      <c r="AZ506" t="inlineStr"/>
+      <c r="BA506" t="inlineStr"/>
+      <c r="BB506" t="inlineStr"/>
+      <c r="BC506" t="inlineStr"/>
+      <c r="BD506" t="inlineStr"/>
+      <c r="BE506" t="inlineStr"/>
+      <c r="BF506" t="inlineStr"/>
+      <c r="BG506" t="inlineStr"/>
+      <c r="BH506" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>W6D6n7qJ</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>30.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr"/>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Estadio Ganzábal
+ (Langreo)</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr"/>
+      <c r="F507" t="inlineStr"/>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>4OH7ewrU</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>Langreo</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>0nDneDfl</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>Orihuela
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M507" t="inlineStr"/>
+      <c r="N507" t="inlineStr"/>
+      <c r="O507" t="inlineStr"/>
+      <c r="P507" t="inlineStr"/>
+      <c r="Q507" t="inlineStr"/>
+      <c r="R507" t="inlineStr"/>
+      <c r="S507" t="inlineStr"/>
+      <c r="T507" t="inlineStr"/>
+      <c r="U507" t="inlineStr"/>
+      <c r="V507" t="inlineStr"/>
+      <c r="W507" t="inlineStr"/>
+      <c r="X507" t="inlineStr"/>
+      <c r="Y507" t="inlineStr"/>
+      <c r="Z507" t="inlineStr"/>
+      <c r="AA507" t="inlineStr"/>
+      <c r="AB507" t="inlineStr"/>
+      <c r="AC507" t="inlineStr"/>
+      <c r="AD507" t="inlineStr"/>
+      <c r="AE507" t="inlineStr"/>
+      <c r="AF507" t="inlineStr"/>
+      <c r="AG507" t="inlineStr"/>
+      <c r="AH507" t="inlineStr"/>
+      <c r="AI507" t="inlineStr"/>
+      <c r="AJ507" t="inlineStr"/>
+      <c r="AK507" t="inlineStr"/>
+      <c r="AL507" t="inlineStr"/>
+      <c r="AM507" t="inlineStr"/>
+      <c r="AN507" t="inlineStr"/>
+      <c r="AO507" t="inlineStr"/>
+      <c r="AP507" t="inlineStr"/>
+      <c r="AQ507" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR507" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS507" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT507" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU507" t="inlineStr"/>
+      <c r="AV507" t="inlineStr"/>
+      <c r="AW507" t="inlineStr"/>
+      <c r="AX507" t="inlineStr"/>
+      <c r="AY507" t="inlineStr"/>
+      <c r="AZ507" t="inlineStr"/>
+      <c r="BA507" t="inlineStr"/>
+      <c r="BB507" t="inlineStr"/>
+      <c r="BC507" t="inlineStr"/>
+      <c r="BD507" t="inlineStr"/>
+      <c r="BE507" t="inlineStr"/>
+      <c r="BF507" t="inlineStr"/>
+      <c r="BG507" t="inlineStr"/>
+      <c r="BH507" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="inlineStr">
+        <is>
+          <t>xAwncOpA</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>30.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Nuevo Estadio Municipal
+ (Lucena)</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr"/>
+      <c r="F508" t="inlineStr"/>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>x6jWHUPa</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>Ciudad de Lucena</t>
+        </is>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>Leganes
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr"/>
+      <c r="N508" t="inlineStr"/>
+      <c r="O508" t="inlineStr"/>
+      <c r="P508" t="inlineStr"/>
+      <c r="Q508" t="inlineStr"/>
+      <c r="R508" t="inlineStr"/>
+      <c r="S508" t="inlineStr"/>
+      <c r="T508" t="inlineStr"/>
+      <c r="U508" t="inlineStr"/>
+      <c r="V508" t="inlineStr"/>
+      <c r="W508" t="inlineStr"/>
+      <c r="X508" t="inlineStr"/>
+      <c r="Y508" t="inlineStr"/>
+      <c r="Z508" t="inlineStr"/>
+      <c r="AA508" t="inlineStr"/>
+      <c r="AB508" t="inlineStr"/>
+      <c r="AC508" t="inlineStr"/>
+      <c r="AD508" t="inlineStr"/>
+      <c r="AE508" t="inlineStr"/>
+      <c r="AF508" t="inlineStr"/>
+      <c r="AG508" t="inlineStr"/>
+      <c r="AH508" t="inlineStr"/>
+      <c r="AI508" t="inlineStr"/>
+      <c r="AJ508" t="inlineStr"/>
+      <c r="AK508" t="inlineStr"/>
+      <c r="AL508" t="inlineStr"/>
+      <c r="AM508" t="inlineStr"/>
+      <c r="AN508" t="inlineStr"/>
+      <c r="AO508" t="inlineStr"/>
+      <c r="AP508" t="inlineStr"/>
+      <c r="AQ508" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR508" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS508" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT508" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU508" t="inlineStr"/>
+      <c r="AV508" t="inlineStr"/>
+      <c r="AW508" t="inlineStr"/>
+      <c r="AX508" t="inlineStr"/>
+      <c r="AY508" t="inlineStr"/>
+      <c r="AZ508" t="inlineStr"/>
+      <c r="BA508" t="inlineStr"/>
+      <c r="BB508" t="inlineStr"/>
+      <c r="BC508" t="inlineStr"/>
+      <c r="BD508" t="inlineStr"/>
+      <c r="BE508" t="inlineStr"/>
+      <c r="BF508" t="inlineStr"/>
+      <c r="BG508" t="inlineStr"/>
+      <c r="BH508" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="inlineStr">
+        <is>
+          <t>KY6Lt30T</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>30.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr"/>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Estadio Dehesa de Navalcarbon
+ (Las Rozas de Madrid)</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>3 000</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr"/>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>8QjqTbZI</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>Las Rozas</t>
+        </is>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>Sevilla
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr"/>
+      <c r="N509" t="inlineStr"/>
+      <c r="O509" t="inlineStr"/>
+      <c r="P509" t="inlineStr"/>
+      <c r="Q509" t="inlineStr"/>
+      <c r="R509" t="inlineStr"/>
+      <c r="S509" t="inlineStr"/>
+      <c r="T509" t="inlineStr"/>
+      <c r="U509" t="inlineStr"/>
+      <c r="V509" t="inlineStr"/>
+      <c r="W509" t="inlineStr"/>
+      <c r="X509" t="inlineStr"/>
+      <c r="Y509" t="inlineStr"/>
+      <c r="Z509" t="inlineStr"/>
+      <c r="AA509" t="inlineStr"/>
+      <c r="AB509" t="inlineStr"/>
+      <c r="AC509" t="inlineStr"/>
+      <c r="AD509" t="inlineStr"/>
+      <c r="AE509" t="inlineStr"/>
+      <c r="AF509" t="inlineStr"/>
+      <c r="AG509" t="inlineStr"/>
+      <c r="AH509" t="inlineStr"/>
+      <c r="AI509" t="inlineStr"/>
+      <c r="AJ509" t="inlineStr"/>
+      <c r="AK509" t="inlineStr"/>
+      <c r="AL509" t="inlineStr"/>
+      <c r="AM509" t="inlineStr"/>
+      <c r="AN509" t="inlineStr"/>
+      <c r="AO509" t="inlineStr"/>
+      <c r="AP509" t="inlineStr"/>
+      <c r="AQ509" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR509" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS509" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT509" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU509" t="inlineStr"/>
+      <c r="AV509" t="inlineStr"/>
+      <c r="AW509" t="inlineStr"/>
+      <c r="AX509" t="inlineStr"/>
+      <c r="AY509" t="inlineStr"/>
+      <c r="AZ509" t="inlineStr"/>
+      <c r="BA509" t="inlineStr"/>
+      <c r="BB509" t="inlineStr"/>
+      <c r="BC509" t="inlineStr"/>
+      <c r="BD509" t="inlineStr"/>
+      <c r="BE509" t="inlineStr"/>
+      <c r="BF509" t="inlineStr"/>
+      <c r="BG509" t="inlineStr"/>
+      <c r="BH509" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="inlineStr">
+        <is>
+          <t>WYTIG9s0</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>30.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr"/>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Estadi Municipal d'Olot
+ (Olot)</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>6 000</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr"/>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>rBb3kKjb</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+Olot</t>
+        </is>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>Cordoba</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr"/>
+      <c r="N510" t="inlineStr"/>
+      <c r="O510" t="inlineStr"/>
+      <c r="P510" t="inlineStr"/>
+      <c r="Q510" t="inlineStr"/>
+      <c r="R510" t="inlineStr"/>
+      <c r="S510" t="inlineStr"/>
+      <c r="T510" t="inlineStr"/>
+      <c r="U510" t="inlineStr"/>
+      <c r="V510" t="inlineStr"/>
+      <c r="W510" t="inlineStr"/>
+      <c r="X510" t="inlineStr"/>
+      <c r="Y510" t="inlineStr"/>
+      <c r="Z510" t="inlineStr"/>
+      <c r="AA510" t="inlineStr"/>
+      <c r="AB510" t="inlineStr"/>
+      <c r="AC510" t="inlineStr"/>
+      <c r="AD510" t="inlineStr"/>
+      <c r="AE510" t="inlineStr"/>
+      <c r="AF510" t="inlineStr"/>
+      <c r="AG510" t="inlineStr"/>
+      <c r="AH510" t="inlineStr"/>
+      <c r="AI510" t="inlineStr"/>
+      <c r="AJ510" t="inlineStr"/>
+      <c r="AK510" t="inlineStr"/>
+      <c r="AL510" t="inlineStr"/>
+      <c r="AM510" t="inlineStr"/>
+      <c r="AN510" t="inlineStr"/>
+      <c r="AO510" t="inlineStr"/>
+      <c r="AP510" t="inlineStr"/>
+      <c r="AQ510" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR510" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS510" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT510" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU510" t="inlineStr"/>
+      <c r="AV510" t="inlineStr"/>
+      <c r="AW510" t="inlineStr"/>
+      <c r="AX510" t="inlineStr"/>
+      <c r="AY510" t="inlineStr"/>
+      <c r="AZ510" t="inlineStr"/>
+      <c r="BA510" t="inlineStr"/>
+      <c r="BB510" t="inlineStr"/>
+      <c r="BC510" t="inlineStr"/>
+      <c r="BD510" t="inlineStr"/>
+      <c r="BE510" t="inlineStr"/>
+      <c r="BF510" t="inlineStr"/>
+      <c r="BG510" t="inlineStr"/>
+      <c r="BH510" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="inlineStr">
+        <is>
+          <t>O6gkNjG7</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>30.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Estadi Municipal de Can Misses
+ (Ibiza)</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>4 500</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr"/>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>zFFr9NXc</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>SD Ibiza</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>WSv960Hk</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>Gimnastic
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr"/>
+      <c r="N511" t="inlineStr"/>
+      <c r="O511" t="inlineStr"/>
+      <c r="P511" t="inlineStr"/>
+      <c r="Q511" t="inlineStr"/>
+      <c r="R511" t="inlineStr"/>
+      <c r="S511" t="inlineStr"/>
+      <c r="T511" t="inlineStr"/>
+      <c r="U511" t="inlineStr"/>
+      <c r="V511" t="inlineStr"/>
+      <c r="W511" t="inlineStr"/>
+      <c r="X511" t="inlineStr"/>
+      <c r="Y511" t="inlineStr"/>
+      <c r="Z511" t="inlineStr"/>
+      <c r="AA511" t="inlineStr"/>
+      <c r="AB511" t="inlineStr"/>
+      <c r="AC511" t="inlineStr"/>
+      <c r="AD511" t="inlineStr"/>
+      <c r="AE511" t="inlineStr"/>
+      <c r="AF511" t="inlineStr"/>
+      <c r="AG511" t="inlineStr"/>
+      <c r="AH511" t="inlineStr"/>
+      <c r="AI511" t="inlineStr"/>
+      <c r="AJ511" t="inlineStr"/>
+      <c r="AK511" t="inlineStr"/>
+      <c r="AL511" t="inlineStr"/>
+      <c r="AM511" t="inlineStr"/>
+      <c r="AN511" t="inlineStr"/>
+      <c r="AO511" t="inlineStr"/>
+      <c r="AP511" t="inlineStr"/>
+      <c r="AQ511" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR511" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS511" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT511" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU511" t="inlineStr"/>
+      <c r="AV511" t="inlineStr"/>
+      <c r="AW511" t="inlineStr"/>
+      <c r="AX511" t="inlineStr"/>
+      <c r="AY511" t="inlineStr"/>
+      <c r="AZ511" t="inlineStr"/>
+      <c r="BA511" t="inlineStr"/>
+      <c r="BB511" t="inlineStr"/>
+      <c r="BC511" t="inlineStr"/>
+      <c r="BD511" t="inlineStr"/>
+      <c r="BE511" t="inlineStr"/>
+      <c r="BF511" t="inlineStr"/>
+      <c r="BG511" t="inlineStr"/>
+      <c r="BH511" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="inlineStr">
+        <is>
+          <t>Yw2h0lcJ</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>30.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr"/>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Nou Sardenya Municipal Stadium
+ (Barcelona)</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr"/>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>UkEeaAlL</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>Advancing to next round
+CE Europa</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr"/>
+      <c r="N512" t="inlineStr"/>
+      <c r="O512" t="inlineStr"/>
+      <c r="P512" t="inlineStr"/>
+      <c r="Q512" t="inlineStr"/>
+      <c r="R512" t="inlineStr"/>
+      <c r="S512" t="inlineStr"/>
+      <c r="T512" t="inlineStr"/>
+      <c r="U512" t="inlineStr"/>
+      <c r="V512" t="inlineStr"/>
+      <c r="W512" t="inlineStr"/>
+      <c r="X512" t="inlineStr"/>
+      <c r="Y512" t="inlineStr"/>
+      <c r="Z512" t="inlineStr"/>
+      <c r="AA512" t="inlineStr"/>
+      <c r="AB512" t="inlineStr"/>
+      <c r="AC512" t="inlineStr"/>
+      <c r="AD512" t="inlineStr"/>
+      <c r="AE512" t="inlineStr"/>
+      <c r="AF512" t="inlineStr"/>
+      <c r="AG512" t="inlineStr"/>
+      <c r="AH512" t="inlineStr"/>
+      <c r="AI512" t="inlineStr"/>
+      <c r="AJ512" t="inlineStr"/>
+      <c r="AK512" t="inlineStr"/>
+      <c r="AL512" t="inlineStr"/>
+      <c r="AM512" t="inlineStr"/>
+      <c r="AN512" t="inlineStr"/>
+      <c r="AO512" t="inlineStr"/>
+      <c r="AP512" t="inlineStr"/>
+      <c r="AQ512" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR512" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS512" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT512" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU512" t="inlineStr"/>
+      <c r="AV512" t="inlineStr"/>
+      <c r="AW512" t="inlineStr"/>
+      <c r="AX512" t="inlineStr"/>
+      <c r="AY512" t="inlineStr"/>
+      <c r="AZ512" t="inlineStr"/>
+      <c r="BA512" t="inlineStr"/>
+      <c r="BB512" t="inlineStr"/>
+      <c r="BC512" t="inlineStr"/>
+      <c r="BD512" t="inlineStr"/>
+      <c r="BE512" t="inlineStr"/>
+      <c r="BF512" t="inlineStr"/>
+      <c r="BG512" t="inlineStr"/>
+      <c r="BH512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="inlineStr">
+        <is>
+          <t>Mu2KHeR0</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>29.10.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr"/>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Estadio Hermanos Llana
+ (Oviedo)</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr"/>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>dKlL6OBq</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>Astur</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>Valladolid
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr"/>
+      <c r="N513" t="inlineStr"/>
+      <c r="O513" t="inlineStr"/>
+      <c r="P513" t="inlineStr"/>
+      <c r="Q513" t="inlineStr"/>
+      <c r="R513" t="inlineStr"/>
+      <c r="S513" t="inlineStr"/>
+      <c r="T513" t="inlineStr"/>
+      <c r="U513" t="inlineStr"/>
+      <c r="V513" t="inlineStr"/>
+      <c r="W513" t="inlineStr"/>
+      <c r="X513" t="inlineStr"/>
+      <c r="Y513" t="inlineStr"/>
+      <c r="Z513" t="inlineStr"/>
+      <c r="AA513" t="inlineStr"/>
+      <c r="AB513" t="inlineStr"/>
+      <c r="AC513" t="inlineStr"/>
+      <c r="AD513" t="inlineStr"/>
+      <c r="AE513" t="inlineStr"/>
+      <c r="AF513" t="inlineStr"/>
+      <c r="AG513" t="inlineStr"/>
+      <c r="AH513" t="inlineStr"/>
+      <c r="AI513" t="inlineStr"/>
+      <c r="AJ513" t="inlineStr"/>
+      <c r="AK513" t="inlineStr"/>
+      <c r="AL513" t="inlineStr"/>
+      <c r="AM513" t="inlineStr"/>
+      <c r="AN513" t="inlineStr"/>
+      <c r="AO513" t="inlineStr"/>
+      <c r="AP513" t="inlineStr"/>
+      <c r="AQ513" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR513" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS513" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT513" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU513" t="inlineStr"/>
+      <c r="AV513" t="inlineStr"/>
+      <c r="AW513" t="inlineStr"/>
+      <c r="AX513" t="inlineStr"/>
+      <c r="AY513" t="inlineStr"/>
+      <c r="AZ513" t="inlineStr"/>
+      <c r="BA513" t="inlineStr"/>
+      <c r="BB513" t="inlineStr"/>
+      <c r="BC513" t="inlineStr"/>
+      <c r="BD513" t="inlineStr"/>
+      <c r="BE513" t="inlineStr"/>
+      <c r="BF513" t="inlineStr"/>
+      <c r="BG513" t="inlineStr"/>
+      <c r="BH513" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="inlineStr">
+        <is>
+          <t>OtUL91UF</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>29.10.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr"/>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Nuevo Estadio de La Victoria
+ (Jaén)</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>12 569</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr"/>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>zssYlsNI</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>Jaen</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>Cadiz CF
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr"/>
+      <c r="N514" t="inlineStr"/>
+      <c r="O514" t="inlineStr"/>
+      <c r="P514" t="inlineStr"/>
+      <c r="Q514" t="inlineStr"/>
+      <c r="R514" t="inlineStr"/>
+      <c r="S514" t="inlineStr"/>
+      <c r="T514" t="inlineStr"/>
+      <c r="U514" t="inlineStr"/>
+      <c r="V514" t="inlineStr"/>
+      <c r="W514" t="inlineStr"/>
+      <c r="X514" t="inlineStr"/>
+      <c r="Y514" t="inlineStr"/>
+      <c r="Z514" t="inlineStr"/>
+      <c r="AA514" t="inlineStr"/>
+      <c r="AB514" t="inlineStr"/>
+      <c r="AC514" t="inlineStr"/>
+      <c r="AD514" t="inlineStr"/>
+      <c r="AE514" t="inlineStr"/>
+      <c r="AF514" t="inlineStr"/>
+      <c r="AG514" t="inlineStr"/>
+      <c r="AH514" t="inlineStr"/>
+      <c r="AI514" t="inlineStr"/>
+      <c r="AJ514" t="inlineStr"/>
+      <c r="AK514" t="inlineStr"/>
+      <c r="AL514" t="inlineStr"/>
+      <c r="AM514" t="inlineStr"/>
+      <c r="AN514" t="inlineStr"/>
+      <c r="AO514" t="inlineStr"/>
+      <c r="AP514" t="inlineStr"/>
+      <c r="AQ514" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR514" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS514" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT514" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU514" t="inlineStr"/>
+      <c r="AV514" t="inlineStr"/>
+      <c r="AW514" t="inlineStr"/>
+      <c r="AX514" t="inlineStr"/>
+      <c r="AY514" t="inlineStr"/>
+      <c r="AZ514" t="inlineStr"/>
+      <c r="BA514" t="inlineStr"/>
+      <c r="BB514" t="inlineStr"/>
+      <c r="BC514" t="inlineStr"/>
+      <c r="BD514" t="inlineStr"/>
+      <c r="BE514" t="inlineStr"/>
+      <c r="BF514" t="inlineStr"/>
+      <c r="BG514" t="inlineStr"/>
+      <c r="BH514" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="inlineStr">
+        <is>
+          <t>UudgigEl</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>29.10.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr"/>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Estadi La Feixa Llarga
+ (L'Hospitalet)</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>2 500</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr"/>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>SGHHewxm</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>L Hospitalet</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>Zaragoza
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr"/>
+      <c r="N515" t="inlineStr"/>
+      <c r="O515" t="inlineStr"/>
+      <c r="P515" t="inlineStr"/>
+      <c r="Q515" t="inlineStr"/>
+      <c r="R515" t="inlineStr"/>
+      <c r="S515" t="inlineStr"/>
+      <c r="T515" t="inlineStr"/>
+      <c r="U515" t="inlineStr"/>
+      <c r="V515" t="inlineStr"/>
+      <c r="W515" t="inlineStr"/>
+      <c r="X515" t="inlineStr"/>
+      <c r="Y515" t="inlineStr"/>
+      <c r="Z515" t="inlineStr"/>
+      <c r="AA515" t="inlineStr"/>
+      <c r="AB515" t="inlineStr"/>
+      <c r="AC515" t="inlineStr"/>
+      <c r="AD515" t="inlineStr"/>
+      <c r="AE515" t="inlineStr"/>
+      <c r="AF515" t="inlineStr"/>
+      <c r="AG515" t="inlineStr"/>
+      <c r="AH515" t="inlineStr"/>
+      <c r="AI515" t="inlineStr"/>
+      <c r="AJ515" t="inlineStr"/>
+      <c r="AK515" t="inlineStr"/>
+      <c r="AL515" t="inlineStr"/>
+      <c r="AM515" t="inlineStr"/>
+      <c r="AN515" t="inlineStr"/>
+      <c r="AO515" t="inlineStr"/>
+      <c r="AP515" t="inlineStr"/>
+      <c r="AQ515" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR515" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS515" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT515" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU515" t="inlineStr"/>
+      <c r="AV515" t="inlineStr"/>
+      <c r="AW515" t="inlineStr"/>
+      <c r="AX515" t="inlineStr"/>
+      <c r="AY515" t="inlineStr"/>
+      <c r="AZ515" t="inlineStr"/>
+      <c r="BA515" t="inlineStr"/>
+      <c r="BB515" t="inlineStr"/>
+      <c r="BC515" t="inlineStr"/>
+      <c r="BD515" t="inlineStr"/>
+      <c r="BE515" t="inlineStr"/>
+      <c r="BF515" t="inlineStr"/>
+      <c r="BG515" t="inlineStr"/>
+      <c r="BH515" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="inlineStr">
+        <is>
+          <t>ITbLBNa3</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>29.10.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr"/>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Ciudad Deportiva de Lanzarote
+ (Arrecife)</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>7 000</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr"/>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>YLYYrUoE</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>Lanzarote</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>Racing Santander
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr"/>
+      <c r="N516" t="inlineStr"/>
+      <c r="O516" t="inlineStr"/>
+      <c r="P516" t="inlineStr"/>
+      <c r="Q516" t="inlineStr"/>
+      <c r="R516" t="inlineStr"/>
+      <c r="S516" t="inlineStr"/>
+      <c r="T516" t="inlineStr"/>
+      <c r="U516" t="inlineStr"/>
+      <c r="V516" t="inlineStr"/>
+      <c r="W516" t="inlineStr"/>
+      <c r="X516" t="inlineStr"/>
+      <c r="Y516" t="inlineStr"/>
+      <c r="Z516" t="inlineStr"/>
+      <c r="AA516" t="inlineStr"/>
+      <c r="AB516" t="inlineStr"/>
+      <c r="AC516" t="inlineStr"/>
+      <c r="AD516" t="inlineStr"/>
+      <c r="AE516" t="inlineStr"/>
+      <c r="AF516" t="inlineStr"/>
+      <c r="AG516" t="inlineStr"/>
+      <c r="AH516" t="inlineStr"/>
+      <c r="AI516" t="inlineStr"/>
+      <c r="AJ516" t="inlineStr"/>
+      <c r="AK516" t="inlineStr"/>
+      <c r="AL516" t="inlineStr"/>
+      <c r="AM516" t="inlineStr"/>
+      <c r="AN516" t="inlineStr"/>
+      <c r="AO516" t="inlineStr"/>
+      <c r="AP516" t="inlineStr"/>
+      <c r="AQ516" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR516" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS516" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT516" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU516" t="inlineStr"/>
+      <c r="AV516" t="inlineStr"/>
+      <c r="AW516" t="inlineStr"/>
+      <c r="AX516" t="inlineStr"/>
+      <c r="AY516" t="inlineStr"/>
+      <c r="AZ516" t="inlineStr"/>
+      <c r="BA516" t="inlineStr"/>
+      <c r="BB516" t="inlineStr"/>
+      <c r="BC516" t="inlineStr"/>
+      <c r="BD516" t="inlineStr"/>
+      <c r="BE516" t="inlineStr"/>
+      <c r="BF516" t="inlineStr"/>
+      <c r="BG516" t="inlineStr"/>
+      <c r="BH516" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="inlineStr">
+        <is>
+          <t>xjF4po14</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>29.10.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr"/>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Nou Camp de Sa Pobla
+ (Sa Pobla)</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr"/>
+      <c r="F517" t="inlineStr"/>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>EZFEeKEC</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>Poblense</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>Villarreal
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr"/>
+      <c r="N517" t="inlineStr"/>
+      <c r="O517" t="inlineStr"/>
+      <c r="P517" t="inlineStr"/>
+      <c r="Q517" t="inlineStr"/>
+      <c r="R517" t="inlineStr"/>
+      <c r="S517" t="inlineStr"/>
+      <c r="T517" t="inlineStr"/>
+      <c r="U517" t="inlineStr"/>
+      <c r="V517" t="inlineStr"/>
+      <c r="W517" t="inlineStr"/>
+      <c r="X517" t="inlineStr"/>
+      <c r="Y517" t="inlineStr"/>
+      <c r="Z517" t="inlineStr"/>
+      <c r="AA517" t="inlineStr"/>
+      <c r="AB517" t="inlineStr"/>
+      <c r="AC517" t="inlineStr"/>
+      <c r="AD517" t="inlineStr"/>
+      <c r="AE517" t="inlineStr"/>
+      <c r="AF517" t="inlineStr"/>
+      <c r="AG517" t="inlineStr"/>
+      <c r="AH517" t="inlineStr"/>
+      <c r="AI517" t="inlineStr"/>
+      <c r="AJ517" t="inlineStr"/>
+      <c r="AK517" t="inlineStr"/>
+      <c r="AL517" t="inlineStr"/>
+      <c r="AM517" t="inlineStr"/>
+      <c r="AN517" t="inlineStr"/>
+      <c r="AO517" t="inlineStr"/>
+      <c r="AP517" t="inlineStr"/>
+      <c r="AQ517" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR517" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS517" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT517" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU517" t="inlineStr"/>
+      <c r="AV517" t="inlineStr"/>
+      <c r="AW517" t="inlineStr"/>
+      <c r="AX517" t="inlineStr"/>
+      <c r="AY517" t="inlineStr"/>
+      <c r="AZ517" t="inlineStr"/>
+      <c r="BA517" t="inlineStr"/>
+      <c r="BB517" t="inlineStr"/>
+      <c r="BC517" t="inlineStr"/>
+      <c r="BD517" t="inlineStr"/>
+      <c r="BE517" t="inlineStr"/>
+      <c r="BF517" t="inlineStr"/>
+      <c r="BG517" t="inlineStr"/>
+      <c r="BH517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>f1IshBFs</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr"/>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Guijuelo
+ (Guijuelo)</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>2 000</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr"/>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>Ei0mGd4p</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>Guijuelo</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>M9KnSe0f</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>Ourense CF
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr"/>
+      <c r="N518" t="inlineStr"/>
+      <c r="O518" t="inlineStr"/>
+      <c r="P518" t="inlineStr"/>
+      <c r="Q518" t="inlineStr"/>
+      <c r="R518" t="inlineStr"/>
+      <c r="S518" t="inlineStr"/>
+      <c r="T518" t="inlineStr"/>
+      <c r="U518" t="inlineStr"/>
+      <c r="V518" t="inlineStr"/>
+      <c r="W518" t="inlineStr"/>
+      <c r="X518" t="inlineStr"/>
+      <c r="Y518" t="inlineStr"/>
+      <c r="Z518" t="inlineStr"/>
+      <c r="AA518" t="inlineStr"/>
+      <c r="AB518" t="inlineStr"/>
+      <c r="AC518" t="inlineStr"/>
+      <c r="AD518" t="inlineStr"/>
+      <c r="AE518" t="inlineStr"/>
+      <c r="AF518" t="inlineStr"/>
+      <c r="AG518" t="inlineStr"/>
+      <c r="AH518" t="inlineStr"/>
+      <c r="AI518" t="inlineStr"/>
+      <c r="AJ518" t="inlineStr"/>
+      <c r="AK518" t="inlineStr"/>
+      <c r="AL518" t="inlineStr"/>
+      <c r="AM518" t="inlineStr"/>
+      <c r="AN518" t="inlineStr"/>
+      <c r="AO518" t="inlineStr"/>
+      <c r="AP518" t="inlineStr"/>
+      <c r="AQ518" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR518" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS518" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT518" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU518" t="inlineStr"/>
+      <c r="AV518" t="inlineStr"/>
+      <c r="AW518" t="inlineStr"/>
+      <c r="AX518" t="inlineStr"/>
+      <c r="AY518" t="inlineStr"/>
+      <c r="AZ518" t="inlineStr"/>
+      <c r="BA518" t="inlineStr"/>
+      <c r="BB518" t="inlineStr"/>
+      <c r="BC518" t="inlineStr"/>
+      <c r="BD518" t="inlineStr"/>
+      <c r="BE518" t="inlineStr"/>
+      <c r="BF518" t="inlineStr"/>
+      <c r="BG518" t="inlineStr"/>
+      <c r="BH518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="inlineStr">
+        <is>
+          <t>8drFZTnn</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>29.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Municipal Rafael Vázquez Sedano
+ (Villamuriel de Cerrato)</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr"/>
+      <c r="F519" t="inlineStr"/>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>vBEEUw07</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>CD Villamuriel</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr"/>
+      <c r="N519" t="inlineStr"/>
+      <c r="O519" t="inlineStr"/>
+      <c r="P519" t="inlineStr"/>
+      <c r="Q519" t="inlineStr"/>
+      <c r="R519" t="inlineStr"/>
+      <c r="S519" t="inlineStr"/>
+      <c r="T519" t="inlineStr"/>
+      <c r="U519" t="inlineStr"/>
+      <c r="V519" t="inlineStr"/>
+      <c r="W519" t="inlineStr"/>
+      <c r="X519" t="inlineStr"/>
+      <c r="Y519" t="inlineStr"/>
+      <c r="Z519" t="inlineStr"/>
+      <c r="AA519" t="inlineStr"/>
+      <c r="AB519" t="inlineStr"/>
+      <c r="AC519" t="inlineStr"/>
+      <c r="AD519" t="inlineStr"/>
+      <c r="AE519" t="inlineStr"/>
+      <c r="AF519" t="inlineStr"/>
+      <c r="AG519" t="inlineStr"/>
+      <c r="AH519" t="inlineStr"/>
+      <c r="AI519" t="inlineStr"/>
+      <c r="AJ519" t="inlineStr"/>
+      <c r="AK519" t="inlineStr"/>
+      <c r="AL519" t="inlineStr"/>
+      <c r="AM519" t="inlineStr"/>
+      <c r="AN519" t="inlineStr"/>
+      <c r="AO519" t="inlineStr"/>
+      <c r="AP519" t="inlineStr"/>
+      <c r="AQ519" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR519" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS519" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT519" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU519" t="inlineStr"/>
+      <c r="AV519" t="inlineStr"/>
+      <c r="AW519" t="inlineStr"/>
+      <c r="AX519" t="inlineStr"/>
+      <c r="AY519" t="inlineStr"/>
+      <c r="AZ519" t="inlineStr"/>
+      <c r="BA519" t="inlineStr"/>
+      <c r="BB519" t="inlineStr"/>
+      <c r="BC519" t="inlineStr"/>
+      <c r="BD519" t="inlineStr"/>
+      <c r="BE519" t="inlineStr"/>
+      <c r="BF519" t="inlineStr"/>
+      <c r="BG519" t="inlineStr"/>
+      <c r="BH519" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="inlineStr">
+        <is>
+          <t>O6DCrPVG</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>29.10.2024 15:00</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr"/>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Estadio Vero Boquete de San Lázaro
+ (Santiago de Compostela)</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr"/>
+      <c r="F520" t="inlineStr"/>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>raYBFLs1</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>Compostela</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>Alaves
+Advancing to next round</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr"/>
+      <c r="N520" t="inlineStr"/>
+      <c r="O520" t="inlineStr"/>
+      <c r="P520" t="inlineStr"/>
+      <c r="Q520" t="inlineStr"/>
+      <c r="R520" t="inlineStr"/>
+      <c r="S520" t="inlineStr"/>
+      <c r="T520" t="inlineStr"/>
+      <c r="U520" t="inlineStr"/>
+      <c r="V520" t="inlineStr"/>
+      <c r="W520" t="inlineStr"/>
+      <c r="X520" t="inlineStr"/>
+      <c r="Y520" t="inlineStr"/>
+      <c r="Z520" t="inlineStr"/>
+      <c r="AA520" t="inlineStr"/>
+      <c r="AB520" t="inlineStr"/>
+      <c r="AC520" t="inlineStr"/>
+      <c r="AD520" t="inlineStr"/>
+      <c r="AE520" t="inlineStr"/>
+      <c r="AF520" t="inlineStr"/>
+      <c r="AG520" t="inlineStr"/>
+      <c r="AH520" t="inlineStr"/>
+      <c r="AI520" t="inlineStr"/>
+      <c r="AJ520" t="inlineStr"/>
+      <c r="AK520" t="inlineStr"/>
+      <c r="AL520" t="inlineStr"/>
+      <c r="AM520" t="inlineStr"/>
+      <c r="AN520" t="inlineStr"/>
+      <c r="AO520" t="inlineStr"/>
+      <c r="AP520" t="inlineStr"/>
+      <c r="AQ520" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR520" t="n">
+        <v>1483</v>
+      </c>
+      <c r="AS520" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT520" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU520" t="inlineStr"/>
+      <c r="AV520" t="inlineStr"/>
+      <c r="AW520" t="inlineStr"/>
+      <c r="AX520" t="inlineStr"/>
+      <c r="AY520" t="inlineStr"/>
+      <c r="AZ520" t="inlineStr"/>
+      <c r="BA520" t="inlineStr"/>
+      <c r="BB520" t="inlineStr"/>
+      <c r="BC520" t="inlineStr"/>
+      <c r="BD520" t="inlineStr"/>
+      <c r="BE520" t="inlineStr"/>
+      <c r="BF520" t="inlineStr"/>
+      <c r="BG520" t="inlineStr"/>
+      <c r="BH520" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/all/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH520"/>
+  <dimension ref="A1:BH535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92045,15 +92045,11 @@
         </is>
       </c>
       <c r="F473" t="inlineStr"/>
-      <c r="G473" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H473" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G473" t="n">
+        <v>0</v>
+      </c>
+      <c r="H473" t="n">
+        <v>2</v>
       </c>
       <c r="I473" t="inlineStr">
         <is>
@@ -92159,15 +92155,11 @@
         </is>
       </c>
       <c r="F474" t="inlineStr"/>
-      <c r="G474" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H474" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G474" t="n">
+        <v>3</v>
+      </c>
+      <c r="H474" t="n">
+        <v>2</v>
       </c>
       <c r="I474" t="inlineStr">
         <is>
@@ -92269,15 +92261,11 @@
       </c>
       <c r="E475" t="inlineStr"/>
       <c r="F475" t="inlineStr"/>
-      <c r="G475" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H475" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G475" t="n">
+        <v>1</v>
+      </c>
+      <c r="H475" t="n">
+        <v>3</v>
       </c>
       <c r="I475" t="inlineStr">
         <is>
@@ -92383,15 +92371,11 @@
         </is>
       </c>
       <c r="F476" t="inlineStr"/>
-      <c r="G476" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H476" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="G476" t="n">
+        <v>1</v>
+      </c>
+      <c r="H476" t="n">
+        <v>6</v>
       </c>
       <c r="I476" t="inlineStr">
         <is>
@@ -92497,15 +92481,11 @@
         </is>
       </c>
       <c r="F477" t="inlineStr"/>
-      <c r="G477" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H477" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G477" t="n">
+        <v>0</v>
+      </c>
+      <c r="H477" t="n">
+        <v>2</v>
       </c>
       <c r="I477" t="inlineStr">
         <is>
@@ -92607,15 +92587,11 @@
       </c>
       <c r="E478" t="inlineStr"/>
       <c r="F478" t="inlineStr"/>
-      <c r="G478" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H478" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="G478" t="n">
+        <v>0</v>
+      </c>
+      <c r="H478" t="n">
+        <v>7</v>
       </c>
       <c r="I478" t="inlineStr">
         <is>
@@ -92721,15 +92697,11 @@
         </is>
       </c>
       <c r="F479" t="inlineStr"/>
-      <c r="G479" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H479" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G479" t="n">
+        <v>1</v>
+      </c>
+      <c r="H479" t="n">
+        <v>2</v>
       </c>
       <c r="I479" t="inlineStr">
         <is>
@@ -92835,15 +92807,11 @@
         </is>
       </c>
       <c r="F480" t="inlineStr"/>
-      <c r="G480" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H480" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G480" t="n">
+        <v>1</v>
+      </c>
+      <c r="H480" t="n">
+        <v>0</v>
       </c>
       <c r="I480" t="inlineStr">
         <is>
@@ -92949,15 +92917,11 @@
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
-      <c r="G481" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H481" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="G481" t="n">
+        <v>0</v>
+      </c>
+      <c r="H481" t="n">
+        <v>5</v>
       </c>
       <c r="I481" t="inlineStr">
         <is>
@@ -93059,15 +93023,11 @@
       </c>
       <c r="E482" t="inlineStr"/>
       <c r="F482" t="inlineStr"/>
-      <c r="G482" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H482" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G482" t="n">
+        <v>4</v>
+      </c>
+      <c r="H482" t="n">
+        <v>0</v>
       </c>
       <c r="I482" t="inlineStr">
         <is>
@@ -93169,15 +93129,11 @@
       </c>
       <c r="E483" t="inlineStr"/>
       <c r="F483" t="inlineStr"/>
-      <c r="G483" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H483" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G483" t="n">
+        <v>0</v>
+      </c>
+      <c r="H483" t="n">
+        <v>4</v>
       </c>
       <c r="I483" t="inlineStr">
         <is>
@@ -93279,15 +93235,11 @@
       </c>
       <c r="E484" t="inlineStr"/>
       <c r="F484" t="inlineStr"/>
-      <c r="G484" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H484" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G484" t="n">
+        <v>0</v>
+      </c>
+      <c r="H484" t="n">
+        <v>2</v>
       </c>
       <c r="I484" t="inlineStr">
         <is>
@@ -93389,15 +93341,11 @@
       </c>
       <c r="E485" t="inlineStr"/>
       <c r="F485" t="inlineStr"/>
-      <c r="G485" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H485" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G485" t="n">
+        <v>0</v>
+      </c>
+      <c r="H485" t="n">
+        <v>1</v>
       </c>
       <c r="I485" t="inlineStr">
         <is>
@@ -93503,15 +93451,11 @@
         </is>
       </c>
       <c r="F486" t="inlineStr"/>
-      <c r="G486" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H486" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G486" t="n">
+        <v>0</v>
+      </c>
+      <c r="H486" t="n">
+        <v>1</v>
       </c>
       <c r="I486" t="inlineStr">
         <is>
@@ -93617,15 +93561,11 @@
         </is>
       </c>
       <c r="F487" t="inlineStr"/>
-      <c r="G487" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H487" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G487" t="n">
+        <v>0</v>
+      </c>
+      <c r="H487" t="n">
+        <v>4</v>
       </c>
       <c r="I487" t="inlineStr">
         <is>
@@ -93731,15 +93671,11 @@
         </is>
       </c>
       <c r="F488" t="inlineStr"/>
-      <c r="G488" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H488" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G488" t="n">
+        <v>1</v>
+      </c>
+      <c r="H488" t="n">
+        <v>2</v>
       </c>
       <c r="I488" t="inlineStr">
         <is>
@@ -93845,15 +93781,11 @@
         </is>
       </c>
       <c r="F489" t="inlineStr"/>
-      <c r="G489" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H489" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="G489" t="n">
+        <v>1</v>
+      </c>
+      <c r="H489" t="n">
+        <v>5</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -93959,15 +93891,11 @@
         </is>
       </c>
       <c r="F490" t="inlineStr"/>
-      <c r="G490" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H490" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G490" t="n">
+        <v>2</v>
+      </c>
+      <c r="H490" t="n">
+        <v>1</v>
       </c>
       <c r="I490" t="inlineStr">
         <is>
@@ -94073,15 +94001,11 @@
         </is>
       </c>
       <c r="F491" t="inlineStr"/>
-      <c r="G491" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H491" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G491" t="n">
+        <v>0</v>
+      </c>
+      <c r="H491" t="n">
+        <v>3</v>
       </c>
       <c r="I491" t="inlineStr">
         <is>
@@ -94183,15 +94107,11 @@
       </c>
       <c r="E492" t="inlineStr"/>
       <c r="F492" t="inlineStr"/>
-      <c r="G492" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H492" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G492" t="n">
+        <v>1</v>
+      </c>
+      <c r="H492" t="n">
+        <v>0</v>
       </c>
       <c r="I492" t="inlineStr">
         <is>
@@ -94297,15 +94217,11 @@
         </is>
       </c>
       <c r="F493" t="inlineStr"/>
-      <c r="G493" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H493" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G493" t="n">
+        <v>0</v>
+      </c>
+      <c r="H493" t="n">
+        <v>2</v>
       </c>
       <c r="I493" t="inlineStr">
         <is>
@@ -94411,15 +94327,11 @@
         </is>
       </c>
       <c r="F494" t="inlineStr"/>
-      <c r="G494" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H494" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G494" t="n">
+        <v>0</v>
+      </c>
+      <c r="H494" t="n">
+        <v>2</v>
       </c>
       <c r="I494" t="inlineStr">
         <is>
@@ -94525,15 +94437,11 @@
         </is>
       </c>
       <c r="F495" t="inlineStr"/>
-      <c r="G495" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H495" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G495" t="n">
+        <v>0</v>
+      </c>
+      <c r="H495" t="n">
+        <v>1</v>
       </c>
       <c r="I495" t="inlineStr">
         <is>
@@ -94635,15 +94543,11 @@
       </c>
       <c r="E496" t="inlineStr"/>
       <c r="F496" t="inlineStr"/>
-      <c r="G496" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H496" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="G496" t="n">
+        <v>0</v>
+      </c>
+      <c r="H496" t="n">
+        <v>6</v>
       </c>
       <c r="I496" t="inlineStr">
         <is>
@@ -94749,15 +94653,11 @@
         </is>
       </c>
       <c r="F497" t="inlineStr"/>
-      <c r="G497" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H497" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G497" t="n">
+        <v>1</v>
+      </c>
+      <c r="H497" t="n">
+        <v>3</v>
       </c>
       <c r="I497" t="inlineStr">
         <is>
@@ -94863,15 +94763,11 @@
         </is>
       </c>
       <c r="F498" t="inlineStr"/>
-      <c r="G498" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H498" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G498" t="n">
+        <v>0</v>
+      </c>
+      <c r="H498" t="n">
+        <v>1</v>
       </c>
       <c r="I498" t="inlineStr">
         <is>
@@ -94977,15 +94873,11 @@
         </is>
       </c>
       <c r="F499" t="inlineStr"/>
-      <c r="G499" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H499" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G499" t="n">
+        <v>1</v>
+      </c>
+      <c r="H499" t="n">
+        <v>0</v>
       </c>
       <c r="I499" t="inlineStr">
         <is>
@@ -95091,15 +94983,11 @@
         </is>
       </c>
       <c r="F500" t="inlineStr"/>
-      <c r="G500" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H500" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G500" t="n">
+        <v>2</v>
+      </c>
+      <c r="H500" t="n">
+        <v>1</v>
       </c>
       <c r="I500" t="inlineStr">
         <is>
@@ -95201,15 +95089,11 @@
       </c>
       <c r="E501" t="inlineStr"/>
       <c r="F501" t="inlineStr"/>
-      <c r="G501" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H501" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G501" t="n">
+        <v>1</v>
+      </c>
+      <c r="H501" t="n">
+        <v>2</v>
       </c>
       <c r="I501" t="inlineStr">
         <is>
@@ -95315,15 +95199,11 @@
         </is>
       </c>
       <c r="F502" t="inlineStr"/>
-      <c r="G502" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H502" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G502" t="n">
+        <v>1</v>
+      </c>
+      <c r="H502" t="n">
+        <v>0</v>
       </c>
       <c r="I502" t="inlineStr">
         <is>
@@ -95425,15 +95305,11 @@
       </c>
       <c r="E503" t="inlineStr"/>
       <c r="F503" t="inlineStr"/>
-      <c r="G503" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H503" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G503" t="n">
+        <v>0</v>
+      </c>
+      <c r="H503" t="n">
+        <v>4</v>
       </c>
       <c r="I503" t="inlineStr">
         <is>
@@ -95535,15 +95411,11 @@
       </c>
       <c r="E504" t="inlineStr"/>
       <c r="F504" t="inlineStr"/>
-      <c r="G504" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H504" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G504" t="n">
+        <v>0</v>
+      </c>
+      <c r="H504" t="n">
+        <v>1</v>
       </c>
       <c r="I504" t="inlineStr">
         <is>
@@ -95649,15 +95521,11 @@
         </is>
       </c>
       <c r="F505" t="inlineStr"/>
-      <c r="G505" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H505" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G505" t="n">
+        <v>1</v>
+      </c>
+      <c r="H505" t="n">
+        <v>2</v>
       </c>
       <c r="I505" t="inlineStr">
         <is>
@@ -95759,15 +95627,11 @@
       </c>
       <c r="E506" t="inlineStr"/>
       <c r="F506" t="inlineStr"/>
-      <c r="G506" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H506" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="G506" t="n">
+        <v>2</v>
+      </c>
+      <c r="H506" t="n">
+        <v>5</v>
       </c>
       <c r="I506" t="inlineStr">
         <is>
@@ -95869,15 +95733,11 @@
       </c>
       <c r="E507" t="inlineStr"/>
       <c r="F507" t="inlineStr"/>
-      <c r="G507" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H507" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G507" t="n">
+        <v>1</v>
+      </c>
+      <c r="H507" t="n">
+        <v>2</v>
       </c>
       <c r="I507" t="inlineStr">
         <is>
@@ -95979,15 +95839,11 @@
       </c>
       <c r="E508" t="inlineStr"/>
       <c r="F508" t="inlineStr"/>
-      <c r="G508" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H508" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G508" t="n">
+        <v>1</v>
+      </c>
+      <c r="H508" t="n">
+        <v>2</v>
       </c>
       <c r="I508" t="inlineStr">
         <is>
@@ -96093,15 +95949,11 @@
         </is>
       </c>
       <c r="F509" t="inlineStr"/>
-      <c r="G509" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H509" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G509" t="n">
+        <v>0</v>
+      </c>
+      <c r="H509" t="n">
+        <v>3</v>
       </c>
       <c r="I509" t="inlineStr">
         <is>
@@ -96207,15 +96059,11 @@
         </is>
       </c>
       <c r="F510" t="inlineStr"/>
-      <c r="G510" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H510" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G510" t="n">
+        <v>2</v>
+      </c>
+      <c r="H510" t="n">
+        <v>1</v>
       </c>
       <c r="I510" t="inlineStr">
         <is>
@@ -96321,15 +96169,11 @@
         </is>
       </c>
       <c r="F511" t="inlineStr"/>
-      <c r="G511" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H511" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G511" t="n">
+        <v>1</v>
+      </c>
+      <c r="H511" t="n">
+        <v>2</v>
       </c>
       <c r="I511" t="inlineStr">
         <is>
@@ -96435,15 +96279,11 @@
         </is>
       </c>
       <c r="F512" t="inlineStr"/>
-      <c r="G512" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H512" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G512" t="n">
+        <v>2</v>
+      </c>
+      <c r="H512" t="n">
+        <v>1</v>
       </c>
       <c r="I512" t="inlineStr">
         <is>
@@ -96549,15 +96389,11 @@
         </is>
       </c>
       <c r="F513" t="inlineStr"/>
-      <c r="G513" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H513" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G513" t="n">
+        <v>1</v>
+      </c>
+      <c r="H513" t="n">
+        <v>4</v>
       </c>
       <c r="I513" t="inlineStr">
         <is>
@@ -96663,15 +96499,11 @@
         </is>
       </c>
       <c r="F514" t="inlineStr"/>
-      <c r="G514" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H514" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="G514" t="n">
+        <v>0</v>
+      </c>
+      <c r="H514" t="n">
+        <v>3</v>
       </c>
       <c r="I514" t="inlineStr">
         <is>
@@ -96777,15 +96609,11 @@
         </is>
       </c>
       <c r="F515" t="inlineStr"/>
-      <c r="G515" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H515" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="G515" t="n">
+        <v>1</v>
+      </c>
+      <c r="H515" t="n">
+        <v>5</v>
       </c>
       <c r="I515" t="inlineStr">
         <is>
@@ -96891,15 +96719,11 @@
         </is>
       </c>
       <c r="F516" t="inlineStr"/>
-      <c r="G516" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H516" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="G516" t="n">
+        <v>3</v>
+      </c>
+      <c r="H516" t="n">
+        <v>4</v>
       </c>
       <c r="I516" t="inlineStr">
         <is>
@@ -97001,15 +96825,11 @@
       </c>
       <c r="E517" t="inlineStr"/>
       <c r="F517" t="inlineStr"/>
-      <c r="G517" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H517" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="G517" t="n">
+        <v>1</v>
+      </c>
+      <c r="H517" t="n">
+        <v>6</v>
       </c>
       <c r="I517" t="inlineStr">
         <is>
@@ -97115,15 +96935,11 @@
         </is>
       </c>
       <c r="F518" t="inlineStr"/>
-      <c r="G518" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H518" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="G518" t="n">
+        <v>1</v>
+      </c>
+      <c r="H518" t="n">
+        <v>2</v>
       </c>
       <c r="I518" t="inlineStr">
         <is>
@@ -97225,15 +97041,11 @@
       </c>
       <c r="E519" t="inlineStr"/>
       <c r="F519" t="inlineStr"/>
-      <c r="G519" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H519" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="G519" t="n">
+        <v>0</v>
+      </c>
+      <c r="H519" t="n">
+        <v>5</v>
       </c>
       <c r="I519" t="inlineStr">
         <is>
@@ -97335,15 +97147,11 @@
       </c>
       <c r="E520" t="inlineStr"/>
       <c r="F520" t="inlineStr"/>
-      <c r="G520" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H520" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G520" t="n">
+        <v>0</v>
+      </c>
+      <c r="H520" t="n">
+        <v>1</v>
       </c>
       <c r="I520" t="inlineStr">
         <is>
@@ -97425,6 +97233,3032 @@
       <c r="BG520" t="inlineStr"/>
       <c r="BH520" t="inlineStr"/>
     </row>
+    <row r="521">
+      <c r="A521" s="1" t="inlineStr">
+        <is>
+          <t>U5mYDMJ0</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>03.11.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Rojas J. A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Estadio San Mamés
+ (Bilbao)</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>53 331</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>46 898</t>
+        </is>
+      </c>
+      <c r="G521" t="n">
+        <v>1</v>
+      </c>
+      <c r="H521" t="n">
+        <v>1</v>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="M521" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="N521" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q521" t="n">
+        <v>17</v>
+      </c>
+      <c r="R521" t="n">
+        <v>7</v>
+      </c>
+      <c r="S521" t="n">
+        <v>8</v>
+      </c>
+      <c r="T521" t="n">
+        <v>4</v>
+      </c>
+      <c r="U521" t="n">
+        <v>7</v>
+      </c>
+      <c r="V521" t="n">
+        <v>1</v>
+      </c>
+      <c r="W521" t="n">
+        <v>2</v>
+      </c>
+      <c r="X521" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y521" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z521" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA521" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB521" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC521" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD521" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE521" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF521" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG521" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH521" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI521" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ521" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK521" t="inlineStr"/>
+      <c r="AL521" t="inlineStr"/>
+      <c r="AM521" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="AN521" t="inlineStr">
+        <is>
+          <t>valverde tejedor ernesto</t>
+        </is>
+      </c>
+      <c r="AO521" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="AP521" t="inlineStr">
+        <is>
+          <t>pellegrini manuel</t>
+        </is>
+      </c>
+      <c r="AQ521" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR521" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS521" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT521" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU521" t="inlineStr"/>
+      <c r="AV521" t="inlineStr"/>
+      <c r="AW521" t="inlineStr"/>
+      <c r="AX521" t="inlineStr"/>
+      <c r="AY521" t="inlineStr"/>
+      <c r="AZ521" t="inlineStr"/>
+      <c r="BA521" t="n">
+        <v>475</v>
+      </c>
+      <c r="BB521" t="n">
+        <v>498</v>
+      </c>
+      <c r="BC521" t="n">
+        <v>403</v>
+      </c>
+      <c r="BD521" t="n">
+        <v>412</v>
+      </c>
+      <c r="BE521" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF521" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG521" t="n">
+        <v>13</v>
+      </c>
+      <c r="BH521" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="inlineStr">
+        <is>
+          <t>rsizUY9b</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>03.11.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Ruiz A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Estadio Ramón Sánchez Pizjuán
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>42 714</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>37 619</t>
+        </is>
+      </c>
+      <c r="G522" t="n">
+        <v>0</v>
+      </c>
+      <c r="H522" t="n">
+        <v>2</v>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="M522" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N522" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q522" t="n">
+        <v>8</v>
+      </c>
+      <c r="R522" t="n">
+        <v>9</v>
+      </c>
+      <c r="S522" t="n">
+        <v>0</v>
+      </c>
+      <c r="T522" t="n">
+        <v>3</v>
+      </c>
+      <c r="U522" t="n">
+        <v>5</v>
+      </c>
+      <c r="V522" t="n">
+        <v>4</v>
+      </c>
+      <c r="W522" t="n">
+        <v>3</v>
+      </c>
+      <c r="X522" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y522" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z522" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA522" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB522" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC522" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD522" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE522" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF522" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG522" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH522" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI522" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ522" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK522" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL522" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM522" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="AN522" t="inlineStr">
+        <is>
+          <t>pimienta francisco</t>
+        </is>
+      </c>
+      <c r="AO522" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="AP522" t="inlineStr">
+        <is>
+          <t>alguacil imanol</t>
+        </is>
+      </c>
+      <c r="AQ522" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR522" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS522" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT522" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU522" t="inlineStr"/>
+      <c r="AV522" t="inlineStr"/>
+      <c r="AW522" t="inlineStr"/>
+      <c r="AX522" t="inlineStr"/>
+      <c r="AY522" t="inlineStr"/>
+      <c r="AZ522" t="inlineStr"/>
+      <c r="BA522" t="n">
+        <v>497</v>
+      </c>
+      <c r="BB522" t="n">
+        <v>413</v>
+      </c>
+      <c r="BC522" t="n">
+        <v>393</v>
+      </c>
+      <c r="BD522" t="n">
+        <v>329</v>
+      </c>
+      <c r="BE522" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF522" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG522" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH522" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="inlineStr">
+        <is>
+          <t>UaS8aGMt</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>03.11.2024 12:15</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Munuera Montero J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Estadi Olímpic Lluís Companys
+ (Barcelona)</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>55 926</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>48 843</t>
+        </is>
+      </c>
+      <c r="G523" t="n">
+        <v>3</v>
+      </c>
+      <c r="H523" t="n">
+        <v>1</v>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="M523" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="N523" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="Q523" t="n">
+        <v>14</v>
+      </c>
+      <c r="R523" t="n">
+        <v>10</v>
+      </c>
+      <c r="S523" t="n">
+        <v>9</v>
+      </c>
+      <c r="T523" t="n">
+        <v>3</v>
+      </c>
+      <c r="U523" t="n">
+        <v>3</v>
+      </c>
+      <c r="V523" t="n">
+        <v>3</v>
+      </c>
+      <c r="W523" t="n">
+        <v>2</v>
+      </c>
+      <c r="X523" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y523" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z523" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA523" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB523" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC523" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD523" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE523" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF523" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG523" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH523" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI523" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ523" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK523" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL523" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM523" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="AN523" t="inlineStr">
+        <is>
+          <t>flick hans dieter</t>
+        </is>
+      </c>
+      <c r="AO523" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="AP523" t="inlineStr">
+        <is>
+          <t>gonzalez manolo</t>
+        </is>
+      </c>
+      <c r="AQ523" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR523" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS523" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT523" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU523" t="inlineStr"/>
+      <c r="AV523" t="inlineStr"/>
+      <c r="AW523" t="inlineStr"/>
+      <c r="AX523" t="inlineStr"/>
+      <c r="AY523" t="inlineStr"/>
+      <c r="AZ523" t="inlineStr"/>
+      <c r="BA523" t="n">
+        <v>761</v>
+      </c>
+      <c r="BB523" t="n">
+        <v>208</v>
+      </c>
+      <c r="BC523" t="n">
+        <v>696</v>
+      </c>
+      <c r="BD523" t="n">
+        <v>140</v>
+      </c>
+      <c r="BE523" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF523" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG523" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH523" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="inlineStr">
+        <is>
+          <t>QXtsC0lD</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>03.11.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Bengoetxea R.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Metropolitano Stadium
+ (Madrid)</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>70 460</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>56 610</t>
+        </is>
+      </c>
+      <c r="G524" t="n">
+        <v>2</v>
+      </c>
+      <c r="H524" t="n">
+        <v>0</v>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="M524" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="N524" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q524" t="n">
+        <v>15</v>
+      </c>
+      <c r="R524" t="n">
+        <v>1</v>
+      </c>
+      <c r="S524" t="n">
+        <v>3</v>
+      </c>
+      <c r="T524" t="n">
+        <v>1</v>
+      </c>
+      <c r="U524" t="n">
+        <v>8</v>
+      </c>
+      <c r="V524" t="n">
+        <v>0</v>
+      </c>
+      <c r="W524" t="n">
+        <v>4</v>
+      </c>
+      <c r="X524" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y524" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z524" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA524" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB524" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC524" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD524" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE524" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF524" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG524" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH524" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI524" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ524" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK524" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL524" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM524" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="AN524" t="inlineStr">
+        <is>
+          <t>simeone diego</t>
+        </is>
+      </c>
+      <c r="AO524" t="inlineStr">
+        <is>
+          <t>tI57YghG</t>
+        </is>
+      </c>
+      <c r="AP524" t="inlineStr">
+        <is>
+          <t>martinez diego</t>
+        </is>
+      </c>
+      <c r="AQ524" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR524" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS524" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT524" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU524" t="inlineStr"/>
+      <c r="AV524" t="inlineStr"/>
+      <c r="AW524" t="inlineStr"/>
+      <c r="AX524" t="inlineStr"/>
+      <c r="AY524" t="inlineStr"/>
+      <c r="AZ524" t="inlineStr"/>
+      <c r="BA524" t="n">
+        <v>540</v>
+      </c>
+      <c r="BB524" t="n">
+        <v>407</v>
+      </c>
+      <c r="BC524" t="n">
+        <v>455</v>
+      </c>
+      <c r="BD524" t="n">
+        <v>312</v>
+      </c>
+      <c r="BE524" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF524" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG524" t="n">
+        <v>7</v>
+      </c>
+      <c r="BH524" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="inlineStr">
+        <is>
+          <t>dA00HeQh</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>02.11.2024 12:15</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Busquets Ferrer M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Montilivi
+ (Girona)</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>14 624</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>10 839</t>
+        </is>
+      </c>
+      <c r="G525" t="n">
+        <v>4</v>
+      </c>
+      <c r="H525" t="n">
+        <v>3</v>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="M525" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="N525" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="Q525" t="n">
+        <v>15</v>
+      </c>
+      <c r="R525" t="n">
+        <v>8</v>
+      </c>
+      <c r="S525" t="n">
+        <v>6</v>
+      </c>
+      <c r="T525" t="n">
+        <v>5</v>
+      </c>
+      <c r="U525" t="n">
+        <v>4</v>
+      </c>
+      <c r="V525" t="n">
+        <v>2</v>
+      </c>
+      <c r="W525" t="n">
+        <v>5</v>
+      </c>
+      <c r="X525" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y525" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z525" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA525" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB525" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC525" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD525" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE525" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF525" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG525" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH525" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI525" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ525" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK525" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL525" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM525" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="AN525" t="inlineStr">
+        <is>
+          <t>michel</t>
+        </is>
+      </c>
+      <c r="AO525" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="AP525" t="inlineStr">
+        <is>
+          <t>jimenez borja</t>
+        </is>
+      </c>
+      <c r="AQ525" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR525" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS525" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT525" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU525" t="inlineStr"/>
+      <c r="AV525" t="inlineStr"/>
+      <c r="AW525" t="inlineStr"/>
+      <c r="AX525" t="inlineStr"/>
+      <c r="AY525" t="inlineStr"/>
+      <c r="AZ525" t="inlineStr"/>
+      <c r="BA525" t="n">
+        <v>487</v>
+      </c>
+      <c r="BB525" t="n">
+        <v>410</v>
+      </c>
+      <c r="BC525" t="n">
+        <v>419</v>
+      </c>
+      <c r="BD525" t="n">
+        <v>329</v>
+      </c>
+      <c r="BE525" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF525" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG525" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH525" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="inlineStr">
+        <is>
+          <t>4z48FZf5</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>02.11.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Garcia V.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>23 516</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>20 430</t>
+        </is>
+      </c>
+      <c r="G526" t="n">
+        <v>1</v>
+      </c>
+      <c r="H526" t="n">
+        <v>0</v>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="M526" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="N526" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q526" t="n">
+        <v>20</v>
+      </c>
+      <c r="R526" t="n">
+        <v>7</v>
+      </c>
+      <c r="S526" t="n">
+        <v>4</v>
+      </c>
+      <c r="T526" t="n">
+        <v>4</v>
+      </c>
+      <c r="U526" t="n">
+        <v>11</v>
+      </c>
+      <c r="V526" t="n">
+        <v>1</v>
+      </c>
+      <c r="W526" t="n">
+        <v>5</v>
+      </c>
+      <c r="X526" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y526" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z526" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA526" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB526" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC526" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD526" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE526" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF526" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG526" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH526" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI526" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ526" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK526" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL526" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM526" t="inlineStr">
+        <is>
+          <t>YaDNxIRF</t>
+        </is>
+      </c>
+      <c r="AN526" t="inlineStr">
+        <is>
+          <t>alturo ramon</t>
+        </is>
+      </c>
+      <c r="AO526" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="AP526" t="inlineStr">
+        <is>
+          <t>pezzolano paulo</t>
+        </is>
+      </c>
+      <c r="AQ526" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR526" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS526" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT526" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU526" t="inlineStr"/>
+      <c r="AV526" t="inlineStr"/>
+      <c r="AW526" t="inlineStr"/>
+      <c r="AX526" t="inlineStr"/>
+      <c r="AY526" t="inlineStr"/>
+      <c r="AZ526" t="inlineStr"/>
+      <c r="BA526" t="n">
+        <v>352</v>
+      </c>
+      <c r="BB526" t="n">
+        <v>357</v>
+      </c>
+      <c r="BC526" t="n">
+        <v>265</v>
+      </c>
+      <c r="BD526" t="n">
+        <v>274</v>
+      </c>
+      <c r="BE526" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF526" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG526" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH526" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="inlineStr">
+        <is>
+          <t>02cHDDPH</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>01.11.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Fuertes P.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Estadio Mendizorrotza
+ (Vitoria-Gasteiz)</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>19 840</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>17 212</t>
+        </is>
+      </c>
+      <c r="G527" t="n">
+        <v>1</v>
+      </c>
+      <c r="H527" t="n">
+        <v>0</v>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="M527" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N527" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="Q527" t="n">
+        <v>13</v>
+      </c>
+      <c r="R527" t="n">
+        <v>7</v>
+      </c>
+      <c r="S527" t="n">
+        <v>3</v>
+      </c>
+      <c r="T527" t="n">
+        <v>2</v>
+      </c>
+      <c r="U527" t="n">
+        <v>4</v>
+      </c>
+      <c r="V527" t="n">
+        <v>3</v>
+      </c>
+      <c r="W527" t="n">
+        <v>6</v>
+      </c>
+      <c r="X527" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y527" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z527" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA527" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB527" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC527" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD527" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE527" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF527" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG527" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH527" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI527" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ527" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK527" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL527" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM527" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="AN527" t="inlineStr">
+        <is>
+          <t>garcia luis</t>
+        </is>
+      </c>
+      <c r="AO527" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="AP527" t="inlineStr">
+        <is>
+          <t>arrasate jagoba</t>
+        </is>
+      </c>
+      <c r="AQ527" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR527" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS527" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT527" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU527" t="inlineStr"/>
+      <c r="AV527" t="inlineStr"/>
+      <c r="AW527" t="inlineStr"/>
+      <c r="AX527" t="inlineStr"/>
+      <c r="AY527" t="inlineStr"/>
+      <c r="AZ527" t="inlineStr"/>
+      <c r="BA527" t="n">
+        <v>323</v>
+      </c>
+      <c r="BB527" t="n">
+        <v>305</v>
+      </c>
+      <c r="BC527" t="n">
+        <v>227</v>
+      </c>
+      <c r="BD527" t="n">
+        <v>225</v>
+      </c>
+      <c r="BE527" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF527" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG527" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH527" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="inlineStr">
+        <is>
+          <t>rRUgTu3b</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>03.11.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Barrera R.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Estadio Heliodoro Rodríguez López
+ (Santa Cruz de Tenerife)</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>22 824</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>14 800</t>
+        </is>
+      </c>
+      <c r="G528" t="n">
+        <v>1</v>
+      </c>
+      <c r="H528" t="n">
+        <v>0</v>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>Tenerife</t>
+        </is>
+      </c>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="M528" t="inlineStr"/>
+      <c r="N528" t="inlineStr"/>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q528" t="n">
+        <v>8</v>
+      </c>
+      <c r="R528" t="n">
+        <v>5</v>
+      </c>
+      <c r="S528" t="n">
+        <v>2</v>
+      </c>
+      <c r="T528" t="n">
+        <v>1</v>
+      </c>
+      <c r="U528" t="n">
+        <v>2</v>
+      </c>
+      <c r="V528" t="n">
+        <v>3</v>
+      </c>
+      <c r="W528" t="n">
+        <v>4</v>
+      </c>
+      <c r="X528" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y528" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z528" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA528" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB528" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC528" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD528" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE528" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF528" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG528" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH528" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI528" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ528" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK528" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL528" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM528" t="inlineStr">
+        <is>
+          <t>CYND5rZG</t>
+        </is>
+      </c>
+      <c r="AN528" t="inlineStr">
+        <is>
+          <t>mel pepe</t>
+        </is>
+      </c>
+      <c r="AO528" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="AP528" t="inlineStr">
+        <is>
+          <t>lisci alessio</t>
+        </is>
+      </c>
+      <c r="AQ528" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR528" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS528" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT528" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU528" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV528" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW528" t="inlineStr"/>
+      <c r="AX528" t="inlineStr"/>
+      <c r="AY528" t="inlineStr"/>
+      <c r="AZ528" t="inlineStr"/>
+      <c r="BA528" t="inlineStr"/>
+      <c r="BB528" t="inlineStr"/>
+      <c r="BC528" t="inlineStr"/>
+      <c r="BD528" t="inlineStr"/>
+      <c r="BE528" t="inlineStr"/>
+      <c r="BF528" t="inlineStr"/>
+      <c r="BG528" t="inlineStr"/>
+      <c r="BH528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>l6zUubV6</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>03.11.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Lax Franco S.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Carlos Tartiere
+ (Oviedo)</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>30 500</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>19 380</t>
+        </is>
+      </c>
+      <c r="G529" t="n">
+        <v>3</v>
+      </c>
+      <c r="H529" t="n">
+        <v>1</v>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>R. Oviedo</t>
+        </is>
+      </c>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>Burgos CF</t>
+        </is>
+      </c>
+      <c r="M529" t="inlineStr"/>
+      <c r="N529" t="inlineStr"/>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q529" t="n">
+        <v>19</v>
+      </c>
+      <c r="R529" t="n">
+        <v>10</v>
+      </c>
+      <c r="S529" t="n">
+        <v>7</v>
+      </c>
+      <c r="T529" t="n">
+        <v>3</v>
+      </c>
+      <c r="U529" t="n">
+        <v>6</v>
+      </c>
+      <c r="V529" t="n">
+        <v>6</v>
+      </c>
+      <c r="W529" t="n">
+        <v>6</v>
+      </c>
+      <c r="X529" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y529" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z529" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA529" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB529" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC529" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD529" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE529" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF529" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG529" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH529" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI529" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ529" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK529" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL529" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM529" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="AN529" t="inlineStr">
+        <is>
+          <t>calleja javier</t>
+        </is>
+      </c>
+      <c r="AO529" t="inlineStr">
+        <is>
+          <t>2T1uiZvq</t>
+        </is>
+      </c>
+      <c r="AP529" t="inlineStr">
+        <is>
+          <t>ramis luis miguel</t>
+        </is>
+      </c>
+      <c r="AQ529" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR529" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS529" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT529" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU529" t="inlineStr"/>
+      <c r="AV529" t="inlineStr"/>
+      <c r="AW529" t="inlineStr"/>
+      <c r="AX529" t="inlineStr"/>
+      <c r="AY529" t="inlineStr"/>
+      <c r="AZ529" t="inlineStr"/>
+      <c r="BA529" t="inlineStr"/>
+      <c r="BB529" t="inlineStr"/>
+      <c r="BC529" t="inlineStr"/>
+      <c r="BD529" t="inlineStr"/>
+      <c r="BE529" t="inlineStr"/>
+      <c r="BF529" t="inlineStr"/>
+      <c r="BG529" t="inlineStr"/>
+      <c r="BH529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="inlineStr">
+        <is>
+          <t>hvsLsK0f</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>02.11.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Fuentes Molina A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Estadio El Sardinero
+ (Santander)</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>22 222</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>20 794</t>
+        </is>
+      </c>
+      <c r="G530" t="n">
+        <v>1</v>
+      </c>
+      <c r="H530" t="n">
+        <v>1</v>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="M530" t="inlineStr"/>
+      <c r="N530" t="inlineStr"/>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q530" t="n">
+        <v>16</v>
+      </c>
+      <c r="R530" t="n">
+        <v>11</v>
+      </c>
+      <c r="S530" t="n">
+        <v>8</v>
+      </c>
+      <c r="T530" t="n">
+        <v>4</v>
+      </c>
+      <c r="U530" t="n">
+        <v>7</v>
+      </c>
+      <c r="V530" t="n">
+        <v>5</v>
+      </c>
+      <c r="W530" t="n">
+        <v>1</v>
+      </c>
+      <c r="X530" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y530" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z530" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA530" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB530" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC530" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD530" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE530" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF530" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG530" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH530" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI530" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ530" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK530" t="inlineStr"/>
+      <c r="AL530" t="inlineStr"/>
+      <c r="AM530" t="inlineStr">
+        <is>
+          <t>rak12p9n</t>
+        </is>
+      </c>
+      <c r="AN530" t="inlineStr">
+        <is>
+          <t>lopez jose</t>
+        </is>
+      </c>
+      <c r="AO530" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="AP530" t="inlineStr">
+        <is>
+          <t>gonzalez alberto</t>
+        </is>
+      </c>
+      <c r="AQ530" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR530" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS530" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT530" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU530" t="inlineStr"/>
+      <c r="AV530" t="inlineStr"/>
+      <c r="AW530" t="inlineStr"/>
+      <c r="AX530" t="inlineStr"/>
+      <c r="AY530" t="inlineStr"/>
+      <c r="AZ530" t="inlineStr"/>
+      <c r="BA530" t="inlineStr"/>
+      <c r="BB530" t="inlineStr"/>
+      <c r="BC530" t="inlineStr"/>
+      <c r="BD530" t="inlineStr"/>
+      <c r="BE530" t="inlineStr"/>
+      <c r="BF530" t="inlineStr"/>
+      <c r="BG530" t="inlineStr"/>
+      <c r="BH530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="inlineStr">
+        <is>
+          <t>xURoV1Yo</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>02.11.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Reig S. A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>La Romareda
+ (Zaragoza)</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>33 608</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>17 642</t>
+        </is>
+      </c>
+      <c r="G531" t="n">
+        <v>2</v>
+      </c>
+      <c r="H531" t="n">
+        <v>1</v>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>Granada CF</t>
+        </is>
+      </c>
+      <c r="M531" t="inlineStr"/>
+      <c r="N531" t="inlineStr"/>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="Q531" t="n">
+        <v>13</v>
+      </c>
+      <c r="R531" t="n">
+        <v>16</v>
+      </c>
+      <c r="S531" t="n">
+        <v>6</v>
+      </c>
+      <c r="T531" t="n">
+        <v>3</v>
+      </c>
+      <c r="U531" t="n">
+        <v>2</v>
+      </c>
+      <c r="V531" t="n">
+        <v>7</v>
+      </c>
+      <c r="W531" t="n">
+        <v>5</v>
+      </c>
+      <c r="X531" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y531" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z531" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA531" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB531" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC531" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD531" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE531" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF531" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG531" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH531" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI531" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ531" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK531" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL531" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM531" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="AN531" t="inlineStr">
+        <is>
+          <t>fernandez braulio victor</t>
+        </is>
+      </c>
+      <c r="AO531" t="inlineStr">
+        <is>
+          <t>K0UZov8F</t>
+        </is>
+      </c>
+      <c r="AP531" t="inlineStr">
+        <is>
+          <t>escriba fran</t>
+        </is>
+      </c>
+      <c r="AQ531" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR531" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS531" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT531" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU531" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV531" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW531" t="inlineStr"/>
+      <c r="AX531" t="inlineStr"/>
+      <c r="AY531" t="inlineStr"/>
+      <c r="AZ531" t="inlineStr"/>
+      <c r="BA531" t="inlineStr"/>
+      <c r="BB531" t="inlineStr"/>
+      <c r="BC531" t="inlineStr"/>
+      <c r="BD531" t="inlineStr"/>
+      <c r="BE531" t="inlineStr"/>
+      <c r="BF531" t="inlineStr"/>
+      <c r="BG531" t="inlineStr"/>
+      <c r="BH531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="inlineStr">
+        <is>
+          <t>vg8vVtHl</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>02.11.2024 12:15</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Guzman Mansilla J. L.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Estadio Municipal Cartagonova
+ (Cartagena)</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>13 745</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>6 862</t>
+        </is>
+      </c>
+      <c r="G532" t="n">
+        <v>1</v>
+      </c>
+      <c r="H532" t="n">
+        <v>5</v>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>FC Cartagena SAD</t>
+        </is>
+      </c>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>Dep. La Coruna</t>
+        </is>
+      </c>
+      <c r="M532" t="inlineStr"/>
+      <c r="N532" t="inlineStr"/>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P532" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q532" t="n">
+        <v>17</v>
+      </c>
+      <c r="R532" t="n">
+        <v>18</v>
+      </c>
+      <c r="S532" t="n">
+        <v>4</v>
+      </c>
+      <c r="T532" t="n">
+        <v>13</v>
+      </c>
+      <c r="U532" t="n">
+        <v>11</v>
+      </c>
+      <c r="V532" t="n">
+        <v>4</v>
+      </c>
+      <c r="W532" t="n">
+        <v>2</v>
+      </c>
+      <c r="X532" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y532" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z532" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA532" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB532" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC532" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD532" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE532" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF532" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG532" t="n">
+        <v>8</v>
+      </c>
+      <c r="AH532" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI532" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ532" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK532" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL532" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM532" t="inlineStr">
+        <is>
+          <t>hlQINAie</t>
+        </is>
+      </c>
+      <c r="AN532" t="inlineStr">
+        <is>
+          <t>jandro</t>
+        </is>
+      </c>
+      <c r="AO532" t="inlineStr">
+        <is>
+          <t>4S35maMi</t>
+        </is>
+      </c>
+      <c r="AP532" t="inlineStr">
+        <is>
+          <t>gilsanz oscar</t>
+        </is>
+      </c>
+      <c r="AQ532" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR532" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS532" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT532" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU532" t="inlineStr"/>
+      <c r="AV532" t="inlineStr"/>
+      <c r="AW532" t="inlineStr"/>
+      <c r="AX532" t="inlineStr"/>
+      <c r="AY532" t="inlineStr"/>
+      <c r="AZ532" t="inlineStr"/>
+      <c r="BA532" t="inlineStr"/>
+      <c r="BB532" t="inlineStr"/>
+      <c r="BC532" t="inlineStr"/>
+      <c r="BD532" t="inlineStr"/>
+      <c r="BE532" t="inlineStr"/>
+      <c r="BF532" t="inlineStr"/>
+      <c r="BG532" t="inlineStr"/>
+      <c r="BH532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="inlineStr">
+        <is>
+          <t>MJYyvx0J</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>02.11.2024 12:15</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Mallo E.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Estadio El Molinón
+ (Gijón)</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>29 029</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>22 250</t>
+        </is>
+      </c>
+      <c r="G533" t="n">
+        <v>2</v>
+      </c>
+      <c r="H533" t="n">
+        <v>0</v>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>Gijon</t>
+        </is>
+      </c>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>Cadiz CF</t>
+        </is>
+      </c>
+      <c r="M533" t="inlineStr"/>
+      <c r="N533" t="inlineStr"/>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="Q533" t="n">
+        <v>4</v>
+      </c>
+      <c r="R533" t="n">
+        <v>9</v>
+      </c>
+      <c r="S533" t="n">
+        <v>2</v>
+      </c>
+      <c r="T533" t="n">
+        <v>0</v>
+      </c>
+      <c r="U533" t="n">
+        <v>2</v>
+      </c>
+      <c r="V533" t="n">
+        <v>6</v>
+      </c>
+      <c r="W533" t="n">
+        <v>0</v>
+      </c>
+      <c r="X533" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y533" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z533" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA533" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB533" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC533" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD533" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE533" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF533" t="n">
+        <v>31</v>
+      </c>
+      <c r="AG533" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH533" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI533" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ533" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK533" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL533" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM533" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="AN533" t="inlineStr">
+        <is>
+          <t>albes ruben</t>
+        </is>
+      </c>
+      <c r="AO533" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="AP533" t="inlineStr">
+        <is>
+          <t>lopez paco</t>
+        </is>
+      </c>
+      <c r="AQ533" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR533" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS533" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT533" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU533" t="inlineStr"/>
+      <c r="AV533" t="inlineStr"/>
+      <c r="AW533" t="inlineStr"/>
+      <c r="AX533" t="inlineStr"/>
+      <c r="AY533" t="inlineStr"/>
+      <c r="AZ533" t="inlineStr"/>
+      <c r="BA533" t="inlineStr"/>
+      <c r="BB533" t="inlineStr"/>
+      <c r="BC533" t="inlineStr"/>
+      <c r="BD533" t="inlineStr"/>
+      <c r="BE533" t="inlineStr"/>
+      <c r="BF533" t="inlineStr"/>
+      <c r="BG533" t="inlineStr"/>
+      <c r="BH533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="inlineStr">
+        <is>
+          <t>8YaeRbGD</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>02.11.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Sanchez Lopez R.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Ipurua
+ (Eibar)</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>8 164</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>4 388</t>
+        </is>
+      </c>
+      <c r="G534" t="n">
+        <v>0</v>
+      </c>
+      <c r="H534" t="n">
+        <v>2</v>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>Eibar</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="M534" t="inlineStr"/>
+      <c r="N534" t="inlineStr"/>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q534" t="n">
+        <v>12</v>
+      </c>
+      <c r="R534" t="n">
+        <v>15</v>
+      </c>
+      <c r="S534" t="n">
+        <v>6</v>
+      </c>
+      <c r="T534" t="n">
+        <v>3</v>
+      </c>
+      <c r="U534" t="n">
+        <v>5</v>
+      </c>
+      <c r="V534" t="n">
+        <v>5</v>
+      </c>
+      <c r="W534" t="n">
+        <v>1</v>
+      </c>
+      <c r="X534" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y534" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z534" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA534" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB534" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC534" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD534" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE534" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF534" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG534" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH534" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI534" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ534" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK534" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL534" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM534" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="AN534" t="inlineStr">
+        <is>
+          <t>etxeberria joseba</t>
+        </is>
+      </c>
+      <c r="AO534" t="inlineStr">
+        <is>
+          <t>zT9gi7i9</t>
+        </is>
+      </c>
+      <c r="AP534" t="inlineStr">
+        <is>
+          <t>sarabia eder</t>
+        </is>
+      </c>
+      <c r="AQ534" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR534" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AS534" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT534" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU534" t="inlineStr"/>
+      <c r="AV534" t="inlineStr"/>
+      <c r="AW534" t="inlineStr"/>
+      <c r="AX534" t="inlineStr"/>
+      <c r="AY534" t="inlineStr"/>
+      <c r="AZ534" t="inlineStr"/>
+      <c r="BA534" t="inlineStr"/>
+      <c r="BB534" t="inlineStr"/>
+      <c r="BC534" t="inlineStr"/>
+      <c r="BD534" t="inlineStr"/>
+      <c r="BE534" t="inlineStr"/>
+      <c r="BF534" t="inlineStr"/>
+      <c r="BG534" t="inlineStr"/>
+      <c r="BH534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="inlineStr">
+        <is>
+          <t>zeCiJHet</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>04.11.2024 17:00</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Gil Manzano J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Estadio de Balaídos
+ (Vigo)</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>24 791</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>19 502</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="Q535" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R535" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S535" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T535" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U535" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V535" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W535" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X535" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y535" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z535" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA535" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB535" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC535" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD535" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE535" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF535" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AG535" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH535" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI535" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ535" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK535" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL535" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM535" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="AN535" t="inlineStr">
+        <is>
+          <t>giraldez claudio</t>
+        </is>
+      </c>
+      <c r="AO535" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="AP535" t="inlineStr">
+        <is>
+          <t>bordalas pepe</t>
+        </is>
+      </c>
+      <c r="AQ535" t="n">
+        <v>148</v>
+      </c>
+      <c r="AR535" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AS535" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT535" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AU535" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AV535" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AW535" t="inlineStr"/>
+      <c r="AX535" t="inlineStr"/>
+      <c r="AY535" t="inlineStr"/>
+      <c r="AZ535" t="inlineStr"/>
+      <c r="BA535" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="BB535" t="inlineStr">
+        <is>
+          <t>413</t>
+        </is>
+      </c>
+      <c r="BC535" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="BD535" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="BE535" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF535" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="BG535" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BH535" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
